--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -5088,7 +5088,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -5858,7 +5858,7 @@
         <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>9</v>
@@ -6243,7 +6243,7 @@
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>8</v>
@@ -6737,7 +6737,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -6755,7 +6755,7 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -6791,7 +6791,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -7217,7 +7217,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -7253,7 +7253,7 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -7353,7 +7353,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -7371,7 +7371,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -7407,7 +7407,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -7528,7 +7528,7 @@
         <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -7738,7 +7738,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -7756,7 +7756,7 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -7792,7 +7792,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -7836,7 +7836,7 @@
         <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -8067,7 +8067,7 @@
         <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>8</v>
@@ -8123,7 +8123,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -8141,7 +8141,7 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -8177,7 +8177,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -8354,7 +8354,7 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -8372,7 +8372,7 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -8408,7 +8408,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -8449,7 +8449,7 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -8485,7 +8485,7 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -8526,7 +8526,7 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -8562,7 +8562,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -8585,7 +8585,7 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>8</v>
@@ -8603,7 +8603,7 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -8639,7 +8639,7 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -8970,7 +8970,7 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -8988,7 +8988,7 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -9024,7 +9024,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -9124,7 +9124,7 @@
         <v>8</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -9142,7 +9142,7 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -9178,7 +9178,7 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -9355,7 +9355,7 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -9373,7 +9373,7 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -9409,7 +9409,7 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>5</v>
@@ -9983,7 +9983,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -10019,7 +10019,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -10273,7 +10273,7 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H13">
         <v>6</v>
@@ -10291,7 +10291,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -18480,7 +18480,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -18557,7 +18557,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -18634,7 +18634,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -18670,7 +18670,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -18711,7 +18711,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -18788,7 +18788,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -18865,7 +18865,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -18942,7 +18942,7 @@
         <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -18978,7 +18978,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -19019,7 +19019,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -19096,7 +19096,7 @@
         <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -19173,7 +19173,7 @@
         <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -19209,7 +19209,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -19250,7 +19250,7 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -19327,7 +19327,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -19404,7 +19404,7 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -19481,7 +19481,7 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -19558,7 +19558,7 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -19635,7 +19635,7 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -19712,7 +19712,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -19789,7 +19789,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -19825,7 +19825,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -19866,7 +19866,7 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -19902,7 +19902,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -19943,7 +19943,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -19979,7 +19979,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -20020,7 +20020,7 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -20174,7 +20174,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -20251,7 +20251,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -20328,7 +20328,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -20405,7 +20405,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -20482,7 +20482,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -20559,7 +20559,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -20636,7 +20636,7 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -20672,7 +20672,7 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -20713,7 +20713,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -20867,7 +20867,7 @@
         <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -20944,7 +20944,7 @@
         <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -21021,7 +21021,7 @@
         <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -21057,7 +21057,7 @@
         <v>8</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -21314,7 +21314,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -21391,7 +21391,7 @@
         <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -21427,7 +21427,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -21545,7 +21545,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -21622,7 +21622,7 @@
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -21699,7 +21699,7 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -21853,7 +21853,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -21930,7 +21930,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -21966,7 +21966,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -22084,7 +22084,7 @@
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -22238,7 +22238,7 @@
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -22315,7 +22315,7 @@
         <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>6</v>
@@ -22351,7 +22351,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -22451,7 +22451,7 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -22505,7 +22505,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -22546,7 +22546,7 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -22582,7 +22582,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -22623,7 +22623,7 @@
         <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -22700,7 +22700,7 @@
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -22777,7 +22777,7 @@
         <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -22854,7 +22854,7 @@
         <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -23008,7 +23008,7 @@
         <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -23239,7 +23239,7 @@
         <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -23275,7 +23275,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -23446,7 +23446,7 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -23482,7 +23482,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -23523,7 +23523,7 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -23559,7 +23559,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -23600,7 +23600,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -23677,7 +23677,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -23754,7 +23754,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -23790,7 +23790,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -23831,7 +23831,7 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -23867,7 +23867,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -23908,7 +23908,7 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>7</v>
@@ -23944,7 +23944,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -23985,7 +23985,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -24062,7 +24062,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -24098,7 +24098,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -24130,7 +24130,7 @@
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>7</v>
@@ -24139,16 +24139,16 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -24184,7 +24184,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -24216,7 +24216,7 @@
         <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>10</v>
@@ -24293,7 +24293,7 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -24370,7 +24370,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -24447,7 +24447,7 @@
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>9</v>
@@ -24524,7 +24524,7 @@
         <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -24560,7 +24560,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -24601,7 +24601,7 @@
         <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -24637,7 +24637,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>-1</v>
@@ -24678,7 +24678,7 @@
         <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>8</v>
@@ -24714,7 +24714,7 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -24755,7 +24755,7 @@
         <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -24791,7 +24791,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -24832,7 +24832,7 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>10</v>
@@ -24909,7 +24909,7 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>10</v>
@@ -24945,7 +24945,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -24986,7 +24986,7 @@
         <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -25022,7 +25022,7 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>-1</v>
@@ -25063,7 +25063,7 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -25140,7 +25140,7 @@
         <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -25176,7 +25176,7 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -25375,7 +25375,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -25464,7 +25464,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -25506,7 +25506,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -25553,7 +25553,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -25595,7 +25595,7 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -25642,7 +25642,7 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -25731,7 +25731,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -25799,7 +25799,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -25862,7 +25862,7 @@
         <v>5</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>9</v>
@@ -25888,7 +25888,7 @@
         <v>6</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -25951,7 +25951,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -25998,7 +25998,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -26087,7 +26087,7 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -26176,7 +26176,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -26333,7 +26333,7 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>6</v>
@@ -26396,7 +26396,7 @@
         <v>5</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -26532,7 +26532,7 @@
         <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -26621,7 +26621,7 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -26710,7 +26710,7 @@
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -26752,7 +26752,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -26799,7 +26799,7 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -26977,7 +26977,7 @@
         <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -27066,7 +27066,7 @@
         <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -27134,7 +27134,7 @@
         <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>6</v>
@@ -27197,7 +27197,7 @@
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>6</v>
@@ -27244,7 +27244,7 @@
         <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -27333,7 +27333,7 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -27511,7 +27511,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -27600,7 +27600,7 @@
         <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>8</v>
@@ -27642,7 +27642,7 @@
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>8</v>
@@ -27689,7 +27689,7 @@
         <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -27778,7 +27778,7 @@
         <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -27820,7 +27820,7 @@
         <v>7</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -27867,7 +27867,7 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -27909,7 +27909,7 @@
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -27956,7 +27956,7 @@
         <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>8</v>
@@ -27998,7 +27998,7 @@
         <v>9</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -28045,7 +28045,7 @@
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -28134,7 +28134,7 @@
         <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -28356,7 +28356,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -28433,7 +28433,7 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -28469,7 +28469,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -28510,7 +28510,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -28587,7 +28587,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -28664,7 +28664,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -28741,7 +28741,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -28818,7 +28818,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -28895,7 +28895,7 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -28931,7 +28931,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -28972,7 +28972,7 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -29049,7 +29049,7 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -29126,7 +29126,7 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -29203,7 +29203,7 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -29280,7 +29280,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -29357,7 +29357,7 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -29434,7 +29434,7 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -29470,7 +29470,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -29511,7 +29511,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -29588,7 +29588,7 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -29624,7 +29624,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -29665,7 +29665,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -29701,7 +29701,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -29742,7 +29742,7 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -29819,7 +29819,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -29896,7 +29896,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -29973,7 +29973,7 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>9</v>
@@ -30009,7 +30009,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -30050,7 +30050,7 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -30127,7 +30127,7 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -30204,7 +30204,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>8</v>
@@ -30240,7 +30240,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -30281,7 +30281,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -30358,7 +30358,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -30512,7 +30512,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -30589,7 +30589,7 @@
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -30666,7 +30666,7 @@
         <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -30743,7 +30743,7 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -30779,7 +30779,7 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -30820,7 +30820,7 @@
         <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>7</v>
@@ -30856,7 +30856,7 @@
         <v>8</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -30897,7 +30897,7 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -34406,7 +34406,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -34637,7 +34637,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -34714,7 +34714,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -35407,7 +35407,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -35561,7 +35561,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -35715,7 +35715,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -35792,7 +35792,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -36562,7 +36562,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -36598,7 +36598,7 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -47272,7 +47272,7 @@
         <v>-1</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -47326,7 +47326,7 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -47885,7 +47885,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -47921,7 +47921,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -48424,7 +48424,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -48578,7 +48578,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -48614,7 +48614,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -48655,7 +48655,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -48691,7 +48691,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -48963,7 +48963,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -49579,7 +49579,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>5</v>
@@ -49810,7 +49810,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>5</v>
@@ -49846,7 +49846,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -49887,7 +49887,7 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -49923,7 +49923,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>5</v>
@@ -50719,7 +50719,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -50755,7 +50755,7 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -50778,7 +50778,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -50796,7 +50796,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -50832,7 +50832,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -50873,7 +50873,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -50909,7 +50909,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -51009,7 +51009,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -51027,7 +51027,7 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -51063,7 +51063,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -51086,7 +51086,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -51104,7 +51104,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -51140,7 +51140,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -51779,7 +51779,7 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -51797,7 +51797,7 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -51833,7 +51833,7 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -51933,7 +51933,7 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -51951,7 +51951,7 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -51987,7 +51987,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -53076,7 +53076,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -53094,7 +53094,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -53130,7 +53130,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>-1</v>
@@ -53325,7 +53325,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -53361,7 +53361,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -53461,7 +53461,7 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -53479,7 +53479,7 @@
         <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -53515,7 +53515,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -54000,7 +54000,7 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -54018,7 +54018,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -54054,7 +54054,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -54231,7 +54231,7 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -54249,7 +54249,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -54285,7 +54285,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -54385,7 +54385,7 @@
         <v>5</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -54403,7 +54403,7 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -54439,7 +54439,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -54462,7 +54462,7 @@
         <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -54480,7 +54480,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -54516,7 +54516,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -54539,7 +54539,7 @@
         <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -54557,7 +54557,7 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -54593,7 +54593,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -54998,7 +54998,7 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -55457,7 +55457,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -55537,7 +55537,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -55573,7 +55573,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -55996,7 +55996,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -56032,7 +56032,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -56153,7 +56153,7 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -56189,7 +56189,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -56615,7 +56615,7 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -57056,7 +57056,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>8</v>
@@ -57074,7 +57074,7 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>8</v>
@@ -57110,7 +57110,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -57231,7 +57231,7 @@
         <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>6</v>
@@ -57267,7 +57267,7 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -57515,7 +57515,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -57592,7 +57592,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -57669,7 +57669,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -57705,7 +57705,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -57746,7 +57746,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -57782,7 +57782,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -57823,10 +57823,10 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -57862,7 +57862,7 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -57900,7 +57900,7 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -57977,10 +57977,10 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -58016,7 +58016,7 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -58054,7 +58054,7 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>8</v>
@@ -58090,7 +58090,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -58131,7 +58131,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>8</v>
@@ -58208,10 +58208,10 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -58247,7 +58247,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -58270,7 +58270,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -58285,10 +58285,10 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -58324,7 +58324,7 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -58362,7 +58362,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>8</v>
@@ -58439,7 +58439,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>8</v>
@@ -58475,7 +58475,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -58501,7 +58501,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -58516,10 +58516,10 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -58555,7 +58555,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -58593,7 +58593,7 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>8</v>
@@ -58629,7 +58629,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -58670,7 +58670,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -58706,7 +58706,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -58732,7 +58732,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -58747,10 +58747,10 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -58786,7 +58786,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -58853,7 +58853,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -58889,7 +58889,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -58930,7 +58930,7 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -58966,7 +58966,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -58992,7 +58992,7 @@
         <v>5</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>-1</v>
@@ -59007,10 +59007,10 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -59046,7 +59046,7 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -59069,7 +59069,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -59084,10 +59084,10 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -59123,7 +59123,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -62704,7 +62704,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -63474,7 +63474,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>7</v>
@@ -63510,7 +63510,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -63705,7 +63705,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -64380,7 +64380,7 @@
         <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -64416,7 +64416,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -64457,7 +64457,7 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -64493,7 +64493,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -64534,7 +64534,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -64570,7 +64570,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -64611,7 +64611,7 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -64688,7 +64688,7 @@
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -64724,7 +64724,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -64765,7 +64765,7 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -64842,7 +64842,7 @@
         <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -64878,7 +64878,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -64919,7 +64919,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -64955,7 +64955,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -65025,7 +65025,7 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -65102,7 +65102,7 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -65138,7 +65138,7 @@
         <v>5</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -65179,7 +65179,7 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -65215,7 +65215,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -65256,7 +65256,7 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -65292,7 +65292,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -65333,7 +65333,7 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>6</v>
@@ -65410,7 +65410,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -65446,7 +65446,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -65487,7 +65487,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>7</v>
@@ -65564,7 +65564,7 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -65641,7 +65641,7 @@
         <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -65677,7 +65677,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -65747,7 +65747,7 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -65824,7 +65824,7 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -65901,7 +65901,7 @@
         <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -65937,7 +65937,7 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -65978,7 +65978,7 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -66014,7 +66014,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -66055,7 +66055,7 @@
         <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -66091,7 +66091,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -66132,7 +66132,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>9</v>
@@ -66209,7 +66209,7 @@
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>8</v>
@@ -66245,7 +66245,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -66286,7 +66286,7 @@
         <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>9</v>
@@ -66363,7 +66363,7 @@
         <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -66399,7 +66399,7 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -66440,7 +66440,7 @@
         <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -66558,7 +66558,7 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -66594,7 +66594,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -66635,7 +66635,7 @@
         <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -66671,7 +66671,7 @@
         <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -66712,7 +66712,7 @@
         <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>8</v>
@@ -66789,7 +66789,7 @@
         <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>10</v>
@@ -66825,7 +66825,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -68435,7 +68435,7 @@
         <v>1033</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -68489,7 +68489,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -70061,7 +70061,7 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -70135,10 +70135,10 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -70174,7 +70174,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -70215,7 +70215,7 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -70289,10 +70289,10 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -70328,7 +70328,7 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -70366,10 +70366,10 @@
         <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>7</v>
@@ -70405,7 +70405,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -70428,7 +70428,7 @@
         <v>7</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -70482,7 +70482,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -70520,10 +70520,10 @@
         <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -70556,10 +70556,10 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -70597,10 +70597,10 @@
         <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -70633,10 +70633,10 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -70659,7 +70659,7 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -70677,7 +70677,7 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -70713,7 +70713,7 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -70751,10 +70751,10 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>7</v>
@@ -70790,7 +70790,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -70828,10 +70828,10 @@
         <v>4</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -70864,7 +70864,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -70905,10 +70905,10 @@
         <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>8</v>
@@ -70944,7 +70944,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -70982,10 +70982,10 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -71018,10 +71018,10 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -71059,10 +71059,10 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -71098,7 +71098,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -71136,10 +71136,10 @@
         <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -71175,7 +71175,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -71213,10 +71213,10 @@
         <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -71249,10 +71249,10 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -71290,10 +71290,10 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -71326,10 +71326,10 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -71367,10 +71367,10 @@
         <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -71406,7 +71406,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -71444,10 +71444,10 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -71483,7 +71483,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -71521,10 +71521,10 @@
         <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -71557,7 +71557,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -71598,10 +71598,10 @@
         <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -71637,7 +71637,7 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -71675,10 +71675,10 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -71714,7 +71714,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -71752,10 +71752,10 @@
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>7</v>
@@ -71791,7 +71791,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -71814,7 +71814,7 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -71868,7 +71868,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -71888,10 +71888,10 @@
         <v>-1</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -71942,10 +71942,10 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -72060,10 +72060,10 @@
         <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -72099,7 +72099,7 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -72160,7 +72160,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -72181,7 +72181,7 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -72214,10 +72214,10 @@
         <v>7</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -72255,10 +72255,10 @@
         <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -72291,10 +72291,10 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -72317,7 +72317,7 @@
         <v>5</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -72335,7 +72335,7 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -72371,7 +72371,7 @@
         <v>5</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>5</v>
@@ -72409,10 +72409,10 @@
         <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>7</v>
@@ -72486,10 +72486,10 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>8</v>
@@ -72522,10 +72522,10 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>8</v>
@@ -72563,10 +72563,10 @@
         <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>7</v>
@@ -72681,10 +72681,10 @@
         <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>7</v>
@@ -72717,10 +72717,10 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X39">
         <v>8</v>
@@ -72740,10 +72740,10 @@
         <v>-1</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F40">
         <v>5</v>
@@ -72794,10 +72794,10 @@
         <v>-1</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X40">
         <v>5</v>
@@ -76193,7 +76193,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -76347,7 +76347,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -76732,7 +76732,7 @@
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -76886,7 +76886,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -77194,7 +77194,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -77579,7 +77579,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -77964,7 +77964,7 @@
         <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -78426,7 +78426,7 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -79640,7 +79640,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -80179,7 +80179,7 @@
         <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -80718,7 +80718,7 @@
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -81950,7 +81950,7 @@
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -82027,7 +82027,7 @@
         <v>9</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -83087,7 +83087,7 @@
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -83318,7 +83318,7 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -84529,10 +84529,10 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -84565,7 +84565,7 @@
         <v>6</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -84606,10 +84606,10 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -84642,7 +84642,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -84683,10 +84683,10 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -84722,7 +84722,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -84760,10 +84760,10 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -84796,10 +84796,10 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -84837,10 +84837,10 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -84873,10 +84873,10 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -84914,10 +84914,10 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -84950,10 +84950,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -84991,10 +84991,10 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -85027,10 +85027,10 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -85068,10 +85068,10 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -85104,10 +85104,10 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -85145,10 +85145,10 @@
         <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -85181,7 +85181,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -85222,10 +85222,10 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -85258,7 +85258,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -85281,10 +85281,10 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -85299,10 +85299,10 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -85335,10 +85335,10 @@
         <v>6</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -85376,10 +85376,10 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -85412,7 +85412,7 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -85453,10 +85453,10 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -85489,7 +85489,7 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -85530,10 +85530,10 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -85566,10 +85566,10 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -85607,10 +85607,10 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -85643,7 +85643,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -85684,10 +85684,10 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -85720,7 +85720,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -85761,10 +85761,10 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -85797,7 +85797,7 @@
         <v>5</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -85838,10 +85838,10 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -85874,7 +85874,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -85915,10 +85915,10 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -85951,7 +85951,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -85992,10 +85992,10 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -86028,10 +86028,10 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -86069,10 +86069,10 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -86105,10 +86105,10 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -86146,10 +86146,10 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>7</v>
@@ -86182,10 +86182,10 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -86223,10 +86223,10 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>5</v>
@@ -86259,10 +86259,10 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -86300,10 +86300,10 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -86336,7 +86336,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -86377,10 +86377,10 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>5</v>
@@ -86413,7 +86413,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -86454,10 +86454,10 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>8</v>
@@ -86490,10 +86490,10 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -86531,10 +86531,10 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -86567,10 +86567,10 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -86608,10 +86608,10 @@
         <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -86644,10 +86644,10 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -86685,10 +86685,10 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>7</v>
@@ -86721,10 +86721,10 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -86762,10 +86762,10 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -86798,7 +86798,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -86839,10 +86839,10 @@
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>7</v>
@@ -86875,10 +86875,10 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -86916,10 +86916,10 @@
         <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -86952,7 +86952,7 @@
         <v>6</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -86993,10 +86993,10 @@
         <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>5</v>
@@ -87029,10 +87029,10 @@
         <v>5</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -87070,10 +87070,10 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
         <v>6</v>
@@ -87106,10 +87106,10 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -87147,10 +87147,10 @@
         <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
         <v>8</v>
@@ -87183,7 +87183,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -87224,10 +87224,10 @@
         <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
         <v>5</v>
@@ -87260,7 +87260,7 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>5</v>
@@ -87508,7 +87508,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -87544,7 +87544,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>8</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -8754,7 +8754,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -9062,7 +9062,7 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>7</v>
@@ -38442,7 +38442,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -38460,7 +38460,7 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -38496,7 +38496,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -41060,7 +41060,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -41214,7 +41214,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>8</v>
@@ -42831,7 +42831,7 @@
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
         <v>6</v>
@@ -42867,7 +42867,7 @@
         <v>7</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -47367,7 +47367,7 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -47403,7 +47403,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -50195,7 +50195,7 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -50231,7 +50231,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -67594,7 +67594,7 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -67612,7 +67612,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -67648,7 +67648,7 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -72734,7 +72734,7 @@
         <v>1088</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>-1</v>
@@ -72788,7 +72788,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>-1</v>
@@ -79169,7 +79169,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -80478,7 +80478,7 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -85752,7 +85752,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -85788,7 +85788,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>5</v>
@@ -85983,7 +85983,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -86019,7 +86019,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -86214,7 +86214,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -86250,7 +86250,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>5</v>
@@ -86291,7 +86291,7 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -86327,7 +86327,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -89276,7 +89276,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -89312,7 +89312,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -90354,7 +90354,7 @@
         <v>5</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I42">
         <v>-1</v>
@@ -90390,7 +90390,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>5</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -5411,7 +5411,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>6</v>
@@ -8873,7 +8873,7 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>6</v>
@@ -12160,7 +12160,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -21335,7 +21335,7 @@
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>7</v>
@@ -21412,7 +21412,7 @@
         <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>7</v>
@@ -21430,7 +21430,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -21471,7 +21471,7 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -21489,7 +21489,7 @@
         <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -21566,7 +21566,7 @@
         <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -21643,7 +21643,7 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -21720,7 +21720,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -21797,7 +21797,7 @@
         <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>7</v>
@@ -21815,7 +21815,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -21874,7 +21874,7 @@
         <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>7</v>
@@ -21951,7 +21951,7 @@
         <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -22010,7 +22010,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -22028,7 +22028,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -22164,7 +22164,7 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -22182,7 +22182,7 @@
         <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>8</v>
@@ -22259,7 +22259,7 @@
         <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -22336,7 +22336,7 @@
         <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -22354,7 +22354,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -22395,7 +22395,7 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>7</v>
@@ -22413,7 +22413,7 @@
         <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>6</v>
@@ -22431,7 +22431,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -22472,7 +22472,7 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>6</v>
@@ -22490,7 +22490,7 @@
         <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>6</v>
@@ -22567,7 +22567,7 @@
         <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -22585,7 +22585,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -22644,7 +22644,7 @@
         <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -22662,7 +22662,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -22721,7 +22721,7 @@
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>8</v>
@@ -22798,7 +22798,7 @@
         <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>9</v>
@@ -22875,7 +22875,7 @@
         <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>8</v>
@@ -22934,7 +22934,7 @@
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>7</v>
@@ -22952,7 +22952,7 @@
         <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>6</v>
@@ -23029,7 +23029,7 @@
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>9</v>
@@ -23088,7 +23088,7 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -23106,7 +23106,7 @@
         <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -23165,7 +23165,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>6</v>
@@ -23183,7 +23183,7 @@
         <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>7</v>
@@ -23201,7 +23201,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -23260,7 +23260,7 @@
         <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
         <v>8</v>
@@ -23278,7 +23278,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -28377,7 +28377,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -28454,7 +28454,7 @@
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -28472,7 +28472,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -28531,7 +28531,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -28608,7 +28608,7 @@
         <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -28685,7 +28685,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -28703,7 +28703,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -28762,7 +28762,7 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -28839,7 +28839,7 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -28916,7 +28916,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -28934,7 +28934,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -28993,7 +28993,7 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>10</v>
@@ -29011,7 +29011,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -29070,7 +29070,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -29147,7 +29147,7 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -29165,7 +29165,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -29224,7 +29224,7 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -29301,7 +29301,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -29319,7 +29319,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -29378,7 +29378,7 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>10</v>
@@ -29396,7 +29396,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -29455,7 +29455,7 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -29473,7 +29473,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -29532,7 +29532,7 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -29609,7 +29609,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -29627,7 +29627,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -29686,7 +29686,7 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -29704,7 +29704,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -29763,7 +29763,7 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>5</v>
@@ -29840,7 +29840,7 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -29858,7 +29858,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -29917,7 +29917,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -29994,7 +29994,7 @@
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -30071,7 +30071,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -30089,7 +30089,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -30148,7 +30148,7 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -30225,7 +30225,7 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -30302,7 +30302,7 @@
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -30379,7 +30379,7 @@
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -30438,7 +30438,7 @@
         <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -30456,7 +30456,7 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -30533,7 +30533,7 @@
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -30551,7 +30551,7 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -30610,7 +30610,7 @@
         <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>10</v>
@@ -30687,7 +30687,7 @@
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -30764,7 +30764,7 @@
         <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
@@ -30841,7 +30841,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>10</v>
@@ -30918,7 +30918,7 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
         <v>7</v>
@@ -30936,7 +30936,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -53159,7 +53159,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -53177,7 +53177,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -53390,7 +53390,7 @@
         <v>6</v>
       </c>
       <c r="R8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -53408,7 +53408,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -54083,7 +54083,7 @@
         <v>5</v>
       </c>
       <c r="R17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>5</v>
@@ -54101,7 +54101,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -54237,7 +54237,7 @@
         <v>9</v>
       </c>
       <c r="R19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>5</v>
@@ -54255,7 +54255,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -54468,7 +54468,7 @@
         <v>5</v>
       </c>
       <c r="R22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -54486,7 +54486,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -54622,7 +54622,7 @@
         <v>8</v>
       </c>
       <c r="R24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -54640,7 +54640,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -70102,7 +70102,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -70120,7 +70120,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -70197,7 +70197,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -70256,7 +70256,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -70274,7 +70274,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -70292,7 +70292,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -70351,7 +70351,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -70428,7 +70428,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -70487,7 +70487,7 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>6</v>
@@ -70505,7 +70505,7 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -70523,7 +70523,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -70582,7 +70582,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -70600,7 +70600,7 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -70659,7 +70659,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -70677,7 +70677,7 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -70718,7 +70718,7 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>7</v>
@@ -70736,7 +70736,7 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>7</v>
@@ -70754,7 +70754,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -70813,7 +70813,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -70831,7 +70831,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -70890,7 +70890,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -70908,7 +70908,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -70967,7 +70967,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -71044,7 +71044,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -71121,7 +71121,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>9</v>
@@ -71198,7 +71198,7 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -71275,7 +71275,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -71352,7 +71352,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -71429,7 +71429,7 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -71447,7 +71447,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -71506,7 +71506,7 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -71524,7 +71524,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -71583,7 +71583,7 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -71660,7 +71660,7 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -71737,7 +71737,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -71814,7 +71814,7 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -71867,13 +71867,13 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -71885,13 +71885,13 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>7</v>
@@ -71950,7 +71950,7 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -71968,7 +71968,7 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>7</v>
@@ -72027,7 +72027,7 @@
         <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -72045,7 +72045,7 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -72122,7 +72122,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -72222,7 +72222,7 @@
         <v>4</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>9</v>
@@ -72240,7 +72240,7 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>9</v>
@@ -72258,7 +72258,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -72317,7 +72317,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -72376,7 +72376,7 @@
         <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>7</v>
@@ -72394,7 +72394,7 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>7</v>
@@ -72412,7 +72412,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -72471,7 +72471,7 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
         <v>8</v>
@@ -72489,7 +72489,7 @@
         <v>7</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -72548,7 +72548,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>9</v>
@@ -72566,7 +72566,7 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -72625,7 +72625,7 @@
         <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>9</v>
@@ -72643,7 +72643,7 @@
         <v>6</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -72669,7 +72669,7 @@
         <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -72678,7 +72678,7 @@
         <v>7</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
         <v>5</v>
@@ -72743,7 +72743,7 @@
         <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
         <v>9</v>
@@ -72802,7 +72802,7 @@
         <v>5</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K40">
         <v>8</v>
@@ -72820,7 +72820,7 @@
         <v>5</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>8</v>
@@ -72838,7 +72838,7 @@
         <v>5</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>7</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -66847,7 +66847,7 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -66901,7 +66901,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -67771,7 +67771,7 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -67825,7 +67825,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>5</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -57553,7 +57553,7 @@
         <v>-1</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -57607,7 +57607,7 @@
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -58323,7 +58323,7 @@
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -58377,7 +58377,7 @@
         <v>-1</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -11304,7 +11304,7 @@
         <v>6</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -11367,7 +11367,7 @@
         <v>6</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -50709,7 +50709,7 @@
         <v>6</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -50772,7 +50772,7 @@
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -51243,7 +51243,7 @@
         <v>-1</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -51306,7 +51306,7 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -51385,7 +51385,7 @@
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>9</v>
@@ -51448,7 +51448,7 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA20">
         <v>9</v>
@@ -51474,7 +51474,7 @@
         <v>-1</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -51537,7 +51537,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>5</v>
@@ -51741,7 +51741,7 @@
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>9</v>
@@ -51804,7 +51804,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA24">
         <v>9</v>
@@ -52008,7 +52008,7 @@
         <v>-1</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -52071,7 +52071,7 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA27">
         <v>6</v>
@@ -52186,7 +52186,7 @@
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>7</v>
@@ -52249,7 +52249,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -52275,7 +52275,7 @@
         <v>8</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F30">
         <v>10</v>
@@ -52338,7 +52338,7 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -52364,7 +52364,7 @@
         <v>-1</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
         <v>9</v>
@@ -52427,7 +52427,7 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>9</v>
@@ -54604,7 +54604,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -54658,7 +54658,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -54681,7 +54681,7 @@
         <v>-1</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -54735,7 +54735,7 @@
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -54835,7 +54835,7 @@
         <v>-1</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -54889,7 +54889,7 @@
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -54989,7 +54989,7 @@
         <v>8</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -55043,7 +55043,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -55220,7 +55220,7 @@
         <v>-1</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -55274,7 +55274,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -55528,7 +55528,7 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -55582,7 +55582,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -55605,7 +55605,7 @@
         <v>7</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -55659,7 +55659,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -55682,7 +55682,7 @@
         <v>8</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -55736,7 +55736,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -55990,7 +55990,7 @@
         <v>-1</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -56044,7 +56044,7 @@
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -56067,7 +56067,7 @@
         <v>8</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -56121,7 +56121,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -56298,7 +56298,7 @@
         <v>7</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -56352,7 +56352,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -56452,7 +56452,7 @@
         <v>-1</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -56506,7 +56506,7 @@
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -56606,7 +56606,7 @@
         <v>9</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -56660,7 +56660,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -56683,7 +56683,7 @@
         <v>9</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -56737,7 +56737,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -56760,7 +56760,7 @@
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -56814,7 +56814,7 @@
         <v>-1</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -56837,7 +56837,7 @@
         <v>6</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -56891,7 +56891,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -57068,7 +57068,7 @@
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -57122,7 +57122,7 @@
         <v>-1</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -57322,7 +57322,7 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -57376,7 +57376,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -57399,7 +57399,7 @@
         <v>7</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -57453,7 +57453,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -57476,7 +57476,7 @@
         <v>-1</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -57530,7 +57530,7 @@
         <v>-1</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -57630,7 +57630,7 @@
         <v>7</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -57684,7 +57684,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -57784,7 +57784,7 @@
         <v>-1</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -57838,7 +57838,7 @@
         <v>-1</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -57861,7 +57861,7 @@
         <v>-1</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -57915,7 +57915,7 @@
         <v>-1</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -57938,7 +57938,7 @@
         <v>-1</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -57992,7 +57992,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -58015,7 +58015,7 @@
         <v>-1</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -58069,7 +58069,7 @@
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -58092,7 +58092,7 @@
         <v>-1</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -58146,7 +58146,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -58169,7 +58169,7 @@
         <v>-1</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -58223,7 +58223,7 @@
         <v>-1</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -58246,7 +58246,7 @@
         <v>-1</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -58300,7 +58300,7 @@
         <v>-1</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -58400,7 +58400,7 @@
         <v>-1</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -58454,7 +58454,7 @@
         <v>-1</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -58477,7 +58477,7 @@
         <v>-1</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -58531,7 +58531,7 @@
         <v>-1</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -58554,7 +58554,7 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -58608,7 +58608,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -58631,7 +58631,7 @@
         <v>-1</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -58685,7 +58685,7 @@
         <v>-1</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -58708,7 +58708,7 @@
         <v>-1</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -58762,7 +58762,7 @@
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -9349,7 +9349,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -9438,7 +9438,7 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -9480,7 +9480,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -9527,7 +9527,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -9616,7 +9616,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -9658,7 +9658,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -9705,7 +9705,7 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>7</v>
@@ -9794,7 +9794,7 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>7</v>
@@ -9836,7 +9836,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -9883,7 +9883,7 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>9</v>
@@ -9972,7 +9972,7 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -10061,7 +10061,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>9</v>
@@ -10150,7 +10150,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -10239,7 +10239,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>9</v>
@@ -10328,7 +10328,7 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>8</v>
@@ -10417,7 +10417,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>8</v>
@@ -10506,7 +10506,7 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>9</v>
@@ -10595,7 +10595,7 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -10684,7 +10684,7 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -10773,7 +10773,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -10951,7 +10951,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>9</v>
@@ -11040,7 +11040,7 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -11082,7 +11082,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -11129,7 +11129,7 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -11171,7 +11171,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -11218,7 +11218,7 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>5</v>
@@ -11307,7 +11307,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -11349,7 +11349,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -11396,7 +11396,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -11438,7 +11438,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -11485,7 +11485,7 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>7</v>
@@ -11574,7 +11574,7 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -11663,7 +11663,7 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>9</v>
@@ -11752,7 +11752,7 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -11794,7 +11794,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -11841,7 +11841,7 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -11883,7 +11883,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -11930,7 +11930,7 @@
         <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>7</v>
@@ -12019,7 +12019,7 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>7</v>
@@ -12108,7 +12108,7 @@
         <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>9</v>
@@ -36713,7 +36713,7 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -37204,7 +37204,7 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -37666,7 +37666,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -37702,7 +37702,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -38116,7 +38116,7 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>8</v>
@@ -38347,7 +38347,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -38915,7 +38915,7 @@
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>9</v>
@@ -38992,7 +38992,7 @@
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
         <v>9</v>
@@ -43474,7 +43474,7 @@
         <v>7</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -43492,7 +43492,7 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -43528,7 +43528,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -43877,7 +43877,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -52638,7 +52638,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -52680,7 +52680,7 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -52706,7 +52706,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -52769,7 +52769,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -52816,7 +52816,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -52858,7 +52858,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -52884,7 +52884,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -52947,7 +52947,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -52973,7 +52973,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -53036,7 +53036,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -53062,7 +53062,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -53083,7 +53083,7 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -53125,7 +53125,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -53261,7 +53261,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -53350,7 +53350,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -53392,7 +53392,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -53418,7 +53418,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -53439,7 +53439,7 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>9</v>
@@ -53481,7 +53481,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -53507,7 +53507,7 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -53528,7 +53528,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>10</v>
@@ -53570,7 +53570,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -53617,7 +53617,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -53659,7 +53659,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -53706,7 +53706,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -53774,7 +53774,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -53837,7 +53837,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -53863,7 +53863,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -53884,7 +53884,7 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -53926,7 +53926,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -54207,7 +54207,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -54270,7 +54270,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -54296,7 +54296,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -54359,7 +54359,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>-1</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -9984,7 +9984,7 @@
         <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>10</v>
@@ -10026,7 +10026,7 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>9</v>
@@ -25250,7 +25250,7 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -25327,7 +25327,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -25558,7 +25558,7 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>7</v>
@@ -25594,7 +25594,7 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -25712,7 +25712,7 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -25866,7 +25866,7 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -26020,7 +26020,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>7</v>
@@ -26056,7 +26056,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -26097,7 +26097,7 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -26174,7 +26174,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>10</v>
@@ -26210,7 +26210,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -26328,7 +26328,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>10</v>
@@ -26636,7 +26636,7 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -26713,7 +26713,7 @@
         <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -26790,7 +26790,7 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -26826,7 +26826,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -27098,7 +27098,7 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>10</v>
@@ -27252,7 +27252,7 @@
         <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>10</v>
@@ -27329,7 +27329,7 @@
         <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>9</v>
@@ -27365,7 +27365,7 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -42796,7 +42796,7 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -42832,7 +42832,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>-1</v>
@@ -44028,7 +44028,7 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -44064,7 +44064,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>-1</v>
@@ -44490,7 +44490,7 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -44567,7 +44567,7 @@
         <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>7</v>
@@ -44603,7 +44603,7 @@
         <v>6</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -45476,7 +45476,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -45553,7 +45553,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -45659,7 +45659,7 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -45736,7 +45736,7 @@
         <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -45813,7 +45813,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -45890,7 +45890,7 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -45926,7 +45926,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -46008,7 +46008,7 @@
         <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -46085,7 +46085,7 @@
         <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -46121,7 +46121,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -46239,7 +46239,7 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>8</v>
@@ -46316,7 +46316,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -46352,7 +46352,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -46470,7 +46470,7 @@
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -46506,7 +46506,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -46547,7 +46547,7 @@
         <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -46624,7 +46624,7 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -46660,7 +46660,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -46730,7 +46730,7 @@
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -46766,7 +46766,7 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -46959,7 +46959,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -47116,7 +47116,7 @@
         <v>4</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -47137,7 +47137,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -47179,7 +47179,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -47315,7 +47315,7 @@
         <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -47357,7 +47357,7 @@
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -47727,7 +47727,7 @@
         <v>4</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -47790,7 +47790,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -47837,10 +47837,10 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -47879,7 +47879,7 @@
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -47926,7 +47926,7 @@
         <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -47968,7 +47968,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -48460,7 +48460,7 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>6</v>
@@ -48502,7 +48502,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -48638,7 +48638,7 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -48905,7 +48905,7 @@
         <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -48947,7 +48947,7 @@
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>9</v>
@@ -49083,7 +49083,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -49261,7 +49261,7 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>6</v>
@@ -49329,7 +49329,7 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F31">
         <v>8</v>
@@ -49350,7 +49350,7 @@
         <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>6</v>
@@ -49392,7 +49392,7 @@
         <v>6</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>7</v>
@@ -49418,7 +49418,7 @@
         <v>4</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F32">
         <v>-1</v>
@@ -49439,7 +49439,7 @@
         <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -49481,7 +49481,7 @@
         <v>5</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA32">
         <v>-1</v>
@@ -49528,7 +49528,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -49570,7 +49570,7 @@
         <v>5</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>-1</v>
@@ -49858,7 +49858,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -49900,7 +49900,7 @@
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>5</v>
@@ -49947,7 +49947,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -49989,7 +49989,7 @@
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -50036,7 +50036,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -50125,7 +50125,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -50167,7 +50167,7 @@
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -50303,7 +50303,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -50481,7 +50481,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -50523,7 +50523,7 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -50570,7 +50570,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -50612,7 +50612,7 @@
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -50659,7 +50659,7 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -50701,7 +50701,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>6</v>
@@ -50748,7 +50748,7 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -50790,7 +50790,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -50837,7 +50837,7 @@
         <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -50879,7 +50879,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA15">
         <v>9</v>
@@ -50926,7 +50926,7 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -50968,7 +50968,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -51015,7 +51015,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -51104,7 +51104,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -51246,7 +51246,7 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -51513,7 +51513,7 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -51602,7 +51602,7 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -51691,7 +51691,7 @@
         <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -51733,7 +51733,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -51780,7 +51780,7 @@
         <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -51869,7 +51869,7 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -51958,7 +51958,7 @@
         <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -52047,7 +52047,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -52089,7 +52089,7 @@
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>6</v>
@@ -52225,7 +52225,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>8</v>
@@ -52314,7 +52314,7 @@
         <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -52356,7 +52356,7 @@
         <v>8</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -52653,7 +52653,7 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -52831,7 +52831,7 @@
         <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -52873,7 +52873,7 @@
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -52920,7 +52920,7 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -53098,7 +53098,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -53187,7 +53187,7 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -53229,7 +53229,7 @@
         <v>5</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -53276,7 +53276,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -53318,7 +53318,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -53365,7 +53365,7 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -53543,7 +53543,7 @@
         <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -53585,7 +53585,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -53632,7 +53632,7 @@
         <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -53674,7 +53674,7 @@
         <v>6</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -53721,7 +53721,7 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -53899,7 +53899,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -53941,7 +53941,7 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -54551,7 +54551,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -54587,7 +54587,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -54628,7 +54628,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -54705,7 +54705,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -54859,7 +54859,7 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -55090,7 +55090,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -55167,7 +55167,7 @@
         <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -55203,7 +55203,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -55244,7 +55244,7 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -55321,7 +55321,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -55357,7 +55357,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -55398,7 +55398,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -55475,7 +55475,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -55552,7 +55552,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -55629,7 +55629,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -55783,7 +55783,7 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -55860,7 +55860,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -56014,7 +56014,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -56091,7 +56091,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -56168,7 +56168,7 @@
         <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -56204,7 +56204,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -56245,7 +56245,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -56322,7 +56322,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -56399,7 +56399,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -56435,7 +56435,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -56476,7 +56476,7 @@
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -56553,7 +56553,7 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -56630,7 +56630,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -56707,7 +56707,7 @@
         <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -56784,7 +56784,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -56820,7 +56820,7 @@
         <v>5</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -56843,7 +56843,7 @@
         <v>4</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H34">
         <v>8</v>
@@ -56897,7 +56897,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -56938,7 +56938,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -57269,7 +57269,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -57577,7 +57577,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -57654,7 +57654,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -57731,7 +57731,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -57808,7 +57808,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -57885,7 +57885,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -57962,7 +57962,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -57998,7 +57998,7 @@
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -58039,7 +58039,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -58116,7 +58116,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -58270,7 +58270,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -58306,7 +58306,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -58347,7 +58347,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -58383,7 +58383,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -58424,7 +58424,7 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -58460,7 +58460,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -58501,7 +58501,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -58578,7 +58578,7 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -58655,7 +58655,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -58691,7 +58691,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -71621,7 +71621,7 @@
         <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -71657,7 +71657,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -6443,7 +6443,7 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -6520,7 +6520,7 @@
         <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -6597,7 +6597,7 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -6674,7 +6674,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -6692,7 +6692,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -6751,7 +6751,7 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -6828,7 +6828,7 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -6905,7 +6905,7 @@
         <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -6982,7 +6982,7 @@
         <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -7000,7 +7000,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -7059,7 +7059,7 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -7136,7 +7136,7 @@
         <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -7213,7 +7213,7 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -7231,7 +7231,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -7290,7 +7290,7 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -7367,7 +7367,7 @@
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -7385,7 +7385,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -7444,7 +7444,7 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -7462,7 +7462,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -7521,7 +7521,7 @@
         <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -7539,7 +7539,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -7752,7 +7752,7 @@
         <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -7829,7 +7829,7 @@
         <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -7906,7 +7906,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -7924,7 +7924,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -7983,7 +7983,7 @@
         <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -8060,7 +8060,7 @@
         <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -8078,7 +8078,7 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -8137,7 +8137,7 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -8214,7 +8214,7 @@
         <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -8291,7 +8291,7 @@
         <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -8368,7 +8368,7 @@
         <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -8445,7 +8445,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -8463,7 +8463,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -8522,7 +8522,7 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -8599,7 +8599,7 @@
         <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -8676,7 +8676,7 @@
         <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -8753,7 +8753,7 @@
         <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -8830,7 +8830,7 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -8848,7 +8848,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -8984,7 +8984,7 @@
         <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -9061,7 +9061,7 @@
         <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -9138,7 +9138,7 @@
         <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -15404,7 +15404,7 @@
         <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>7</v>
@@ -15481,7 +15481,7 @@
         <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -15558,7 +15558,7 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>10</v>
@@ -15635,7 +15635,7 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>10</v>
@@ -15712,7 +15712,7 @@
         <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>5</v>
@@ -15730,7 +15730,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -15866,7 +15866,7 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>10</v>
@@ -15943,7 +15943,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -16020,7 +16020,7 @@
         <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -16038,7 +16038,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -16097,7 +16097,7 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>10</v>
@@ -16174,7 +16174,7 @@
         <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -16192,7 +16192,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -16251,7 +16251,7 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>5</v>
@@ -16269,7 +16269,7 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -16328,7 +16328,7 @@
         <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>10</v>
@@ -16405,7 +16405,7 @@
         <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -16482,7 +16482,7 @@
         <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>10</v>
@@ -16559,7 +16559,7 @@
         <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>10</v>
@@ -16636,7 +16636,7 @@
         <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -16654,7 +16654,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -16790,7 +16790,7 @@
         <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>7</v>
@@ -16808,7 +16808,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -16867,7 +16867,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>9</v>
@@ -16944,7 +16944,7 @@
         <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>9</v>
@@ -17021,7 +17021,7 @@
         <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>9</v>
@@ -17039,7 +17039,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -17098,7 +17098,7 @@
         <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -17116,7 +17116,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -17175,7 +17175,7 @@
         <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>9</v>
@@ -45491,7 +45491,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>7</v>
@@ -45509,7 +45509,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -45568,7 +45568,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -45615,7 +45615,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -45674,7 +45674,7 @@
         <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -45751,7 +45751,7 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -45769,7 +45769,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -45828,7 +45828,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>9</v>
@@ -45905,7 +45905,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -45923,7 +45923,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -45961,7 +45961,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -45970,7 +45970,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -46023,7 +46023,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -46100,7 +46100,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -46177,7 +46177,7 @@
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -46195,7 +46195,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -46254,7 +46254,7 @@
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>8</v>
@@ -46331,7 +46331,7 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -46408,7 +46408,7 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -46485,7 +46485,7 @@
         <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -46562,7 +46562,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>9</v>
@@ -46639,7 +46639,7 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>8</v>
@@ -46686,7 +46686,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -46745,7 +46745,7 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>8</v>
@@ -46989,7 +46989,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -47078,7 +47078,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -47167,7 +47167,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -47188,7 +47188,7 @@
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -47256,7 +47256,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -47345,7 +47345,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -47434,7 +47434,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -47523,7 +47523,7 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -47544,7 +47544,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -47603,7 +47603,7 @@
         <v>4</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -47778,7 +47778,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -47799,7 +47799,7 @@
         <v>6</v>
       </c>
       <c r="AC13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -47867,7 +47867,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -47888,7 +47888,7 @@
         <v>7</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -47956,7 +47956,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -48045,7 +48045,7 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -48134,7 +48134,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -48223,7 +48223,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -48312,7 +48312,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -48401,7 +48401,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -48422,7 +48422,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -48490,7 +48490,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -48579,7 +48579,7 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -48668,7 +48668,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -48757,7 +48757,7 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -48846,7 +48846,7 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -48935,7 +48935,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -48956,7 +48956,7 @@
         <v>8</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -49024,7 +49024,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -49113,7 +49113,7 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -49202,7 +49202,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -49291,7 +49291,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -49380,7 +49380,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -49469,7 +49469,7 @@
         <v>7</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -49558,7 +49558,7 @@
         <v>6</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -49647,7 +49647,7 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -52662,7 +52662,7 @@
         <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>9</v>
@@ -52751,7 +52751,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -52772,7 +52772,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>6</v>
@@ -52840,7 +52840,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -52929,7 +52929,7 @@
         <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -53018,7 +53018,7 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -53039,7 +53039,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -53107,7 +53107,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -53154,7 +53154,7 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -53175,7 +53175,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -53196,7 +53196,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -53217,7 +53217,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -53285,7 +53285,7 @@
         <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -53374,7 +53374,7 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -53463,7 +53463,7 @@
         <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>5</v>
@@ -53552,7 +53552,7 @@
         <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -53641,7 +53641,7 @@
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>9</v>
@@ -53730,7 +53730,7 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>9</v>
@@ -53819,7 +53819,7 @@
         <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>9</v>
@@ -53908,7 +53908,7 @@
         <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -53991,7 +53991,7 @@
         <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -54009,7 +54009,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -54074,7 +54074,7 @@
         <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -54163,7 +54163,7 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>9</v>
@@ -54252,7 +54252,7 @@
         <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>5</v>
@@ -54273,7 +54273,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -54299,7 +54299,7 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -54320,7 +54320,7 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -54341,7 +54341,7 @@
         <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -54362,7 +54362,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -57272,7 +57272,7 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -57349,7 +57349,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -57367,7 +57367,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -57426,7 +57426,7 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -57444,7 +57444,7 @@
         <v>7</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -57503,7 +57503,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -57580,7 +57580,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -57657,7 +57657,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -57734,7 +57734,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -57811,7 +57811,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -57888,7 +57888,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -57965,7 +57965,7 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -57983,7 +57983,7 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -58042,7 +58042,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -58119,7 +58119,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -58160,7 +58160,7 @@
         <v>934</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -58178,7 +58178,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -58196,7 +58196,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -58214,7 +58214,7 @@
         <v>5</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -58273,7 +58273,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -58350,7 +58350,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -58427,7 +58427,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -58504,7 +58504,7 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -58522,7 +58522,7 @@
         <v>6</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -58581,7 +58581,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -58658,7 +58658,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -63034,7 +63034,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -63111,7 +63111,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -63129,7 +63129,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -63188,7 +63188,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -63265,7 +63265,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -63342,7 +63342,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -63419,7 +63419,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -63496,7 +63496,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -63514,7 +63514,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -63564,7 +63564,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -63679,7 +63679,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>9</v>
@@ -63756,7 +63756,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -63774,7 +63774,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -63833,7 +63833,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -63910,7 +63910,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -63987,7 +63987,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>10</v>
@@ -64064,7 +64064,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -64141,7 +64141,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -64159,7 +64159,7 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -64218,7 +64218,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -64295,7 +64295,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>5</v>
@@ -64313,7 +64313,7 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -64372,7 +64372,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>10</v>
@@ -64390,7 +64390,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -64449,7 +64449,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -64526,7 +64526,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -64603,7 +64603,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>9</v>
@@ -64680,7 +64680,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -64698,7 +64698,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -64757,7 +64757,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -64834,7 +64834,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -64852,7 +64852,7 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -64911,7 +64911,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -64929,7 +64929,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -64988,7 +64988,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -65065,7 +65065,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -65142,7 +65142,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -65160,7 +65160,7 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -65219,7 +65219,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>10</v>
@@ -65296,7 +65296,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -65314,7 +65314,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -65373,7 +65373,7 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
@@ -65391,7 +65391,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -65580,7 +65580,7 @@
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -65657,7 +65657,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -65675,7 +65675,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -65734,7 +65734,7 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -65752,7 +65752,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -65811,7 +65811,7 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -65888,7 +65888,7 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -65906,7 +65906,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -65965,7 +65965,7 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -66042,7 +66042,7 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -66119,7 +66119,7 @@
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -66196,7 +66196,7 @@
         <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -66214,7 +66214,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -66273,7 +66273,7 @@
         <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -66291,7 +66291,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -66350,7 +66350,7 @@
         <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -66427,7 +66427,7 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -66504,7 +66504,7 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -66581,7 +66581,7 @@
         <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -66658,7 +66658,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -66735,7 +66735,7 @@
         <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -66812,7 +66812,7 @@
         <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -66889,7 +66889,7 @@
         <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -66966,7 +66966,7 @@
         <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -66984,7 +66984,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -67043,7 +67043,7 @@
         <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -67084,7 +67084,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -67102,7 +67102,7 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -67120,7 +67120,7 @@
         <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -67138,7 +67138,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -67197,7 +67197,7 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -67274,7 +67274,7 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -67351,7 +67351,7 @@
         <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -67428,7 +67428,7 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -67469,7 +67469,7 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>-1</v>
@@ -67487,7 +67487,7 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -67505,7 +67505,7 @@
         <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -67523,7 +67523,7 @@
         <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -67582,7 +67582,7 @@
         <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -67659,7 +67659,7 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -67736,7 +67736,7 @@
         <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -67754,7 +67754,7 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -67813,7 +67813,7 @@
         <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -67831,7 +67831,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -67890,7 +67890,7 @@
         <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -67908,7 +67908,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -67931,7 +67931,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>-1</v>
@@ -67949,7 +67949,7 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -67967,7 +67967,7 @@
         <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -67985,7 +67985,7 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V35">
         <v>-1</v>
@@ -73463,7 +73463,7 @@
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -73540,7 +73540,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -73617,7 +73617,7 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -73694,7 +73694,7 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -73712,7 +73712,7 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -73771,7 +73771,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -73848,7 +73848,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -73866,7 +73866,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -73925,7 +73925,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -74002,7 +74002,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -74079,7 +74079,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -74097,7 +74097,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -74156,7 +74156,7 @@
         <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -74233,7 +74233,7 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -74310,7 +74310,7 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -74328,7 +74328,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -74387,7 +74387,7 @@
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -74464,7 +74464,7 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -74482,7 +74482,7 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -74541,7 +74541,7 @@
         <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -74559,7 +74559,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -74618,7 +74618,7 @@
         <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -74695,7 +74695,7 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -74772,7 +74772,7 @@
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -74790,7 +74790,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -74849,7 +74849,7 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -74926,7 +74926,7 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -75003,7 +75003,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -75080,7 +75080,7 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -75098,7 +75098,7 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -75157,7 +75157,7 @@
         <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -75175,7 +75175,7 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -75234,7 +75234,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -75252,7 +75252,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -75311,7 +75311,7 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -75388,7 +75388,7 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -75465,7 +75465,7 @@
         <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -75542,7 +75542,7 @@
         <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -75619,7 +75619,7 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -75696,7 +75696,7 @@
         <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -75714,7 +75714,7 @@
         <v>7</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -75773,7 +75773,7 @@
         <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -75791,7 +75791,7 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -75850,7 +75850,7 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -75927,7 +75927,7 @@
         <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -76004,7 +76004,7 @@
         <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -76022,7 +76022,7 @@
         <v>5</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -76081,7 +76081,7 @@
         <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -76099,7 +76099,7 @@
         <v>10</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -76158,7 +76158,7 @@
         <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -76235,7 +76235,7 @@
         <v>6</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -76253,7 +76253,7 @@
         <v>6</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>8</v>
@@ -76445,7 +76445,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -76522,7 +76522,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -76599,7 +76599,7 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -76676,7 +76676,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -76694,7 +76694,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -76753,7 +76753,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -76771,7 +76771,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -76830,7 +76830,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -76848,7 +76848,7 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -76907,7 +76907,7 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -76984,7 +76984,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -77002,7 +77002,7 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -77061,7 +77061,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -77079,7 +77079,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -77138,7 +77138,7 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -77156,7 +77156,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -77215,7 +77215,7 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -77292,7 +77292,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -77369,7 +77369,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -77387,7 +77387,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -77446,7 +77446,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -77523,7 +77523,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>7</v>
@@ -77600,7 +77600,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -77618,7 +77618,7 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -77677,7 +77677,7 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -77754,7 +77754,7 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -77772,7 +77772,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -77831,7 +77831,7 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>8</v>
@@ -77849,7 +77849,7 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -77908,7 +77908,7 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -77926,7 +77926,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -77985,7 +77985,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>8</v>
@@ -78062,7 +78062,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -78080,7 +78080,7 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -78139,7 +78139,7 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -78216,7 +78216,7 @@
         <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>8</v>
@@ -78293,7 +78293,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -78311,7 +78311,7 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -78370,7 +78370,7 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -78447,7 +78447,7 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>7</v>
@@ -78465,7 +78465,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -78524,7 +78524,7 @@
         <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -78601,7 +78601,7 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -78678,7 +78678,7 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -78755,7 +78755,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -78832,7 +78832,7 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>10</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -55731,7 +55731,7 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -55785,7 +55785,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -56193,7 +56193,7 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -56247,7 +56247,7 @@
         <v>-1</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -56501,7 +56501,7 @@
         <v>-1</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -56555,7 +56555,7 @@
         <v>-1</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>-1</v>
@@ -56732,7 +56732,7 @@
         <v>8</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -56786,7 +56786,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -57040,7 +57040,7 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -57094,7 +57094,7 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -57117,7 +57117,7 @@
         <v>-1</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -57171,7 +57171,7 @@
         <v>-1</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -57271,7 +57271,7 @@
         <v>7</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>7</v>
@@ -57325,7 +57325,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -57483,7 +57483,7 @@
         <v>8</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -57537,7 +57537,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>-1</v>
@@ -57560,7 +57560,7 @@
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>-1</v>
@@ -57614,7 +57614,7 @@
         <v>-1</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>-1</v>
@@ -71712,7 +71712,7 @@
         <v>-1</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -71766,7 +71766,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -72328,7 +72328,7 @@
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -72382,7 +72382,7 @@
         <v>-1</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -73707,7 +73707,7 @@
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -73761,7 +73761,7 @@
         <v>-1</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -73772,7 +73772,7 @@
         <v>8</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -73790,7 +73790,7 @@
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -2214,6 +2214,9 @@
     <t>GUERRA RIVERA CLAUDIA PAOLA</t>
   </si>
   <si>
+    <t>HERNANDEZ CADENA DANA PAOLA</t>
+  </si>
+  <si>
     <t>HERNANDEZ ROJAS LILIANA</t>
   </si>
   <si>
@@ -2221,9 +2224,6 @@
   </si>
   <si>
     <t>JIMENEZ COLMENARES ROSARIO DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ PEREZ KATIA GUADALUPE</t>
   </si>
   <si>
     <t>MARTINEZ RODRIGUEZ EVIAN ISSAIAS</t>
@@ -38423,16 +38423,16 @@
         <v>-1</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="E16">
         <v>-1</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -38477,16 +38477,16 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="W16">
         <v>-1</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -38494,19 +38494,19 @@
         <v>723</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>-1</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -38548,19 +38548,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>-1</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -38571,22 +38571,22 @@
         <v>724</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -38625,22 +38625,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -38648,22 +38648,22 @@
         <v>725</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -38702,22 +38702,22 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -49747,7 +49747,7 @@
         <v>-1</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -49801,7 +49801,7 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -49889,7 +49889,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -49943,7 +49943,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -49966,7 +49966,7 @@
         <v>-1</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -50020,7 +50020,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -50072,7 +50072,7 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -50126,7 +50126,7 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -50149,7 +50149,7 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -50203,7 +50203,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -50226,7 +50226,7 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -50280,7 +50280,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -50303,7 +50303,7 @@
         <v>8</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -50357,7 +50357,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -50380,7 +50380,7 @@
         <v>8</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -50434,7 +50434,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -50534,7 +50534,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -50588,7 +50588,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -50611,7 +50611,7 @@
         <v>8</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -50665,7 +50665,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -50688,7 +50688,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>8</v>
@@ -50742,7 +50742,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -50765,7 +50765,7 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -50819,7 +50819,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -50859,7 +50859,7 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -50936,7 +50936,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -50990,7 +50990,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -51013,7 +51013,7 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -51067,7 +51067,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -51090,7 +51090,7 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -51144,7 +51144,7 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -51167,7 +51167,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>8</v>
@@ -51221,7 +51221,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -51244,7 +51244,7 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>8</v>
@@ -51298,7 +51298,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -51321,7 +51321,7 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>8</v>
@@ -51375,7 +51375,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -51439,7 +51439,7 @@
         <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -51493,7 +51493,7 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -51670,7 +51670,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -51724,7 +51724,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -51747,7 +51747,7 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -51801,7 +51801,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -51853,7 +51853,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E34">
         <v>9</v>
@@ -51907,7 +51907,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -51930,7 +51930,7 @@
         <v>9</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -51984,7 +51984,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -52007,7 +52007,7 @@
         <v>8</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E36">
         <v>7</v>
@@ -52061,7 +52061,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -52084,7 +52084,7 @@
         <v>8</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E37">
         <v>9</v>
@@ -52138,7 +52138,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -52238,7 +52238,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E39">
         <v>7</v>
@@ -52292,7 +52292,7 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>7</v>
@@ -52315,7 +52315,7 @@
         <v>9</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E40">
         <v>9</v>
@@ -52369,7 +52369,7 @@
         <v>9</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -52392,7 +52392,7 @@
         <v>-1</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E41">
         <v>6</v>
@@ -52446,7 +52446,7 @@
         <v>-1</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W41">
         <v>6</v>
@@ -52640,7 +52640,7 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -52694,7 +52694,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -52871,7 +52871,7 @@
         <v>9</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -52925,7 +52925,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -52948,7 +52948,7 @@
         <v>9</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -53002,7 +53002,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -53025,7 +53025,7 @@
         <v>9</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -53079,7 +53079,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -53102,7 +53102,7 @@
         <v>9</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -53156,7 +53156,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -53179,7 +53179,7 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -53233,7 +53233,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -53256,7 +53256,7 @@
         <v>9</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>9</v>
@@ -53310,7 +53310,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -53333,7 +53333,7 @@
         <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>7</v>
@@ -53387,7 +53387,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -53410,7 +53410,7 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -53464,7 +53464,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -53487,7 +53487,7 @@
         <v>9</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -53541,7 +53541,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -53564,7 +53564,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>9</v>
@@ -53618,7 +53618,7 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -53641,7 +53641,7 @@
         <v>6</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -53695,7 +53695,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>-1</v>
@@ -53718,7 +53718,7 @@
         <v>9</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G18">
         <v>6</v>
@@ -53772,7 +53772,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -53795,7 +53795,7 @@
         <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>9</v>
@@ -53849,7 +53849,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -53872,7 +53872,7 @@
         <v>9</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -53926,7 +53926,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -53949,7 +53949,7 @@
         <v>9</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>6</v>
@@ -54003,7 +54003,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -54026,7 +54026,7 @@
         <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>6</v>
@@ -54080,7 +54080,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -54103,7 +54103,7 @@
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -54157,7 +54157,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -54209,7 +54209,7 @@
         <v>9</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G25">
         <v>8</v>
@@ -54263,7 +54263,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -54286,7 +54286,7 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>6</v>
@@ -54340,7 +54340,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -54363,7 +54363,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>9</v>
@@ -54417,7 +54417,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -54440,7 +54440,7 @@
         <v>9</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G28">
         <v>8</v>
@@ -54494,7 +54494,7 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -54517,7 +54517,7 @@
         <v>7</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>9</v>
@@ -54571,7 +54571,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -54671,7 +54671,7 @@
         <v>9</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G31">
         <v>8</v>
@@ -54725,7 +54725,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -54748,7 +54748,7 @@
         <v>8</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -54802,7 +54802,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -54825,7 +54825,7 @@
         <v>9</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G33">
         <v>6</v>
@@ -54879,7 +54879,7 @@
         <v>9</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -54902,7 +54902,7 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G34">
         <v>9</v>
@@ -54956,7 +54956,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -54979,7 +54979,7 @@
         <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G35">
         <v>6</v>
@@ -55033,7 +55033,7 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -55056,7 +55056,7 @@
         <v>8</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -55110,7 +55110,7 @@
         <v>8</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -55133,7 +55133,7 @@
         <v>8</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G37">
         <v>8</v>
@@ -55187,7 +55187,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -55210,7 +55210,7 @@
         <v>5</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>-1</v>
@@ -55264,7 +55264,7 @@
         <v>5</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>-1</v>
@@ -55287,7 +55287,7 @@
         <v>9</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G39">
         <v>9</v>
@@ -55341,7 +55341,7 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>9</v>
@@ -55364,7 +55364,7 @@
         <v>9</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G40">
         <v>8</v>
@@ -55418,7 +55418,7 @@
         <v>9</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -55518,7 +55518,7 @@
         <v>9</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G42">
         <v>9</v>
@@ -55572,7 +55572,7 @@
         <v>9</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y42">
         <v>9</v>
@@ -57847,7 +57847,7 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>9</v>
@@ -57901,7 +57901,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -57924,7 +57924,7 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -57978,7 +57978,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -58001,7 +58001,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -58055,7 +58055,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -58078,7 +58078,7 @@
         <v>-1</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -58132,7 +58132,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -58155,7 +58155,7 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -58209,7 +58209,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -58232,7 +58232,7 @@
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -58286,7 +58286,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -58309,7 +58309,7 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -58363,7 +58363,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -58386,7 +58386,7 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -58440,7 +58440,7 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -58463,7 +58463,7 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -58517,7 +58517,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -58540,7 +58540,7 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -58594,7 +58594,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -58617,7 +58617,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>9</v>
@@ -58671,7 +58671,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -58694,7 +58694,7 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>9</v>
@@ -58748,7 +58748,7 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -58771,7 +58771,7 @@
         <v>8</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -58825,7 +58825,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -58848,7 +58848,7 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -58902,7 +58902,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -58925,7 +58925,7 @@
         <v>10</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -58979,7 +58979,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -59002,7 +59002,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>8</v>
@@ -59056,7 +59056,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -59079,7 +59079,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -59133,7 +59133,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -59156,7 +59156,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -59210,7 +59210,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -59310,7 +59310,7 @@
         <v>9</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F23">
         <v>9</v>
@@ -59364,7 +59364,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -59387,7 +59387,7 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>10</v>
@@ -59441,7 +59441,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -59464,7 +59464,7 @@
         <v>9</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -59518,7 +59518,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -59541,7 +59541,7 @@
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -59595,7 +59595,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -59618,7 +59618,7 @@
         <v>7</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F27">
         <v>9</v>
@@ -59672,7 +59672,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -59695,7 +59695,7 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F28">
         <v>8</v>
@@ -59749,7 +59749,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -59772,7 +59772,7 @@
         <v>9</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F29">
         <v>10</v>
@@ -59826,7 +59826,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -59849,7 +59849,7 @@
         <v>7</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F30">
         <v>8</v>
@@ -59903,7 +59903,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -59926,7 +59926,7 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
         <v>8</v>
@@ -59980,7 +59980,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -60080,7 +60080,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -60134,7 +60134,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -60157,7 +60157,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -60211,7 +60211,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -60234,7 +60234,7 @@
         <v>-1</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F35">
         <v>5</v>
@@ -60288,7 +60288,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -61760,7 +61760,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -61823,7 +61823,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -61849,7 +61849,7 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -61912,7 +61912,7 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -61938,7 +61938,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -62001,7 +62001,7 @@
         <v>10</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -62027,7 +62027,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>10</v>
@@ -62090,7 +62090,7 @@
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -62101,7 +62101,7 @@
         <v>1020</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -62164,7 +62164,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -62279,7 +62279,7 @@
         <v>1022</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -62342,7 +62342,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -62472,7 +62472,7 @@
         <v>9</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H12">
         <v>7</v>
@@ -62535,7 +62535,7 @@
         <v>9</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>7</v>
@@ -62561,7 +62561,7 @@
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>8</v>
@@ -62624,7 +62624,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -62650,7 +62650,7 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>7</v>
@@ -62713,7 +62713,7 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>7</v>
@@ -62828,7 +62828,7 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -62891,7 +62891,7 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -62917,7 +62917,7 @@
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>7</v>
@@ -62980,7 +62980,7 @@
         <v>-1</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>7</v>
@@ -63095,7 +63095,7 @@
         <v>6</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H19">
         <v>8</v>
@@ -63158,7 +63158,7 @@
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -63184,7 +63184,7 @@
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -63247,7 +63247,7 @@
         <v>-1</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -63273,7 +63273,7 @@
         <v>-1</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -63336,7 +63336,7 @@
         <v>-1</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -63362,7 +63362,7 @@
         <v>9</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H22">
         <v>8</v>
@@ -63425,7 +63425,7 @@
         <v>9</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -63451,7 +63451,7 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H23">
         <v>10</v>
@@ -63514,7 +63514,7 @@
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -63540,7 +63540,7 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>7</v>
@@ -63603,7 +63603,7 @@
         <v>10</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -63614,7 +63614,7 @@
         <v>1037</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -63677,7 +63677,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -63703,7 +63703,7 @@
         <v>1038</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -63766,7 +63766,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -63807,7 +63807,7 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H27">
         <v>8</v>
@@ -63870,7 +63870,7 @@
         <v>6</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -63985,7 +63985,7 @@
         <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -64048,7 +64048,7 @@
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC29">
         <v>5</v>
@@ -71244,7 +71244,7 @@
         <v>6</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -71298,7 +71298,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>-1</v>
@@ -71321,7 +71321,7 @@
         <v>7</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -71375,7 +71375,7 @@
         <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -71398,7 +71398,7 @@
         <v>7</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -71452,7 +71452,7 @@
         <v>7</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -71475,7 +71475,7 @@
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -71529,7 +71529,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -71552,7 +71552,7 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -71606,7 +71606,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -71783,7 +71783,7 @@
         <v>6</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -71837,7 +71837,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>-1</v>
@@ -71860,7 +71860,7 @@
         <v>-1</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -71914,7 +71914,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -71937,7 +71937,7 @@
         <v>-1</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -71991,7 +71991,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>-1</v>
@@ -72091,7 +72091,7 @@
         <v>-1</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -72145,7 +72145,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>-1</v>
@@ -72168,7 +72168,7 @@
         <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -72222,7 +72222,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>-1</v>
@@ -72322,7 +72322,7 @@
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -72376,7 +72376,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>-1</v>
@@ -72476,7 +72476,7 @@
         <v>-1</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -72530,7 +72530,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>-1</v>
@@ -72553,7 +72553,7 @@
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -72607,7 +72607,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>-1</v>
@@ -72630,7 +72630,7 @@
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -72684,7 +72684,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>-1</v>
@@ -72707,7 +72707,7 @@
         <v>-1</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>-1</v>
@@ -72761,7 +72761,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>-1</v>
@@ -72784,7 +72784,7 @@
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
         <v>-1</v>
@@ -72838,7 +72838,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>-1</v>
@@ -72902,7 +72902,7 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>-1</v>
@@ -72956,7 +72956,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>-1</v>
@@ -72979,7 +72979,7 @@
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F29">
         <v>-1</v>
@@ -73033,7 +73033,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>-1</v>
@@ -73056,7 +73056,7 @@
         <v>7</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>-1</v>
@@ -73110,7 +73110,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>-1</v>
@@ -73133,7 +73133,7 @@
         <v>-1</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
         <v>-1</v>
@@ -73187,7 +73187,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>-1</v>
@@ -73210,7 +73210,7 @@
         <v>-1</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>-1</v>
@@ -73264,7 +73264,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>-1</v>
@@ -73287,7 +73287,7 @@
         <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -73341,7 +73341,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -73364,7 +73364,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F34">
         <v>8</v>
@@ -73418,7 +73418,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -73441,7 +73441,7 @@
         <v>-1</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F35">
         <v>-1</v>
@@ -73495,7 +73495,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>-1</v>
@@ -73547,7 +73547,7 @@
         <v>-1</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F37">
         <v>-1</v>
@@ -73601,7 +73601,7 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>-1</v>
@@ -73624,7 +73624,7 @@
         <v>9</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F38">
         <v>8</v>
@@ -73678,7 +73678,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -74031,7 +74031,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -74085,7 +74085,7 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -74339,7 +74339,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -74393,7 +74393,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -74493,7 +74493,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -74547,7 +74547,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -74878,7 +74878,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -74932,7 +74932,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -79080,7 +79080,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -79134,7 +79134,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -79311,7 +79311,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>9</v>
@@ -79365,7 +79365,7 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -79388,7 +79388,7 @@
         <v>8</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>9</v>
@@ -79442,7 +79442,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -79465,7 +79465,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -79519,7 +79519,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -79773,7 +79773,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -79827,7 +79827,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -79850,7 +79850,7 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -79904,7 +79904,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -79927,7 +79927,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -79981,7 +79981,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -80004,7 +80004,7 @@
         <v>8</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -80058,7 +80058,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -80235,7 +80235,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>8</v>
@@ -80289,7 +80289,7 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -80697,7 +80697,7 @@
         <v>8</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>7</v>
@@ -80751,7 +80751,7 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -80928,7 +80928,7 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -80982,7 +80982,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -81005,7 +81005,7 @@
         <v>9</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -81059,7 +81059,7 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -81159,7 +81159,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -81213,7 +81213,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -81236,7 +81236,7 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -81290,7 +81290,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -81390,7 +81390,7 @@
         <v>10</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>8</v>
@@ -81444,7 +81444,7 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -81467,7 +81467,7 @@
         <v>9</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -81521,7 +81521,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -81544,7 +81544,7 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -81598,7 +81598,7 @@
         <v>5</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -81698,7 +81698,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>7</v>
@@ -81752,7 +81752,7 @@
         <v>7</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -81775,7 +81775,7 @@
         <v>10</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E39">
         <v>8</v>
@@ -81829,7 +81829,7 @@
         <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W39">
         <v>8</v>
@@ -81929,7 +81929,7 @@
         <v>10</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E41">
         <v>8</v>
@@ -81983,7 +81983,7 @@
         <v>10</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -82006,7 +82006,7 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -82060,7 +82060,7 @@
         <v>10</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W42">
         <v>6</v>
@@ -82083,7 +82083,7 @@
         <v>10</v>
       </c>
       <c r="D43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E43">
         <v>9</v>
@@ -82137,7 +82137,7 @@
         <v>10</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W43">
         <v>9</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -6750,7 +6750,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -6827,7 +6827,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -6863,7 +6863,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -6904,7 +6904,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -6981,7 +6981,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -7058,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -7135,7 +7135,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -7212,7 +7212,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -7248,7 +7248,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -7289,7 +7289,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -7366,7 +7366,7 @@
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -7443,7 +7443,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -7520,7 +7520,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -7597,7 +7597,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -7633,7 +7633,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -7674,7 +7674,7 @@
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -7751,7 +7751,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -7828,7 +7828,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -7864,7 +7864,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -7905,7 +7905,7 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -7941,7 +7941,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -7982,7 +7982,7 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -8059,7 +8059,7 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -8095,7 +8095,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -8136,7 +8136,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -8172,7 +8172,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -8213,7 +8213,7 @@
         <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -8249,7 +8249,7 @@
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -8290,7 +8290,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -8326,7 +8326,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -8367,7 +8367,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -8444,7 +8444,7 @@
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -8521,7 +8521,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -8557,7 +8557,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -8598,7 +8598,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -8675,7 +8675,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -8752,7 +8752,7 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -8829,7 +8829,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -8906,7 +8906,7 @@
         <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -8983,7 +8983,7 @@
         <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -9060,7 +9060,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -9096,7 +9096,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -9137,7 +9137,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -9214,7 +9214,7 @@
         <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -9250,7 +9250,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -9291,7 +9291,7 @@
         <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -9368,7 +9368,7 @@
         <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -9445,7 +9445,7 @@
         <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -9481,7 +9481,7 @@
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -9522,7 +9522,7 @@
         <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -9558,7 +9558,7 @@
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -9599,7 +9599,7 @@
         <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -9635,7 +9635,7 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -9676,7 +9676,7 @@
         <v>8</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -9712,7 +9712,7 @@
         <v>8</v>
       </c>
       <c r="Y42">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -23614,7 +23614,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -23650,7 +23650,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -23768,7 +23768,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -23804,7 +23804,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -24920,7 +24920,7 @@
         <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -24956,7 +24956,7 @@
         <v>9</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -25000,7 +25000,7 @@
         <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -25036,7 +25036,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -25308,7 +25308,7 @@
         <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -25385,7 +25385,7 @@
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -25421,7 +25421,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -26232,7 +26232,7 @@
         <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -26268,7 +26268,7 @@
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -30629,7 +30629,7 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>7</v>
@@ -30665,7 +30665,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -30783,7 +30783,7 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -30819,7 +30819,7 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -31014,7 +31014,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -31050,7 +31050,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -40034,7 +40034,7 @@
         <v>4</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -40111,7 +40111,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -40147,7 +40147,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -40188,7 +40188,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -40224,7 +40224,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>-1</v>
@@ -40265,7 +40265,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -40342,7 +40342,7 @@
         <v>4</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -40419,7 +40419,7 @@
         <v>4</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -40455,7 +40455,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -40496,7 +40496,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -40532,7 +40532,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -40573,7 +40573,7 @@
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -40609,7 +40609,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -40650,7 +40650,7 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -40686,7 +40686,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -40727,7 +40727,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -40763,7 +40763,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -40804,7 +40804,7 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -40881,7 +40881,7 @@
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -40958,7 +40958,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -41035,7 +41035,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -41071,7 +41071,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -41112,7 +41112,7 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -41148,7 +41148,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -41189,7 +41189,7 @@
         <v>4</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -41225,7 +41225,7 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -41266,7 +41266,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -41343,7 +41343,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -41420,7 +41420,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -41456,7 +41456,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -41497,7 +41497,7 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -41533,7 +41533,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -41574,7 +41574,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -41610,7 +41610,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -41651,7 +41651,7 @@
         <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -41687,7 +41687,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -41728,7 +41728,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -41805,7 +41805,7 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -41841,7 +41841,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -41882,7 +41882,7 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -41959,7 +41959,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -41995,7 +41995,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -42036,7 +42036,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>9</v>
@@ -42072,7 +42072,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -42113,7 +42113,7 @@
         <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -42190,7 +42190,7 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -42226,7 +42226,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -42267,7 +42267,7 @@
         <v>4</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -42344,7 +42344,7 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -42421,7 +42421,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -42498,7 +42498,7 @@
         <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>9</v>
@@ -42575,7 +42575,7 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
         <v>9</v>
@@ -42611,7 +42611,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -42652,7 +42652,7 @@
         <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>10</v>
@@ -42688,7 +42688,7 @@
         <v>6</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -42729,7 +42729,7 @@
         <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>10</v>
@@ -42765,7 +42765,7 @@
         <v>9</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -42806,7 +42806,7 @@
         <v>4</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -42883,7 +42883,7 @@
         <v>8</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>9</v>
@@ -42960,7 +42960,7 @@
         <v>8</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
         <v>9</v>
@@ -42996,7 +42996,7 @@
         <v>7</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>9</v>
@@ -43037,7 +43037,7 @@
         <v>9</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L43">
         <v>9</v>
@@ -43073,7 +43073,7 @@
         <v>9</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X43">
         <v>9</v>
@@ -43114,7 +43114,7 @@
         <v>8</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L44">
         <v>10</v>
@@ -43150,7 +43150,7 @@
         <v>9</v>
       </c>
       <c r="W44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>10</v>
@@ -43404,7 +43404,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>8</v>
@@ -43440,7 +43440,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -43481,7 +43481,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -43517,7 +43517,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -44020,7 +44020,7 @@
         <v>4</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>7</v>
@@ -44328,7 +44328,7 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -44364,7 +44364,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -44636,7 +44636,7 @@
         <v>4</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -44790,7 +44790,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -45560,7 +45560,7 @@
         <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -45868,7 +45868,7 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -70951,7 +70951,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -70987,7 +70987,7 @@
         <v>-1</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -71721,7 +71721,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -71757,7 +71757,7 @@
         <v>-1</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -71798,7 +71798,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -71834,7 +71834,7 @@
         <v>-1</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -72106,7 +72106,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -72142,7 +72142,7 @@
         <v>-1</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -72337,7 +72337,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -72491,7 +72491,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -72527,7 +72527,7 @@
         <v>-1</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -73148,7 +73148,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -73184,7 +73184,7 @@
         <v>-1</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -73254,7 +73254,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -73290,7 +73290,7 @@
         <v>-1</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -73408,7 +73408,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -73461,7 +73461,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -73473,7 +73473,7 @@
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -73555,7 +73555,7 @@
         <v>-1</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -85684,7 +85684,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -85761,7 +85761,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -85838,7 +85838,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -85874,7 +85874,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -85915,7 +85915,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -85951,7 +85951,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -85992,7 +85992,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -86028,7 +86028,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -86069,7 +86069,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -86146,7 +86146,7 @@
         <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -86182,7 +86182,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -86223,7 +86223,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -86300,7 +86300,7 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -86336,7 +86336,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -86377,7 +86377,7 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -86454,7 +86454,7 @@
         <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -86531,7 +86531,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -86567,7 +86567,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -86608,7 +86608,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -86685,7 +86685,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -86762,7 +86762,7 @@
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -86798,7 +86798,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -86839,7 +86839,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -86916,7 +86916,7 @@
         <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -86952,7 +86952,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -86993,7 +86993,7 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -87029,7 +87029,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -87070,7 +87070,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -87147,7 +87147,7 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -87183,7 +87183,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -87224,7 +87224,7 @@
         <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -87260,7 +87260,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -87301,7 +87301,7 @@
         <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -87378,7 +87378,7 @@
         <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -87455,7 +87455,7 @@
         <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -87532,7 +87532,7 @@
         <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -87568,7 +87568,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -87609,7 +87609,7 @@
         <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -87686,7 +87686,7 @@
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -87763,7 +87763,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -87840,7 +87840,7 @@
         <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -87876,7 +87876,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -87917,7 +87917,7 @@
         <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -87953,7 +87953,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -87994,7 +87994,7 @@
         <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -88071,7 +88071,7 @@
         <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -88107,7 +88107,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -88284,7 +88284,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -88361,7 +88361,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -88438,7 +88438,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -88515,7 +88515,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -88592,7 +88592,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -88669,7 +88669,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -88705,7 +88705,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -88746,7 +88746,7 @@
         <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -88823,7 +88823,7 @@
         <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -88859,7 +88859,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -88900,7 +88900,7 @@
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -88977,7 +88977,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -89054,7 +89054,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -89131,7 +89131,7 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -89167,7 +89167,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -89208,7 +89208,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -89285,7 +89285,7 @@
         <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -89362,7 +89362,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -89439,7 +89439,7 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -89475,7 +89475,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -89516,7 +89516,7 @@
         <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -89593,7 +89593,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -89670,7 +89670,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -89747,7 +89747,7 @@
         <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -89824,7 +89824,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -89860,7 +89860,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -89901,7 +89901,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -89978,7 +89978,7 @@
         <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -90014,7 +90014,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -90055,7 +90055,7 @@
         <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -90091,7 +90091,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -90132,7 +90132,7 @@
         <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -90168,7 +90168,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -90209,7 +90209,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -90245,7 +90245,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -90286,7 +90286,7 @@
         <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -90322,7 +90322,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -90363,7 +90363,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -90440,7 +90440,7 @@
         <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -90476,7 +90476,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -90517,7 +90517,7 @@
         <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -90594,7 +90594,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -90671,7 +90671,7 @@
         <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -90748,7 +90748,7 @@
         <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -90825,7 +90825,7 @@
         <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -90902,7 +90902,7 @@
         <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -90979,7 +90979,7 @@
         <v>7</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -91015,7 +91015,7 @@
         <v>6</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -91056,7 +91056,7 @@
         <v>7</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -91133,7 +91133,7 @@
         <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -91169,7 +91169,7 @@
         <v>8</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -91210,7 +91210,7 @@
         <v>9</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -91287,7 +91287,7 @@
         <v>7</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -91323,7 +91323,7 @@
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -2154,7 +2154,7 @@
     <t>TZOMPOLE COLOHUA JOSE LEONARDO</t>
   </si>
   <si>
-    <t>VAZQUEZ COLOHUA NAHUM HIRAM</t>
+    <t>VASQUEZ COLOHUA NAHUM HIRAM</t>
   </si>
   <si>
     <t>VERA GONZALEZ ISRAEL</t>
@@ -3996,7 +3996,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -4073,7 +4073,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -4150,7 +4150,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -4227,7 +4227,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -4263,7 +4263,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -4304,7 +4304,7 @@
         <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -4381,7 +4381,7 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -4458,7 +4458,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -4494,7 +4494,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -4535,7 +4535,7 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -4612,7 +4612,7 @@
         <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -4648,7 +4648,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -4689,7 +4689,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -4766,7 +4766,7 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -4843,7 +4843,7 @@
         <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -4920,7 +4920,7 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -5074,7 +5074,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -5151,7 +5151,7 @@
         <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -5187,7 +5187,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -5228,7 +5228,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -5264,7 +5264,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -5305,7 +5305,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -5382,7 +5382,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -5459,7 +5459,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -5536,7 +5536,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -5572,7 +5572,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -5613,7 +5613,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -5649,7 +5649,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -5690,7 +5690,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -5726,7 +5726,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -5767,7 +5767,7 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -5844,7 +5844,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -5880,7 +5880,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -5921,7 +5921,7 @@
         <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -5957,7 +5957,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -5998,7 +5998,7 @@
         <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -6034,7 +6034,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -6075,7 +6075,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -6152,7 +6152,7 @@
         <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -6188,7 +6188,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -6229,7 +6229,7 @@
         <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -6265,7 +6265,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -6306,7 +6306,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -6383,7 +6383,7 @@
         <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -6460,7 +6460,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -6496,7 +6496,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -6537,7 +6537,7 @@
         <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -6573,7 +6573,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9889,7 +9889,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -9966,7 +9966,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -10043,7 +10043,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -10120,7 +10120,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -10156,7 +10156,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -10197,7 +10197,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -10274,7 +10274,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -10351,7 +10351,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -10428,7 +10428,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -10505,7 +10505,7 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -10582,7 +10582,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -10659,7 +10659,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -10736,7 +10736,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -10813,7 +10813,7 @@
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -10890,7 +10890,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -10926,7 +10926,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -10967,7 +10967,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -11044,7 +11044,7 @@
         <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -11121,7 +11121,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -11198,7 +11198,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -11234,7 +11234,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -11275,7 +11275,7 @@
         <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -11311,7 +11311,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -11352,7 +11352,7 @@
         <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -11388,7 +11388,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -11429,7 +11429,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -11506,7 +11506,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -11583,7 +11583,7 @@
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -11660,7 +11660,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -11737,7 +11737,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -11814,7 +11814,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -11891,7 +11891,7 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -11968,7 +11968,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -12045,7 +12045,7 @@
         <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -12122,7 +12122,7 @@
         <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -12199,7 +12199,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -12235,7 +12235,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -12400,7 +12400,7 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -12477,7 +12477,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -12513,7 +12513,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -12631,7 +12631,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -12667,7 +12667,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -12708,7 +12708,7 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>7</v>
@@ -12744,7 +12744,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -12785,7 +12785,7 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -12862,7 +12862,7 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -12939,7 +12939,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>7</v>
@@ -13016,7 +13016,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>7</v>
@@ -13093,7 +13093,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>7</v>
@@ -13129,7 +13129,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -13170,7 +13170,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -13247,7 +13247,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -13324,7 +13324,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -13360,7 +13360,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -13401,7 +13401,7 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -13437,7 +13437,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -13478,7 +13478,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -13555,7 +13555,7 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -13591,7 +13591,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -13632,7 +13632,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -13709,7 +13709,7 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -13786,7 +13786,7 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -13822,7 +13822,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -13863,7 +13863,7 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>8</v>
@@ -13940,7 +13940,7 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>8</v>
@@ -13976,7 +13976,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -14017,7 +14017,7 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -14094,7 +14094,7 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>7</v>
@@ -14130,7 +14130,7 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -14200,7 +14200,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>5</v>
@@ -14212,7 +14212,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -14236,7 +14236,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -14248,7 +14248,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -14277,7 +14277,7 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -14354,7 +14354,7 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>5</v>
@@ -14431,7 +14431,7 @@
         <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>8</v>
@@ -14467,7 +14467,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -14508,7 +14508,7 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>8</v>
@@ -14544,7 +14544,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -14585,7 +14585,7 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -14621,7 +14621,7 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -14662,7 +14662,7 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -14739,7 +14739,7 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>8</v>
@@ -14775,7 +14775,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -14816,7 +14816,7 @@
         <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>7</v>
@@ -14893,7 +14893,7 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
         <v>7</v>
@@ -14929,7 +14929,7 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -14970,7 +14970,7 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
         <v>8</v>
@@ -15006,7 +15006,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V38">
         <v>9</v>
@@ -15047,7 +15047,7 @@
         <v>8</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -15124,7 +15124,7 @@
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
         <v>7</v>
@@ -15160,7 +15160,7 @@
         <v>10</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>8</v>
@@ -15201,7 +15201,7 @@
         <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>8</v>
@@ -15237,7 +15237,7 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -15278,7 +15278,7 @@
         <v>6</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J42">
         <v>6</v>
@@ -15355,7 +15355,7 @@
         <v>7</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J43">
         <v>6</v>
@@ -15391,7 +15391,7 @@
         <v>8</v>
       </c>
       <c r="U43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V43">
         <v>7</v>
@@ -15432,7 +15432,7 @@
         <v>10</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J44">
         <v>8</v>
@@ -15509,7 +15509,7 @@
         <v>10</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J45">
         <v>7</v>
@@ -15586,7 +15586,7 @@
         <v>9</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J46">
         <v>5</v>
@@ -15663,7 +15663,7 @@
         <v>9</v>
       </c>
       <c r="I47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J47">
         <v>7</v>
@@ -15740,7 +15740,7 @@
         <v>9</v>
       </c>
       <c r="I48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J48">
         <v>7</v>
@@ -19711,7 +19711,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -19747,7 +19747,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -32613,7 +32613,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -33152,7 +33152,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -33188,7 +33188,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -33229,7 +33229,7 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>9</v>
@@ -33768,7 +33768,7 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>5</v>
@@ -33804,7 +33804,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>5</v>
@@ -33845,7 +33845,7 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -33881,7 +33881,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>6</v>
@@ -40336,7 +40336,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -40372,7 +40372,7 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -41722,7 +41722,7 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -41758,7 +41758,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -41953,7 +41953,7 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -41989,7 +41989,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -43333,7 +43333,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -43410,7 +43410,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -45862,7 +45862,7 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>7</v>
@@ -45898,7 +45898,7 @@
         <v>-1</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -46691,7 +46691,7 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -46727,7 +46727,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -47461,7 +47461,7 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -47497,7 +47497,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -47615,7 +47615,7 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -47651,7 +47651,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -48539,7 +48539,7 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>7</v>
@@ -48575,7 +48575,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -57542,7 +57542,7 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -57554,7 +57554,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -57578,7 +57578,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -57619,7 +57619,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -57631,7 +57631,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -57667,7 +57667,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -57696,7 +57696,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -57708,7 +57708,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -57744,7 +57744,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -57773,7 +57773,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -57785,7 +57785,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -57809,7 +57809,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -57821,7 +57821,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -57850,7 +57850,7 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -57862,7 +57862,7 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -57886,7 +57886,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -57927,7 +57927,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -57939,7 +57939,7 @@
         <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -57963,7 +57963,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -58004,7 +58004,7 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -58016,7 +58016,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -58040,7 +58040,7 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -58081,7 +58081,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -58093,7 +58093,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -58129,7 +58129,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -58158,7 +58158,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -58170,7 +58170,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -58194,7 +58194,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -58235,7 +58235,7 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -58247,7 +58247,7 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -58283,7 +58283,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -58312,7 +58312,7 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>9</v>
@@ -58324,7 +58324,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -58348,7 +58348,7 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -58389,7 +58389,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>10</v>
@@ -58401,7 +58401,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -58437,7 +58437,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -58466,7 +58466,7 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -58478,7 +58478,7 @@
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -58502,7 +58502,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -58543,7 +58543,7 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>6</v>
@@ -58555,7 +58555,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -58579,7 +58579,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -58620,7 +58620,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -58632,7 +58632,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -58656,7 +58656,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -58697,7 +58697,7 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>7</v>
@@ -58709,7 +58709,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -58774,7 +58774,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -58786,7 +58786,7 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -58822,7 +58822,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -58851,7 +58851,7 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>10</v>
@@ -58863,7 +58863,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -58928,7 +58928,7 @@
         <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -58940,7 +58940,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -59005,7 +59005,7 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>9</v>
@@ -59017,7 +59017,7 @@
         <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -59041,7 +59041,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -59053,7 +59053,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -59082,7 +59082,7 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>10</v>
@@ -59094,7 +59094,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -59130,7 +59130,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -59159,7 +59159,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -59171,7 +59171,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -59236,7 +59236,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -59248,7 +59248,7 @@
         <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -59272,7 +59272,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -59313,7 +59313,7 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
         <v>9</v>
@@ -59325,7 +59325,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -59390,7 +59390,7 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -59402,7 +59402,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -59426,7 +59426,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -59438,7 +59438,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -59467,7 +59467,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -59479,7 +59479,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -59503,7 +59503,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -59515,7 +59515,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -59544,7 +59544,7 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>8</v>
@@ -59556,7 +59556,7 @@
         <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -59621,7 +59621,7 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>10</v>
@@ -59633,7 +59633,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -59669,7 +59669,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -59698,7 +59698,7 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -59710,7 +59710,7 @@
         <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -59775,7 +59775,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>10</v>
@@ -59787,7 +59787,7 @@
         <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -59852,7 +59852,7 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>7</v>
@@ -59864,7 +59864,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -59888,7 +59888,7 @@
         <v>9</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -59929,7 +59929,7 @@
         <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>6</v>
@@ -59941,7 +59941,7 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -59977,7 +59977,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -60142,7 +60142,7 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -60219,7 +60219,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -60296,7 +60296,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -60332,7 +60332,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -60373,7 +60373,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -60450,7 +60450,7 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -60486,7 +60486,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -60527,7 +60527,7 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -60604,7 +60604,7 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -60640,7 +60640,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -60681,7 +60681,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -60717,7 +60717,7 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -60758,7 +60758,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -60794,7 +60794,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -60835,7 +60835,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -60871,7 +60871,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -60912,7 +60912,7 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -60989,7 +60989,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -61025,7 +61025,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -61066,7 +61066,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>9</v>
@@ -61102,7 +61102,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -61143,7 +61143,7 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -61220,7 +61220,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -84923,7 +84923,7 @@
         <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
         <v>7</v>
@@ -91494,7 +91494,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -91530,7 +91530,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -91571,7 +91571,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -91648,7 +91648,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -91725,7 +91725,7 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -91802,7 +91802,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -91879,7 +91879,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -91956,7 +91956,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -92033,7 +92033,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -92110,7 +92110,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -92187,7 +92187,7 @@
         <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -92264,7 +92264,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -92300,7 +92300,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -92341,7 +92341,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -92418,7 +92418,7 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -92454,7 +92454,7 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -92495,7 +92495,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -92572,7 +92572,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -92608,7 +92608,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -92649,7 +92649,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -92726,7 +92726,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -92803,7 +92803,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -92880,7 +92880,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -92916,7 +92916,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -92957,7 +92957,7 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -92993,7 +92993,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -93034,7 +93034,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -93111,7 +93111,7 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>8</v>
@@ -93188,7 +93188,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -93224,7 +93224,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -93265,7 +93265,7 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -93342,7 +93342,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -93419,7 +93419,7 @@
         <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -93496,7 +93496,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -4686,7 +4686,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -5225,7 +5225,7 @@
         <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -5379,7 +5379,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -5415,7 +5415,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -6457,7 +6457,7 @@
         <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>9</v>
@@ -23611,7 +23611,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -24612,10 +24612,10 @@
         <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -31775,7 +31775,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -31852,7 +31852,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -31929,7 +31929,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -32083,7 +32083,7 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>7</v>
@@ -32160,7 +32160,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -32237,7 +32237,7 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -32314,7 +32314,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -32391,7 +32391,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>8</v>
@@ -32468,7 +32468,7 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -32545,7 +32545,7 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -32622,7 +32622,7 @@
         <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -32658,7 +32658,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -32699,7 +32699,7 @@
         <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -32776,7 +32776,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -32853,7 +32853,7 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -32930,7 +32930,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -32966,7 +32966,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -33007,7 +33007,7 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -33084,7 +33084,7 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -33161,7 +33161,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -33238,7 +33238,7 @@
         <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -33315,7 +33315,7 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -33392,7 +33392,7 @@
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -33469,7 +33469,7 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -33546,7 +33546,7 @@
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -33623,7 +33623,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -33700,7 +33700,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>7</v>
@@ -33777,7 +33777,7 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>5</v>
@@ -33813,7 +33813,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -33854,7 +33854,7 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -33890,7 +33890,7 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>-1</v>
@@ -34085,7 +34085,7 @@
         <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -34121,7 +34121,7 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -34162,7 +34162,7 @@
         <v>5</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -34198,7 +34198,7 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>-1</v>
@@ -34239,7 +34239,7 @@
         <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -34275,7 +34275,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>-1</v>
@@ -34310,13 +34310,13 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -34346,7 +34346,7 @@
         <v>-1</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -34393,7 +34393,7 @@
         <v>5</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -34429,7 +34429,7 @@
         <v>6</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>-1</v>
@@ -34470,7 +34470,7 @@
         <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -34547,7 +34547,7 @@
         <v>7</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
         <v>9</v>
@@ -34615,7 +34615,7 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
         <v>6</v>
@@ -34624,7 +34624,7 @@
         <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -34651,7 +34651,7 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V41">
         <v>5</v>
@@ -34660,7 +34660,7 @@
         <v>5</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>-1</v>
@@ -34840,7 +34840,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -34917,7 +34917,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -34994,7 +34994,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -35071,7 +35071,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -35148,7 +35148,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -35225,7 +35225,7 @@
         <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -35302,7 +35302,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -35338,7 +35338,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -35379,7 +35379,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -35456,7 +35456,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -35533,7 +35533,7 @@
         <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -35610,7 +35610,7 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -35687,7 +35687,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -35764,7 +35764,7 @@
         <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -35841,7 +35841,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -35877,7 +35877,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -35918,7 +35918,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -35995,7 +35995,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -36031,7 +36031,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -36072,7 +36072,7 @@
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -36108,7 +36108,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -36149,7 +36149,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -36185,7 +36185,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -36226,7 +36226,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -36303,7 +36303,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -36380,7 +36380,7 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -36457,7 +36457,7 @@
         <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -36534,7 +36534,7 @@
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -36611,7 +36611,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -36647,7 +36647,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -36688,7 +36688,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -36765,7 +36765,7 @@
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -36842,7 +36842,7 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -36878,7 +36878,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -36919,7 +36919,7 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -36955,7 +36955,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -36996,7 +36996,7 @@
         <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -37073,7 +37073,7 @@
         <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -37109,7 +37109,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -37271,7 +37271,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -37283,7 +37283,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -37307,7 +37307,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -37348,7 +37348,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -37425,7 +37425,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -37502,7 +37502,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -37538,7 +37538,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -37579,7 +37579,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -37615,7 +37615,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -37656,7 +37656,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -37692,7 +37692,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -37733,7 +37733,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -37769,7 +37769,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -37810,7 +37810,7 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -37887,7 +37887,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -37964,7 +37964,7 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -38118,7 +38118,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -38349,7 +38349,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -38426,7 +38426,7 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -38503,7 +38503,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -38580,7 +38580,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -38616,7 +38616,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>6</v>
@@ -38657,7 +38657,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -38693,7 +38693,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -38734,7 +38734,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -38811,7 +38811,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -38888,7 +38888,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>5</v>
@@ -38924,7 +38924,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -38965,7 +38965,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>10</v>
@@ -39042,7 +39042,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>8</v>
@@ -39078,7 +39078,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -39119,7 +39119,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>10</v>
@@ -39196,7 +39196,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -39232,7 +39232,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -39350,7 +39350,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -39427,7 +39427,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>10</v>
@@ -39504,7 +39504,7 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>10</v>
@@ -39581,7 +39581,7 @@
         <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -39658,7 +39658,7 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -39694,7 +39694,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -39735,7 +39735,7 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I36">
         <v>10</v>
@@ -39812,7 +39812,7 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -40025,7 +40025,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -40040,7 +40040,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -40102,7 +40102,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -40117,7 +40117,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -40138,7 +40138,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -40179,7 +40179,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -40194,7 +40194,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -40256,7 +40256,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -40271,7 +40271,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -40333,7 +40333,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>5</v>
@@ -40348,7 +40348,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -40369,7 +40369,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -40410,7 +40410,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -40425,7 +40425,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -40446,7 +40446,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -40487,7 +40487,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -40502,7 +40502,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -40538,7 +40538,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -40564,7 +40564,7 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -40579,7 +40579,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -40600,7 +40600,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -40641,7 +40641,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -40656,7 +40656,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -40677,7 +40677,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -40718,7 +40718,7 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -40733,7 +40733,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -40754,7 +40754,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -40810,7 +40810,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -40846,7 +40846,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -40872,7 +40872,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -40887,7 +40887,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -40949,7 +40949,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -40964,7 +40964,7 @@
         <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -40985,7 +40985,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -41026,7 +41026,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -41041,7 +41041,7 @@
         <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -41103,7 +41103,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -41118,7 +41118,7 @@
         <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -41139,7 +41139,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -41180,7 +41180,7 @@
         <v>-1</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -41257,7 +41257,7 @@
         <v>-1</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -41334,7 +41334,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -41349,7 +41349,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -41370,7 +41370,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -41411,7 +41411,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -41426,7 +41426,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -41447,7 +41447,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -41488,7 +41488,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -41503,7 +41503,7 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -41524,7 +41524,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -41539,7 +41539,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -41565,7 +41565,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -41580,7 +41580,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -41601,7 +41601,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -41642,7 +41642,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>7</v>
@@ -41657,7 +41657,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -41678,7 +41678,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -41693,7 +41693,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -41719,7 +41719,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>5</v>
@@ -41734,7 +41734,7 @@
         <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -41770,7 +41770,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -41796,7 +41796,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -41811,7 +41811,7 @@
         <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -41832,7 +41832,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -41873,7 +41873,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -41888,7 +41888,7 @@
         <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -41909,7 +41909,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>6</v>
@@ -41924,7 +41924,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -41950,7 +41950,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>5</v>
@@ -41965,7 +41965,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -42027,7 +42027,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -42042,7 +42042,7 @@
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -42104,7 +42104,7 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -42119,7 +42119,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -42140,7 +42140,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -42181,7 +42181,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -42196,7 +42196,7 @@
         <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -42258,7 +42258,7 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -42273,7 +42273,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -42335,7 +42335,7 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>10</v>
@@ -42350,7 +42350,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -42371,7 +42371,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -42386,7 +42386,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -42412,7 +42412,7 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>8</v>
@@ -42427,7 +42427,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -42463,7 +42463,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -42489,7 +42489,7 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>6</v>
@@ -42504,7 +42504,7 @@
         <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -42540,7 +42540,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -42566,7 +42566,7 @@
         <v>-1</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>6</v>
@@ -42643,7 +42643,7 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
         <v>10</v>
@@ -42658,7 +42658,7 @@
         <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -42679,7 +42679,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>9</v>
@@ -42720,7 +42720,7 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
         <v>6</v>
@@ -42735,7 +42735,7 @@
         <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -42756,7 +42756,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -42771,7 +42771,7 @@
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -42812,7 +42812,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -42874,7 +42874,7 @@
         <v>6</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -42889,7 +42889,7 @@
         <v>9</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -42951,7 +42951,7 @@
         <v>6</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>7</v>
@@ -42966,7 +42966,7 @@
         <v>9</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -43028,7 +43028,7 @@
         <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>8</v>
@@ -43043,7 +43043,7 @@
         <v>9</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -43079,7 +43079,7 @@
         <v>9</v>
       </c>
       <c r="Y43">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -43105,7 +43105,7 @@
         <v>6</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I44">
         <v>7</v>
@@ -43120,7 +43120,7 @@
         <v>10</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -43564,7 +43564,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -43600,7 +43600,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -43718,7 +43718,7 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -43754,7 +43754,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -43786,7 +43786,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>6</v>
@@ -43872,7 +43872,7 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -43949,7 +43949,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -44103,7 +44103,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -44139,7 +44139,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -44180,7 +44180,7 @@
         <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -44248,7 +44248,7 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>5</v>
@@ -44411,7 +44411,7 @@
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -44447,7 +44447,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -44488,7 +44488,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -44565,7 +44565,7 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -44601,7 +44601,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -44639,7 +44639,7 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -44675,7 +44675,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -44719,7 +44719,7 @@
         <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -44755,7 +44755,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -44796,7 +44796,7 @@
         <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -44873,7 +44873,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -44950,7 +44950,7 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -44986,7 +44986,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -45027,7 +45027,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -45104,7 +45104,7 @@
         <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -45140,7 +45140,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -45181,7 +45181,7 @@
         <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -45217,7 +45217,7 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -45258,7 +45258,7 @@
         <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -45294,7 +45294,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -45335,7 +45335,7 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -45412,7 +45412,7 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -45448,7 +45448,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -45489,7 +45489,7 @@
         <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -45525,7 +45525,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -45566,7 +45566,7 @@
         <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -45720,7 +45720,7 @@
         <v>6</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -45794,7 +45794,7 @@
         <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -45874,7 +45874,7 @@
         <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -45951,7 +45951,7 @@
         <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -45987,7 +45987,7 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -46028,7 +46028,7 @@
         <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -46064,7 +46064,7 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -46105,7 +46105,7 @@
         <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -46182,7 +46182,7 @@
         <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -46218,7 +46218,7 @@
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -46259,7 +46259,7 @@
         <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -46336,7 +46336,7 @@
         <v>7</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -46372,7 +46372,7 @@
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -46534,7 +46534,7 @@
         <v>-1</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -46611,7 +46611,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -46688,7 +46688,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -46765,7 +46765,7 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -46801,7 +46801,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -46842,7 +46842,7 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -46919,7 +46919,7 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -46955,7 +46955,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -46996,7 +46996,7 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -47032,7 +47032,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -47073,13 +47073,13 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>8</v>
@@ -47109,13 +47109,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -47150,7 +47150,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -47227,7 +47227,7 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -47239,7 +47239,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -47304,7 +47304,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -47340,7 +47340,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -47381,7 +47381,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -47458,7 +47458,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -47494,7 +47494,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -47535,7 +47535,7 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -47612,7 +47612,7 @@
         <v>-1</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -47648,7 +47648,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -47689,13 +47689,13 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -47731,7 +47731,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -47766,7 +47766,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -47843,13 +47843,13 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>8</v>
@@ -47879,13 +47879,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>6</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -47920,7 +47920,7 @@
         <v>-1</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>5</v>
@@ -47997,7 +47997,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -48033,7 +48033,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -48074,7 +48074,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -48110,7 +48110,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -48151,7 +48151,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -48187,7 +48187,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -48228,7 +48228,7 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -48264,7 +48264,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -48305,7 +48305,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -48382,7 +48382,7 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -48418,7 +48418,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -48459,7 +48459,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -48536,7 +48536,7 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>5</v>
@@ -48572,7 +48572,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -48613,7 +48613,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -48690,7 +48690,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -48726,7 +48726,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -48767,7 +48767,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>10</v>
@@ -48779,7 +48779,7 @@
         <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -48844,7 +48844,7 @@
         <v>-1</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>10</v>
@@ -48998,7 +48998,7 @@
         <v>-1</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -49075,7 +49075,7 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>6</v>
@@ -49111,7 +49111,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -49152,7 +49152,7 @@
         <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -49188,7 +49188,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>-1</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -18870,7 +18870,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -18947,7 +18947,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -18983,7 +18983,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>-1</v>
@@ -19024,7 +19024,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -19101,7 +19101,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -19178,7 +19178,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -19214,7 +19214,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -19255,7 +19255,7 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>9</v>
@@ -19332,7 +19332,7 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -19409,7 +19409,7 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -19486,7 +19486,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -19522,7 +19522,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -19563,7 +19563,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -19599,7 +19599,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -19640,7 +19640,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -19717,7 +19717,7 @@
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -19794,7 +19794,7 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -19830,7 +19830,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -19871,7 +19871,7 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -19948,7 +19948,7 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -20102,7 +20102,7 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>9</v>
@@ -20179,7 +20179,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -20256,7 +20256,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -20333,7 +20333,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -20369,7 +20369,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -20410,7 +20410,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>9</v>
@@ -20564,7 +20564,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -20641,7 +20641,7 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -20718,7 +20718,7 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -20754,7 +20754,7 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -20795,7 +20795,7 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -20872,7 +20872,7 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>9</v>
@@ -20949,7 +20949,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -21026,7 +21026,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -21103,7 +21103,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>9</v>
@@ -21180,7 +21180,7 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>9</v>
@@ -21257,7 +21257,7 @@
         <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>9</v>
@@ -21334,7 +21334,7 @@
         <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>9</v>
@@ -21411,7 +21411,7 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>9</v>
@@ -21447,7 +21447,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -21488,7 +21488,7 @@
         <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>9</v>
@@ -21704,7 +21704,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>7</v>
@@ -21740,7 +21740,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -21781,7 +21781,7 @@
         <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -21858,7 +21858,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -21935,7 +21935,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -21971,7 +21971,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -22012,7 +22012,7 @@
         <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -22089,7 +22089,7 @@
         <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -22166,7 +22166,7 @@
         <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -22243,7 +22243,7 @@
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -22279,7 +22279,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -22356,7 +22356,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -22397,7 +22397,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -22474,7 +22474,7 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -22510,7 +22510,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -22551,7 +22551,7 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -22628,7 +22628,7 @@
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -22705,7 +22705,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -22782,7 +22782,7 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -22859,7 +22859,7 @@
         <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -22936,7 +22936,7 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -23013,7 +23013,7 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>7</v>
@@ -23090,7 +23090,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -23126,7 +23126,7 @@
         <v>-1</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -23167,7 +23167,7 @@
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -23244,7 +23244,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -23280,7 +23280,7 @@
         <v>-1</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -23451,7 +23451,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -23528,7 +23528,7 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>9</v>
@@ -23605,7 +23605,7 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -23682,7 +23682,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -23759,7 +23759,7 @@
         <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>9</v>
@@ -23836,7 +23836,7 @@
         <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -23872,7 +23872,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -23913,7 +23913,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>9</v>
@@ -23990,7 +23990,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>9</v>
@@ -24026,7 +24026,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -24067,7 +24067,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>9</v>
@@ -24144,7 +24144,7 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>9</v>
@@ -24221,7 +24221,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>9</v>
@@ -24298,7 +24298,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -24334,7 +24334,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -24375,7 +24375,7 @@
         <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>9</v>
@@ -24452,7 +24452,7 @@
         <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>9</v>
@@ -24488,7 +24488,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -24529,7 +24529,7 @@
         <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>9</v>
@@ -24565,7 +24565,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -24606,7 +24606,7 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>9</v>
@@ -24683,7 +24683,7 @@
         <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>9</v>
@@ -24760,7 +24760,7 @@
         <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -24837,7 +24837,7 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>9</v>
@@ -24914,7 +24914,7 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -24991,7 +24991,7 @@
         <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -25068,7 +25068,7 @@
         <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>9</v>
@@ -25104,7 +25104,7 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -25145,7 +25145,7 @@
         <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>9</v>
@@ -25222,7 +25222,7 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>9</v>
@@ -25299,7 +25299,7 @@
         <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>9</v>
@@ -25376,7 +25376,7 @@
         <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>9</v>
@@ -25530,7 +25530,7 @@
         <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>9</v>
@@ -25607,7 +25607,7 @@
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>9</v>
@@ -25684,7 +25684,7 @@
         <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>9</v>
@@ -25720,7 +25720,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -25761,7 +25761,7 @@
         <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
         <v>9</v>
@@ -25797,7 +25797,7 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -25838,7 +25838,7 @@
         <v>7</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>9</v>
@@ -25915,7 +25915,7 @@
         <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>9</v>
@@ -25951,7 +25951,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -25992,7 +25992,7 @@
         <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K37">
         <v>9</v>
@@ -26069,7 +26069,7 @@
         <v>8</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>9</v>
@@ -26146,7 +26146,7 @@
         <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
         <v>9</v>
@@ -26223,7 +26223,7 @@
         <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>9</v>
@@ -29172,7 +29172,7 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -29249,7 +29249,7 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -29326,7 +29326,7 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -29362,7 +29362,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -29403,7 +29403,7 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -29480,7 +29480,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -29516,7 +29516,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -29557,7 +29557,7 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -29634,7 +29634,7 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -29670,7 +29670,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -29711,7 +29711,7 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -29788,7 +29788,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -29824,7 +29824,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -29865,7 +29865,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -29901,7 +29901,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -29942,7 +29942,7 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -29978,7 +29978,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -30019,7 +30019,7 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -30055,7 +30055,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -30096,7 +30096,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -30132,7 +30132,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -30173,7 +30173,7 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -30250,7 +30250,7 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -30286,7 +30286,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -30327,7 +30327,7 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -30363,7 +30363,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -30404,7 +30404,7 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -30481,7 +30481,7 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -30558,7 +30558,7 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -30594,7 +30594,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -30635,7 +30635,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -30671,7 +30671,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -30712,7 +30712,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -30748,7 +30748,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -30789,7 +30789,7 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -30825,7 +30825,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -30866,7 +30866,7 @@
         <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -30902,7 +30902,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -30943,7 +30943,7 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -31020,7 +31020,7 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -31056,7 +31056,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -31097,7 +31097,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -31174,7 +31174,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -31251,7 +31251,7 @@
         <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -31287,7 +31287,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -31328,7 +31328,7 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -31405,7 +31405,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -31441,7 +31441,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -31482,7 +31482,7 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -31559,7 +31559,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -31595,7 +31595,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -43318,7 +43318,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -43395,7 +43395,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -43472,7 +43472,7 @@
         <v>-1</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -43508,7 +43508,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -43549,7 +43549,7 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -43585,7 +43585,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -43703,7 +43703,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -43780,7 +43780,7 @@
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -43816,7 +43816,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -43857,7 +43857,7 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -43893,7 +43893,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -43934,7 +43934,7 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -44088,7 +44088,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -44124,7 +44124,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -44165,7 +44165,7 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -44201,7 +44201,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -44396,7 +44396,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -44473,7 +44473,7 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>6</v>
@@ -44509,7 +44509,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -44550,7 +44550,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -44627,7 +44627,7 @@
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -44704,7 +44704,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -44740,7 +44740,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -44781,7 +44781,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -44817,7 +44817,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -44858,7 +44858,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -44935,7 +44935,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>6</v>
@@ -45012,7 +45012,7 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>7</v>
@@ -45089,7 +45089,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -45166,7 +45166,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -45243,7 +45243,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -45279,7 +45279,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -45320,7 +45320,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -45397,7 +45397,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -45433,7 +45433,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -45474,7 +45474,7 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>7</v>
@@ -45510,7 +45510,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -45551,7 +45551,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>6</v>
@@ -45628,7 +45628,7 @@
         <v>-1</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>6</v>
@@ -45705,7 +45705,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>6</v>
@@ -45782,7 +45782,7 @@
         <v>-1</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -45936,7 +45936,7 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I38">
         <v>5</v>
@@ -46013,7 +46013,7 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>6</v>
@@ -46090,7 +46090,7 @@
         <v>6</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>6</v>
@@ -46126,7 +46126,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -46167,7 +46167,7 @@
         <v>8</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -46244,7 +46244,7 @@
         <v>8</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I42">
         <v>6</v>
@@ -46280,7 +46280,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>7</v>
@@ -46321,7 +46321,7 @@
         <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>6</v>
@@ -49365,7 +49365,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -49401,7 +49401,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -49439,7 +49439,7 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -49469,7 +49469,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -49507,7 +49507,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -49584,7 +49584,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -49620,7 +49620,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -49767,7 +49767,7 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -49803,7 +49803,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -49844,7 +49844,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>9</v>
@@ -49880,7 +49880,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -49921,7 +49921,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I12">
         <v>5</v>
@@ -49957,7 +49957,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -49998,7 +49998,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -50034,7 +50034,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -50075,7 +50075,7 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>5</v>
@@ -50111,7 +50111,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -50152,7 +50152,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -50188,7 +50188,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -50229,7 +50229,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -50265,7 +50265,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -50306,7 +50306,7 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>9</v>
@@ -50342,7 +50342,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -50383,7 +50383,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -50460,7 +50460,7 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -50496,7 +50496,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -50554,7 +50554,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -50631,7 +50631,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -50667,7 +50667,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -50708,7 +50708,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>5</v>
@@ -50785,7 +50785,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -50862,7 +50862,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -50939,7 +50939,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -50975,7 +50975,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -51016,7 +51016,7 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -51134,7 +51134,7 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>7</v>
@@ -51170,7 +51170,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -51288,7 +51288,7 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>5</v>
@@ -51324,7 +51324,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>5</v>
@@ -51365,7 +51365,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
         <v>5</v>
@@ -51442,7 +51442,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>8</v>
@@ -51548,7 +51548,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -51625,7 +51625,7 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>8</v>
@@ -51661,7 +51661,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>9</v>
@@ -51702,7 +51702,7 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>7</v>
@@ -51738,7 +51738,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>8</v>
@@ -51779,7 +51779,7 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
         <v>10</v>
@@ -51856,7 +51856,7 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I39">
         <v>5</v>
@@ -51892,7 +51892,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>5</v>
@@ -51933,7 +51933,7 @@
         <v>7</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
         <v>5</v>
@@ -52010,7 +52010,7 @@
         <v>8</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I41">
         <v>9</v>
@@ -52087,7 +52087,7 @@
         <v>7</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>5</v>
@@ -52123,7 +52123,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -61458,7 +61458,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -61500,7 +61500,7 @@
         <v>9</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -61636,7 +61636,7 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -61678,7 +61678,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -61725,7 +61725,7 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -62081,7 +62081,7 @@
         <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -62123,7 +62123,7 @@
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>7</v>
@@ -62170,7 +62170,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -62212,7 +62212,7 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -63149,7 +63149,7 @@
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -63238,7 +63238,7 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M24">
         <v>7</v>
@@ -63280,7 +63280,7 @@
         <v>7</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>9</v>
@@ -67275,7 +67275,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -68122,7 +68122,7 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -68158,7 +68158,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -68199,7 +68199,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -68353,7 +68353,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -68507,7 +68507,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -68543,7 +68543,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -68969,7 +68969,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -69005,7 +69005,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -70860,7 +70860,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -70878,7 +70878,7 @@
         <v>-1</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -70942,7 +70942,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -70978,7 +70978,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -71019,13 +71019,13 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -71055,13 +71055,13 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -71096,13 +71096,13 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -71132,13 +71132,13 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -71179,7 +71179,7 @@
         <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -71215,7 +71215,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -71256,7 +71256,7 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -71292,7 +71292,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -71481,7 +71481,7 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -71517,7 +71517,7 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -71866,7 +71866,7 @@
         <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -71902,7 +71902,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -72600,7 +72600,7 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>10</v>
@@ -72636,7 +72636,7 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -72754,7 +72754,7 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
         <v>10</v>
@@ -72985,13 +72985,13 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -73062,13 +73062,13 @@
         <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -73098,13 +73098,13 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -73198,7 +73198,7 @@
         <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -73210,7 +73210,7 @@
         <v>-1</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -73322,13 +73322,13 @@
         <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>9</v>
@@ -73358,13 +73358,13 @@
         <v>9</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>10</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -73399,7 +73399,7 @@
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -73435,7 +73435,7 @@
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>-1</v>
@@ -73458,7 +73458,7 @@
         <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -73470,7 +73470,7 @@
         <v>-1</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -73741,7 +73741,7 @@
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -73895,7 +73895,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -73931,7 +73931,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -73972,7 +73972,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -74049,7 +74049,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -74203,7 +74203,7 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -74280,7 +74280,7 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -74588,7 +74588,7 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>8</v>
@@ -74665,7 +74665,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -74701,7 +74701,7 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -74973,7 +74973,7 @@
         <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -75009,7 +75009,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>7</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -18932,7 +18932,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -18950,7 +18950,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -18986,7 +18986,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -20549,7 +20549,7 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G26">
         <v>9</v>
@@ -20567,7 +20567,7 @@
         <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -20603,7 +20603,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -20617,7 +20617,7 @@
         <v>8</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -20635,7 +20635,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -20671,7 +20671,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -21674,7 +21674,7 @@
         <v>549</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -21692,7 +21692,7 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -21728,7 +21728,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -21751,7 +21751,7 @@
         <v>550</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -21769,7 +21769,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -21805,7 +21805,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -21982,7 +21982,7 @@
         <v>553</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -22000,7 +22000,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -22036,7 +22036,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -22136,7 +22136,7 @@
         <v>555</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -22154,7 +22154,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -22190,7 +22190,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -22213,7 +22213,7 @@
         <v>556</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -22231,7 +22231,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -22267,7 +22267,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -22290,7 +22290,7 @@
         <v>557</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -22308,7 +22308,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -22344,7 +22344,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -22444,7 +22444,7 @@
         <v>559</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -22462,7 +22462,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>8</v>
@@ -22498,7 +22498,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -22675,7 +22675,7 @@
         <v>562</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -22684,7 +22684,7 @@
         <v>6</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>4</v>
@@ -22702,7 +22702,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -22729,7 +22729,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -22738,7 +22738,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -22983,7 +22983,7 @@
         <v>566</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -23001,7 +23001,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -23037,7 +23037,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -23060,7 +23060,7 @@
         <v>567</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -23069,7 +23069,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>6</v>
@@ -23078,7 +23078,7 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -23114,7 +23114,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -23123,7 +23123,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -23223,7 +23223,7 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>6</v>
@@ -23241,7 +23241,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>8</v>
@@ -23277,7 +23277,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -23581,7 +23581,7 @@
         <v>574</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -23599,7 +23599,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -23635,7 +23635,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -23735,7 +23735,7 @@
         <v>576</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -23753,7 +23753,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -23789,7 +23789,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -24120,7 +24120,7 @@
         <v>581</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -24138,7 +24138,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -24174,7 +24174,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -24523,7 +24523,7 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -24559,7 +24559,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -24582,7 +24582,7 @@
         <v>587</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -24600,7 +24600,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -24636,7 +24636,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -24890,7 +24890,7 @@
         <v>591</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>-1</v>
@@ -24908,7 +24908,7 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -24944,7 +24944,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -24967,7 +24967,7 @@
         <v>592</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -24985,7 +24985,7 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -25021,7 +25021,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -25198,7 +25198,7 @@
         <v>595</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>-1</v>
@@ -25216,7 +25216,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -25252,7 +25252,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -25352,7 +25352,7 @@
         <v>597</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -25370,7 +25370,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>7</v>
@@ -25406,7 +25406,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -25429,7 +25429,7 @@
         <v>598</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -25447,7 +25447,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>7</v>
@@ -25483,7 +25483,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -25506,7 +25506,7 @@
         <v>599</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -25524,7 +25524,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -25560,7 +25560,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -26199,7 +26199,7 @@
         <v>608</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>7</v>
@@ -26217,7 +26217,7 @@
         <v>9</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>6</v>
@@ -26253,7 +26253,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>7</v>
@@ -29995,7 +29995,7 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -30013,7 +30013,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -30049,7 +30049,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -30321,7 +30321,7 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -30357,7 +30357,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -31988,7 +31988,7 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -32006,7 +32006,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -32042,7 +32042,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -32823,7 +32823,7 @@
         <v>684</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>-1</v>
@@ -32841,7 +32841,7 @@
         <v>-1</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -32877,7 +32877,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -33439,7 +33439,7 @@
         <v>692</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>-1</v>
@@ -33457,7 +33457,7 @@
         <v>-1</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -33493,7 +33493,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -33913,7 +33913,7 @@
         <v>9</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>6</v>
@@ -33931,7 +33931,7 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -33967,7 +33967,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -33978,7 +33978,7 @@
         <v>699</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>-1</v>
@@ -33990,13 +33990,13 @@
         <v>6</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>-1</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -34008,7 +34008,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -34032,7 +34032,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -34044,7 +34044,7 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>-1</v>
@@ -34286,7 +34286,7 @@
         <v>703</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>-1</v>
@@ -34304,7 +34304,7 @@
         <v>-1</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -34340,7 +34340,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -34440,7 +34440,7 @@
         <v>705</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C39">
         <v>-1</v>
@@ -34458,7 +34458,7 @@
         <v>-1</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -34494,7 +34494,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -34594,7 +34594,7 @@
         <v>707</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -34612,7 +34612,7 @@
         <v>-1</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>5</v>
@@ -34648,7 +34648,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U41">
         <v>5</v>
@@ -35269,7 +35269,7 @@
         <v>52</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -35287,7 +35287,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>7</v>
@@ -35323,7 +35323,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -35346,7 +35346,7 @@
         <v>53</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -35364,7 +35364,7 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -35400,7 +35400,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -35654,7 +35654,7 @@
         <v>57</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -35672,7 +35672,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>9</v>
@@ -35708,7 +35708,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -35731,7 +35731,7 @@
         <v>58</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -35749,7 +35749,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -35785,7 +35785,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -35885,7 +35885,7 @@
         <v>60</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -35903,7 +35903,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -35939,7 +35939,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -36193,7 +36193,7 @@
         <v>64</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -36211,7 +36211,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>5</v>
@@ -36247,7 +36247,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -36809,7 +36809,7 @@
         <v>72</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -36827,7 +36827,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -36863,7 +36863,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -38177,7 +38177,7 @@
         <v>720</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>-1</v>
@@ -38192,10 +38192,10 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -38210,7 +38210,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -38231,7 +38231,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -38246,7 +38246,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -38254,7 +38254,7 @@
         <v>721</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>-1</v>
@@ -38272,7 +38272,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -38308,7 +38308,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -39255,7 +39255,7 @@
         <v>734</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>9</v>
@@ -39273,7 +39273,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>10</v>
@@ -39309,7 +39309,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -40010,7 +40010,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -40028,7 +40028,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -40064,7 +40064,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -40241,7 +40241,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -40259,7 +40259,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -40295,7 +40295,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -40549,7 +40549,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -40567,7 +40567,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -40603,7 +40603,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -40777,10 +40777,10 @@
         <v>752</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -40795,10 +40795,10 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -40831,10 +40831,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -41165,7 +41165,7 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -41177,13 +41177,13 @@
         <v>7</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -41195,7 +41195,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -41219,7 +41219,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -41231,7 +41231,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -41242,7 +41242,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -41254,13 +41254,13 @@
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -41272,7 +41272,7 @@
         <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -41296,7 +41296,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -41308,7 +41308,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -42243,7 +42243,7 @@
         <v>5</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -42261,7 +42261,7 @@
         <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -42297,7 +42297,7 @@
         <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -42563,7 +42563,7 @@
         <v>8</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -42581,7 +42581,7 @@
         <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -42617,7 +42617,7 @@
         <v>9</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -42779,10 +42779,10 @@
         <v>778</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -42797,10 +42797,10 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>4</v>
@@ -42833,10 +42833,10 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V40">
         <v>5</v>
@@ -43457,7 +43457,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -43469,13 +43469,13 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -43487,7 +43487,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -43511,7 +43511,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -43523,7 +43523,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -43608,10 +43608,10 @@
         <v>787</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -43623,13 +43623,13 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>7</v>
@@ -43641,7 +43641,7 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -43662,10 +43662,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -43677,7 +43677,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -43777,7 +43777,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -43795,7 +43795,7 @@
         <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -43831,7 +43831,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -43993,10 +43993,10 @@
         <v>792</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -44008,13 +44008,13 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -44026,7 +44026,7 @@
         <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -44047,10 +44047,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -44062,7 +44062,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -44224,10 +44224,10 @@
         <v>795</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -44239,13 +44239,13 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -44257,7 +44257,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -44278,10 +44278,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -44293,7 +44293,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -44301,10 +44301,10 @@
         <v>796</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -44316,13 +44316,13 @@
         <v>5</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -44334,7 +44334,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -44355,10 +44355,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -44370,7 +44370,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -44535,7 +44535,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -44553,7 +44553,7 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -44589,7 +44589,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -44624,7 +44624,7 @@
         <v>8</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -44642,7 +44642,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -44678,7 +44678,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -45625,7 +45625,7 @@
         <v>8</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -45643,7 +45643,7 @@
         <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -45679,7 +45679,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -45767,7 +45767,7 @@
         <v>5</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -45779,13 +45779,13 @@
         <v>7</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>4</v>
@@ -45797,7 +45797,7 @@
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -45821,7 +45821,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -45833,7 +45833,7 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -45841,7 +45841,7 @@
         <v>816</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>7</v>
@@ -45859,7 +45859,7 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>5</v>
@@ -45895,7 +45895,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>6</v>
@@ -46519,7 +46519,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -46531,13 +46531,13 @@
         <v>8</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -46549,7 +46549,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -46573,7 +46573,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -46585,7 +46585,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -46596,7 +46596,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -46614,7 +46614,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>9</v>
@@ -46650,7 +46650,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -46750,7 +46750,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -46768,7 +46768,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -46804,7 +46804,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -47135,7 +47135,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -47153,7 +47153,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -47189,7 +47189,7 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -47609,7 +47609,7 @@
         <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -47627,7 +47627,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -47663,7 +47663,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -47674,7 +47674,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -47692,7 +47692,7 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -47728,7 +47728,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -47917,7 +47917,7 @@
         <v>7</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>5</v>
@@ -47935,7 +47935,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -47971,7 +47971,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -48059,7 +48059,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -48077,7 +48077,7 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>7</v>
@@ -48113,7 +48113,7 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -48136,7 +48136,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -48154,7 +48154,7 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>7</v>
@@ -48190,7 +48190,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -48290,7 +48290,7 @@
         <v>7</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -48308,7 +48308,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -48344,7 +48344,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -48444,7 +48444,7 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -48462,7 +48462,7 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>7</v>
@@ -48498,7 +48498,7 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -48675,7 +48675,7 @@
         <v>6</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -48693,7 +48693,7 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -48729,7 +48729,7 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -48841,7 +48841,7 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -48859,7 +48859,7 @@
         <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -48895,7 +48895,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -48903,7 +48903,7 @@
         <v>854</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -48921,7 +48921,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>6</v>
@@ -48957,7 +48957,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>6</v>
@@ -48983,7 +48983,7 @@
         <v>5</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>7</v>
@@ -48995,13 +48995,13 @@
         <v>8</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -49013,7 +49013,7 @@
         <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -49037,7 +49037,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -49049,7 +49049,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -49137,7 +49137,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -49155,7 +49155,7 @@
         <v>7</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -49191,7 +49191,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -49371,7 +49371,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -49407,7 +49407,7 @@
         <v>5</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -49513,7 +49513,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -49590,7 +49590,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -49626,7 +49626,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -49696,7 +49696,7 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -49732,7 +49732,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -49773,7 +49773,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -49927,7 +49927,7 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>9</v>
@@ -49963,7 +49963,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -50004,7 +50004,7 @@
         <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>8</v>
@@ -50040,7 +50040,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -50063,7 +50063,7 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -50081,7 +50081,7 @@
         <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>5</v>
@@ -50117,7 +50117,7 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -50235,7 +50235,7 @@
         <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>7</v>
@@ -50445,7 +50445,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -50466,10 +50466,10 @@
         <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -50499,13 +50499,13 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>5</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -50714,7 +50714,7 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>7</v>
@@ -50868,7 +50868,7 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>9</v>
@@ -51199,7 +51199,7 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>5</v>
@@ -51217,7 +51217,7 @@
         <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>5</v>
@@ -51253,7 +51253,7 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -51276,7 +51276,7 @@
         <v>6</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -51294,7 +51294,7 @@
         <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>8</v>
@@ -51330,7 +51330,7 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -51708,7 +51708,7 @@
         <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>8</v>
@@ -51744,7 +51744,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -51844,7 +51844,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>6</v>
@@ -51862,7 +51862,7 @@
         <v>5</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>5</v>
@@ -51898,7 +51898,7 @@
         <v>5</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>5</v>
@@ -51927,7 +51927,7 @@
         <v>7</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G40">
         <v>7</v>
@@ -51945,7 +51945,7 @@
         <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
         <v>7</v>
@@ -51981,7 +51981,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -52093,7 +52093,7 @@
         <v>5</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
         <v>5</v>
@@ -52129,7 +52129,7 @@
         <v>5</v>
       </c>
       <c r="V42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W42">
         <v>5</v>
@@ -52394,16 +52394,16 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -52412,16 +52412,16 @@
         <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -52448,16 +52448,16 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>-1</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -52477,7 +52477,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -52495,7 +52495,7 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -52531,7 +52531,7 @@
         <v>5</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -53188,7 +53188,7 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -53224,7 +53224,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -53327,7 +53327,7 @@
         <v>7</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>6</v>
@@ -53342,10 +53342,10 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -53378,10 +53378,10 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -53727,7 +53727,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -53763,7 +53763,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -54218,7 +54218,7 @@
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -54254,7 +54254,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -54277,7 +54277,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>9</v>
@@ -54295,7 +54295,7 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -54331,7 +54331,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -54834,7 +54834,7 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>5</v>
@@ -54870,7 +54870,7 @@
         <v>7</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y37">
         <v>7</v>
@@ -54896,7 +54896,7 @@
         <v>6</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>7</v>
@@ -54911,10 +54911,10 @@
         <v>5</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -54950,7 +54950,7 @@
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -55124,10 +55124,10 @@
         <v>6</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <v>7</v>
@@ -55142,10 +55142,10 @@
         <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -55178,10 +55178,10 @@
         <v>5</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -55491,7 +55491,7 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -55509,7 +55509,7 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -55545,7 +55545,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>-1</v>
@@ -55722,7 +55722,7 @@
         <v>5</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -55740,7 +55740,7 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -55776,7 +55776,7 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>-1</v>
@@ -56338,7 +56338,7 @@
         <v>5</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -56356,7 +56356,7 @@
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -56392,7 +56392,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>-1</v>
@@ -57320,7 +57320,7 @@
         <v>7</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G30">
         <v>-1</v>
@@ -57338,7 +57338,7 @@
         <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -57374,7 +57374,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>-1</v>
@@ -58010,7 +58010,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -58703,7 +58703,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -58916,7 +58916,7 @@
         <v>5</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -58934,7 +58934,7 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -58970,7 +58970,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -59242,7 +59242,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -59686,7 +59686,7 @@
         <v>5</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>5</v>
@@ -59704,7 +59704,7 @@
         <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -59740,7 +59740,7 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -59935,7 +59935,7 @@
         <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -60361,7 +60361,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -60379,7 +60379,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -60415,7 +60415,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -61526,7 +61526,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>9</v>
@@ -61547,13 +61547,13 @@
         <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>7</v>
@@ -61589,7 +61589,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -61793,13 +61793,13 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -61814,13 +61814,13 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M8">
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -61856,13 +61856,13 @@
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -61882,13 +61882,13 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -61903,13 +61903,13 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M9">
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -61945,13 +61945,13 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC9">
         <v>5</v>
@@ -61971,13 +61971,13 @@
         <v>6</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -61992,13 +61992,13 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -62034,13 +62034,13 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -62066,7 +62066,7 @@
         <v>7</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -62087,7 +62087,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -62129,7 +62129,7 @@
         <v>7</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>5</v>
@@ -62238,7 +62238,7 @@
         <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -62259,7 +62259,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -62301,7 +62301,7 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -62327,7 +62327,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -62348,7 +62348,7 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -62390,7 +62390,7 @@
         <v>9</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -62416,13 +62416,13 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>8</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -62437,13 +62437,13 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M15">
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>8</v>
@@ -62479,13 +62479,13 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>7</v>
@@ -62505,7 +62505,7 @@
         <v>5</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>6</v>
@@ -62526,7 +62526,7 @@
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -62568,7 +62568,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -62594,7 +62594,7 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -62615,7 +62615,7 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -62657,7 +62657,7 @@
         <v>5</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <v>5</v>
@@ -62683,13 +62683,13 @@
         <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F18">
         <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -62704,13 +62704,13 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M18">
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>7</v>
@@ -62746,13 +62746,13 @@
         <v>5</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -62772,7 +62772,7 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -62793,7 +62793,7 @@
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -62835,7 +62835,7 @@
         <v>6</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>5</v>
@@ -62861,7 +62861,7 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F20">
         <v>6</v>
@@ -62882,13 +62882,13 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -62924,13 +62924,13 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -62950,7 +62950,7 @@
         <v>5</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -62971,13 +62971,13 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M21">
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>9</v>
@@ -63013,13 +63013,13 @@
         <v>5</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -63039,7 +63039,7 @@
         <v>9</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>9</v>
@@ -63060,7 +63060,7 @@
         <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -63102,7 +63102,7 @@
         <v>9</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -63306,13 +63306,13 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F25">
         <v>6</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>6</v>
@@ -63327,13 +63327,13 @@
         <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M25">
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>7</v>
@@ -63369,13 +63369,13 @@
         <v>5</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA25">
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -63395,13 +63395,13 @@
         <v>5</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F26">
         <v>6</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -63416,13 +63416,13 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M26">
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -63458,13 +63458,13 @@
         <v>5</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA26">
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC26">
         <v>5</v>
@@ -63484,7 +63484,7 @@
         <v>8</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -63505,7 +63505,7 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -63547,7 +63547,7 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -63573,13 +63573,13 @@
         <v>5</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F28">
         <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -63594,13 +63594,13 @@
         <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M28">
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>8</v>
@@ -63636,13 +63636,13 @@
         <v>5</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -63662,7 +63662,7 @@
         <v>5</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>6</v>
@@ -63683,13 +63683,13 @@
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M29">
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -63725,13 +63725,13 @@
         <v>5</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>5</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>5</v>
@@ -67103,7 +67103,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -67121,7 +67121,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -67157,7 +67157,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -67180,7 +67180,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -67198,7 +67198,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -67234,7 +67234,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -67334,7 +67334,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -67352,7 +67352,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -67388,7 +67388,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -67411,7 +67411,7 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -67429,7 +67429,7 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -67465,7 +67465,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -67488,7 +67488,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F9">
         <v>6</v>
@@ -67506,7 +67506,7 @@
         <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -67542,7 +67542,7 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -67565,7 +67565,7 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -67583,7 +67583,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -67619,7 +67619,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -67642,7 +67642,7 @@
         <v>6</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -67660,7 +67660,7 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -67696,7 +67696,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -67719,7 +67719,7 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -67737,7 +67737,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -67773,7 +67773,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -67796,7 +67796,7 @@
         <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>10</v>
@@ -67814,7 +67814,7 @@
         <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -67850,7 +67850,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -67873,7 +67873,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -67891,7 +67891,7 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -67927,7 +67927,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -67947,10 +67947,10 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -67965,10 +67965,10 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <v>6</v>
@@ -68001,10 +68001,10 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -68027,7 +68027,7 @@
         <v>7</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -68045,7 +68045,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -68081,7 +68081,7 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -68258,7 +68258,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -68276,7 +68276,7 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -68312,7 +68312,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -68412,7 +68412,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -68430,7 +68430,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>6</v>
@@ -68466,7 +68466,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -68566,7 +68566,7 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -68584,7 +68584,7 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -68620,7 +68620,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -68643,7 +68643,7 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>10</v>
@@ -68661,7 +68661,7 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -68697,7 +68697,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -68720,7 +68720,7 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F25">
         <v>9</v>
@@ -68738,7 +68738,7 @@
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -68774,7 +68774,7 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -68797,7 +68797,7 @@
         <v>5</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -68815,7 +68815,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L26">
         <v>6</v>
@@ -68851,7 +68851,7 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -68874,7 +68874,7 @@
         <v>7</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <v>8</v>
@@ -68892,7 +68892,7 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -68928,7 +68928,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -69028,7 +69028,7 @@
         <v>5</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -69046,7 +69046,7 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -69082,7 +69082,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -69421,7 +69421,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -69439,7 +69439,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -69475,7 +69475,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -69498,7 +69498,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -69516,7 +69516,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -69552,7 +69552,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>-1</v>
@@ -69806,7 +69806,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -69824,7 +69824,7 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>8</v>
@@ -69860,7 +69860,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -69883,7 +69883,7 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -69898,7 +69898,7 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -69928,7 +69928,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -70410,7 +70410,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>7</v>
@@ -70428,7 +70428,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -70464,7 +70464,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -70848,7 +70848,7 @@
         <v>1085</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>9</v>
@@ -70857,7 +70857,7 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -70875,7 +70875,7 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -70889,13 +70889,13 @@
         <v>1086</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -70907,7 +70907,7 @@
         <v>-1</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -70930,7 +70930,7 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -70948,7 +70948,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -70984,7 +70984,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -71155,7 +71155,7 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -71173,7 +71173,7 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -71209,7 +71209,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -71232,7 +71232,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -71250,7 +71250,7 @@
         <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -71286,7 +71286,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -71309,13 +71309,13 @@
         <v>5</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -71327,13 +71327,13 @@
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -71363,13 +71363,13 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -71383,16 +71383,16 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -71401,16 +71401,16 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -71437,16 +71437,16 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -71469,7 +71469,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>9</v>
@@ -71487,7 +71487,7 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -71523,7 +71523,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -71540,13 +71540,13 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>9</v>
@@ -71558,13 +71558,13 @@
         <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -71594,13 +71594,13 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -71617,13 +71617,13 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>10</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>9</v>
@@ -71635,13 +71635,13 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -71671,13 +71671,13 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -71691,16 +71691,16 @@
         <v>8</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>7</v>
@@ -71709,16 +71709,16 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -71745,16 +71745,16 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -71771,13 +71771,13 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>7</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -71789,13 +71789,13 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>4</v>
@@ -71825,13 +71825,13 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -71854,7 +71854,7 @@
         <v>9</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>9</v>
@@ -71872,7 +71872,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -71908,7 +71908,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -71922,16 +71922,16 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -71940,16 +71940,16 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -71976,16 +71976,16 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -72002,13 +72002,13 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>10</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>9</v>
@@ -72020,13 +72020,13 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>8</v>
@@ -72056,13 +72056,13 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -72076,16 +72076,16 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>7</v>
@@ -72094,16 +72094,16 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -72130,16 +72130,16 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -72156,13 +72156,13 @@
         <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E22">
         <v>9</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>8</v>
@@ -72174,13 +72174,13 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>9</v>
@@ -72210,13 +72210,13 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -72233,13 +72233,13 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -72251,13 +72251,13 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -72287,13 +72287,13 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -72310,13 +72310,13 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>8</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -72328,13 +72328,13 @@
         <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -72364,13 +72364,13 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -72387,13 +72387,13 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>10</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>8</v>
@@ -72405,13 +72405,13 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -72441,13 +72441,13 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -72464,13 +72464,13 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <v>7</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>8</v>
@@ -72482,13 +72482,13 @@
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>4</v>
@@ -72518,13 +72518,13 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -72535,19 +72535,19 @@
         <v>1108</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>6</v>
@@ -72562,10 +72562,10 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -72588,7 +72588,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>9</v>
@@ -72606,7 +72606,7 @@
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -72642,7 +72642,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -72659,13 +72659,13 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E29">
         <v>8</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>9</v>
@@ -72677,13 +72677,13 @@
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>7</v>
@@ -72713,13 +72713,13 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -72742,7 +72742,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>9</v>
@@ -72760,7 +72760,7 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>9</v>
@@ -72796,7 +72796,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -72813,13 +72813,13 @@
         <v>6</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>8</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>9</v>
@@ -72831,13 +72831,13 @@
         <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -72867,13 +72867,13 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -72890,13 +72890,13 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -72908,13 +72908,13 @@
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>9</v>
@@ -72944,13 +72944,13 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>10</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -73121,13 +73121,13 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E35">
         <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G35">
         <v>8</v>
@@ -73136,16 +73136,16 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>4</v>
@@ -73172,16 +73172,16 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>9</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -73227,13 +73227,13 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E37">
         <v>9</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G37">
         <v>9</v>
@@ -73245,13 +73245,13 @@
         <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>7</v>
@@ -73281,13 +73281,13 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>9</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -73378,16 +73378,16 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>6</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -73396,16 +73396,16 @@
         <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
         <v>5</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
         <v>5</v>
@@ -73432,16 +73432,16 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V39">
         <v>5</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -73484,13 +73484,13 @@
         <v>-1</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -73499,13 +73499,13 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>5</v>
@@ -73529,13 +73529,13 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y41">
         <v>5</v>
@@ -73546,13 +73546,13 @@
         <v>1123</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G42">
         <v>5</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>5</v>
@@ -73564,7 +73564,7 @@
         <v>-1</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y42">
         <v>5</v>
@@ -73800,7 +73800,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -73818,7 +73818,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -73854,7 +73854,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -74108,7 +74108,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -74126,7 +74126,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -74162,7 +74162,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -74339,7 +74339,7 @@
         <v>8</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -74357,7 +74357,7 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -74393,7 +74393,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -74416,7 +74416,7 @@
         <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G13">
         <v>9</v>
@@ -74434,7 +74434,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -74470,7 +74470,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -74493,7 +74493,7 @@
         <v>9</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -74511,7 +74511,7 @@
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -74547,7 +74547,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -74724,7 +74724,7 @@
         <v>9</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -74742,7 +74742,7 @@
         <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -74778,7 +74778,7 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -74801,7 +74801,7 @@
         <v>9</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -74819,7 +74819,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -74855,7 +74855,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -74878,7 +74878,7 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>7</v>
@@ -74896,7 +74896,7 @@
         <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -74932,7 +74932,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -75032,7 +75032,7 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>6</v>
@@ -75050,7 +75050,7 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -75086,7 +75086,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -84144,7 +84144,7 @@
         <v>7</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>9</v>
@@ -84162,7 +84162,7 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -84198,7 +84198,7 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -91470,7 +91470,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -91488,7 +91488,7 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>9</v>
@@ -91524,7 +91524,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>10</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -4369,7 +4369,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -4405,7 +4405,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -4505,7 +4505,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -4523,7 +4523,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -4559,7 +4559,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -4659,7 +4659,7 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -4677,7 +4677,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -4713,7 +4713,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -4736,7 +4736,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -4754,7 +4754,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -4790,7 +4790,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -4890,7 +4890,7 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -4908,7 +4908,7 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -4944,7 +4944,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -5044,7 +5044,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -5062,7 +5062,7 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -5098,7 +5098,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -5275,7 +5275,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -5293,7 +5293,7 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -5329,7 +5329,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -5506,7 +5506,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -5524,7 +5524,7 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -5560,7 +5560,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -5814,7 +5814,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -5832,7 +5832,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -5868,7 +5868,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -6199,7 +6199,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -6217,7 +6217,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -6253,7 +6253,7 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -6430,7 +6430,7 @@
         <v>8</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -6448,7 +6448,7 @@
         <v>7</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -6484,7 +6484,7 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -24893,7 +24893,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -24911,7 +24911,7 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -24947,7 +24947,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -25201,7 +25201,7 @@
         <v>5</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -25219,7 +25219,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>6</v>
@@ -25255,7 +25255,7 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -29151,7 +29151,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -29169,7 +29169,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -29205,7 +29205,7 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -29305,7 +29305,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>7</v>
@@ -29323,7 +29323,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -29359,7 +29359,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -29921,7 +29921,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -29939,7 +29939,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>9</v>
@@ -29975,7 +29975,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -29998,7 +29998,7 @@
         <v>5</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -30016,7 +30016,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -30052,7 +30052,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -30152,7 +30152,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>4</v>
@@ -30170,7 +30170,7 @@
         <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>6</v>
@@ -30206,7 +30206,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -30306,7 +30306,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -30324,7 +30324,7 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>7</v>
@@ -30360,7 +30360,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -30460,7 +30460,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>4</v>
@@ -30478,7 +30478,7 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -30514,7 +30514,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -30768,7 +30768,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>8</v>
@@ -30786,7 +30786,7 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>9</v>
@@ -30822,7 +30822,7 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -30922,7 +30922,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -30940,7 +30940,7 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -30976,7 +30976,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -30999,7 +30999,7 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -31017,7 +31017,7 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>7</v>
@@ -31053,7 +31053,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -37256,7 +37256,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -37274,7 +37274,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -37310,7 +37310,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -37641,7 +37641,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -37659,7 +37659,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -37695,7 +37695,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -37795,7 +37795,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -37813,7 +37813,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -37849,7 +37849,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -37872,7 +37872,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -37890,7 +37890,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>8</v>
@@ -37926,7 +37926,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -38026,7 +38026,7 @@
         <v>-1</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -38044,7 +38044,7 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -38080,7 +38080,7 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -38180,7 +38180,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -38198,7 +38198,7 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -38234,7 +38234,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -38257,7 +38257,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -38275,7 +38275,7 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -38311,7 +38311,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>6</v>
@@ -38488,7 +38488,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -38506,7 +38506,7 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -38542,7 +38542,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -38642,7 +38642,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -38660,7 +38660,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>9</v>
@@ -38696,7 +38696,7 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -38719,7 +38719,7 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -38737,7 +38737,7 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>7</v>
@@ -38773,7 +38773,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -39566,7 +39566,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -39584,7 +39584,7 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>5</v>
@@ -39620,7 +39620,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -39797,7 +39797,7 @@
         <v>6</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>6</v>
@@ -39815,7 +39815,7 @@
         <v>6</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
         <v>8</v>
@@ -39851,7 +39851,7 @@
         <v>6</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -49672,7 +49672,7 @@
         <v>863</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -49690,7 +49690,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -49726,7 +49726,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>5</v>
@@ -51075,7 +51075,7 @@
         <v>882</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -51084,7 +51084,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -51102,7 +51102,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -51193,7 +51193,7 @@
         <v>884</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -51211,7 +51211,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I30">
         <v>5</v>
@@ -51247,7 +51247,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -52397,7 +52397,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -52415,7 +52415,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -52451,7 +52451,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -55417,7 +55417,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -55435,7 +55435,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -55471,7 +55471,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -55482,7 +55482,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -55494,13 +55494,13 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -55512,7 +55512,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -55536,7 +55536,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -55548,7 +55548,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -55636,7 +55636,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -55654,7 +55654,7 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -55690,7 +55690,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -55713,7 +55713,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -55725,13 +55725,13 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -55743,7 +55743,7 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -55767,7 +55767,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -55779,7 +55779,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -56021,7 +56021,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -56033,13 +56033,13 @@
         <v>6</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H12">
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>8</v>
@@ -56051,7 +56051,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -56075,7 +56075,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -56087,7 +56087,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -56175,7 +56175,7 @@
         <v>6</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -56187,13 +56187,13 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -56205,7 +56205,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -56229,7 +56229,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -56241,7 +56241,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -56329,7 +56329,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -56341,13 +56341,13 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>9</v>
@@ -56359,7 +56359,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -56383,7 +56383,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -56395,7 +56395,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -56560,7 +56560,7 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -56572,13 +56572,13 @@
         <v>8</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H19">
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -56590,7 +56590,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -56614,7 +56614,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -56626,7 +56626,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -56637,7 +56637,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -56649,13 +56649,13 @@
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -56667,7 +56667,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -56691,7 +56691,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -56703,7 +56703,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -56714,7 +56714,7 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -56726,13 +56726,13 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -56744,7 +56744,7 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -56768,7 +56768,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -56780,7 +56780,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -57169,7 +57169,7 @@
         <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>7</v>
@@ -57187,7 +57187,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -57223,7 +57223,7 @@
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -57246,7 +57246,7 @@
         <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H29">
         <v>6</v>
@@ -57264,7 +57264,7 @@
         <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -57300,7 +57300,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -57323,7 +57323,7 @@
         <v>5</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -57341,7 +57341,7 @@
         <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -57377,7 +57377,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -60136,7 +60136,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -60154,7 +60154,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -60190,7 +60190,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -60367,7 +60367,7 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -60385,7 +60385,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -60421,7 +60421,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -60521,7 +60521,7 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -60539,7 +60539,7 @@
         <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -60575,7 +60575,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -60829,7 +60829,7 @@
         <v>8</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>7</v>
@@ -60847,7 +60847,7 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -60883,7 +60883,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -60906,7 +60906,7 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>7</v>
@@ -60924,7 +60924,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -60960,7 +60960,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -61137,7 +61137,7 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>8</v>
@@ -61155,7 +61155,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -61191,7 +61191,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -69501,7 +69501,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -69519,7 +69519,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -69555,7 +69555,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -14262,7 +14262,7 @@
         <v>6</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>5</v>
@@ -14280,7 +14280,7 @@
         <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>5</v>
@@ -14316,7 +14316,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -32210,7 +32210,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -32222,13 +32222,13 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -32240,7 +32240,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -32264,7 +32264,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -32276,7 +32276,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -32749,7 +32749,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -32761,13 +32761,13 @@
         <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>6</v>
@@ -32779,7 +32779,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -32803,7 +32803,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -32815,7 +32815,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -32826,7 +32826,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>6</v>
@@ -32838,13 +32838,13 @@
         <v>7</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>5</v>
@@ -32856,7 +32856,7 @@
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -32880,7 +32880,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -32892,7 +32892,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -32903,7 +32903,7 @@
         <v>10</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -32921,7 +32921,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -32957,7 +32957,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -32980,7 +32980,7 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -32992,13 +32992,13 @@
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -33010,7 +33010,7 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -33034,7 +33034,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -33046,7 +33046,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -33057,7 +33057,7 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -33069,13 +33069,13 @@
         <v>8</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>7</v>
@@ -33087,7 +33087,7 @@
         <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -33111,7 +33111,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -33123,7 +33123,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -33146,7 +33146,7 @@
         <v>8</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>6</v>
@@ -33164,7 +33164,7 @@
         <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -33200,7 +33200,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -33377,7 +33377,7 @@
         <v>9</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>6</v>
@@ -33395,7 +33395,7 @@
         <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -33431,7 +33431,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -33442,7 +33442,7 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -33454,13 +33454,13 @@
         <v>6</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>6</v>
@@ -33472,7 +33472,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -33496,7 +33496,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -33508,7 +33508,7 @@
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -33531,7 +33531,7 @@
         <v>8</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -33549,7 +33549,7 @@
         <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -33585,7 +33585,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -33839,7 +33839,7 @@
         <v>6</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H31">
         <v>5</v>
@@ -33857,7 +33857,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -33893,7 +33893,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -33981,7 +33981,7 @@
         <v>5</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -33993,13 +33993,13 @@
         <v>5</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H33">
         <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -34011,7 +34011,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -34035,7 +34035,7 @@
         <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -34047,7 +34047,7 @@
         <v>5</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -34147,7 +34147,7 @@
         <v>6</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -34165,7 +34165,7 @@
         <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -34201,7 +34201,7 @@
         <v>7</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -34224,7 +34224,7 @@
         <v>6</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>6</v>
@@ -34242,7 +34242,7 @@
         <v>7</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -34278,7 +34278,7 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -34289,7 +34289,7 @@
         <v>5</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>6</v>
@@ -34301,16 +34301,16 @@
         <v>8</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>6</v>
@@ -34319,7 +34319,7 @@
         <v>8</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -34343,10 +34343,10 @@
         <v>5</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -34355,7 +34355,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -34366,7 +34366,7 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -34378,13 +34378,13 @@
         <v>6</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -34396,7 +34396,7 @@
         <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -34420,7 +34420,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -34432,7 +34432,7 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -34443,7 +34443,7 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -34455,13 +34455,13 @@
         <v>6</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H39">
         <v>7</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -34473,7 +34473,7 @@
         <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -34497,7 +34497,7 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>5</v>
@@ -34509,7 +34509,7 @@
         <v>6</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -34609,7 +34609,7 @@
         <v>8</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -34627,7 +34627,7 @@
         <v>6</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -34663,7 +34663,7 @@
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -40416,7 +40416,7 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -40452,7 +40452,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>8</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -9898,7 +9898,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -9975,7 +9975,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -10052,7 +10052,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -10129,7 +10129,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -10147,7 +10147,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -10206,7 +10206,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -10283,7 +10283,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -10301,7 +10301,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -10360,7 +10360,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -10437,7 +10437,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -10514,7 +10514,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -10591,7 +10591,7 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -10668,7 +10668,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -10745,7 +10745,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -10822,7 +10822,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -10840,7 +10840,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -10899,7 +10899,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -10917,7 +10917,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -10976,7 +10976,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -11053,7 +11053,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -11071,7 +11071,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -11130,7 +11130,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -11207,7 +11207,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -11225,7 +11225,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -11284,7 +11284,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -11361,7 +11361,7 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -11438,7 +11438,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -11515,7 +11515,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -11533,7 +11533,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -11592,7 +11592,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -11610,7 +11610,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -11669,7 +11669,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -11746,7 +11746,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -11841,7 +11841,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -11900,7 +11900,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -11977,7 +11977,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -11995,7 +11995,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -12054,7 +12054,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -12072,7 +12072,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -12131,7 +12131,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -12149,7 +12149,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>5</v>
@@ -12208,7 +12208,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -18885,7 +18885,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -18900,7 +18900,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -18962,7 +18962,7 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -18977,7 +18977,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -19039,7 +19039,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -19054,7 +19054,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -19116,7 +19116,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -19131,7 +19131,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -19193,7 +19193,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -19208,7 +19208,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -19270,7 +19270,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -19285,10 +19285,10 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -19303,7 +19303,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -19347,7 +19347,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -19362,7 +19362,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -19424,7 +19424,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -19439,10 +19439,10 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -19457,7 +19457,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -19501,7 +19501,7 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -19516,10 +19516,10 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -19534,7 +19534,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -19578,7 +19578,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -19593,7 +19593,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -19655,7 +19655,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -19670,7 +19670,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -19732,7 +19732,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -19747,7 +19747,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -19809,7 +19809,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -19824,7 +19824,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -19886,7 +19886,7 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -19901,7 +19901,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -19963,7 +19963,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -19978,7 +19978,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -20040,7 +20040,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -20055,7 +20055,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -20117,7 +20117,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -20132,10 +20132,10 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -20150,7 +20150,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -20194,7 +20194,7 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -20209,7 +20209,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -20271,7 +20271,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -20286,7 +20286,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -20348,7 +20348,7 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -20363,7 +20363,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -20381,7 +20381,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -20425,7 +20425,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -20440,10 +20440,10 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -20458,7 +20458,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -20502,7 +20502,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -20517,7 +20517,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -20579,7 +20579,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -20594,7 +20594,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -20656,7 +20656,7 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -20671,7 +20671,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -20733,7 +20733,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -20748,10 +20748,10 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -20766,7 +20766,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -20810,7 +20810,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -20825,7 +20825,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -20887,7 +20887,7 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -20902,10 +20902,10 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -20920,7 +20920,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -20964,7 +20964,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -20979,7 +20979,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -21041,7 +21041,7 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -21056,7 +21056,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -21118,7 +21118,7 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -21133,7 +21133,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -21195,7 +21195,7 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -21210,7 +21210,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>8</v>
@@ -21272,7 +21272,7 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -21287,7 +21287,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -21349,7 +21349,7 @@
         <v>8</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -21364,7 +21364,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -21426,7 +21426,7 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -21441,7 +21441,7 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -21503,7 +21503,7 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -21518,7 +21518,7 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -21802,7 +21802,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -21879,7 +21879,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -21956,7 +21956,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -22110,7 +22110,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -22341,7 +22341,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -22572,7 +22572,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -22649,7 +22649,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -22726,7 +22726,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -22880,7 +22880,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -23111,7 +23111,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -23129,7 +23129,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -23265,7 +23265,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -23283,7 +23283,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -29187,7 +29187,7 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -29202,10 +29202,10 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -29220,7 +29220,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -29264,7 +29264,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -29279,7 +29279,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -29341,7 +29341,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -29356,7 +29356,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -29418,7 +29418,7 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -29433,7 +29433,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -29495,7 +29495,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -29510,7 +29510,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -29572,7 +29572,7 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -29587,7 +29587,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -29649,7 +29649,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -29664,7 +29664,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -29726,7 +29726,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -29741,7 +29741,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -29803,7 +29803,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -29818,7 +29818,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -29880,7 +29880,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -29895,7 +29895,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -29957,7 +29957,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -29972,10 +29972,10 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -30034,7 +30034,7 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -30049,10 +30049,10 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -30067,7 +30067,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -30111,7 +30111,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -30126,10 +30126,10 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -30144,7 +30144,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -30188,7 +30188,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -30203,10 +30203,10 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -30221,7 +30221,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -30265,7 +30265,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -30280,7 +30280,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -30342,7 +30342,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -30357,10 +30357,10 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -30375,7 +30375,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -30419,7 +30419,7 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -30434,7 +30434,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -30496,7 +30496,7 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -30511,10 +30511,10 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -30529,7 +30529,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -30573,7 +30573,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -30588,7 +30588,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -30650,7 +30650,7 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -30665,10 +30665,10 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -30683,7 +30683,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -30727,7 +30727,7 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -30742,7 +30742,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -30804,7 +30804,7 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -30819,7 +30819,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -30881,7 +30881,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -30896,7 +30896,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -30958,7 +30958,7 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -30973,10 +30973,10 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -30991,7 +30991,7 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -31035,7 +31035,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -31050,7 +31050,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -31068,7 +31068,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -31112,7 +31112,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -31127,7 +31127,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -31189,7 +31189,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -31204,10 +31204,10 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -31266,7 +31266,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -31281,10 +31281,10 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -31343,7 +31343,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -31358,10 +31358,10 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -31420,7 +31420,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -31435,7 +31435,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -31497,7 +31497,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -31512,7 +31512,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -31574,7 +31574,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -31589,7 +31589,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -40058,7 +40058,7 @@
         <v>4</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -40076,7 +40076,7 @@
         <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -40135,7 +40135,7 @@
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -40153,7 +40153,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -40212,7 +40212,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -40230,7 +40230,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>-1</v>
@@ -40289,7 +40289,7 @@
         <v>4</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -40366,7 +40366,7 @@
         <v>4</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -40384,7 +40384,7 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>-1</v>
@@ -40443,7 +40443,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -40461,7 +40461,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -40520,7 +40520,7 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -40597,7 +40597,7 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -40615,7 +40615,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -40674,7 +40674,7 @@
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -40751,7 +40751,7 @@
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -40828,7 +40828,7 @@
         <v>4</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -40846,7 +40846,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -40905,7 +40905,7 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -40923,7 +40923,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -40982,7 +40982,7 @@
         <v>4</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -41000,7 +41000,7 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -41059,7 +41059,7 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -41136,7 +41136,7 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -41213,7 +41213,7 @@
         <v>4</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -41231,7 +41231,7 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -41290,7 +41290,7 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -41308,7 +41308,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -41367,7 +41367,7 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -41444,7 +41444,7 @@
         <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -41521,7 +41521,7 @@
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -41598,7 +41598,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -41616,7 +41616,7 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -41675,7 +41675,7 @@
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -41752,7 +41752,7 @@
         <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -41770,7 +41770,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -41829,7 +41829,7 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -41906,7 +41906,7 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -41924,7 +41924,7 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -41983,7 +41983,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -42060,7 +42060,7 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -42137,7 +42137,7 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -42155,7 +42155,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -42214,7 +42214,7 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -42232,7 +42232,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -42291,7 +42291,7 @@
         <v>4</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -42368,7 +42368,7 @@
         <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -42386,7 +42386,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -42445,7 +42445,7 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -42522,7 +42522,7 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -42540,7 +42540,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -42599,7 +42599,7 @@
         <v>4</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -42676,7 +42676,7 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -42753,7 +42753,7 @@
         <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -42830,7 +42830,7 @@
         <v>4</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -42907,7 +42907,7 @@
         <v>4</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -42925,7 +42925,7 @@
         <v>6</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X41">
         <v>9</v>
@@ -42984,7 +42984,7 @@
         <v>7</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -43061,7 +43061,7 @@
         <v>5</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -43138,7 +43138,7 @@
         <v>7</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
         <v>-1</v>
@@ -49389,13 +49389,13 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -49407,7 +49407,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -49460,7 +49460,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -49531,13 +49531,13 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -49549,7 +49549,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -49608,13 +49608,13 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -49714,7 +49714,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -49791,13 +49791,13 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -49815,7 +49815,7 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -49868,13 +49868,13 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -49945,13 +49945,13 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -50022,13 +50022,13 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -50040,13 +50040,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -50099,13 +50099,13 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -50176,13 +50176,13 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -50253,13 +50253,13 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -50271,13 +50271,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>7</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -50330,13 +50330,13 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -50407,13 +50407,13 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -50425,13 +50425,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>7</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -50484,13 +50484,13 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -50502,13 +50502,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>8</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -50578,13 +50578,13 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -50596,7 +50596,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -50655,13 +50655,13 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -50673,7 +50673,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -50732,13 +50732,13 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -50750,13 +50750,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>7</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -50809,13 +50809,13 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -50886,13 +50886,13 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -50904,7 +50904,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -50963,13 +50963,13 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -51040,13 +51040,13 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -51099,7 +51099,7 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -51158,13 +51158,13 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -51176,7 +51176,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -51235,13 +51235,13 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -51259,7 +51259,7 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -51312,13 +51312,13 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -51330,7 +51330,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>5</v>
@@ -51389,13 +51389,13 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -51407,7 +51407,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -51466,13 +51466,13 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -51484,7 +51484,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>9</v>
@@ -51572,13 +51572,13 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -51596,7 +51596,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -51649,13 +51649,13 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -51726,13 +51726,13 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -51744,7 +51744,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>8</v>
@@ -51803,13 +51803,13 @@
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -51880,13 +51880,13 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -51898,7 +51898,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U39">
         <v>5</v>
@@ -51957,13 +51957,13 @@
         <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -52034,13 +52034,13 @@
         <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -52052,7 +52052,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U41">
         <v>9</v>
@@ -52111,7 +52111,7 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -52129,7 +52129,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -55444,7 +55444,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -55462,7 +55462,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -55521,7 +55521,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -55539,7 +55539,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -55598,7 +55598,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -55675,7 +55675,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -55693,7 +55693,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -55752,7 +55752,7 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -55829,7 +55829,7 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -55906,7 +55906,7 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -55924,7 +55924,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -55983,7 +55983,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -56060,7 +56060,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -56137,7 +56137,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -56155,7 +56155,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -56214,7 +56214,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -56232,7 +56232,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -56291,7 +56291,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -56368,7 +56368,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -56386,7 +56386,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -56445,7 +56445,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -56463,7 +56463,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -56522,7 +56522,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -56599,7 +56599,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -56617,7 +56617,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -56676,7 +56676,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -56694,7 +56694,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -56753,7 +56753,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -56771,7 +56771,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -56830,7 +56830,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -56848,7 +56848,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -56907,7 +56907,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -56984,7 +56984,7 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -57002,7 +57002,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -57061,7 +57061,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -57114,7 +57114,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -57143,13 +57143,13 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -57196,7 +57196,7 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -57214,7 +57214,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -57273,7 +57273,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -57350,7 +57350,7 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -57572,7 +57572,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>7</v>
@@ -57590,7 +57590,7 @@
         <v>6</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -57649,7 +57649,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -57726,7 +57726,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -57803,7 +57803,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>7</v>
@@ -57821,7 +57821,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -57880,7 +57880,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>6</v>
@@ -57898,7 +57898,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -57957,7 +57957,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -58034,7 +58034,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -58111,7 +58111,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -58129,7 +58129,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -58188,7 +58188,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>5</v>
@@ -58206,7 +58206,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -58265,7 +58265,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -58283,7 +58283,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -58342,7 +58342,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>7</v>
@@ -58360,7 +58360,7 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -58419,7 +58419,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -58496,7 +58496,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -58573,7 +58573,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -58650,7 +58650,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -58727,7 +58727,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -58745,7 +58745,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -58804,7 +58804,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -58881,7 +58881,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>10</v>
@@ -58899,7 +58899,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -58958,7 +58958,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>5</v>
@@ -59035,7 +59035,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>8</v>
@@ -59112,7 +59112,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -59189,7 +59189,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -59266,7 +59266,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>5</v>
@@ -59284,7 +59284,7 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -59343,7 +59343,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -59361,7 +59361,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -59420,7 +59420,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -59497,7 +59497,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -59574,7 +59574,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>6</v>
@@ -59651,7 +59651,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>6</v>
@@ -59669,7 +59669,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -59728,7 +59728,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
         <v>5</v>
@@ -59805,7 +59805,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
         <v>7</v>
@@ -59823,7 +59823,7 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -59882,7 +59882,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
         <v>8</v>
@@ -60175,7 +60175,7 @@
         <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -60193,7 +60193,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -60252,7 +60252,7 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -60329,7 +60329,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -60347,7 +60347,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -60406,7 +60406,7 @@
         <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -60424,7 +60424,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -60483,7 +60483,7 @@
         <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -60501,7 +60501,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -60560,7 +60560,7 @@
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -60637,7 +60637,7 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -60714,7 +60714,7 @@
         <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -60732,7 +60732,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -60791,7 +60791,7 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -60868,7 +60868,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -60886,7 +60886,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -60945,7 +60945,7 @@
         <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -60963,7 +60963,7 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -61022,7 +61022,7 @@
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -61040,7 +61040,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -61099,7 +61099,7 @@
         <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -61176,7 +61176,7 @@
         <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -61194,7 +61194,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -61253,7 +61253,7 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -61485,7 +61485,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -61574,7 +61574,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -61663,7 +61663,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -61752,7 +61752,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -61841,7 +61841,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -61930,7 +61930,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -62019,7 +62019,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -62108,7 +62108,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -62197,7 +62197,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -62286,7 +62286,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -62375,7 +62375,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -62396,7 +62396,7 @@
         <v>9</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -62464,7 +62464,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -62553,7 +62553,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -62642,7 +62642,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -62731,7 +62731,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -62820,7 +62820,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -62841,7 +62841,7 @@
         <v>6</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>6</v>
@@ -62909,7 +62909,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -62998,7 +62998,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -63087,7 +63087,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -63108,7 +63108,7 @@
         <v>9</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -63176,7 +63176,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -63265,7 +63265,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -63286,7 +63286,7 @@
         <v>7</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -63354,7 +63354,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -63443,7 +63443,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -63532,7 +63532,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -63553,7 +63553,7 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -63621,7 +63621,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -63710,7 +63710,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -67145,7 +67145,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -67222,7 +67222,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -67299,7 +67299,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -67376,7 +67376,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -67394,7 +67394,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -67453,7 +67453,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -67530,7 +67530,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -67607,7 +67607,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -67625,7 +67625,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -67684,7 +67684,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -67761,7 +67761,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -67838,7 +67838,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -67915,7 +67915,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -67992,7 +67992,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -68069,7 +68069,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -68146,7 +68146,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -68223,7 +68223,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -68241,7 +68241,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -68300,7 +68300,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -68318,7 +68318,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -68377,7 +68377,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -68454,7 +68454,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -68531,7 +68531,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -68608,7 +68608,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -68685,7 +68685,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -68762,7 +68762,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -68839,7 +68839,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -68916,7 +68916,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -68993,7 +68993,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -69070,7 +69070,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -69306,7 +69306,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -69324,7 +69324,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -69383,7 +69383,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -69460,7 +69460,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -69478,7 +69478,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -69537,7 +69537,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -69614,7 +69614,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -69632,7 +69632,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -69691,7 +69691,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -69709,7 +69709,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -69768,7 +69768,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -69845,7 +69845,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -69916,7 +69916,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -69987,7 +69987,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -70005,7 +70005,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -70064,7 +70064,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -70082,7 +70082,7 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -70141,7 +70141,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -70159,7 +70159,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -70218,7 +70218,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -70236,7 +70236,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -70295,7 +70295,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -70372,7 +70372,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -70390,7 +70390,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -70449,7 +70449,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -70467,7 +70467,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -70526,7 +70526,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -70603,7 +70603,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -70621,7 +70621,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -70680,7 +70680,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -70698,7 +70698,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -70872,19 +70872,19 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -70907,7 +70907,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -70966,13 +70966,13 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -70984,13 +70984,13 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>9</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -71043,13 +71043,13 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -71120,13 +71120,13 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -71138,7 +71138,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -71197,13 +71197,13 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -71215,13 +71215,13 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -71274,13 +71274,13 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -71292,13 +71292,13 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -71351,13 +71351,13 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -71369,13 +71369,13 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -71428,13 +71428,13 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -71505,13 +71505,13 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -71529,7 +71529,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -71582,13 +71582,13 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -71659,13 +71659,13 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -71736,13 +71736,13 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -71813,13 +71813,13 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -71831,13 +71831,13 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -71890,13 +71890,13 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -71967,13 +71967,13 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -72044,13 +72044,13 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -72062,13 +72062,13 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -72121,13 +72121,13 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -72198,13 +72198,13 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -72216,13 +72216,13 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -72275,13 +72275,13 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -72352,13 +72352,13 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -72429,13 +72429,13 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -72447,7 +72447,7 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -72506,13 +72506,13 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -72524,13 +72524,13 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -72559,19 +72559,19 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -72624,13 +72624,13 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -72701,13 +72701,13 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -72719,7 +72719,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -72778,13 +72778,13 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -72796,13 +72796,13 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>10</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -72855,13 +72855,13 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -72873,7 +72873,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -72932,13 +72932,13 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -73038,13 +73038,13 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -73115,13 +73115,13 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -73133,7 +73133,7 @@
         <v>7</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -73221,13 +73221,13 @@
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -73245,7 +73245,7 @@
         <v>9</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -73268,13 +73268,13 @@
         <v>6</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
         <v>-1</v>
       </c>
       <c r="X38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>7</v>
@@ -73327,13 +73327,13 @@
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q39">
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -73345,13 +73345,13 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>9</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -73404,13 +73404,13 @@
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -73481,13 +73481,13 @@
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q41">
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -73528,7 +73528,7 @@
         <v>5</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -73581,10 +73581,10 @@
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -73622,7 +73622,7 @@
         <v>5</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S44">
         <v>-1</v>
@@ -73820,10 +73820,10 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -73897,10 +73897,10 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -73974,10 +73974,10 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -74051,10 +74051,10 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -74128,10 +74128,10 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -74205,10 +74205,10 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -74223,10 +74223,10 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -74282,10 +74282,10 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -74303,7 +74303,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -74359,10 +74359,10 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -74377,7 +74377,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -74436,10 +74436,10 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -74513,10 +74513,10 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -74590,10 +74590,10 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -74667,10 +74667,10 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -74688,7 +74688,7 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -74744,10 +74744,10 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -74821,10 +74821,10 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -74839,7 +74839,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -74898,10 +74898,10 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -74975,10 +74975,10 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -74993,10 +74993,10 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -75052,10 +75052,10 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -75073,7 +75073,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -75129,10 +75129,10 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -75150,7 +75150,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -85751,7 +85751,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -85828,7 +85828,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -85905,7 +85905,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -85923,7 +85923,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -85982,7 +85982,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -86000,7 +86000,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -86059,7 +86059,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -86136,7 +86136,7 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -86213,7 +86213,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -86290,7 +86290,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -86367,7 +86367,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -86444,7 +86444,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -86521,7 +86521,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -86539,7 +86539,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -86598,7 +86598,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -86616,7 +86616,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>5</v>
@@ -86675,7 +86675,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -86693,7 +86693,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -86752,7 +86752,7 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -86829,7 +86829,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -86847,7 +86847,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -86906,7 +86906,7 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -86924,7 +86924,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -86983,7 +86983,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -87060,7 +87060,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -87078,7 +87078,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -87137,7 +87137,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -87155,7 +87155,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -87214,7 +87214,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -87291,7 +87291,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -87309,7 +87309,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -87368,7 +87368,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -87386,7 +87386,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -87445,7 +87445,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -87522,7 +87522,7 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -87540,7 +87540,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -87599,7 +87599,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -87676,7 +87676,7 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -87753,7 +87753,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -87830,7 +87830,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -87907,7 +87907,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -87984,7 +87984,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -88061,7 +88061,7 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -88138,7 +88138,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -88360,7 +88360,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>6</v>
@@ -88437,7 +88437,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>6</v>
@@ -88514,7 +88514,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>8</v>
@@ -88591,7 +88591,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -88668,7 +88668,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>9</v>
@@ -88686,7 +88686,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -88745,7 +88745,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -88763,7 +88763,7 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -88822,7 +88822,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>7</v>
@@ -88899,7 +88899,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>9</v>
@@ -88976,7 +88976,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>8</v>
@@ -89053,7 +89053,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -89130,7 +89130,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -89148,7 +89148,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -89207,7 +89207,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>8</v>
@@ -89284,7 +89284,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>8</v>
@@ -89361,7 +89361,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -89438,7 +89438,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>8</v>
@@ -89515,7 +89515,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>7</v>
@@ -89592,7 +89592,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -89669,7 +89669,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>9</v>
@@ -89687,7 +89687,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -89746,7 +89746,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>9</v>
@@ -89823,7 +89823,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -89900,7 +89900,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -89977,7 +89977,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>9</v>
@@ -90054,7 +90054,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -90131,7 +90131,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -90208,7 +90208,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>9</v>
@@ -90285,7 +90285,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>8</v>
@@ -90362,7 +90362,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -90439,7 +90439,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -90516,7 +90516,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>9</v>
@@ -90593,7 +90593,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>10</v>
@@ -90670,7 +90670,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -90747,7 +90747,7 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -90824,7 +90824,7 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -90901,7 +90901,7 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>7</v>
@@ -90919,7 +90919,7 @@
         <v>5</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -90978,7 +90978,7 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
         <v>6</v>
@@ -90996,7 +90996,7 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -91055,7 +91055,7 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>8</v>
@@ -91073,7 +91073,7 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -91132,7 +91132,7 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
         <v>5</v>
@@ -91209,7 +91209,7 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
         <v>7</v>
@@ -91286,7 +91286,7 @@
         <v>-1</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>7</v>
@@ -91363,7 +91363,7 @@
         <v>-1</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
         <v>8</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -12436,7 +12436,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -12454,7 +12454,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -12513,7 +12513,7 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -12531,7 +12531,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -12590,7 +12590,7 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -12608,7 +12608,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -12667,7 +12667,7 @@
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -12744,7 +12744,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -12821,7 +12821,7 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -12898,7 +12898,7 @@
         <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -12975,7 +12975,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -13052,7 +13052,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -13070,7 +13070,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -13129,7 +13129,7 @@
         <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -13147,7 +13147,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -13206,7 +13206,7 @@
         <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -13224,7 +13224,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -13283,7 +13283,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -13360,7 +13360,7 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -13437,7 +13437,7 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -13591,7 +13591,7 @@
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -13668,7 +13668,7 @@
         <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -13745,7 +13745,7 @@
         <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -13822,7 +13822,7 @@
         <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -13899,7 +13899,7 @@
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -13917,7 +13917,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -13976,7 +13976,7 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -13994,7 +13994,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -14053,7 +14053,7 @@
         <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -14130,7 +14130,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -14148,7 +14148,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -14236,7 +14236,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -14254,7 +14254,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -14390,7 +14390,7 @@
         <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -14467,7 +14467,7 @@
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -14544,7 +14544,7 @@
         <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -14621,7 +14621,7 @@
         <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -14698,7 +14698,7 @@
         <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -14775,7 +14775,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -14852,7 +14852,7 @@
         <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -14929,7 +14929,7 @@
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -15006,7 +15006,7 @@
         <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -15083,7 +15083,7 @@
         <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -15101,7 +15101,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -15160,7 +15160,7 @@
         <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>10</v>
@@ -15237,7 +15237,7 @@
         <v>7</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T41">
         <v>10</v>
@@ -15255,7 +15255,7 @@
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -15314,7 +15314,7 @@
         <v>6</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T42">
         <v>5</v>
@@ -15391,7 +15391,7 @@
         <v>7</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
         <v>8</v>
@@ -15409,7 +15409,7 @@
         <v>6</v>
       </c>
       <c r="Y43">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -15468,7 +15468,7 @@
         <v>7</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T44">
         <v>10</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="Y44">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -15545,7 +15545,7 @@
         <v>9</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T45">
         <v>10</v>
@@ -15563,7 +15563,7 @@
         <v>9</v>
       </c>
       <c r="Y45">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -15622,7 +15622,7 @@
         <v>9</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T46">
         <v>9</v>
@@ -15699,7 +15699,7 @@
         <v>8</v>
       </c>
       <c r="S47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T47">
         <v>9</v>
@@ -15776,7 +15776,7 @@
         <v>9</v>
       </c>
       <c r="S48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T48">
         <v>9</v>
@@ -37295,7 +37295,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>7</v>
@@ -37310,10 +37310,10 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -37372,7 +37372,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>7</v>
@@ -37387,10 +37387,10 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -37405,7 +37405,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -37449,7 +37449,7 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -37464,7 +37464,7 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -37526,7 +37526,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -37541,7 +37541,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -37559,7 +37559,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -37603,7 +37603,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -37618,7 +37618,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -37680,7 +37680,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -37695,10 +37695,10 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -37713,7 +37713,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -37757,7 +37757,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -37772,7 +37772,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -37790,7 +37790,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -37834,7 +37834,7 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -37849,10 +37849,10 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -37867,7 +37867,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -37911,7 +37911,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>9</v>
@@ -37926,7 +37926,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -37988,7 +37988,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -38003,7 +38003,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -38080,7 +38080,7 @@
         <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -38142,7 +38142,7 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>9</v>
@@ -38157,10 +38157,10 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -38219,7 +38219,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>9</v>
@@ -38234,7 +38234,7 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -38252,7 +38252,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -38296,7 +38296,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -38311,10 +38311,10 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -38373,7 +38373,7 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>7</v>
@@ -38388,10 +38388,10 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -38450,7 +38450,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -38465,7 +38465,7 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -38483,7 +38483,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -38527,7 +38527,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>7</v>
@@ -38542,10 +38542,10 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -38560,7 +38560,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -38604,7 +38604,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>9</v>
@@ -38619,10 +38619,10 @@
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -38637,7 +38637,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -38681,7 +38681,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>8</v>
@@ -38696,10 +38696,10 @@
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -38758,7 +38758,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -38773,10 +38773,10 @@
         <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -38835,7 +38835,7 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>9</v>
@@ -38850,7 +38850,7 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -38868,7 +38868,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -38912,7 +38912,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>8</v>
@@ -38927,10 +38927,10 @@
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -38989,7 +38989,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -39004,7 +39004,7 @@
         <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -39066,7 +39066,7 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>8</v>
@@ -39081,10 +39081,10 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -39099,7 +39099,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -39143,7 +39143,7 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>7</v>
@@ -39158,7 +39158,7 @@
         <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -39176,7 +39176,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -39220,7 +39220,7 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -39235,7 +39235,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -39297,7 +39297,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>9</v>
@@ -39312,7 +39312,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>6</v>
@@ -39374,7 +39374,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>7</v>
@@ -39389,7 +39389,7 @@
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -39407,7 +39407,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -39451,7 +39451,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>10</v>
@@ -39466,10 +39466,10 @@
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -39484,7 +39484,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -39528,7 +39528,7 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>10</v>
@@ -39543,7 +39543,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -39561,7 +39561,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -39605,7 +39605,7 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>7</v>
@@ -39620,10 +39620,10 @@
         <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>6</v>
@@ -39682,7 +39682,7 @@
         <v>7</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>10</v>
@@ -39697,7 +39697,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -39759,7 +39759,7 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
         <v>8</v>
@@ -39774,7 +39774,7 @@
         <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -39836,7 +39836,7 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>8</v>
@@ -39851,7 +39851,7 @@
         <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>6</v>
@@ -55456,7 +55456,7 @@
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -55474,7 +55474,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -55533,7 +55533,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -55551,7 +55551,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -55610,7 +55610,7 @@
         <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -55687,7 +55687,7 @@
         <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -55764,7 +55764,7 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -55841,7 +55841,7 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -55918,7 +55918,7 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>6</v>
@@ -55936,7 +55936,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -55995,7 +55995,7 @@
         <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -56072,7 +56072,7 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -56149,7 +56149,7 @@
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -56226,7 +56226,7 @@
         <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>6</v>
@@ -56244,7 +56244,7 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -56303,7 +56303,7 @@
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>10</v>
@@ -56380,7 +56380,7 @@
         <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -56398,7 +56398,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -56457,7 +56457,7 @@
         <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>8</v>
@@ -56534,7 +56534,7 @@
         <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -56611,7 +56611,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>5</v>
@@ -56629,7 +56629,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -56688,7 +56688,7 @@
         <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>5</v>
@@ -56765,7 +56765,7 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>5</v>
@@ -56783,7 +56783,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -56842,7 +56842,7 @@
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>6</v>
@@ -56860,7 +56860,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -56919,7 +56919,7 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>8</v>
@@ -56996,7 +56996,7 @@
         <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>7</v>
@@ -57014,7 +57014,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -57073,7 +57073,7 @@
         <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -57208,7 +57208,7 @@
         <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>5</v>
@@ -57285,7 +57285,7 @@
         <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
         <v>5</v>
@@ -57303,7 +57303,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -57362,7 +57362,7 @@
         <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>5</v>
@@ -63926,7 +63926,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -63944,7 +63944,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -64003,7 +64003,7 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -64080,7 +64080,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -64098,7 +64098,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -64157,7 +64157,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -64234,7 +64234,7 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -64311,7 +64311,7 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -64388,7 +64388,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -64465,7 +64465,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -64542,7 +64542,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -64560,7 +64560,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -64619,7 +64619,7 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -64696,7 +64696,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -64714,7 +64714,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -64773,7 +64773,7 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -64850,7 +64850,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -64868,7 +64868,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -64927,7 +64927,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -65004,7 +65004,7 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -65081,7 +65081,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -65158,7 +65158,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -65176,7 +65176,7 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -65235,7 +65235,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -65253,7 +65253,7 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -65312,7 +65312,7 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -65389,7 +65389,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -65466,7 +65466,7 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -65543,7 +65543,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -65620,7 +65620,7 @@
         <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -65697,7 +65697,7 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -65774,7 +65774,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -65792,7 +65792,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -65851,7 +65851,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -65928,7 +65928,7 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -65946,7 +65946,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -66005,7 +66005,7 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -66082,7 +66082,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -66159,7 +66159,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -66177,7 +66177,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -66236,7 +66236,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -66313,7 +66313,7 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -66390,7 +66390,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -66467,7 +66467,7 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -66485,7 +66485,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -66544,7 +66544,7 @@
         <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -66562,7 +66562,7 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -66621,7 +66621,7 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -66698,7 +66698,7 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -66775,7 +66775,7 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -66793,7 +66793,7 @@
         <v>10</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>10</v>
@@ -66852,7 +66852,7 @@
         <v>7</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -66929,7 +66929,7 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -66947,7 +66947,7 @@
         <v>10</v>
       </c>
       <c r="V43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W43">
         <v>9</v>
@@ -75339,7 +75339,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -75357,7 +75357,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -75416,7 +75416,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -75493,7 +75493,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -75570,7 +75570,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -75588,7 +75588,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -75647,7 +75647,7 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -75724,7 +75724,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -75801,7 +75801,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -75878,7 +75878,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -75896,7 +75896,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -75955,7 +75955,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -75973,7 +75973,7 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -76032,7 +76032,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -76109,7 +76109,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -76186,7 +76186,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -76204,7 +76204,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -76263,7 +76263,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -76340,7 +76340,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -76417,7 +76417,7 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -76494,7 +76494,7 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -76512,7 +76512,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -76571,7 +76571,7 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -76589,7 +76589,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -76648,7 +76648,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -76725,7 +76725,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -76743,7 +76743,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -76802,7 +76802,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -76879,7 +76879,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -76956,7 +76956,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -77033,7 +77033,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -77110,7 +77110,7 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -77187,7 +77187,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -77205,7 +77205,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -77264,7 +77264,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -77282,7 +77282,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -77341,7 +77341,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -77359,7 +77359,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -77418,7 +77418,7 @@
         <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -77495,7 +77495,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -77572,7 +77572,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -77590,7 +77590,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -77649,7 +77649,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -77726,7 +77726,7 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -77803,7 +77803,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -77821,7 +77821,7 @@
         <v>9</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>8</v>
@@ -77880,7 +77880,7 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -77957,7 +77957,7 @@
         <v>7</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -78034,7 +78034,7 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -78111,7 +78111,7 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -78188,7 +78188,7 @@
         <v>9</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -78206,7 +78206,7 @@
         <v>8</v>
       </c>
       <c r="V41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -78265,7 +78265,7 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -78342,7 +78342,7 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -78360,7 +78360,7 @@
         <v>8</v>
       </c>
       <c r="V43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W43">
         <v>6</v>
@@ -78419,7 +78419,7 @@
         <v>7</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -78437,7 +78437,7 @@
         <v>9</v>
       </c>
       <c r="V44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W44">
         <v>8</v>
@@ -78496,7 +78496,7 @@
         <v>5</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q45">
         <v>-1</v>
@@ -78573,7 +78573,7 @@
         <v>10</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q46">
         <v>-1</v>
@@ -78650,7 +78650,7 @@
         <v>10</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q47">
         <v>-1</v>
@@ -78863,7 +78863,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -78881,7 +78881,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -78940,7 +78940,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -78958,7 +78958,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -79017,7 +79017,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -79035,7 +79035,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -79094,7 +79094,7 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -79112,7 +79112,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -79171,7 +79171,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -79248,7 +79248,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -79325,7 +79325,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -79402,7 +79402,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -79479,7 +79479,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -79556,7 +79556,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -79633,7 +79633,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -79651,7 +79651,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -79710,7 +79710,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -79728,7 +79728,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -79787,7 +79787,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -79805,7 +79805,7 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -79864,7 +79864,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -79882,7 +79882,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -79941,7 +79941,7 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -80018,7 +80018,7 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -80095,7 +80095,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -80172,7 +80172,7 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -80190,7 +80190,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -80249,7 +80249,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -80326,7 +80326,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -80403,7 +80403,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -80480,7 +80480,7 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -80557,7 +80557,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -80575,7 +80575,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -80634,7 +80634,7 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -80711,7 +80711,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -80788,7 +80788,7 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -80865,7 +80865,7 @@
         <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -80942,7 +80942,7 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -81019,7 +81019,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -81096,7 +81096,7 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -81173,7 +81173,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -81250,7 +81250,7 @@
         <v>7</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -81327,7 +81327,7 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -81345,7 +81345,7 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -81404,7 +81404,7 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -81422,7 +81422,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -81481,7 +81481,7 @@
         <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -81558,7 +81558,7 @@
         <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -81635,7 +81635,7 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -81653,7 +81653,7 @@
         <v>10</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W40">
         <v>7</v>
@@ -81712,7 +81712,7 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -81789,7 +81789,7 @@
         <v>5</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -81866,7 +81866,7 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -81884,7 +81884,7 @@
         <v>10</v>
       </c>
       <c r="V43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W43">
         <v>10</v>
@@ -81943,7 +81943,7 @@
         <v>9</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -82020,7 +82020,7 @@
         <v>10</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q45">
         <v>-1</v>
@@ -82038,7 +82038,7 @@
         <v>10</v>
       </c>
       <c r="V45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W45">
         <v>10</v>
@@ -82097,7 +82097,7 @@
         <v>10</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q46">
         <v>-1</v>
@@ -82115,7 +82115,7 @@
         <v>10</v>
       </c>
       <c r="V46">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W46">
         <v>7</v>
@@ -82310,7 +82310,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -82387,7 +82387,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -82464,7 +82464,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -82541,7 +82541,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -82618,7 +82618,7 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -82636,7 +82636,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -82695,7 +82695,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -82772,7 +82772,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -82849,7 +82849,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -82926,7 +82926,7 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -82944,7 +82944,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -83003,7 +83003,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -83080,7 +83080,7 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -83157,7 +83157,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -83234,7 +83234,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -83311,7 +83311,7 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -83388,7 +83388,7 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -83465,7 +83465,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -83483,7 +83483,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -83542,7 +83542,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -83619,7 +83619,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -83696,7 +83696,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -83714,7 +83714,7 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -83773,7 +83773,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -83791,7 +83791,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -83850,7 +83850,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -83927,7 +83927,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -84004,7 +84004,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -84022,7 +84022,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -84081,7 +84081,7 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -84158,7 +84158,7 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -84235,7 +84235,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -84253,7 +84253,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -84312,7 +84312,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -84389,7 +84389,7 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -84466,7 +84466,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -84543,7 +84543,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -84620,7 +84620,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -84697,7 +84697,7 @@
         <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -84774,7 +84774,7 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -84792,7 +84792,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -84851,7 +84851,7 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -84869,7 +84869,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -84928,7 +84928,7 @@
         <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -85005,7 +85005,7 @@
         <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -85082,7 +85082,7 @@
         <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -85159,7 +85159,7 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -85236,7 +85236,7 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -85313,7 +85313,7 @@
         <v>7</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -85331,7 +85331,7 @@
         <v>9</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>8</v>
@@ -85390,7 +85390,7 @@
         <v>10</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -85408,7 +85408,7 @@
         <v>10</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W44">
         <v>9</v>
@@ -85467,7 +85467,7 @@
         <v>10</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q45">
         <v>-1</v>
@@ -85485,7 +85485,7 @@
         <v>8</v>
       </c>
       <c r="V45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W45">
         <v>8</v>
@@ -85544,7 +85544,7 @@
         <v>10</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q46">
         <v>-1</v>
@@ -85562,7 +85562,7 @@
         <v>9</v>
       </c>
       <c r="V46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W46">
         <v>5</v>
@@ -91582,7 +91582,7 @@
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -91600,7 +91600,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -91659,7 +91659,7 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -91677,7 +91677,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -91736,7 +91736,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -91754,7 +91754,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -91813,7 +91813,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -91890,7 +91890,7 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -91908,7 +91908,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -91967,7 +91967,7 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -92044,7 +92044,7 @@
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -92121,7 +92121,7 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -92139,7 +92139,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -92198,7 +92198,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -92216,7 +92216,7 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -92275,7 +92275,7 @@
         <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -92352,7 +92352,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -92370,7 +92370,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -92429,7 +92429,7 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -92447,7 +92447,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -92506,7 +92506,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -92583,7 +92583,7 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -92601,7 +92601,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -92660,7 +92660,7 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -92737,7 +92737,7 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -92755,7 +92755,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -92814,7 +92814,7 @@
         <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -92891,7 +92891,7 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -92968,7 +92968,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -93045,7 +93045,7 @@
         <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -93122,7 +93122,7 @@
         <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -93199,7 +93199,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -93276,7 +93276,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -93353,7 +93353,7 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -93430,7 +93430,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -93448,7 +93448,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -93507,7 +93507,7 @@
         <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -93525,7 +93525,7 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -93584,7 +93584,7 @@
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -4014,7 +4014,7 @@
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -4091,7 +4091,7 @@
         <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>7</v>
@@ -4245,7 +4245,7 @@
         <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -4322,7 +4322,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>7</v>
@@ -4340,7 +4340,7 @@
         <v>7</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -4399,7 +4399,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -4417,7 +4417,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -4476,7 +4476,7 @@
         <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>7</v>
@@ -4553,7 +4553,7 @@
         <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>5</v>
@@ -4630,7 +4630,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>7</v>
@@ -4707,7 +4707,7 @@
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -4784,7 +4784,7 @@
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -4802,7 +4802,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -4861,7 +4861,7 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -4938,7 +4938,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -5015,7 +5015,7 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>7</v>
@@ -5092,7 +5092,7 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -5110,7 +5110,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -5169,7 +5169,7 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>7</v>
@@ -5246,7 +5246,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -5323,7 +5323,7 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>6</v>
@@ -5400,7 +5400,7 @@
         <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -5418,7 +5418,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -5477,7 +5477,7 @@
         <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -5554,7 +5554,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>5</v>
@@ -5631,7 +5631,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -5708,7 +5708,7 @@
         <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -5785,7 +5785,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>6</v>
@@ -5803,7 +5803,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -5862,7 +5862,7 @@
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>7</v>
@@ -5880,7 +5880,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -5939,7 +5939,7 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>9</v>
@@ -6016,7 +6016,7 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -6093,7 +6093,7 @@
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -6170,7 +6170,7 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>8</v>
@@ -6188,7 +6188,7 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>8</v>
@@ -6247,7 +6247,7 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>10</v>
@@ -6265,7 +6265,7 @@
         <v>6</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -6324,7 +6324,7 @@
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -6401,7 +6401,7 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>8</v>
@@ -6478,7 +6478,7 @@
         <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -6555,7 +6555,7 @@
         <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>8</v>
@@ -6774,7 +6774,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -6851,7 +6851,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -6928,7 +6928,7 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -7005,7 +7005,7 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -7082,7 +7082,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -7159,7 +7159,7 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -7236,7 +7236,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -7254,7 +7254,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -7313,7 +7313,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -7390,7 +7390,7 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -7467,7 +7467,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -7544,7 +7544,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -7621,7 +7621,7 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -7698,7 +7698,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -7775,7 +7775,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -7852,7 +7852,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -7929,7 +7929,7 @@
         <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -8006,7 +8006,7 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -8083,7 +8083,7 @@
         <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -8101,7 +8101,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -8160,7 +8160,7 @@
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -8237,7 +8237,7 @@
         <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -8255,7 +8255,7 @@
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -8314,7 +8314,7 @@
         <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -8332,7 +8332,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -8391,7 +8391,7 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -8468,7 +8468,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -8545,7 +8545,7 @@
         <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -8563,7 +8563,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -8622,7 +8622,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -8699,7 +8699,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -8776,7 +8776,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -8853,7 +8853,7 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -8930,7 +8930,7 @@
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -9007,7 +9007,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -9084,7 +9084,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -9161,7 +9161,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -9238,7 +9238,7 @@
         <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -9256,7 +9256,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -9315,7 +9315,7 @@
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -9469,7 +9469,7 @@
         <v>5</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T39">
         <v>5</v>
@@ -9546,7 +9546,7 @@
         <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>10</v>
@@ -9623,7 +9623,7 @@
         <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>10</v>
@@ -9700,7 +9700,7 @@
         <v>8</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>9</v>
@@ -9718,7 +9718,7 @@
         <v>8</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9913,7 +9913,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -9990,7 +9990,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -10067,7 +10067,7 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -10144,7 +10144,7 @@
         <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -10162,7 +10162,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -10221,7 +10221,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -10298,7 +10298,7 @@
         <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -10375,7 +10375,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -10452,7 +10452,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -10470,7 +10470,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -10529,7 +10529,7 @@
         <v>3</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -10606,7 +10606,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -10624,7 +10624,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -10683,7 +10683,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -10914,7 +10914,7 @@
         <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>6</v>
@@ -10932,7 +10932,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -10991,7 +10991,7 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -11068,7 +11068,7 @@
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -11086,7 +11086,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -11145,7 +11145,7 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -11222,7 +11222,7 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>6</v>
@@ -11240,7 +11240,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -11299,7 +11299,7 @@
         <v>3</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -11376,7 +11376,7 @@
         <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -11394,7 +11394,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -11453,7 +11453,7 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -11530,7 +11530,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -11607,7 +11607,7 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -11684,7 +11684,7 @@
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -11761,7 +11761,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -11838,7 +11838,7 @@
         <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -11856,7 +11856,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -11915,7 +11915,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -11992,7 +11992,7 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -12069,7 +12069,7 @@
         <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -12087,7 +12087,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -12146,7 +12146,7 @@
         <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>6</v>
@@ -12164,7 +12164,7 @@
         <v>5</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -12223,7 +12223,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -12421,7 +12421,7 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>8</v>
@@ -12498,7 +12498,7 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -12575,7 +12575,7 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -12593,7 +12593,7 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -12652,7 +12652,7 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>7</v>
@@ -12729,7 +12729,7 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -12806,7 +12806,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>9</v>
@@ -12824,7 +12824,7 @@
         <v>7</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -12883,7 +12883,7 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -12960,7 +12960,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -13037,7 +13037,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>8</v>
@@ -13114,7 +13114,7 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>8</v>
@@ -13268,7 +13268,7 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>7</v>
@@ -13345,7 +13345,7 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>7</v>
@@ -13422,7 +13422,7 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -13440,7 +13440,7 @@
         <v>7</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>6</v>
@@ -13499,7 +13499,7 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>7</v>
@@ -13517,7 +13517,7 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -13576,7 +13576,7 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -13653,7 +13653,7 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>7</v>
@@ -13730,7 +13730,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>7</v>
@@ -13807,7 +13807,7 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -13884,7 +13884,7 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -13961,7 +13961,7 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -14038,7 +14038,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -14115,7 +14115,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>7</v>
@@ -14221,7 +14221,7 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
         <v>5</v>
@@ -14298,7 +14298,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>5</v>
@@ -14375,7 +14375,7 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -14393,7 +14393,7 @@
         <v>5</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -14452,7 +14452,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -14470,7 +14470,7 @@
         <v>7</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -14529,7 +14529,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>7</v>
@@ -14606,7 +14606,7 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>7</v>
@@ -14683,7 +14683,7 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>7</v>
@@ -14701,7 +14701,7 @@
         <v>8</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>6</v>
@@ -14760,7 +14760,7 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>10</v>
@@ -14837,7 +14837,7 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -14914,7 +14914,7 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>9</v>
@@ -14991,7 +14991,7 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>8</v>
@@ -15068,7 +15068,7 @@
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -15145,7 +15145,7 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>7</v>
@@ -15222,7 +15222,7 @@
         <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>5</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -15376,7 +15376,7 @@
         <v>7</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>7</v>
@@ -15394,7 +15394,7 @@
         <v>6</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U43">
         <v>6</v>
@@ -15453,7 +15453,7 @@
         <v>5</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O44">
         <v>7</v>
@@ -15471,7 +15471,7 @@
         <v>8</v>
       </c>
       <c r="T44">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U44">
         <v>8</v>
@@ -15530,7 +15530,7 @@
         <v>9</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O45">
         <v>7</v>
@@ -15607,7 +15607,7 @@
         <v>6</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O46">
         <v>7</v>
@@ -15684,7 +15684,7 @@
         <v>10</v>
       </c>
       <c r="N47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O47">
         <v>7</v>
@@ -15761,7 +15761,7 @@
         <v>6</v>
       </c>
       <c r="N48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O48">
         <v>6</v>
@@ -34858,7 +34858,7 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>8</v>
@@ -34876,7 +34876,7 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -34935,7 +34935,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -35012,7 +35012,7 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -35089,7 +35089,7 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -35166,7 +35166,7 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -35243,7 +35243,7 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -35320,7 +35320,7 @@
         <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -35338,7 +35338,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -35397,7 +35397,7 @@
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -35474,7 +35474,7 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -35492,7 +35492,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -35551,7 +35551,7 @@
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>9</v>
@@ -35628,7 +35628,7 @@
         <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -35705,7 +35705,7 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -35782,7 +35782,7 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>5</v>
@@ -35859,7 +35859,7 @@
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>7</v>
@@ -35936,7 +35936,7 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>5</v>
@@ -36013,7 +36013,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -36090,7 +36090,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -36108,7 +36108,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -36167,7 +36167,7 @@
         <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>8</v>
@@ -36244,7 +36244,7 @@
         <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -36321,7 +36321,7 @@
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -36398,7 +36398,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>6</v>
@@ -36475,7 +36475,7 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>7</v>
@@ -36493,7 +36493,7 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -36552,7 +36552,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>6</v>
@@ -36629,7 +36629,7 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>7</v>
@@ -36647,7 +36647,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -36706,7 +36706,7 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>7</v>
@@ -36724,7 +36724,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -36783,7 +36783,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>6</v>
@@ -36801,7 +36801,7 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -36860,7 +36860,7 @@
         <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
         <v>7</v>
@@ -36937,7 +36937,7 @@
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>8</v>
@@ -37014,7 +37014,7 @@
         <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>6</v>
@@ -37032,7 +37032,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -37091,7 +37091,7 @@
         <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>8</v>
@@ -52362,7 +52362,7 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>9</v>
@@ -52380,7 +52380,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -52439,7 +52439,7 @@
         <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -52516,7 +52516,7 @@
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>7</v>
@@ -52593,7 +52593,7 @@
         <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -52670,7 +52670,7 @@
         <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -52688,7 +52688,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -52747,7 +52747,7 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -52824,7 +52824,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -52901,7 +52901,7 @@
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -52978,7 +52978,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>10</v>
@@ -53055,7 +53055,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -53073,7 +53073,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -53132,7 +53132,7 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>7</v>
@@ -53209,7 +53209,7 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -53286,7 +53286,7 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -53363,7 +53363,7 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>7</v>
@@ -53381,7 +53381,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -53440,7 +53440,7 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -53517,7 +53517,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -53594,7 +53594,7 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -53671,7 +53671,7 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>9</v>
@@ -53748,7 +53748,7 @@
         <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -53766,7 +53766,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -53825,7 +53825,7 @@
         <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -53872,7 +53872,7 @@
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -53931,7 +53931,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -54008,7 +54008,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -54026,7 +54026,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -54162,7 +54162,7 @@
         <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -54239,7 +54239,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>5</v>
@@ -54257,7 +54257,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -54316,7 +54316,7 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -54393,7 +54393,7 @@
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>7</v>
@@ -54411,7 +54411,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -54470,7 +54470,7 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -54488,7 +54488,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -54547,7 +54547,7 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>8</v>
@@ -54624,7 +54624,7 @@
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -54701,7 +54701,7 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
@@ -54778,7 +54778,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>6</v>
@@ -54796,7 +54796,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -54855,7 +54855,7 @@
         <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
         <v>7</v>
@@ -54873,7 +54873,7 @@
         <v>6</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -54932,7 +54932,7 @@
         <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
         <v>6</v>
@@ -55009,7 +55009,7 @@
         <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>7</v>
@@ -55086,7 +55086,7 @@
         <v>5</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
         <v>9</v>
@@ -55163,7 +55163,7 @@
         <v>7</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R41">
         <v>8</v>
@@ -55181,7 +55181,7 @@
         <v>7</v>
       </c>
       <c r="W41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>6</v>
@@ -55240,7 +55240,7 @@
         <v>9</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>10</v>
@@ -60169,7 +60169,7 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -60187,7 +60187,7 @@
         <v>5</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -60246,7 +60246,7 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -60323,7 +60323,7 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>9</v>
@@ -60400,7 +60400,7 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -60418,7 +60418,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -60477,7 +60477,7 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -60554,7 +60554,7 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -60572,7 +60572,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -60631,7 +60631,7 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -60708,7 +60708,7 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -60785,7 +60785,7 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -60862,7 +60862,7 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -60939,7 +60939,7 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -61016,7 +61016,7 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -61034,7 +61034,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -61093,7 +61093,7 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -61170,7 +61170,7 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -61247,7 +61247,7 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -67136,7 +67136,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -67213,7 +67213,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -67290,7 +67290,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -67308,7 +67308,7 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -67367,7 +67367,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -67444,7 +67444,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -67521,7 +67521,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -67598,7 +67598,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -67616,7 +67616,7 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -67675,7 +67675,7 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -67752,7 +67752,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -67829,7 +67829,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -67906,7 +67906,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -67983,7 +67983,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -68060,7 +68060,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -68137,7 +68137,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -68214,7 +68214,7 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -68291,7 +68291,7 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -68309,7 +68309,7 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -68368,7 +68368,7 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>10</v>
@@ -68445,7 +68445,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>8</v>
@@ -68522,7 +68522,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -68599,7 +68599,7 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -68676,7 +68676,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>8</v>
@@ -68753,7 +68753,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -68830,7 +68830,7 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>7</v>
@@ -68907,7 +68907,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>10</v>
@@ -68925,7 +68925,7 @@
         <v>7</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -68984,7 +68984,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -69061,7 +69061,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -69079,7 +69079,7 @@
         <v>6</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -69114,7 +69114,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -75345,7 +75345,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -75422,7 +75422,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -75499,7 +75499,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -75576,7 +75576,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -75594,7 +75594,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -75653,7 +75653,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>7</v>
@@ -75671,7 +75671,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -75730,7 +75730,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -75748,7 +75748,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -75807,7 +75807,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>7</v>
@@ -75825,7 +75825,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -75884,7 +75884,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>5</v>
@@ -75902,7 +75902,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -75961,7 +75961,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -76038,7 +76038,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>6</v>
@@ -76115,7 +76115,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>7</v>
@@ -76192,7 +76192,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>6</v>
@@ -76269,7 +76269,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>7</v>
@@ -76346,7 +76346,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>10</v>
@@ -76423,7 +76423,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>7</v>
@@ -76500,7 +76500,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>7</v>
@@ -76518,7 +76518,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -76577,7 +76577,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -76595,7 +76595,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -76654,7 +76654,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>6</v>
@@ -76731,7 +76731,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>8</v>
@@ -76808,7 +76808,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -76885,7 +76885,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>10</v>
@@ -76962,7 +76962,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -77039,7 +77039,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>8</v>
@@ -77116,7 +77116,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>10</v>
@@ -77193,7 +77193,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>8</v>
@@ -77211,7 +77211,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -77270,7 +77270,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>8</v>
@@ -77347,7 +77347,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>7</v>
@@ -77365,7 +77365,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -77424,7 +77424,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>9</v>
@@ -77442,7 +77442,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -77501,7 +77501,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>7</v>
@@ -77578,7 +77578,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>9</v>
@@ -77655,7 +77655,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
         <v>7</v>
@@ -77732,7 +77732,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>8</v>
@@ -77809,7 +77809,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
         <v>6</v>
@@ -77886,7 +77886,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
         <v>6</v>
@@ -77963,7 +77963,7 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
         <v>6</v>
@@ -78040,7 +78040,7 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>10</v>
@@ -78117,7 +78117,7 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
         <v>8</v>
@@ -78194,7 +78194,7 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
         <v>7</v>
@@ -78271,7 +78271,7 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
         <v>10</v>
@@ -78289,7 +78289,7 @@
         <v>10</v>
       </c>
       <c r="X42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>9</v>
@@ -78348,7 +78348,7 @@
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S43">
         <v>8</v>
@@ -78425,7 +78425,7 @@
         <v>-1</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S44">
         <v>8</v>
@@ -78443,7 +78443,7 @@
         <v>8</v>
       </c>
       <c r="X44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y44">
         <v>8</v>
@@ -78502,7 +78502,7 @@
         <v>-1</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S45">
         <v>5</v>
@@ -78520,7 +78520,7 @@
         <v>5</v>
       </c>
       <c r="X45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y45">
         <v>5</v>
@@ -78579,7 +78579,7 @@
         <v>-1</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S46">
         <v>10</v>
@@ -78597,7 +78597,7 @@
         <v>9</v>
       </c>
       <c r="X46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y46">
         <v>9</v>
@@ -78656,7 +78656,7 @@
         <v>-1</v>
       </c>
       <c r="R47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S47">
         <v>10</v>
@@ -78869,7 +78869,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>7</v>
@@ -78887,7 +78887,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -78946,7 +78946,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>7</v>
@@ -78964,7 +78964,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -79023,7 +79023,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -79041,7 +79041,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -79100,7 +79100,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -79118,7 +79118,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -79177,7 +79177,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>6</v>
@@ -79254,7 +79254,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>7</v>
@@ -79272,7 +79272,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -79331,7 +79331,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -79408,7 +79408,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -79485,7 +79485,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -79503,7 +79503,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -79562,7 +79562,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -79639,7 +79639,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -79716,7 +79716,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>7</v>
@@ -79793,7 +79793,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>7</v>
@@ -79870,7 +79870,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -79947,7 +79947,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -80024,7 +80024,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -80101,7 +80101,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -80119,7 +80119,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -80178,7 +80178,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -80196,7 +80196,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -80255,7 +80255,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>6</v>
@@ -80273,7 +80273,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -80332,7 +80332,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -80409,7 +80409,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>10</v>
@@ -80427,7 +80427,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -80486,7 +80486,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>5</v>
@@ -80504,7 +80504,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -80563,7 +80563,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -80640,7 +80640,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>10</v>
@@ -80717,7 +80717,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>9</v>
@@ -80794,7 +80794,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>6</v>
@@ -80812,7 +80812,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -80871,7 +80871,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>5</v>
@@ -80948,7 +80948,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
         <v>5</v>
@@ -81025,7 +81025,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>9</v>
@@ -81043,7 +81043,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -81102,7 +81102,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>5</v>
@@ -81179,7 +81179,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>7</v>
@@ -81256,7 +81256,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>5</v>
@@ -81274,7 +81274,7 @@
         <v>5</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -81333,7 +81333,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
         <v>7</v>
@@ -81351,7 +81351,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -81410,7 +81410,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>7</v>
@@ -81487,7 +81487,7 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
         <v>6</v>
@@ -81505,7 +81505,7 @@
         <v>8</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>6</v>
@@ -81564,7 +81564,7 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
         <v>7</v>
@@ -81582,7 +81582,7 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -81641,7 +81641,7 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
         <v>8</v>
@@ -81659,7 +81659,7 @@
         <v>7</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -81718,7 +81718,7 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S41">
         <v>6</v>
@@ -81736,7 +81736,7 @@
         <v>8</v>
       </c>
       <c r="X41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>7</v>
@@ -81795,7 +81795,7 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S42">
         <v>5</v>
@@ -81872,7 +81872,7 @@
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S43">
         <v>8</v>
@@ -81949,7 +81949,7 @@
         <v>-1</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S44">
         <v>6</v>
@@ -82026,7 +82026,7 @@
         <v>-1</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S45">
         <v>10</v>
@@ -82103,7 +82103,7 @@
         <v>-1</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S46">
         <v>6</v>
@@ -82121,7 +82121,7 @@
         <v>7</v>
       </c>
       <c r="X46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y46">
         <v>7</v>
@@ -85766,7 +85766,7 @@
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -85784,7 +85784,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -85843,7 +85843,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -85920,7 +85920,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -85938,7 +85938,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -85997,7 +85997,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -86015,7 +86015,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -86074,7 +86074,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -86151,7 +86151,7 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -86169,7 +86169,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -86228,7 +86228,7 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -86305,7 +86305,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -86382,7 +86382,7 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -86459,7 +86459,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -86536,7 +86536,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -86613,7 +86613,7 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -86690,7 +86690,7 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -86708,7 +86708,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -86767,7 +86767,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -86844,7 +86844,7 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -86862,7 +86862,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -86921,7 +86921,7 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>5</v>
@@ -86939,7 +86939,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -86998,7 +86998,7 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -87075,7 +87075,7 @@
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -87093,7 +87093,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -87152,7 +87152,7 @@
         <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -87229,7 +87229,7 @@
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -87306,7 +87306,7 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -87324,7 +87324,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -87383,7 +87383,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -87460,7 +87460,7 @@
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -87537,7 +87537,7 @@
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -87614,7 +87614,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -87632,7 +87632,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -87691,7 +87691,7 @@
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -87709,7 +87709,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -87768,7 +87768,7 @@
         <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -87845,7 +87845,7 @@
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -87863,7 +87863,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -87922,7 +87922,7 @@
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -87999,7 +87999,7 @@
         <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -88017,7 +88017,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -88076,7 +88076,7 @@
         <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -88153,7 +88153,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -88366,7 +88366,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -88443,7 +88443,7 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -88461,7 +88461,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -88520,7 +88520,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -88538,7 +88538,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -88597,7 +88597,7 @@
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -88674,7 +88674,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -88751,7 +88751,7 @@
         <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -88828,7 +88828,7 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -88905,7 +88905,7 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -88982,7 +88982,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -89059,7 +89059,7 @@
         <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -89136,7 +89136,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -89213,7 +89213,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -89290,7 +89290,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -89367,7 +89367,7 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -89444,7 +89444,7 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -89521,7 +89521,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -89598,7 +89598,7 @@
         <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -89675,7 +89675,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -89752,7 +89752,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -89829,7 +89829,7 @@
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -89906,7 +89906,7 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -89983,7 +89983,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -90060,7 +90060,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -90137,7 +90137,7 @@
         <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -90214,7 +90214,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -90291,7 +90291,7 @@
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -90368,7 +90368,7 @@
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -90445,7 +90445,7 @@
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -90522,7 +90522,7 @@
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -90599,7 +90599,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -90676,7 +90676,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -90753,7 +90753,7 @@
         <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -90830,7 +90830,7 @@
         <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -90907,7 +90907,7 @@
         <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
         <v>8</v>
@@ -90925,7 +90925,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -90984,7 +90984,7 @@
         <v>6</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -91002,7 +91002,7 @@
         <v>8</v>
       </c>
       <c r="Y38">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -91061,7 +91061,7 @@
         <v>8</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>9</v>
@@ -91079,7 +91079,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -91138,7 +91138,7 @@
         <v>5</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -91215,7 +91215,7 @@
         <v>7</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>9</v>
@@ -91292,7 +91292,7 @@
         <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>9</v>
@@ -91369,7 +91369,7 @@
         <v>8</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T43">
         <v>9</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -16011,7 +16011,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -16100,7 +16100,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -16189,7 +16189,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -16278,7 +16278,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -16367,7 +16367,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -16456,7 +16456,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -16545,7 +16545,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -16634,7 +16634,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -16723,7 +16723,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -16901,7 +16901,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -16922,7 +16922,7 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -16990,7 +16990,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -17079,7 +17079,7 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -17168,7 +17168,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -17257,7 +17257,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -17346,7 +17346,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -17435,7 +17435,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -17524,7 +17524,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -17613,7 +17613,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -17702,7 +17702,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -17723,7 +17723,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -17743,7 +17743,7 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>7</v>
@@ -17785,13 +17785,13 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -17806,7 +17806,7 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -17880,7 +17880,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -17969,7 +17969,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -18058,7 +18058,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -18147,7 +18147,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -18236,7 +18236,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -18325,7 +18325,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -18414,7 +18414,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -18435,7 +18435,7 @@
         <v>7</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -18455,7 +18455,7 @@
         <v>7</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>8</v>
@@ -18476,7 +18476,7 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>9</v>
@@ -18497,13 +18497,13 @@
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -18518,13 +18518,13 @@
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA32">
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -18592,7 +18592,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -18681,7 +18681,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -18894,7 +18894,7 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>9</v>
@@ -18971,7 +18971,7 @@
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -18989,7 +18989,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -19048,7 +19048,7 @@
         <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>9</v>
@@ -19066,7 +19066,7 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -19125,7 +19125,7 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>9</v>
@@ -19202,7 +19202,7 @@
         <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>9</v>
@@ -19220,7 +19220,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -19279,7 +19279,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>9</v>
@@ -19297,7 +19297,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -19356,7 +19356,7 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>9</v>
@@ -19433,7 +19433,7 @@
         <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>9</v>
@@ -19510,7 +19510,7 @@
         <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -19528,7 +19528,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -19587,7 +19587,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>9</v>
@@ -19605,7 +19605,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -19664,7 +19664,7 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -19741,7 +19741,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>9</v>
@@ -19759,7 +19759,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -19818,7 +19818,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -19895,7 +19895,7 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -19913,7 +19913,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -19972,7 +19972,7 @@
         <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>9</v>
@@ -20049,7 +20049,7 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>9</v>
@@ -20067,7 +20067,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -20126,7 +20126,7 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>9</v>
@@ -20203,7 +20203,7 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>9</v>
@@ -20221,7 +20221,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -20280,7 +20280,7 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>10</v>
@@ -20357,7 +20357,7 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -20375,7 +20375,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -20434,7 +20434,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -20511,7 +20511,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>9</v>
@@ -20588,7 +20588,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -20606,7 +20606,7 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -20665,7 +20665,7 @@
         <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -20683,7 +20683,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -20742,7 +20742,7 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>9</v>
@@ -20760,7 +20760,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -20819,7 +20819,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>9</v>
@@ -20837,7 +20837,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -20896,7 +20896,7 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>9</v>
@@ -20914,7 +20914,7 @@
         <v>5</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -20973,7 +20973,7 @@
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -21050,7 +21050,7 @@
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>9</v>
@@ -21127,7 +21127,7 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -21145,7 +21145,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -21204,7 +21204,7 @@
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
         <v>9</v>
@@ -21281,7 +21281,7 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -21358,7 +21358,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>9</v>
@@ -21435,7 +21435,7 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>9</v>
@@ -21512,7 +21512,7 @@
         <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>9</v>
@@ -21728,7 +21728,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -21805,7 +21805,7 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>7</v>
@@ -21823,7 +21823,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -21882,7 +21882,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -21900,7 +21900,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -21959,7 +21959,7 @@
         <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>7</v>
@@ -21977,7 +21977,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -22036,7 +22036,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -22113,7 +22113,7 @@
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -22190,7 +22190,7 @@
         <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>8</v>
@@ -22267,7 +22267,7 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>9</v>
@@ -22285,7 +22285,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -22344,7 +22344,7 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -22362,7 +22362,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -22421,7 +22421,7 @@
         <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>10</v>
@@ -22439,7 +22439,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -22498,7 +22498,7 @@
         <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -22516,7 +22516,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -22575,7 +22575,7 @@
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>9</v>
@@ -22652,7 +22652,7 @@
         <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -22670,7 +22670,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -22699,7 +22699,7 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>5</v>
@@ -22717,7 +22717,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -22729,13 +22729,13 @@
         <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>5</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -22806,7 +22806,7 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>8</v>
@@ -22824,7 +22824,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -22883,7 +22883,7 @@
         <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>10</v>
@@ -22960,7 +22960,7 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>10</v>
@@ -23037,7 +23037,7 @@
         <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -23055,7 +23055,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -23114,7 +23114,7 @@
         <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>9</v>
@@ -23132,7 +23132,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -23191,7 +23191,7 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -23209,7 +23209,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -23268,7 +23268,7 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -23475,7 +23475,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -23552,7 +23552,7 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -23629,7 +23629,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>9</v>
@@ -23647,7 +23647,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -23706,7 +23706,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -23724,7 +23724,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -23783,7 +23783,7 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -23801,7 +23801,7 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -23860,7 +23860,7 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -23937,7 +23937,7 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -24014,7 +24014,7 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -24091,7 +24091,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -24109,7 +24109,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -24168,7 +24168,7 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -24186,7 +24186,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -24245,7 +24245,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -24322,7 +24322,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -24399,7 +24399,7 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -24476,7 +24476,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -24494,7 +24494,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -24553,7 +24553,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -24630,7 +24630,7 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>9</v>
@@ -24707,7 +24707,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -24784,7 +24784,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -24861,7 +24861,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -24938,7 +24938,7 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -24956,7 +24956,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -25015,7 +25015,7 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -25033,7 +25033,7 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -25092,7 +25092,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -25169,7 +25169,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -25246,7 +25246,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -25400,7 +25400,7 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>9</v>
@@ -25418,7 +25418,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -25477,13 +25477,13 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>9</v>
@@ -25554,7 +25554,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -25631,7 +25631,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -25708,7 +25708,7 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -25785,7 +25785,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -25820,7 +25820,7 @@
         <v>603</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>7</v>
@@ -25838,7 +25838,7 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>7</v>
@@ -25856,13 +25856,13 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -25874,13 +25874,13 @@
         <v>8</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>7</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -25939,7 +25939,7 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -26016,7 +26016,7 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -26093,7 +26093,7 @@
         <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -26111,7 +26111,7 @@
         <v>8</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>9</v>
@@ -26170,7 +26170,7 @@
         <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>9</v>
@@ -26247,7 +26247,7 @@
         <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>10</v>
@@ -26265,7 +26265,7 @@
         <v>7</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -26491,7 +26491,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -26580,7 +26580,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -26601,7 +26601,7 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -26669,7 +26669,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -26758,7 +26758,7 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -26847,7 +26847,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -26936,7 +26936,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -26957,7 +26957,7 @@
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -27025,7 +27025,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -27114,7 +27114,7 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -27203,7 +27203,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -27292,7 +27292,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -27313,7 +27313,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -27381,7 +27381,7 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -27402,7 +27402,7 @@
         <v>6</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -27470,7 +27470,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -27491,7 +27491,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -27559,7 +27559,7 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -27648,7 +27648,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -27669,7 +27669,7 @@
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>9</v>
@@ -27737,7 +27737,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -27826,7 +27826,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -27915,7 +27915,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -27936,7 +27936,7 @@
         <v>10</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>9</v>
@@ -28004,7 +28004,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -28093,7 +28093,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -28182,7 +28182,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -28203,7 +28203,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -28271,7 +28271,7 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -28292,7 +28292,7 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -28360,7 +28360,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -28449,7 +28449,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -28538,7 +28538,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -28627,7 +28627,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -28716,7 +28716,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -28737,7 +28737,7 @@
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -28805,7 +28805,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -28826,7 +28826,7 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>7</v>
@@ -28894,7 +28894,7 @@
         <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>2</v>
@@ -28983,7 +28983,7 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -29196,10 +29196,10 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -29273,10 +29273,10 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -29291,7 +29291,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -29350,10 +29350,10 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -29427,10 +29427,10 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -29504,10 +29504,10 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -29581,10 +29581,10 @@
         <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -29658,10 +29658,10 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>10</v>
@@ -29735,10 +29735,10 @@
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -29753,7 +29753,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -29812,10 +29812,10 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -29889,10 +29889,10 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -29907,7 +29907,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -29966,10 +29966,10 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>10</v>
@@ -30043,10 +30043,10 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>5</v>
@@ -30061,7 +30061,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -30120,10 +30120,10 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -30138,10 +30138,10 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -30197,10 +30197,10 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>7</v>
@@ -30215,7 +30215,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -30274,10 +30274,10 @@
         <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -30292,10 +30292,10 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -30351,10 +30351,10 @@
         <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>6</v>
@@ -30369,10 +30369,10 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -30428,10 +30428,10 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -30446,7 +30446,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -30505,10 +30505,10 @@
         <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -30523,10 +30523,10 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -30582,10 +30582,10 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>10</v>
@@ -30659,10 +30659,10 @@
         <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -30677,7 +30677,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -30736,10 +30736,10 @@
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>10</v>
@@ -30813,10 +30813,10 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>8</v>
@@ -30831,10 +30831,10 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -30890,10 +30890,10 @@
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>9</v>
@@ -30908,7 +30908,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -30967,10 +30967,10 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -30985,10 +30985,10 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -31044,10 +31044,10 @@
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>8</v>
@@ -31121,10 +31121,10 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>10</v>
@@ -31139,7 +31139,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -31198,10 +31198,10 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -31216,7 +31216,7 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -31275,10 +31275,10 @@
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>9</v>
@@ -31352,10 +31352,10 @@
         <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>8</v>
@@ -31370,10 +31370,10 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -31429,10 +31429,10 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>10</v>
@@ -31447,7 +31447,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -31506,10 +31506,10 @@
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>10</v>
@@ -31524,7 +31524,7 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -31583,10 +31583,10 @@
         <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>10</v>
@@ -34849,7 +34849,7 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>9</v>
@@ -34926,7 +34926,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -35003,7 +35003,7 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -35080,7 +35080,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -35157,7 +35157,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -35234,7 +35234,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -35252,7 +35252,7 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -35311,7 +35311,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -35329,7 +35329,7 @@
         <v>6</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -35373,7 +35373,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -35388,10 +35388,10 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -35406,7 +35406,7 @@
         <v>7</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -35465,7 +35465,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -35483,7 +35483,7 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -35542,7 +35542,7 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -35619,7 +35619,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>7</v>
@@ -35637,7 +35637,7 @@
         <v>6</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -35696,7 +35696,7 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -35714,7 +35714,7 @@
         <v>6</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -35773,7 +35773,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -35791,7 +35791,7 @@
         <v>7</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -35850,7 +35850,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -35868,7 +35868,7 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>6</v>
@@ -35927,7 +35927,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -36004,7 +36004,7 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -36066,7 +36066,7 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -36081,10 +36081,10 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -36102,7 +36102,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -36158,7 +36158,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>8</v>
@@ -36235,7 +36235,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -36253,7 +36253,7 @@
         <v>6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -36312,7 +36312,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -36330,7 +36330,7 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -36389,7 +36389,7 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>7</v>
@@ -36407,7 +36407,7 @@
         <v>7</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -36466,7 +36466,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>5</v>
@@ -36484,7 +36484,7 @@
         <v>6</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>5</v>
@@ -36543,7 +36543,7 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>5</v>
@@ -36561,7 +36561,7 @@
         <v>6</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -36620,7 +36620,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>7</v>
@@ -36638,7 +36638,7 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -36697,7 +36697,7 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>7</v>
@@ -36715,7 +36715,7 @@
         <v>8</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -36774,7 +36774,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>5</v>
@@ -36792,7 +36792,7 @@
         <v>7</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -36851,7 +36851,7 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -36869,7 +36869,7 @@
         <v>7</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -36928,7 +36928,7 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -37005,7 +37005,7 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>7</v>
@@ -37082,7 +37082,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>10</v>
@@ -40179,7 +40179,7 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -40197,7 +40197,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -40215,7 +40215,7 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>8</v>
@@ -40233,7 +40233,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -40333,7 +40333,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -40351,7 +40351,7 @@
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -40369,7 +40369,7 @@
         <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -40387,7 +40387,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -40795,7 +40795,7 @@
         <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -40813,7 +40813,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -40831,7 +40831,7 @@
         <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>7</v>
@@ -40849,7 +40849,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -42258,7 +42258,7 @@
         <v>5</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -42276,7 +42276,7 @@
         <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -42294,7 +42294,7 @@
         <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>5</v>
@@ -42312,7 +42312,7 @@
         <v>5</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -42797,7 +42797,7 @@
         <v>5</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -42815,7 +42815,7 @@
         <v>5</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -42833,7 +42833,7 @@
         <v>5</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
         <v>5</v>
@@ -42851,7 +42851,7 @@
         <v>5</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -46573,7 +46573,7 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -46650,7 +46650,7 @@
         <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -46668,7 +46668,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -46727,7 +46727,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -46804,7 +46804,7 @@
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -46881,7 +46881,7 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>6</v>
@@ -46958,7 +46958,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -47035,7 +47035,7 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -47053,7 +47053,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -47112,7 +47112,7 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -47130,7 +47130,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -47189,7 +47189,7 @@
         <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -47266,7 +47266,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -47343,7 +47343,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -47420,7 +47420,7 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>6</v>
@@ -47438,7 +47438,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -47497,7 +47497,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -47515,7 +47515,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -47574,7 +47574,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -47651,7 +47651,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -47669,7 +47669,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -47728,7 +47728,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -47746,7 +47746,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -47805,7 +47805,7 @@
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -47882,7 +47882,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -47900,7 +47900,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -47959,7 +47959,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>6</v>
@@ -47977,7 +47977,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -48036,7 +48036,7 @@
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -48054,7 +48054,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -48113,7 +48113,7 @@
         <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -48190,7 +48190,7 @@
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -48267,7 +48267,7 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>6</v>
@@ -48344,7 +48344,7 @@
         <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -48362,7 +48362,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -48421,7 +48421,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -48498,7 +48498,7 @@
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -48516,7 +48516,7 @@
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -48575,7 +48575,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -48652,7 +48652,7 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -48729,7 +48729,7 @@
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>6</v>
@@ -48806,7 +48806,7 @@
         <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>6</v>
@@ -48883,7 +48883,7 @@
         <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>6</v>
@@ -48960,7 +48960,7 @@
         <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>6</v>
@@ -49037,7 +49037,7 @@
         <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>6</v>
@@ -49114,7 +49114,7 @@
         <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>6</v>
@@ -49132,7 +49132,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -49191,7 +49191,7 @@
         <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>7</v>
@@ -59959,7 +59959,7 @@
         <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
         <v>5</v>
@@ -60166,7 +60166,7 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>8</v>
@@ -60184,7 +60184,7 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -60243,7 +60243,7 @@
         <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -60320,7 +60320,7 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>7</v>
@@ -60397,7 +60397,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>8</v>
@@ -60415,7 +60415,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -60474,7 +60474,7 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -60551,7 +60551,7 @@
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>7</v>
@@ -60569,7 +60569,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -60628,7 +60628,7 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -60646,7 +60646,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -60705,7 +60705,7 @@
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>5</v>
@@ -60723,7 +60723,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -60782,7 +60782,7 @@
         <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>8</v>
@@ -60800,7 +60800,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -60859,7 +60859,7 @@
         <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -60936,7 +60936,7 @@
         <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>5</v>
@@ -60954,7 +60954,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -61013,7 +61013,7 @@
         <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>7</v>
@@ -61090,7 +61090,7 @@
         <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>9</v>
@@ -61167,7 +61167,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>5</v>
@@ -61185,7 +61185,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -61244,7 +61244,7 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -63929,7 +63929,7 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>7</v>
@@ -63947,7 +63947,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -64006,7 +64006,7 @@
         <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -64083,7 +64083,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -64160,7 +64160,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>6</v>
@@ -64237,7 +64237,7 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>9</v>
@@ -64314,7 +64314,7 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -64391,7 +64391,7 @@
         <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>7</v>
@@ -64468,7 +64468,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -64545,7 +64545,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -64622,7 +64622,7 @@
         <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -64640,7 +64640,7 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -64699,7 +64699,7 @@
         <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>9</v>
@@ -64717,7 +64717,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -64776,7 +64776,7 @@
         <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -64794,7 +64794,7 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -64853,7 +64853,7 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -64930,7 +64930,7 @@
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -64948,7 +64948,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -65007,7 +65007,7 @@
         <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -65025,7 +65025,7 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -65084,7 +65084,7 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>5</v>
@@ -65161,7 +65161,7 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -65179,7 +65179,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -65238,7 +65238,7 @@
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -65315,7 +65315,7 @@
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -65392,7 +65392,7 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -65410,7 +65410,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -65469,7 +65469,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>8</v>
@@ -65546,7 +65546,7 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>8</v>
@@ -65564,7 +65564,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -65623,7 +65623,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>5</v>
@@ -65700,7 +65700,7 @@
         <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>5</v>
@@ -65718,7 +65718,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -65777,7 +65777,7 @@
         <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>8</v>
@@ -65795,7 +65795,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -65854,7 +65854,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>7</v>
@@ -65872,7 +65872,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -65931,7 +65931,7 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
         <v>6</v>
@@ -65949,7 +65949,7 @@
         <v>5</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -66008,7 +66008,7 @@
         <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -66085,7 +66085,7 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>9</v>
@@ -66162,7 +66162,7 @@
         <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -66239,7 +66239,7 @@
         <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>8</v>
@@ -66257,7 +66257,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -66316,7 +66316,7 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -66393,7 +66393,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>10</v>
@@ -66470,7 +66470,7 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>8</v>
@@ -66547,7 +66547,7 @@
         <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>10</v>
@@ -66624,7 +66624,7 @@
         <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>9</v>
@@ -66701,7 +66701,7 @@
         <v>7</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
         <v>8</v>
@@ -66778,7 +66778,7 @@
         <v>7</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>9</v>
@@ -66855,7 +66855,7 @@
         <v>6</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
         <v>7</v>
@@ -66932,7 +66932,7 @@
         <v>6</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R43">
         <v>8</v>
@@ -66950,7 +66950,7 @@
         <v>6</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>7</v>
@@ -67148,7 +67148,7 @@
         <v>4</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -67225,7 +67225,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>6</v>
@@ -67302,7 +67302,7 @@
         <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -67320,7 +67320,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -67379,7 +67379,7 @@
         <v>4</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -67456,7 +67456,7 @@
         <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -67533,7 +67533,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>6</v>
@@ -67551,7 +67551,7 @@
         <v>5</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -67610,7 +67610,7 @@
         <v>4</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -67628,7 +67628,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -67687,7 +67687,7 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>9</v>
@@ -67764,7 +67764,7 @@
         <v>4</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -67782,7 +67782,7 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -67841,7 +67841,7 @@
         <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -67918,7 +67918,7 @@
         <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -67995,7 +67995,7 @@
         <v>4</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>6</v>
@@ -68013,7 +68013,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -68072,7 +68072,7 @@
         <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>9</v>
@@ -68149,7 +68149,7 @@
         <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>9</v>
@@ -68226,7 +68226,7 @@
         <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -68303,7 +68303,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -68380,7 +68380,7 @@
         <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -68457,7 +68457,7 @@
         <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -68534,7 +68534,7 @@
         <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>9</v>
@@ -68611,7 +68611,7 @@
         <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>9</v>
@@ -68688,7 +68688,7 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -68765,7 +68765,7 @@
         <v>4</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>8</v>
@@ -68842,7 +68842,7 @@
         <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>6</v>
@@ -68860,7 +68860,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -68919,7 +68919,7 @@
         <v>4</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>7</v>
@@ -68996,7 +68996,7 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>9</v>
@@ -69014,7 +69014,7 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -69073,7 +69073,7 @@
         <v>4</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>6</v>
@@ -69091,7 +69091,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -69910,7 +69910,7 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -69925,7 +69925,7 @@
         <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -72967,28 +72967,28 @@
         <v>1114</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -73150,28 +73150,28 @@
         <v>1117</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -73490,7 +73490,7 @@
         <v>4</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
         <v>6</v>
@@ -73508,7 +73508,7 @@
         <v>5</v>
       </c>
       <c r="Y41">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -73545,7 +73545,7 @@
         <v>1124</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -73560,7 +73560,7 @@
         <v>5</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <v>5</v>
@@ -73575,7 +73575,7 @@
         <v>5</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>5</v>
@@ -73590,7 +73590,7 @@
         <v>5</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U43">
         <v>5</v>
@@ -73625,13 +73625,13 @@
         <v>6</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>7</v>
       </c>
       <c r="Y44">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -73826,7 +73826,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -73903,7 +73903,7 @@
         <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -73921,7 +73921,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -73980,7 +73980,7 @@
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -74057,7 +74057,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -74075,7 +74075,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -74134,7 +74134,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -74152,7 +74152,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -74211,7 +74211,7 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -74229,7 +74229,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -74288,7 +74288,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -74365,7 +74365,7 @@
         <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -74383,7 +74383,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -74442,7 +74442,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -74460,7 +74460,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -74519,7 +74519,7 @@
         <v>4</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -74537,7 +74537,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -74596,7 +74596,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -74673,7 +74673,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -74750,7 +74750,7 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -74827,7 +74827,7 @@
         <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -74904,7 +74904,7 @@
         <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -74922,7 +74922,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -74981,7 +74981,7 @@
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -75058,7 +75058,7 @@
         <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -75135,7 +75135,7 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -75342,7 +75342,7 @@
         <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>7</v>
@@ -75419,7 +75419,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>8</v>
@@ -75496,7 +75496,7 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -75573,7 +75573,7 @@
         <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>6</v>
@@ -75591,7 +75591,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -75650,7 +75650,7 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>5</v>
@@ -75727,7 +75727,7 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -75804,7 +75804,7 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -75881,7 +75881,7 @@
         <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>9</v>
@@ -75899,7 +75899,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -75958,7 +75958,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -76035,7 +76035,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -76112,7 +76112,7 @@
         <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>7</v>
@@ -76130,7 +76130,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -76189,7 +76189,7 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -76266,7 +76266,7 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>9</v>
@@ -76343,7 +76343,7 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -76361,7 +76361,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -76420,7 +76420,7 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -76497,7 +76497,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>5</v>
@@ -76515,7 +76515,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -76574,7 +76574,7 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -76651,7 +76651,7 @@
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -76728,7 +76728,7 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>9</v>
@@ -76746,7 +76746,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -76805,7 +76805,7 @@
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -76823,7 +76823,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -76882,7 +76882,7 @@
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -76959,7 +76959,7 @@
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -77036,7 +77036,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>7</v>
@@ -77113,7 +77113,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -77190,7 +77190,7 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>8</v>
@@ -77208,7 +77208,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -77267,7 +77267,7 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>9</v>
@@ -77344,7 +77344,7 @@
         <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>6</v>
@@ -77362,7 +77362,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -77421,7 +77421,7 @@
         <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -77439,7 +77439,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -77498,7 +77498,7 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -77575,7 +77575,7 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -77652,7 +77652,7 @@
         <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>8</v>
@@ -77729,7 +77729,7 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>8</v>
@@ -77806,7 +77806,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>6</v>
@@ -77824,7 +77824,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>6</v>
@@ -77883,7 +77883,7 @@
         <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>9</v>
@@ -77960,7 +77960,7 @@
         <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>6</v>
@@ -78037,7 +78037,7 @@
         <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>10</v>
@@ -78114,7 +78114,7 @@
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
         <v>8</v>
@@ -78191,7 +78191,7 @@
         <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
         <v>7</v>
@@ -78268,7 +78268,7 @@
         <v>10</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>10</v>
@@ -78345,7 +78345,7 @@
         <v>7</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R43">
         <v>7</v>
@@ -78363,7 +78363,7 @@
         <v>6</v>
       </c>
       <c r="W43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>6</v>
@@ -78422,7 +78422,7 @@
         <v>5</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
         <v>6</v>
@@ -78499,7 +78499,7 @@
         <v>5</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R45">
         <v>5</v>
@@ -78576,7 +78576,7 @@
         <v>10</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R46">
         <v>10</v>
@@ -78653,7 +78653,7 @@
         <v>10</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R47">
         <v>10</v>
@@ -78866,7 +78866,7 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>9</v>
@@ -78884,7 +78884,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -78943,7 +78943,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -78961,7 +78961,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -79020,7 +79020,7 @@
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>7</v>
@@ -79038,7 +79038,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -79097,7 +79097,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>7</v>
@@ -79115,7 +79115,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -79174,7 +79174,7 @@
         <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -79251,7 +79251,7 @@
         <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>8</v>
@@ -79269,7 +79269,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -79328,7 +79328,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -79405,7 +79405,7 @@
         <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -79482,7 +79482,7 @@
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -79559,7 +79559,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -79577,7 +79577,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -79636,7 +79636,7 @@
         <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>9</v>
@@ -79713,7 +79713,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>9</v>
@@ -79731,7 +79731,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -79790,7 +79790,7 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -79867,7 +79867,7 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -79885,7 +79885,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -79944,7 +79944,7 @@
         <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -80021,7 +80021,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -80098,7 +80098,7 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>8</v>
@@ -80175,7 +80175,7 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -80193,7 +80193,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -80252,7 +80252,7 @@
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -80270,7 +80270,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -80329,7 +80329,7 @@
         <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -80406,7 +80406,7 @@
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -80424,7 +80424,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -80483,7 +80483,7 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>7</v>
@@ -80560,7 +80560,7 @@
         <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -80637,7 +80637,7 @@
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -80714,7 +80714,7 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -80791,7 +80791,7 @@
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>8</v>
@@ -80868,7 +80868,7 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
         <v>5</v>
@@ -80945,7 +80945,7 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
         <v>5</v>
@@ -81022,7 +81022,7 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -81099,7 +81099,7 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>5</v>
@@ -81176,7 +81176,7 @@
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>9</v>
@@ -81253,7 +81253,7 @@
         <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>8</v>
@@ -81271,7 +81271,7 @@
         <v>7</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -81330,7 +81330,7 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -81348,7 +81348,7 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -81407,7 +81407,7 @@
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
         <v>7</v>
@@ -81484,7 +81484,7 @@
         <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>8</v>
@@ -81502,7 +81502,7 @@
         <v>5</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -81561,7 +81561,7 @@
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
         <v>8</v>
@@ -81579,7 +81579,7 @@
         <v>8</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -81638,7 +81638,7 @@
         <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>9</v>
@@ -81656,7 +81656,7 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>7</v>
@@ -81715,7 +81715,7 @@
         <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R41">
         <v>8</v>
@@ -81733,7 +81733,7 @@
         <v>6</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -81792,7 +81792,7 @@
         <v>5</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
         <v>5</v>
@@ -81869,7 +81869,7 @@
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
         <v>8</v>
@@ -81887,7 +81887,7 @@
         <v>8</v>
       </c>
       <c r="W43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X43">
         <v>7</v>
@@ -81946,7 +81946,7 @@
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
         <v>8</v>
@@ -82023,7 +82023,7 @@
         <v>9</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R45">
         <v>10</v>
@@ -82100,7 +82100,7 @@
         <v>7</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R46">
         <v>8</v>
@@ -82118,7 +82118,7 @@
         <v>7</v>
       </c>
       <c r="W46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X46">
         <v>7</v>
@@ -82313,7 +82313,7 @@
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -82390,7 +82390,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -82467,7 +82467,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>8</v>
@@ -82544,7 +82544,7 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -82621,7 +82621,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -82698,7 +82698,7 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -82775,7 +82775,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>7</v>
@@ -82852,7 +82852,7 @@
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -82929,7 +82929,7 @@
         <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -83006,7 +83006,7 @@
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -83083,7 +83083,7 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -83101,7 +83101,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -83160,7 +83160,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -83178,7 +83178,7 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -83237,7 +83237,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>8</v>
@@ -83255,7 +83255,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -83314,7 +83314,7 @@
         <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -83332,7 +83332,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -83391,7 +83391,7 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -83468,7 +83468,7 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -83545,7 +83545,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -83563,7 +83563,7 @@
         <v>5</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -83622,7 +83622,7 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -83699,7 +83699,7 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>8</v>
@@ -83776,7 +83776,7 @@
         <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -83853,7 +83853,7 @@
         <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>6</v>
@@ -83930,7 +83930,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>8</v>
@@ -84007,7 +84007,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>7</v>
@@ -84084,7 +84084,7 @@
         <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>5</v>
@@ -84161,7 +84161,7 @@
         <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>5</v>
@@ -84238,7 +84238,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
         <v>5</v>
@@ -84315,7 +84315,7 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
         <v>7</v>
@@ -84392,7 +84392,7 @@
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>6</v>
@@ -84469,7 +84469,7 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>8</v>
@@ -84546,7 +84546,7 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -84623,7 +84623,7 @@
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>9</v>
@@ -84641,7 +84641,7 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -84700,7 +84700,7 @@
         <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>6</v>
@@ -84718,7 +84718,7 @@
         <v>6</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -84777,7 +84777,7 @@
         <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>6</v>
@@ -84854,7 +84854,7 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>8</v>
@@ -84872,7 +84872,7 @@
         <v>8</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>7</v>
@@ -84931,7 +84931,7 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
         <v>7</v>
@@ -85008,7 +85008,7 @@
         <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>6</v>
@@ -85085,7 +85085,7 @@
         <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>6</v>
@@ -85103,7 +85103,7 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>7</v>
@@ -85162,7 +85162,7 @@
         <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
         <v>10</v>
@@ -85180,7 +85180,7 @@
         <v>10</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>9</v>
@@ -85239,7 +85239,7 @@
         <v>8</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
         <v>7</v>
@@ -85316,7 +85316,7 @@
         <v>5</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R43">
         <v>6</v>
@@ -85334,7 +85334,7 @@
         <v>7</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>6</v>
@@ -85393,7 +85393,7 @@
         <v>7</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R44">
         <v>7</v>
@@ -85411,7 +85411,7 @@
         <v>8</v>
       </c>
       <c r="W44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>7</v>
@@ -85470,7 +85470,7 @@
         <v>5</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R45">
         <v>6</v>
@@ -85547,7 +85547,7 @@
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R46">
         <v>5</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -669,7 +669,7 @@
     <t>BELLO MORALES JOSUE</t>
   </si>
   <si>
-    <t>CALOCA TEXCAHUA ARLETH MALERY</t>
+    <t>CALOCA TEXCAHUA ARLETH MARELY</t>
   </si>
   <si>
     <t>CALVO URIAS ANGEL EMMANUEL</t>
@@ -38029,7 +38029,7 @@
         <v>718</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -38047,7 +38047,7 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>5</v>
@@ -38065,7 +38065,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -38083,7 +38083,7 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>5</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -3852,7 +3852,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -3906,7 +3906,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -3929,7 +3929,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -3983,7 +3983,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -4006,7 +4006,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -4060,7 +4060,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -4083,7 +4083,7 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -4137,7 +4137,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -4160,7 +4160,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -4214,7 +4214,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -4237,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -4291,7 +4291,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -4314,7 +4314,7 @@
         <v>83.3</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D10">
         <v>86.7</v>
@@ -4368,7 +4368,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -4391,7 +4391,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -4445,7 +4445,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -4468,7 +4468,7 @@
         <v>93.3</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -4522,7 +4522,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -4545,7 +4545,7 @@
         <v>93.3</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -4599,7 +4599,7 @@
         <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -4622,7 +4622,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -4676,7 +4676,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -4699,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -4753,7 +4753,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -4776,7 +4776,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -4830,7 +4830,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -4853,7 +4853,7 @@
         <v>93.3</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -4930,7 +4930,7 @@
         <v>96.7</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -4984,7 +4984,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -5007,7 +5007,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -5061,7 +5061,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -5084,7 +5084,7 @@
         <v>96.7</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -5138,7 +5138,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -5161,7 +5161,7 @@
         <v>96.7</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -5215,7 +5215,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -5238,7 +5238,7 @@
         <v>93.3</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -5292,7 +5292,7 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -5315,7 +5315,7 @@
         <v>93.3</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -5369,7 +5369,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -5392,7 +5392,7 @@
         <v>96.7</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -5446,7 +5446,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -5469,7 +5469,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -5523,7 +5523,7 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -5546,7 +5546,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -5600,7 +5600,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -5623,7 +5623,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -5677,7 +5677,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -5700,7 +5700,7 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -5754,7 +5754,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -5777,7 +5777,7 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -5831,7 +5831,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -5854,7 +5854,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -5908,7 +5908,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -5931,7 +5931,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -5985,7 +5985,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -6008,7 +6008,7 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -6062,7 +6062,7 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -6085,7 +6085,7 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D33">
         <v>100</v>
@@ -6139,7 +6139,7 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -6162,7 +6162,7 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -6216,7 +6216,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -6239,7 +6239,7 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -6293,7 +6293,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -6316,7 +6316,7 @@
         <v>80</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -6370,7 +6370,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -6393,7 +6393,7 @@
         <v>100</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -6447,7 +6447,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -6618,7 +6618,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>106.7</v>
@@ -6672,7 +6672,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -6695,7 +6695,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>106.7</v>
@@ -6749,7 +6749,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -6772,7 +6772,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>106.7</v>
@@ -6826,7 +6826,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -6849,7 +6849,7 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>106.7</v>
@@ -6903,7 +6903,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -6926,7 +6926,7 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>106.7</v>
@@ -6980,7 +6980,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -7003,7 +7003,7 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>106.7</v>
@@ -7057,7 +7057,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -7080,7 +7080,7 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>106.7</v>
@@ -7134,7 +7134,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -7157,7 +7157,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>106.7</v>
@@ -7211,7 +7211,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -7234,7 +7234,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>106.7</v>
@@ -7288,7 +7288,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -7311,7 +7311,7 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>106.7</v>
@@ -7365,7 +7365,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -7388,7 +7388,7 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>106.7</v>
@@ -7442,7 +7442,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -7465,7 +7465,7 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>106.7</v>
@@ -7519,7 +7519,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -7542,7 +7542,7 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>106.7</v>
@@ -7596,7 +7596,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -7619,7 +7619,7 @@
         <v>90</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>80</v>
@@ -7673,7 +7673,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -7696,7 +7696,7 @@
         <v>90</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>106.7</v>
@@ -7750,7 +7750,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -7773,7 +7773,7 @@
         <v>90</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>106.7</v>
@@ -7827,7 +7827,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -7850,7 +7850,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>106.7</v>
@@ -7904,7 +7904,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -7927,7 +7927,7 @@
         <v>90</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G21">
         <v>86.7</v>
@@ -7981,7 +7981,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -8004,7 +8004,7 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>106.7</v>
@@ -8058,7 +8058,7 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -8081,7 +8081,7 @@
         <v>90</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -8135,7 +8135,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -8158,7 +8158,7 @@
         <v>90</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G24">
         <v>106.7</v>
@@ -8212,7 +8212,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -8235,7 +8235,7 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>106.7</v>
@@ -8289,7 +8289,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -8312,7 +8312,7 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>106.7</v>
@@ -8366,7 +8366,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -8389,7 +8389,7 @@
         <v>90</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -8443,7 +8443,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -8466,7 +8466,7 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>106.7</v>
@@ -8520,7 +8520,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -8543,7 +8543,7 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>106.7</v>
@@ -8597,7 +8597,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -8620,7 +8620,7 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>106.7</v>
@@ -8674,7 +8674,7 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -8697,7 +8697,7 @@
         <v>100</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>106.7</v>
@@ -8751,7 +8751,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -8774,7 +8774,7 @@
         <v>100</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>106.7</v>
@@ -8828,7 +8828,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>106.7</v>
@@ -8905,7 +8905,7 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -8928,7 +8928,7 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>106.7</v>
@@ -8982,7 +8982,7 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -9005,7 +9005,7 @@
         <v>100</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>106.7</v>
@@ -9059,7 +9059,7 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -9082,7 +9082,7 @@
         <v>100</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>106.7</v>
@@ -9136,7 +9136,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -9159,7 +9159,7 @@
         <v>100</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>106.7</v>
@@ -9213,7 +9213,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -9236,7 +9236,7 @@
         <v>100</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38">
         <v>106.7</v>
@@ -9290,7 +9290,7 @@
         <v>9</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -9313,7 +9313,7 @@
         <v>100</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39">
         <v>106.7</v>
@@ -9367,7 +9367,7 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -9390,7 +9390,7 @@
         <v>100</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G40">
         <v>106.7</v>
@@ -9444,7 +9444,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -9467,7 +9467,7 @@
         <v>100</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G41">
         <v>106.7</v>
@@ -9521,7 +9521,7 @@
         <v>5</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y41">
         <v>5</v>
@@ -23057,7 +23057,7 @@
         <v>132</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>132</v>
@@ -23111,7 +23111,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -23134,7 +23134,7 @@
         <v>132</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>132</v>
@@ -23188,7 +23188,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -23211,7 +23211,7 @@
         <v>132</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F6">
         <v>132</v>
@@ -23265,7 +23265,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -23288,7 +23288,7 @@
         <v>132</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>132</v>
@@ -23342,7 +23342,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -23365,7 +23365,7 @@
         <v>132</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>132</v>
@@ -23419,7 +23419,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -23442,7 +23442,7 @@
         <v>132</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>132</v>
@@ -23496,7 +23496,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -23519,7 +23519,7 @@
         <v>132</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>132</v>
@@ -23573,7 +23573,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -23596,7 +23596,7 @@
         <v>132</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>132</v>
@@ -23650,7 +23650,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -23673,7 +23673,7 @@
         <v>132</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>132</v>
@@ -23727,7 +23727,7 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -23750,7 +23750,7 @@
         <v>132</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>132</v>
@@ -23804,7 +23804,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -23827,7 +23827,7 @@
         <v>132</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>132</v>
@@ -23881,7 +23881,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -23904,7 +23904,7 @@
         <v>132</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>132</v>
@@ -23958,7 +23958,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -23981,7 +23981,7 @@
         <v>132</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>132</v>
@@ -24035,7 +24035,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -24058,7 +24058,7 @@
         <v>132</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>132</v>
@@ -24112,7 +24112,7 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -24135,7 +24135,7 @@
         <v>132</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>132</v>
@@ -24189,7 +24189,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -24212,7 +24212,7 @@
         <v>132</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>132</v>
@@ -24266,7 +24266,7 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -24289,7 +24289,7 @@
         <v>132</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>132</v>
@@ -24343,7 +24343,7 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -24366,7 +24366,7 @@
         <v>128</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F21">
         <v>128</v>
@@ -24420,7 +24420,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -24443,7 +24443,7 @@
         <v>132</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>132</v>
@@ -24497,7 +24497,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -24520,7 +24520,7 @@
         <v>132</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F23">
         <v>132</v>
@@ -24574,7 +24574,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -24597,7 +24597,7 @@
         <v>132</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>132</v>
@@ -24651,7 +24651,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -24674,7 +24674,7 @@
         <v>132</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>132</v>
@@ -24728,7 +24728,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -24751,7 +24751,7 @@
         <v>132</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>132</v>
@@ -24805,7 +24805,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -24828,7 +24828,7 @@
         <v>132</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>132</v>
@@ -24882,7 +24882,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -24905,7 +24905,7 @@
         <v>132</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>132</v>
@@ -24959,7 +24959,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -24982,7 +24982,7 @@
         <v>132</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>132</v>
@@ -25036,7 +25036,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -25059,7 +25059,7 @@
         <v>132</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>132</v>
@@ -25113,7 +25113,7 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -25136,7 +25136,7 @@
         <v>132</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>132</v>
@@ -25190,7 +25190,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -25213,7 +25213,7 @@
         <v>132</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>132</v>
@@ -25267,7 +25267,7 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -25290,7 +25290,7 @@
         <v>132</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>132</v>
@@ -25344,7 +25344,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -25367,7 +25367,7 @@
         <v>132</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>132</v>
@@ -25421,7 +25421,7 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -25444,7 +25444,7 @@
         <v>132</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>132</v>
@@ -25498,7 +25498,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -25521,7 +25521,7 @@
         <v>132</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>132</v>
@@ -25575,7 +25575,7 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -25598,7 +25598,7 @@
         <v>132</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>132</v>
@@ -25652,7 +25652,7 @@
         <v>10</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -25675,7 +25675,7 @@
         <v>124</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F38">
         <v>124</v>
@@ -25729,7 +25729,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -25752,7 +25752,7 @@
         <v>132</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39">
         <v>132</v>
@@ -25806,7 +25806,7 @@
         <v>9</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>9</v>
@@ -30088,7 +30088,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -36888,13 +36888,13 @@
         <v>75</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F4">
         <v>90</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -36942,13 +36942,13 @@
         <v>5</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -36965,13 +36965,13 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F5">
         <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -37019,13 +37019,13 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -37042,13 +37042,13 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F6">
         <v>100</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -37096,13 +37096,13 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -37119,13 +37119,13 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F7">
         <v>95</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -37173,13 +37173,13 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -37196,13 +37196,13 @@
         <v>90</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F8">
         <v>85</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -37250,13 +37250,13 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -37273,13 +37273,13 @@
         <v>75</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F9">
         <v>70</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -37327,13 +37327,13 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -37350,13 +37350,13 @@
         <v>85</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F10">
         <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -37404,13 +37404,13 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -37427,13 +37427,13 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F11">
         <v>95</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -37481,13 +37481,13 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -37504,13 +37504,13 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F12">
         <v>80</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -37558,13 +37558,13 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -37581,13 +37581,13 @@
         <v>60</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F13">
         <v>90</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -37635,13 +37635,13 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -37658,13 +37658,13 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F14">
         <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -37712,13 +37712,13 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -37735,13 +37735,13 @@
         <v>50</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F15">
         <v>80</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -37789,13 +37789,13 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -37812,13 +37812,13 @@
         <v>90</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F16">
         <v>95</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -37866,13 +37866,13 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -37889,13 +37889,13 @@
         <v>85</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F17">
         <v>90</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -37943,13 +37943,13 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -37966,13 +37966,13 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F18">
         <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -38020,13 +38020,13 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -38043,13 +38043,13 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F19">
         <v>100</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -38097,13 +38097,13 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -38120,13 +38120,13 @@
         <v>95</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F20">
         <v>100</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -38174,13 +38174,13 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -38197,13 +38197,13 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F21">
         <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -38251,13 +38251,13 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -38274,13 +38274,13 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F22">
         <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -38328,13 +38328,13 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -38351,13 +38351,13 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F23">
         <v>90</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -38405,13 +38405,13 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -38428,13 +38428,13 @@
         <v>85</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F24">
         <v>90</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -38482,13 +38482,13 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -38505,13 +38505,13 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -38559,13 +38559,13 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -38579,13 +38579,13 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -38624,13 +38624,13 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -38647,13 +38647,13 @@
         <v>80</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F27">
         <v>90</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -38701,13 +38701,13 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -38724,13 +38724,13 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F28">
         <v>100</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -38778,13 +38778,13 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -38801,13 +38801,13 @@
         <v>90</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F29">
         <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -38855,13 +38855,13 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -38869,10 +38869,10 @@
         <v>735</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -38887,10 +38887,10 @@
         <v>0</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -38907,13 +38907,13 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F31">
         <v>90</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -38961,13 +38961,13 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -38984,13 +38984,13 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -39038,13 +39038,13 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -39061,13 +39061,13 @@
         <v>70</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F33">
         <v>100</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -39115,13 +39115,13 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -39138,13 +39138,13 @@
         <v>85</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F34">
         <v>100</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -39192,13 +39192,13 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -39215,13 +39215,13 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F35">
         <v>100</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -39269,13 +39269,13 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -39292,13 +39292,13 @@
         <v>85</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F36">
         <v>100</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -39346,13 +39346,13 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -39369,13 +39369,13 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F37">
         <v>100</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -39423,13 +39423,13 @@
         <v>10</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -39446,13 +39446,13 @@
         <v>100</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F38">
         <v>100</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -39500,13 +39500,13 @@
         <v>6</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X38">
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -39523,13 +39523,13 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F39">
         <v>100</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -39577,13 +39577,13 @@
         <v>5</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X39">
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -39600,13 +39600,13 @@
         <v>100</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F40">
         <v>80</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -39654,13 +39654,13 @@
         <v>10</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X40">
         <v>5</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -39677,13 +39677,13 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F41">
         <v>90</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -39731,13 +39731,13 @@
         <v>8</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X41">
         <v>9</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -39754,13 +39754,13 @@
         <v>100</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F42">
         <v>100</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -39808,13 +39808,13 @@
         <v>6</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X42">
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -39831,13 +39831,13 @@
         <v>80</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F43">
         <v>90</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -39885,13 +39885,13 @@
         <v>6</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>6</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -39908,13 +39908,13 @@
         <v>100</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F44">
         <v>100</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -39962,13 +39962,13 @@
         <v>9</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X44">
         <v>5</v>
       </c>
       <c r="Y44">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -39985,13 +39985,13 @@
         <v>75</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -40039,13 +40039,13 @@
         <v>5</v>
       </c>
       <c r="W45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X45">
         <v>5</v>
       </c>
       <c r="Y45">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -40062,13 +40062,13 @@
         <v>80</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F46">
         <v>100</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -40116,13 +40116,13 @@
         <v>6</v>
       </c>
       <c r="W46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X46">
         <v>5</v>
       </c>
       <c r="Y46">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -40297,7 +40297,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G4">
         <v>70</v>
@@ -40360,7 +40360,7 @@
         <v>-1</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -41187,7 +41187,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>90</v>
@@ -41250,7 +41250,7 @@
         <v>-1</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB14">
         <v>5</v>
@@ -41810,7 +41810,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="G21">
         <v>85</v>
@@ -41873,7 +41873,7 @@
         <v>-1</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>5</v>
@@ -41988,7 +41988,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -42051,7 +42051,7 @@
         <v>-1</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -42077,7 +42077,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -42140,7 +42140,7 @@
         <v>-1</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -42166,7 +42166,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="G25">
         <v>90</v>
@@ -42229,7 +42229,7 @@
         <v>-1</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>5</v>
@@ -42344,7 +42344,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>55</v>
@@ -42407,7 +42407,7 @@
         <v>-1</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB27">
         <v>5</v>
@@ -42433,7 +42433,7 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="G28">
         <v>95</v>
@@ -42496,7 +42496,7 @@
         <v>-1</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -42522,7 +42522,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="G29">
         <v>90</v>
@@ -42585,7 +42585,7 @@
         <v>-1</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>5</v>
@@ -42611,7 +42611,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="G30">
         <v>75</v>
@@ -42674,7 +42674,7 @@
         <v>-1</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB30">
         <v>5</v>
@@ -48440,7 +48440,7 @@
         <v>95</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -48452,7 +48452,7 @@
         <v>76.7</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -48503,7 +48503,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>5</v>
@@ -48515,7 +48515,7 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -48529,7 +48529,7 @@
         <v>95</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>66.7</v>
@@ -48541,7 +48541,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -48592,7 +48592,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -48604,7 +48604,7 @@
         <v>5</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -48618,7 +48618,7 @@
         <v>95</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>66.7</v>
@@ -48630,7 +48630,7 @@
         <v>80</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -48681,7 +48681,7 @@
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>6</v>
@@ -48693,7 +48693,7 @@
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -48707,7 +48707,7 @@
         <v>85</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>60</v>
@@ -48719,7 +48719,7 @@
         <v>76.7</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -48770,7 +48770,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -48782,7 +48782,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -48796,7 +48796,7 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>120</v>
@@ -48808,7 +48808,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -48859,7 +48859,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z8">
         <v>8</v>
@@ -48871,7 +48871,7 @@
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -48885,7 +48885,7 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>93.3</v>
@@ -48897,7 +48897,7 @@
         <v>83.3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -48948,7 +48948,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -48960,7 +48960,7 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -48974,7 +48974,7 @@
         <v>95</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -48986,7 +48986,7 @@
         <v>93.3</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -49037,7 +49037,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -49049,7 +49049,7 @@
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -49063,7 +49063,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>120</v>
@@ -49075,7 +49075,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -49126,7 +49126,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>7</v>
@@ -49138,7 +49138,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -49152,7 +49152,7 @@
         <v>80</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -49164,7 +49164,7 @@
         <v>66.7</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -49215,10 +49215,10 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -49227,7 +49227,7 @@
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -49241,7 +49241,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>120</v>
@@ -49253,7 +49253,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>8</v>
@@ -49316,7 +49316,7 @@
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -49330,7 +49330,7 @@
         <v>95</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>120</v>
@@ -49342,7 +49342,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -49393,7 +49393,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -49405,7 +49405,7 @@
         <v>7</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -49419,7 +49419,7 @@
         <v>90</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>93.3</v>
@@ -49431,7 +49431,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -49482,7 +49482,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -49494,7 +49494,7 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -49508,7 +49508,7 @@
         <v>95</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -49520,7 +49520,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -49571,7 +49571,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -49583,7 +49583,7 @@
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -49597,7 +49597,7 @@
         <v>95</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>120</v>
@@ -49609,7 +49609,7 @@
         <v>86.7</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -49660,7 +49660,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>6</v>
@@ -49672,7 +49672,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -49686,7 +49686,7 @@
         <v>80</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -49698,7 +49698,7 @@
         <v>86.7</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -49749,10 +49749,10 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>5</v>
@@ -49761,7 +49761,7 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -49775,7 +49775,7 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>120</v>
@@ -49787,7 +49787,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -49838,7 +49838,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -49850,7 +49850,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -49864,7 +49864,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>120</v>
@@ -49876,7 +49876,7 @@
         <v>93.3</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -49927,7 +49927,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>8</v>
@@ -49939,7 +49939,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -49953,7 +49953,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -49965,7 +49965,7 @@
         <v>26.7</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -50016,7 +50016,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -50028,7 +50028,7 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -50042,7 +50042,7 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -50054,7 +50054,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -50105,7 +50105,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -50117,7 +50117,7 @@
         <v>9</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -50131,7 +50131,7 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -50143,7 +50143,7 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -50194,7 +50194,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>6</v>
@@ -50206,7 +50206,7 @@
         <v>9</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -50223,7 +50223,7 @@
         <v>66.7</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -50250,7 +50250,7 @@
         <v>0</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -50259,7 +50259,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -50273,7 +50273,7 @@
         <v>95</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>93.3</v>
@@ -50285,7 +50285,7 @@
         <v>83.3</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -50336,10 +50336,10 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -50348,7 +50348,7 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -50362,7 +50362,7 @@
         <v>90</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>66.7</v>
@@ -50371,7 +50371,7 @@
         <v>83.3</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -50416,7 +50416,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>7</v>
@@ -50425,7 +50425,7 @@
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -50439,7 +50439,7 @@
         <v>90</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>66.7</v>
@@ -50448,7 +50448,7 @@
         <v>86.7</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -50493,7 +50493,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>6</v>
@@ -50502,7 +50502,7 @@
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -50516,7 +50516,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>120</v>
@@ -50528,7 +50528,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -50579,7 +50579,7 @@
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>9</v>
@@ -50591,7 +50591,7 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -50605,7 +50605,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>120</v>
@@ -50617,7 +50617,7 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -50668,7 +50668,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>9</v>
@@ -50680,7 +50680,7 @@
         <v>8</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -50694,7 +50694,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>120</v>
@@ -50706,7 +50706,7 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -50757,7 +50757,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>8</v>
@@ -50769,7 +50769,7 @@
         <v>9</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -50783,7 +50783,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>120</v>
@@ -50795,7 +50795,7 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -50846,7 +50846,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -50858,7 +50858,7 @@
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -50872,7 +50872,7 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>93.3</v>
@@ -50884,7 +50884,7 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -50935,7 +50935,7 @@
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z32">
         <v>5</v>
@@ -50947,7 +50947,7 @@
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -50961,7 +50961,7 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>120</v>
@@ -50973,7 +50973,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -51024,7 +51024,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>7</v>
@@ -51036,7 +51036,7 @@
         <v>9</v>
       </c>
       <c r="AC33">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -51050,7 +51050,7 @@
         <v>100</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>120</v>
@@ -51062,7 +51062,7 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -51113,7 +51113,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <v>6</v>
@@ -51125,7 +51125,7 @@
         <v>7</v>
       </c>
       <c r="AC34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -51139,7 +51139,7 @@
         <v>100</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>106.7</v>
@@ -51151,7 +51151,7 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -51202,7 +51202,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z35">
         <v>9</v>
@@ -51214,7 +51214,7 @@
         <v>7</v>
       </c>
       <c r="AC35">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -51228,7 +51228,7 @@
         <v>100</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>120</v>
@@ -51240,7 +51240,7 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -51291,7 +51291,7 @@
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -51303,7 +51303,7 @@
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -51472,7 +51472,7 @@
         <v>80</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>120</v>
@@ -51535,7 +51535,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <v>9</v>
@@ -51561,7 +51561,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E5">
         <v>120</v>
@@ -51624,7 +51624,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>9</v>
@@ -51650,7 +51650,7 @@
         <v>80</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E6">
         <v>120</v>
@@ -51713,7 +51713,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z6">
         <v>6</v>
@@ -51739,7 +51739,7 @@
         <v>75</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E7">
         <v>120</v>
@@ -51802,7 +51802,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>7</v>
@@ -51828,7 +51828,7 @@
         <v>90</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E8">
         <v>120</v>
@@ -51891,7 +51891,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -51917,7 +51917,7 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>120</v>
@@ -51980,7 +51980,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>8</v>
@@ -52006,7 +52006,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>120</v>
@@ -52069,7 +52069,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -52095,7 +52095,7 @@
         <v>90</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -52158,7 +52158,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>7</v>
@@ -52184,7 +52184,7 @@
         <v>80</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E12">
         <v>120</v>
@@ -52247,7 +52247,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>8</v>
@@ -52273,7 +52273,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -52336,7 +52336,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -52362,7 +52362,7 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>120</v>
@@ -52425,7 +52425,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>8</v>
@@ -52492,7 +52492,7 @@
         <v>80</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E16">
         <v>93.3</v>
@@ -52555,7 +52555,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -52581,7 +52581,7 @@
         <v>80</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E17">
         <v>120</v>
@@ -52644,7 +52644,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -52670,7 +52670,7 @@
         <v>90</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E18">
         <v>120</v>
@@ -52733,7 +52733,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>120</v>
@@ -52822,7 +52822,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -52889,7 +52889,7 @@
         <v>80</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>120</v>
@@ -52952,7 +52952,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>7</v>
@@ -52978,7 +52978,7 @@
         <v>80</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E22">
         <v>120</v>
@@ -53041,7 +53041,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -53067,7 +53067,7 @@
         <v>80</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E23">
         <v>120</v>
@@ -53130,7 +53130,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>7</v>
@@ -53156,7 +53156,7 @@
         <v>90</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>120</v>
@@ -53219,7 +53219,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>9</v>
@@ -53245,7 +53245,7 @@
         <v>80</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E25">
         <v>120</v>
@@ -53308,7 +53308,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z25">
         <v>7</v>
@@ -53334,7 +53334,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>120</v>
@@ -53397,7 +53397,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>9</v>
@@ -53423,7 +53423,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E27">
         <v>120</v>
@@ -53486,7 +53486,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z27">
         <v>8</v>
@@ -53575,10 +53575,10 @@
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>5</v>
@@ -53601,7 +53601,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>120</v>
@@ -53664,7 +53664,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>9</v>
@@ -53690,7 +53690,7 @@
         <v>80</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E30">
         <v>120</v>
@@ -53753,7 +53753,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>7</v>
@@ -53779,7 +53779,7 @@
         <v>80</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E31">
         <v>120</v>
@@ -53842,7 +53842,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z31">
         <v>6</v>
@@ -53868,7 +53868,7 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>120</v>
@@ -53931,7 +53931,7 @@
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z32">
         <v>6</v>
@@ -53957,7 +53957,7 @@
         <v>80</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E33">
         <v>120</v>
@@ -54020,7 +54020,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>7</v>
@@ -54046,7 +54046,7 @@
         <v>90</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E34">
         <v>93.3</v>
@@ -54109,7 +54109,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <v>5</v>
@@ -54135,7 +54135,7 @@
         <v>80</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E35">
         <v>93.3</v>
@@ -54198,7 +54198,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z35">
         <v>6</v>
@@ -54224,7 +54224,7 @@
         <v>80</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E36">
         <v>120</v>
@@ -54287,7 +54287,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z36">
         <v>7</v>
@@ -54313,7 +54313,7 @@
         <v>80</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E37">
         <v>66.7</v>
@@ -54376,7 +54376,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z37">
         <v>5</v>
@@ -54402,7 +54402,7 @@
         <v>100</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E38">
         <v>120</v>
@@ -54465,7 +54465,7 @@
         <v>8</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z38">
         <v>8</v>
@@ -57004,10 +57004,10 @@
         <v>86</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -57058,10 +57058,10 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -57081,10 +57081,10 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -57135,10 +57135,10 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -57158,7 +57158,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -57203,7 +57203,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -57223,10 +57223,10 @@
         <v>88</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -57277,10 +57277,10 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -57300,10 +57300,10 @@
         <v>80</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -57354,10 +57354,10 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -57377,10 +57377,10 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -57431,10 +57431,10 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -57454,10 +57454,10 @@
         <v>88</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -57508,10 +57508,10 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -57531,10 +57531,10 @@
         <v>74</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -57585,10 +57585,10 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -57608,10 +57608,10 @@
         <v>96</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -57662,10 +57662,10 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -57685,10 +57685,10 @@
         <v>88</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -57739,10 +57739,10 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -57762,10 +57762,10 @@
         <v>72</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -57816,10 +57816,10 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -57839,10 +57839,10 @@
         <v>92</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -57893,10 +57893,10 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -57916,10 +57916,10 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -57970,10 +57970,10 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -57993,10 +57993,10 @@
         <v>82</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -58047,10 +58047,10 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -58070,10 +58070,10 @@
         <v>90</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -58124,10 +58124,10 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -58147,10 +58147,10 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -58201,10 +58201,10 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -58224,10 +58224,10 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -58278,10 +58278,10 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -58301,10 +58301,10 @@
         <v>98</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -58355,10 +58355,10 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -58378,10 +58378,10 @@
         <v>76</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -58432,10 +58432,10 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -58455,10 +58455,10 @@
         <v>100</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -58509,10 +58509,10 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -58532,10 +58532,10 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -58586,10 +58586,10 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -58609,10 +58609,10 @@
         <v>28</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -58663,10 +58663,10 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -58686,10 +58686,10 @@
         <v>94</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -58740,10 +58740,10 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -58763,10 +58763,10 @@
         <v>92</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -58817,10 +58817,10 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -58840,10 +58840,10 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -58894,10 +58894,10 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -58917,10 +58917,10 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -58971,10 +58971,10 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -58994,10 +58994,10 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -59048,10 +59048,10 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -59071,10 +59071,10 @@
         <v>84</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -59125,10 +59125,10 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -59148,10 +59148,10 @@
         <v>86</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -59202,10 +59202,10 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -59421,7 +59421,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -59444,7 +59444,7 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -59521,7 +59521,7 @@
         <v>90</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -59598,7 +59598,7 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -59652,7 +59652,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -59675,7 +59675,7 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -59752,7 +59752,7 @@
         <v>95</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -59829,7 +59829,7 @@
         <v>95</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -59960,7 +59960,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -59983,7 +59983,7 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -60114,7 +60114,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -60137,7 +60137,7 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -60214,7 +60214,7 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -60345,7 +60345,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -60368,7 +60368,7 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -60575,10 +60575,10 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="F4">
         <v>92</v>
@@ -60629,10 +60629,10 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -60652,10 +60652,10 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <v>84</v>
@@ -60706,10 +60706,10 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -60729,10 +60729,10 @@
         <v>72</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="F6">
         <v>80</v>
@@ -60783,10 +60783,10 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -60806,10 +60806,10 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>102.5</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -60860,10 +60860,10 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -60883,10 +60883,10 @@
         <v>72</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>60</v>
@@ -60937,10 +60937,10 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -60954,10 +60954,10 @@
         <v>993</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -60972,10 +60972,10 @@
         <v>0</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -60989,10 +60989,10 @@
         <v>72</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F10">
         <v>80</v>
@@ -61043,10 +61043,10 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -61066,10 +61066,10 @@
         <v>72</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F11">
         <v>60</v>
@@ -61120,10 +61120,10 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -61143,10 +61143,10 @@
         <v>80</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="F12">
         <v>76</v>
@@ -61197,10 +61197,10 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -61220,10 +61220,10 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -61274,10 +61274,10 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -61297,10 +61297,10 @@
         <v>72</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F14">
         <v>72</v>
@@ -61351,10 +61351,10 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -61374,10 +61374,10 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="F15">
         <v>96</v>
@@ -61428,10 +61428,10 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -61445,10 +61445,10 @@
         <v>1000</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -61463,10 +61463,10 @@
         <v>0</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -61480,10 +61480,10 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="F17">
         <v>72</v>
@@ -61534,10 +61534,10 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -61557,10 +61557,10 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="F18">
         <v>92</v>
@@ -61611,10 +61611,10 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -61675,10 +61675,10 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F20">
         <v>92</v>
@@ -61729,10 +61729,10 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -61752,10 +61752,10 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F21">
         <v>88</v>
@@ -61806,10 +61806,10 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -61829,10 +61829,10 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F22">
         <v>76</v>
@@ -61883,10 +61883,10 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -61906,10 +61906,10 @@
         <v>72</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="F23">
         <v>88</v>
@@ -61960,10 +61960,10 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -61983,10 +61983,10 @@
         <v>68</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="F24">
         <v>60</v>
@@ -62037,10 +62037,10 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -62060,10 +62060,10 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F25">
         <v>96</v>
@@ -62114,10 +62114,10 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -62137,10 +62137,10 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -62191,10 +62191,10 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -62375,7 +62375,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>95</v>
@@ -62438,7 +62438,7 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -62464,7 +62464,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="G5">
         <v>80</v>
@@ -62527,7 +62527,7 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB5">
         <v>10</v>
@@ -62553,7 +62553,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>95</v>
@@ -62616,7 +62616,7 @@
         <v>7</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -62642,7 +62642,7 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>90</v>
@@ -62705,7 +62705,7 @@
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>8</v>
@@ -62731,7 +62731,7 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>85</v>
@@ -62794,7 +62794,7 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -62820,7 +62820,7 @@
         <v>85</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>55</v>
@@ -62883,7 +62883,7 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -62909,7 +62909,7 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>95</v>
@@ -62972,7 +62972,7 @@
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>8</v>
@@ -62998,7 +62998,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -63061,7 +63061,7 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB11">
         <v>10</v>
@@ -63087,7 +63087,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>85</v>
@@ -63150,7 +63150,7 @@
         <v>6</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -63176,7 +63176,7 @@
         <v>85</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="G13">
         <v>70</v>
@@ -63239,7 +63239,7 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>7</v>
@@ -63265,7 +63265,7 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>90</v>
@@ -63328,7 +63328,7 @@
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>7</v>
@@ -63354,7 +63354,7 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -63417,7 +63417,7 @@
         <v>6</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>8</v>
@@ -63443,7 +63443,7 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>80</v>
@@ -63506,7 +63506,7 @@
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -63532,7 +63532,7 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>85</v>
@@ -63595,7 +63595,7 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>10</v>
@@ -63621,7 +63621,7 @@
         <v>100</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>85</v>
@@ -63684,7 +63684,7 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -63710,7 +63710,7 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>80</v>
@@ -63773,7 +63773,7 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -63799,7 +63799,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>95</v>
@@ -63862,7 +63862,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB20">
         <v>8</v>
@@ -63888,7 +63888,7 @@
         <v>100</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>90</v>
@@ -63951,7 +63951,7 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -63977,7 +63977,7 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>90</v>
@@ -64040,7 +64040,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -64066,7 +64066,7 @@
         <v>100</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -64129,7 +64129,7 @@
         <v>6</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>9</v>
@@ -64155,7 +64155,7 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>95</v>
@@ -64218,7 +64218,7 @@
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>9</v>
@@ -64244,7 +64244,7 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>95</v>
@@ -64307,7 +64307,7 @@
         <v>6</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB25">
         <v>10</v>
@@ -64333,7 +64333,7 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>90</v>
@@ -64396,7 +64396,7 @@
         <v>8</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB26">
         <v>10</v>
@@ -64422,7 +64422,7 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -64485,7 +64485,7 @@
         <v>7</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -64511,7 +64511,7 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>95</v>
@@ -64574,7 +64574,7 @@
         <v>7</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>10</v>
@@ -64600,7 +64600,7 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -64663,7 +64663,7 @@
         <v>7</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>10</v>
@@ -64689,7 +64689,7 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
@@ -64752,7 +64752,7 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB30">
         <v>10</v>
@@ -64778,7 +64778,7 @@
         <v>100</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>90</v>
@@ -64841,7 +64841,7 @@
         <v>8</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB31">
         <v>8</v>
@@ -64867,7 +64867,7 @@
         <v>100</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>95</v>
@@ -64930,7 +64930,7 @@
         <v>10</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB32">
         <v>10</v>
@@ -64956,7 +64956,7 @@
         <v>100</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>100</v>
@@ -65019,7 +65019,7 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB33">
         <v>7</v>
@@ -65045,7 +65045,7 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>100</v>
@@ -65108,7 +65108,7 @@
         <v>6</v>
       </c>
       <c r="AA34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB34">
         <v>8</v>
@@ -65134,7 +65134,7 @@
         <v>100</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="G35">
         <v>85</v>
@@ -65197,7 +65197,7 @@
         <v>7</v>
       </c>
       <c r="AA35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB35">
         <v>8</v>
@@ -65223,7 +65223,7 @@
         <v>100</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>80</v>
@@ -65286,7 +65286,7 @@
         <v>7</v>
       </c>
       <c r="AA36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB36">
         <v>10</v>
@@ -65312,7 +65312,7 @@
         <v>100</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>70</v>
@@ -65375,7 +65375,7 @@
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB37">
         <v>8</v>
@@ -65401,7 +65401,7 @@
         <v>100</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38">
         <v>100</v>
@@ -65464,7 +65464,7 @@
         <v>9</v>
       </c>
       <c r="AA38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB38">
         <v>10</v>
@@ -65490,7 +65490,7 @@
         <v>100</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -65553,7 +65553,7 @@
         <v>7</v>
       </c>
       <c r="AA39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB39">
         <v>10</v>
@@ -65579,7 +65579,7 @@
         <v>100</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G40">
         <v>85</v>
@@ -65642,7 +65642,7 @@
         <v>5</v>
       </c>
       <c r="AA40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB40">
         <v>6</v>
@@ -65668,7 +65668,7 @@
         <v>100</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41">
         <v>95</v>
@@ -65731,7 +65731,7 @@
         <v>6</v>
       </c>
       <c r="AA41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB41">
         <v>10</v>
@@ -65757,7 +65757,7 @@
         <v>100</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42">
         <v>90</v>
@@ -65820,7 +65820,7 @@
         <v>6</v>
       </c>
       <c r="AA42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB42">
         <v>8</v>
@@ -65973,7 +65973,7 @@
         <v>1011</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -66027,7 +66027,7 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -66050,7 +66050,7 @@
         <v>1012</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -66104,7 +66104,7 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -66127,7 +66127,7 @@
         <v>1013</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>95</v>
@@ -66181,7 +66181,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -66204,7 +66204,7 @@
         <v>1014</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -66258,7 +66258,7 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -66281,7 +66281,7 @@
         <v>1015</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -66335,7 +66335,7 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -66358,7 +66358,7 @@
         <v>1016</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -66412,7 +66412,7 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -66435,7 +66435,7 @@
         <v>1017</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>95</v>
@@ -66489,7 +66489,7 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -66512,7 +66512,7 @@
         <v>1018</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -66566,7 +66566,7 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -66589,7 +66589,7 @@
         <v>1019</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>90</v>
@@ -66643,7 +66643,7 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -66666,7 +66666,7 @@
         <v>1020</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -66720,7 +66720,7 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -66743,7 +66743,7 @@
         <v>1021</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -66797,7 +66797,7 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -66820,7 +66820,7 @@
         <v>1022</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -66874,7 +66874,7 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -66897,7 +66897,7 @@
         <v>1023</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -66951,7 +66951,7 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -66974,7 +66974,7 @@
         <v>1024</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -67028,7 +67028,7 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -67051,7 +67051,7 @@
         <v>1025</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -67105,7 +67105,7 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -67128,7 +67128,7 @@
         <v>1026</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -67182,7 +67182,7 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -67205,7 +67205,7 @@
         <v>1027</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -67259,7 +67259,7 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -67282,7 +67282,7 @@
         <v>1028</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -67336,7 +67336,7 @@
         <v>0</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -67359,7 +67359,7 @@
         <v>1029</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -67413,7 +67413,7 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>10</v>
@@ -67436,7 +67436,7 @@
         <v>1030</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -67490,7 +67490,7 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -67513,7 +67513,7 @@
         <v>1031</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -67567,7 +67567,7 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -67590,7 +67590,7 @@
         <v>1032</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -67644,7 +67644,7 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -67667,7 +67667,7 @@
         <v>1033</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -67721,7 +67721,7 @@
         <v>0</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -67744,7 +67744,7 @@
         <v>1034</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>95</v>
@@ -67798,7 +67798,7 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -67821,7 +67821,7 @@
         <v>1035</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -67875,7 +67875,7 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -67898,7 +67898,7 @@
         <v>1036</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>95</v>
@@ -67952,7 +67952,7 @@
         <v>0</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -70255,7 +70255,7 @@
         <v>1063</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="C13">
         <v>105</v>
@@ -70309,7 +70309,7 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -70486,7 +70486,7 @@
         <v>1066</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="C16">
         <v>105</v>
@@ -70540,7 +70540,7 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -70549,7 +70549,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -70640,7 +70640,7 @@
         <v>1068</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>105</v>
@@ -70694,7 +70694,7 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -70717,7 +70717,7 @@
         <v>1069</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C19">
         <v>105</v>
@@ -70771,7 +70771,7 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -71718,7 +71718,7 @@
         <v>1082</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C32">
         <v>105</v>
@@ -71772,7 +71772,7 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -71781,7 +71781,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -79876,7 +79876,7 @@
         <v>120</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>120</v>
@@ -79930,7 +79930,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -79953,7 +79953,7 @@
         <v>115</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>115</v>
@@ -80007,7 +80007,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -80030,7 +80030,7 @@
         <v>105</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>70</v>
@@ -80084,7 +80084,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -80107,7 +80107,7 @@
         <v>120</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>110</v>
@@ -80161,7 +80161,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -80184,7 +80184,7 @@
         <v>120</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>120</v>
@@ -80238,7 +80238,7 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -80261,7 +80261,7 @@
         <v>110</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>110</v>
@@ -80315,7 +80315,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -80338,7 +80338,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -80392,7 +80392,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -80415,7 +80415,7 @@
         <v>115</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>120</v>
@@ -80469,7 +80469,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -80492,7 +80492,7 @@
         <v>120</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>120</v>
@@ -80546,7 +80546,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -80569,7 +80569,7 @@
         <v>120</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>120</v>
@@ -80623,7 +80623,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -80646,7 +80646,7 @@
         <v>120</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>120</v>
@@ -80700,7 +80700,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -80723,7 +80723,7 @@
         <v>105</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>120</v>
@@ -80777,7 +80777,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -80800,7 +80800,7 @@
         <v>120</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>120</v>
@@ -80854,7 +80854,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -80877,7 +80877,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>90</v>
@@ -80931,7 +80931,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -80954,7 +80954,7 @@
         <v>115</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -81008,7 +81008,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -81031,7 +81031,7 @@
         <v>120</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>120</v>
@@ -81085,7 +81085,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -81108,7 +81108,7 @@
         <v>120</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>120</v>
@@ -81162,7 +81162,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -81185,7 +81185,7 @@
         <v>85</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="D21">
         <v>110</v>
@@ -81239,7 +81239,7 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -81262,7 +81262,7 @@
         <v>120</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>60</v>
@@ -81316,7 +81316,7 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -81339,7 +81339,7 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>110</v>
@@ -81393,7 +81393,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -81416,7 +81416,7 @@
         <v>120</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>120</v>
@@ -81470,7 +81470,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -81493,7 +81493,7 @@
         <v>110</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>95</v>
@@ -81547,7 +81547,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -81570,7 +81570,7 @@
         <v>120</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>120</v>
@@ -81624,7 +81624,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -81647,7 +81647,7 @@
         <v>120</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>120</v>
@@ -81701,7 +81701,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -81724,7 +81724,7 @@
         <v>115</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>120</v>
@@ -81778,7 +81778,7 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -81801,7 +81801,7 @@
         <v>115</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>120</v>
@@ -81855,7 +81855,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -81878,7 +81878,7 @@
         <v>120</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>120</v>
@@ -81932,7 +81932,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -81955,7 +81955,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -82009,7 +82009,7 @@
         <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -82032,7 +82032,7 @@
         <v>120</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>120</v>
@@ -82086,7 +82086,7 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -82109,7 +82109,7 @@
         <v>120</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>120</v>
@@ -82163,7 +82163,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -82186,7 +82186,7 @@
         <v>105</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>120</v>
@@ -82240,7 +82240,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -82263,7 +82263,7 @@
         <v>120</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>120</v>
@@ -82317,7 +82317,7 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>5</v>
@@ -82340,7 +82340,7 @@
         <v>120</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>120</v>
@@ -82394,7 +82394,7 @@
         <v>6</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -82417,7 +82417,7 @@
         <v>120</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>120</v>
@@ -82471,7 +82471,7 @@
         <v>7</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>6</v>
@@ -82494,7 +82494,7 @@
         <v>120</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>110</v>
@@ -82548,7 +82548,7 @@
         <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -82571,7 +82571,7 @@
         <v>90</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>120</v>
@@ -82625,7 +82625,7 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>5</v>
@@ -82648,7 +82648,7 @@
         <v>110</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>110</v>
@@ -82702,7 +82702,7 @@
         <v>5</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V40">
         <v>5</v>
@@ -82725,7 +82725,7 @@
         <v>120</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>120</v>
@@ -82779,7 +82779,7 @@
         <v>7</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -82802,7 +82802,7 @@
         <v>120</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>120</v>
@@ -82856,7 +82856,7 @@
         <v>7</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V42">
         <v>8</v>
@@ -82879,7 +82879,7 @@
         <v>120</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>120</v>
@@ -82933,7 +82933,7 @@
         <v>9</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V43">
         <v>9</v>
@@ -82956,7 +82956,7 @@
         <v>115</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D44">
         <v>120</v>
@@ -83010,7 +83010,7 @@
         <v>6</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V44">
         <v>7</v>
@@ -86105,7 +86105,7 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>106.7</v>
@@ -86168,7 +86168,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>7</v>
@@ -86194,7 +86194,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>106.7</v>
@@ -86257,7 +86257,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -86283,7 +86283,7 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>106.7</v>
@@ -86346,7 +86346,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -86372,7 +86372,7 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>106.7</v>
@@ -86435,7 +86435,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>8</v>
@@ -86502,7 +86502,7 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>106.7</v>
@@ -86565,7 +86565,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -86591,7 +86591,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>106.7</v>
@@ -86654,7 +86654,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>7</v>
@@ -86680,7 +86680,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>106.7</v>
@@ -86743,7 +86743,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -86769,7 +86769,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>106.7</v>
@@ -86832,7 +86832,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>8</v>
@@ -86858,7 +86858,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>106.7</v>
@@ -86921,7 +86921,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>7</v>
@@ -86947,7 +86947,7 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>106.7</v>
@@ -87010,7 +87010,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -87036,7 +87036,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>106.7</v>
@@ -87099,7 +87099,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>6</v>
@@ -87125,7 +87125,7 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>106.7</v>
@@ -87188,7 +87188,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -87214,7 +87214,7 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>106.7</v>
@@ -87277,7 +87277,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>9</v>
@@ -87303,7 +87303,7 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>106.7</v>
@@ -87366,7 +87366,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>6</v>
@@ -87392,7 +87392,7 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>106.7</v>
@@ -87455,7 +87455,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -87481,7 +87481,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>106.7</v>
@@ -87544,7 +87544,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -87570,7 +87570,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>106.7</v>
@@ -87633,7 +87633,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -87659,7 +87659,7 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>106.7</v>
@@ -87722,7 +87722,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>6</v>
@@ -87748,7 +87748,7 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>106.7</v>
@@ -87811,7 +87811,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>10</v>
@@ -87837,7 +87837,7 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>106.7</v>
@@ -87900,7 +87900,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -87926,7 +87926,7 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>106.7</v>
@@ -87989,7 +87989,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>10</v>
@@ -88015,7 +88015,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>106.7</v>
@@ -88078,7 +88078,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>10</v>
@@ -88104,7 +88104,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>106.7</v>
@@ -88167,7 +88167,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>10</v>
@@ -88193,7 +88193,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>106.7</v>
@@ -88256,7 +88256,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>7</v>
@@ -88282,7 +88282,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>106.7</v>
@@ -88345,7 +88345,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>8</v>
@@ -88371,7 +88371,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>106.7</v>
@@ -88434,7 +88434,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>9</v>
@@ -88460,7 +88460,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>106.7</v>
@@ -88523,7 +88523,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -88549,7 +88549,7 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>106.7</v>
@@ -88612,7 +88612,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z32">
         <v>9</v>
@@ -88638,7 +88638,7 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>106.7</v>
@@ -88701,7 +88701,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>10</v>
@@ -88727,7 +88727,7 @@
         <v>100</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>106.7</v>
@@ -88790,7 +88790,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>8</v>
@@ -88816,7 +88816,7 @@
         <v>100</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>106.7</v>
@@ -88879,7 +88879,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z35">
         <v>10</v>
@@ -88905,7 +88905,7 @@
         <v>100</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>106.7</v>
@@ -88968,7 +88968,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z36">
         <v>8</v>
@@ -88994,7 +88994,7 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E37">
         <v>106.7</v>
@@ -89057,7 +89057,7 @@
         <v>9</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z37">
         <v>8</v>
@@ -89083,7 +89083,7 @@
         <v>100</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E38">
         <v>106.7</v>
@@ -89146,7 +89146,7 @@
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z38">
         <v>9</v>
@@ -89172,7 +89172,7 @@
         <v>100</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E39">
         <v>106.7</v>
@@ -89235,7 +89235,7 @@
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z39">
         <v>5</v>
@@ -89261,7 +89261,7 @@
         <v>100</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E40">
         <v>106.7</v>
@@ -89324,7 +89324,7 @@
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z40">
         <v>10</v>
@@ -89350,7 +89350,7 @@
         <v>100</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E41">
         <v>106.7</v>
@@ -89413,7 +89413,7 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z41">
         <v>5</v>
@@ -89439,7 +89439,7 @@
         <v>100</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42">
         <v>106.7</v>
@@ -89502,7 +89502,7 @@
         <v>9</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z42">
         <v>6</v>
@@ -89528,7 +89528,7 @@
         <v>100</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>106.7</v>
@@ -89591,7 +89591,7 @@
         <v>9</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z43">
         <v>5</v>
@@ -89617,7 +89617,7 @@
         <v>100</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E44">
         <v>106.7</v>
@@ -89680,7 +89680,7 @@
         <v>10</v>
       </c>
       <c r="Y44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z44">
         <v>7</v>
@@ -89706,7 +89706,7 @@
         <v>100</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45">
         <v>106.7</v>
@@ -89769,7 +89769,7 @@
         <v>9</v>
       </c>
       <c r="Y45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z45">
         <v>5</v>
@@ -91368,13 +91368,13 @@
         <v>358</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D20">
         <v>83.3</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H20">
         <v>106.7</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -6606,7 +6606,7 @@
         <v>372</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -6683,7 +6683,7 @@
         <v>373</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6737,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -6760,7 +6760,7 @@
         <v>374</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -6814,7 +6814,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -6837,7 +6837,7 @@
         <v>375</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>95</v>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -6914,7 +6914,7 @@
         <v>376</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -6968,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -6991,7 +6991,7 @@
         <v>377</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>90</v>
@@ -7045,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -7068,7 +7068,7 @@
         <v>378</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -7122,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -7145,7 +7145,7 @@
         <v>379</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>95</v>
@@ -7199,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -7222,7 +7222,7 @@
         <v>380</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>95</v>
@@ -7276,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -7299,7 +7299,7 @@
         <v>381</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -7353,7 +7353,7 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -7376,7 +7376,7 @@
         <v>382</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>95</v>
@@ -7430,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -7453,7 +7453,7 @@
         <v>383</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>85</v>
@@ -7507,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>384</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -7607,7 +7607,7 @@
         <v>385</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>85</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -7684,7 +7684,7 @@
         <v>386</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>80</v>
@@ -7738,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -7761,7 +7761,7 @@
         <v>387</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>85</v>
@@ -7815,7 +7815,7 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -7838,7 +7838,7 @@
         <v>388</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -7892,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -7915,7 +7915,7 @@
         <v>389</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>60</v>
@@ -7969,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -7992,7 +7992,7 @@
         <v>390</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -8046,7 +8046,7 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -8069,7 +8069,7 @@
         <v>391</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>50</v>
@@ -8123,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -8146,7 +8146,7 @@
         <v>392</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>85</v>
@@ -8200,7 +8200,7 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -8223,7 +8223,7 @@
         <v>393</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -8277,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>9</v>
@@ -8300,7 +8300,7 @@
         <v>394</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -8354,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -8377,7 +8377,7 @@
         <v>395</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="C27">
         <v>45</v>
@@ -8431,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -8454,7 +8454,7 @@
         <v>396</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -8508,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>6</v>
@@ -8531,7 +8531,7 @@
         <v>397</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -8585,7 +8585,7 @@
         <v>0</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -8608,7 +8608,7 @@
         <v>398</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>90</v>
@@ -8662,7 +8662,7 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -8685,7 +8685,7 @@
         <v>399</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>90</v>
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -8762,7 +8762,7 @@
         <v>400</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>401</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>95</v>
@@ -8893,7 +8893,7 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -8916,7 +8916,7 @@
         <v>402</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -8993,7 +8993,7 @@
         <v>403</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -9047,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -9070,7 +9070,7 @@
         <v>404</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>85</v>
@@ -9124,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>7</v>
@@ -9147,7 +9147,7 @@
         <v>405</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>95</v>
@@ -9201,7 +9201,7 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -9224,7 +9224,7 @@
         <v>406</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -9278,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
         <v>10</v>
@@ -9301,7 +9301,7 @@
         <v>407</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -9355,7 +9355,7 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -9378,7 +9378,7 @@
         <v>408</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>95</v>
@@ -9432,7 +9432,7 @@
         <v>0</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>7</v>
@@ -9455,7 +9455,7 @@
         <v>409</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C41">
         <v>90</v>
@@ -9509,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U41">
         <v>7</v>
@@ -9693,7 +9693,7 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>106.7</v>
@@ -9756,7 +9756,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -9782,7 +9782,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>106.7</v>
@@ -9845,7 +9845,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>9</v>
@@ -9871,7 +9871,7 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>106.7</v>
@@ -9934,7 +9934,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>10</v>
@@ -9960,7 +9960,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -10023,7 +10023,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -10049,7 +10049,7 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>106.7</v>
@@ -10112,7 +10112,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>9</v>
@@ -10138,7 +10138,7 @@
         <v>70</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>106.7</v>
@@ -10201,7 +10201,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -10227,7 +10227,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>106.7</v>
@@ -10290,7 +10290,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -10316,7 +10316,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>106.7</v>
@@ -10379,7 +10379,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -10405,7 +10405,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>106.7</v>
@@ -10468,7 +10468,7 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -10494,7 +10494,7 @@
         <v>80</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>106.7</v>
@@ -10557,7 +10557,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -10583,7 +10583,7 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>106.7</v>
@@ -10646,7 +10646,7 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -10672,7 +10672,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>106.7</v>
@@ -10735,7 +10735,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>6</v>
@@ -10761,7 +10761,7 @@
         <v>70</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>106.7</v>
@@ -10824,7 +10824,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -10850,7 +10850,7 @@
         <v>70</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>106.7</v>
@@ -10913,7 +10913,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>5</v>
@@ -10939,7 +10939,7 @@
         <v>70</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>106.7</v>
@@ -11002,7 +11002,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -11028,7 +11028,7 @@
         <v>70</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -11091,7 +11091,7 @@
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -11117,7 +11117,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>106.7</v>
@@ -11180,7 +11180,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>10</v>
@@ -11206,7 +11206,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>106.7</v>
@@ -11269,7 +11269,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>8</v>
@@ -11295,7 +11295,7 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>106.7</v>
@@ -11358,7 +11358,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -11384,7 +11384,7 @@
         <v>50</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E23">
         <v>106.7</v>
@@ -11447,7 +11447,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>6</v>
@@ -11473,7 +11473,7 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>106.7</v>
@@ -11536,7 +11536,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -11562,7 +11562,7 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>106.7</v>
@@ -11625,7 +11625,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>6</v>
@@ -11651,7 +11651,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>106.7</v>
@@ -11714,7 +11714,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>6</v>
@@ -11740,7 +11740,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>106.7</v>
@@ -11803,7 +11803,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>10</v>
@@ -11829,7 +11829,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>106.7</v>
@@ -11892,7 +11892,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>10</v>
@@ -11918,7 +11918,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>106.7</v>
@@ -11981,7 +11981,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>7</v>
@@ -12007,7 +12007,7 @@
         <v>60</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E30">
         <v>106.7</v>
@@ -12070,7 +12070,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z30">
         <v>6</v>
@@ -12096,7 +12096,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>106.7</v>
@@ -12159,7 +12159,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z31">
         <v>10</v>
@@ -23051,7 +23051,7 @@
         <v>105</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>132</v>
@@ -23105,7 +23105,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -23128,7 +23128,7 @@
         <v>105</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>132</v>
@@ -23182,7 +23182,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -23205,7 +23205,7 @@
         <v>105</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>132</v>
@@ -23259,7 +23259,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -23282,7 +23282,7 @@
         <v>105</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>132</v>
@@ -23336,7 +23336,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -23359,7 +23359,7 @@
         <v>105</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>132</v>
@@ -23413,7 +23413,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -23436,7 +23436,7 @@
         <v>105</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>132</v>
@@ -23490,7 +23490,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -23513,7 +23513,7 @@
         <v>105</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>132</v>
@@ -23567,7 +23567,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -23590,7 +23590,7 @@
         <v>105</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>132</v>
@@ -23644,7 +23644,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -23667,7 +23667,7 @@
         <v>105</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>132</v>
@@ -23721,7 +23721,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -23744,7 +23744,7 @@
         <v>105</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>132</v>
@@ -23798,7 +23798,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -23821,7 +23821,7 @@
         <v>105</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>132</v>
@@ -23875,7 +23875,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -23898,7 +23898,7 @@
         <v>105</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>132</v>
@@ -23952,7 +23952,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -23975,7 +23975,7 @@
         <v>105</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>132</v>
@@ -24029,7 +24029,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -24052,7 +24052,7 @@
         <v>105</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>132</v>
@@ -24106,7 +24106,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -24129,7 +24129,7 @@
         <v>105</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>132</v>
@@ -24183,7 +24183,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -24206,7 +24206,7 @@
         <v>105</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>132</v>
@@ -24260,7 +24260,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -24283,7 +24283,7 @@
         <v>105</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>132</v>
@@ -24337,7 +24337,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -24360,7 +24360,7 @@
         <v>105</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>128</v>
@@ -24414,7 +24414,7 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -24437,7 +24437,7 @@
         <v>105</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>132</v>
@@ -24491,7 +24491,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -24514,7 +24514,7 @@
         <v>105</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>132</v>
@@ -24568,7 +24568,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -24591,7 +24591,7 @@
         <v>105</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>132</v>
@@ -24645,7 +24645,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -24668,7 +24668,7 @@
         <v>105</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>132</v>
@@ -24722,7 +24722,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -24745,7 +24745,7 @@
         <v>105</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>132</v>
@@ -24799,7 +24799,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -24822,7 +24822,7 @@
         <v>105</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>132</v>
@@ -24876,7 +24876,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -24899,7 +24899,7 @@
         <v>105</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>132</v>
@@ -24953,7 +24953,7 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -24976,7 +24976,7 @@
         <v>105</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>132</v>
@@ -25030,7 +25030,7 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -25053,7 +25053,7 @@
         <v>105</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>132</v>
@@ -25107,7 +25107,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -25130,7 +25130,7 @@
         <v>105</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>132</v>
@@ -25184,7 +25184,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -25207,7 +25207,7 @@
         <v>105</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>132</v>
@@ -25261,7 +25261,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -25284,7 +25284,7 @@
         <v>105</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>132</v>
@@ -25338,7 +25338,7 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -25361,7 +25361,7 @@
         <v>105</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>132</v>
@@ -25415,7 +25415,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -25438,7 +25438,7 @@
         <v>105</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>132</v>
@@ -25492,7 +25492,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -25515,7 +25515,7 @@
         <v>105</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>132</v>
@@ -25569,7 +25569,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>10</v>
@@ -25592,7 +25592,7 @@
         <v>105</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>132</v>
@@ -25646,7 +25646,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>10</v>
@@ -25669,7 +25669,7 @@
         <v>105</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>124</v>
@@ -25723,7 +25723,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>9</v>
@@ -25746,7 +25746,7 @@
         <v>105</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>132</v>
@@ -25800,7 +25800,7 @@
         <v>9</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>9</v>
@@ -30863,7 +30863,7 @@
         <v>95</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E4">
         <v>85</v>
@@ -30917,7 +30917,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -30969,7 +30969,7 @@
         <v>85</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="E6">
         <v>85</v>
@@ -31023,7 +31023,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -31046,7 +31046,7 @@
         <v>95</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -31100,7 +31100,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -31123,7 +31123,7 @@
         <v>80</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -31177,7 +31177,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -31200,7 +31200,7 @@
         <v>60</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="E9">
         <v>50</v>
@@ -31254,7 +31254,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -31277,7 +31277,7 @@
         <v>40</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="E10">
         <v>85</v>
@@ -31331,7 +31331,7 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -31354,7 +31354,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -31408,7 +31408,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -31431,7 +31431,7 @@
         <v>95</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -31485,7 +31485,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -31508,7 +31508,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -31562,7 +31562,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -31585,7 +31585,7 @@
         <v>80</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E14">
         <v>85</v>
@@ -31639,7 +31639,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -31662,7 +31662,7 @@
         <v>95</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="E15">
         <v>80</v>
@@ -31716,7 +31716,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -31739,7 +31739,7 @@
         <v>80</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>95</v>
@@ -31793,7 +31793,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -31816,7 +31816,7 @@
         <v>60</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -31870,7 +31870,7 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -31958,7 +31958,7 @@
         <v>80</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="E19">
         <v>80</v>
@@ -32012,7 +32012,7 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -32035,7 +32035,7 @@
         <v>40</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="E20">
         <v>70</v>
@@ -32089,7 +32089,7 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -32112,7 +32112,7 @@
         <v>80</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -32166,7 +32166,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -32189,7 +32189,7 @@
         <v>95</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E22">
         <v>85</v>
@@ -32243,7 +32243,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -32266,7 +32266,7 @@
         <v>85</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E23">
         <v>85</v>
@@ -32320,7 +32320,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -32372,7 +32372,7 @@
         <v>85</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E25">
         <v>65</v>
@@ -32426,7 +32426,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -32449,7 +32449,7 @@
         <v>85</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -32503,7 +32503,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -32526,7 +32526,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -32580,7 +32580,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -32603,7 +32603,7 @@
         <v>50</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="E28">
         <v>70</v>
@@ -32657,7 +32657,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -32680,7 +32680,7 @@
         <v>85</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E29">
         <v>90</v>
@@ -32734,7 +32734,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -32757,7 +32757,7 @@
         <v>90</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E30">
         <v>90</v>
@@ -32811,7 +32811,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -32834,7 +32834,7 @@
         <v>65</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="E31">
         <v>80</v>
@@ -32888,7 +32888,7 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -32911,7 +32911,7 @@
         <v>95</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -32965,7 +32965,7 @@
         <v>5</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>7</v>
@@ -32988,7 +32988,7 @@
         <v>60</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -33042,7 +33042,7 @@
         <v>5</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -33065,7 +33065,7 @@
         <v>80</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E34">
         <v>90</v>
@@ -33119,7 +33119,7 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -33142,7 +33142,7 @@
         <v>85</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -33196,7 +33196,7 @@
         <v>6</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -33219,7 +33219,7 @@
         <v>65</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E36">
         <v>10</v>
@@ -33273,7 +33273,7 @@
         <v>5</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -40294,7 +40294,7 @@
         <v>96</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F4">
         <v>120</v>
@@ -40357,7 +40357,7 @@
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>6</v>
@@ -40383,7 +40383,7 @@
         <v>96</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>120</v>
@@ -40446,7 +40446,7 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -40472,7 +40472,7 @@
         <v>96</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F6">
         <v>120</v>
@@ -40535,7 +40535,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -40561,7 +40561,7 @@
         <v>96</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F7">
         <v>120</v>
@@ -40624,7 +40624,7 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA7">
         <v>9</v>
@@ -40650,7 +40650,7 @@
         <v>96</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F8">
         <v>120</v>
@@ -40713,7 +40713,7 @@
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -40739,7 +40739,7 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -40802,7 +40802,7 @@
         <v>5</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>5</v>
@@ -40828,7 +40828,7 @@
         <v>96</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F10">
         <v>120</v>
@@ -40891,7 +40891,7 @@
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -40917,7 +40917,7 @@
         <v>96</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F11">
         <v>120</v>
@@ -40980,7 +40980,7 @@
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -41006,7 +41006,7 @@
         <v>96</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F12">
         <v>120</v>
@@ -41069,7 +41069,7 @@
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>9</v>
@@ -41095,7 +41095,7 @@
         <v>96</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F13">
         <v>120</v>
@@ -41158,7 +41158,7 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA13">
         <v>10</v>
@@ -41184,7 +41184,7 @@
         <v>84</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -41247,7 +41247,7 @@
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>6</v>
@@ -41273,7 +41273,7 @@
         <v>96</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F15">
         <v>120</v>
@@ -41336,7 +41336,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>10</v>
@@ -41362,7 +41362,7 @@
         <v>96</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>120</v>
@@ -41425,7 +41425,7 @@
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -41451,7 +41451,7 @@
         <v>96</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F17">
         <v>120</v>
@@ -41514,7 +41514,7 @@
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -41540,7 +41540,7 @@
         <v>96</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F18">
         <v>120</v>
@@ -41603,7 +41603,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>6</v>
@@ -41629,7 +41629,7 @@
         <v>96</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F19">
         <v>120</v>
@@ -41692,7 +41692,7 @@
         <v>9</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -41718,7 +41718,7 @@
         <v>96</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F20">
         <v>120</v>
@@ -41781,7 +41781,7 @@
         <v>6</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>8</v>
@@ -41807,7 +41807,7 @@
         <v>96</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F21">
         <v>113.3</v>
@@ -41870,7 +41870,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>6</v>
@@ -41896,7 +41896,7 @@
         <v>96</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F22">
         <v>120</v>
@@ -41959,7 +41959,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -41985,7 +41985,7 @@
         <v>96</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F23">
         <v>120</v>
@@ -42048,7 +42048,7 @@
         <v>6</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -42074,7 +42074,7 @@
         <v>96</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F24">
         <v>120</v>
@@ -42137,7 +42137,7 @@
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -42163,7 +42163,7 @@
         <v>96</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F25">
         <v>106.7</v>
@@ -42226,7 +42226,7 @@
         <v>5</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA25">
         <v>6</v>
@@ -42252,7 +42252,7 @@
         <v>96</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>120</v>
@@ -42315,7 +42315,7 @@
         <v>5</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA26">
         <v>6</v>
@@ -42341,7 +42341,7 @@
         <v>80</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -42404,7 +42404,7 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA27">
         <v>5</v>
@@ -42430,7 +42430,7 @@
         <v>96</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F28">
         <v>106.7</v>
@@ -42493,7 +42493,7 @@
         <v>6</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>7</v>
@@ -42519,7 +42519,7 @@
         <v>96</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F29">
         <v>113.3</v>
@@ -42582,7 +42582,7 @@
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -42608,7 +42608,7 @@
         <v>76</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F30">
         <v>93.3</v>
@@ -42671,7 +42671,7 @@
         <v>5</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA30">
         <v>6</v>
@@ -42697,7 +42697,7 @@
         <v>96</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F31">
         <v>120</v>
@@ -42760,7 +42760,7 @@
         <v>5</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA31">
         <v>9</v>
@@ -42786,7 +42786,7 @@
         <v>96</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F32">
         <v>120</v>
@@ -42849,7 +42849,7 @@
         <v>6</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA32">
         <v>9</v>
@@ -42875,7 +42875,7 @@
         <v>96</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F33">
         <v>120</v>
@@ -42938,7 +42938,7 @@
         <v>6</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>9</v>
@@ -43100,7 +43100,7 @@
         <v>105.7</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>93.3</v>
@@ -43154,7 +43154,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -43177,7 +43177,7 @@
         <v>105.7</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>60</v>
@@ -43231,7 +43231,7 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -43254,7 +43254,7 @@
         <v>105.7</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -43308,7 +43308,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -43331,7 +43331,7 @@
         <v>105.7</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -43385,7 +43385,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -43408,7 +43408,7 @@
         <v>105.7</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -43462,7 +43462,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -43485,7 +43485,7 @@
         <v>105.7</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -43539,7 +43539,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -43562,7 +43562,7 @@
         <v>105.7</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -43616,7 +43616,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -43639,7 +43639,7 @@
         <v>105.7</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -43693,7 +43693,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -43716,7 +43716,7 @@
         <v>105.7</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E12">
         <v>93.3</v>
@@ -43770,7 +43770,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -43793,7 +43793,7 @@
         <v>105.7</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -43847,7 +43847,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -43870,7 +43870,7 @@
         <v>105.7</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -43924,7 +43924,7 @@
         <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -43947,7 +43947,7 @@
         <v>105.7</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -44001,7 +44001,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -44024,7 +44024,7 @@
         <v>105.7</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -44078,7 +44078,7 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -44101,7 +44101,7 @@
         <v>105.7</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -44155,7 +44155,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -44178,7 +44178,7 @@
         <v>105.7</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -44232,7 +44232,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -44255,7 +44255,7 @@
         <v>105.7</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -44309,7 +44309,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -44332,7 +44332,7 @@
         <v>105.7</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -44386,7 +44386,7 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -44409,7 +44409,7 @@
         <v>105.7</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -44436,7 +44436,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -44450,7 +44450,7 @@
         <v>105.7</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -44504,7 +44504,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -44527,7 +44527,7 @@
         <v>105.7</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -44581,7 +44581,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -44604,7 +44604,7 @@
         <v>105.7</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -44658,7 +44658,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -44681,7 +44681,7 @@
         <v>105.7</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -44735,7 +44735,7 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -44758,7 +44758,7 @@
         <v>105.7</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -44812,7 +44812,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -44835,7 +44835,7 @@
         <v>105.7</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -44889,7 +44889,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -44912,7 +44912,7 @@
         <v>105.7</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -44966,7 +44966,7 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -44989,7 +44989,7 @@
         <v>105.7</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -45043,7 +45043,7 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -45066,7 +45066,7 @@
         <v>105.7</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -45120,7 +45120,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -45143,7 +45143,7 @@
         <v>105.7</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E31">
         <v>100</v>
@@ -45197,7 +45197,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -45220,7 +45220,7 @@
         <v>105.7</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -45274,7 +45274,7 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -45297,7 +45297,7 @@
         <v>105.7</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -45351,7 +45351,7 @@
         <v>6</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -45374,7 +45374,7 @@
         <v>105.7</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -45428,7 +45428,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -45451,7 +45451,7 @@
         <v>105.7</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -45505,7 +45505,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -45528,7 +45528,7 @@
         <v>105.7</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E36">
         <v>100</v>
@@ -45582,7 +45582,7 @@
         <v>9</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -45741,7 +45741,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -45795,7 +45795,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -45818,7 +45818,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -45872,7 +45872,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -45895,7 +45895,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -45949,7 +45949,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -45972,7 +45972,7 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -46026,7 +46026,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -46049,7 +46049,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -46103,7 +46103,7 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -46126,7 +46126,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -46180,7 +46180,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -46203,7 +46203,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -46257,7 +46257,7 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -46280,7 +46280,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -46334,7 +46334,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -46357,7 +46357,7 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -46411,7 +46411,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -46434,7 +46434,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -46488,7 +46488,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -46511,7 +46511,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -46565,7 +46565,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -46588,7 +46588,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -46642,7 +46642,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -46665,7 +46665,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -46719,7 +46719,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -46742,7 +46742,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -46796,7 +46796,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -46819,7 +46819,7 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -46873,7 +46873,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -46896,7 +46896,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -46950,7 +46950,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -46973,7 +46973,7 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -47027,7 +47027,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -47050,7 +47050,7 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -47104,7 +47104,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -47127,7 +47127,7 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -47181,7 +47181,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -47204,7 +47204,7 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -47258,7 +47258,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -47281,7 +47281,7 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -47335,7 +47335,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -47358,7 +47358,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -47412,7 +47412,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -47435,7 +47435,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -47489,7 +47489,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -47512,7 +47512,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -47566,7 +47566,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -47589,7 +47589,7 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -47643,7 +47643,7 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -47666,7 +47666,7 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -47720,7 +47720,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -47743,7 +47743,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -47797,7 +47797,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -47820,7 +47820,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -47874,7 +47874,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -47897,7 +47897,7 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -47951,7 +47951,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>6</v>
@@ -47974,7 +47974,7 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D33">
         <v>100</v>
@@ -48028,7 +48028,7 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -48051,7 +48051,7 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -48105,7 +48105,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -48128,7 +48128,7 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -48182,7 +48182,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>7</v>
@@ -48205,7 +48205,7 @@
         <v>100</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -48259,7 +48259,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -54652,7 +54652,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -54715,7 +54715,7 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -54741,7 +54741,7 @@
         <v>86.7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -54804,7 +54804,7 @@
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -54830,7 +54830,7 @@
         <v>63.3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G6">
         <v>70</v>
@@ -54893,7 +54893,7 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB6">
         <v>5</v>
@@ -54919,7 +54919,7 @@
         <v>83.3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -54982,7 +54982,7 @@
         <v>9</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>6</v>
@@ -55008,7 +55008,7 @@
         <v>63.3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>85</v>
@@ -55071,7 +55071,7 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB8">
         <v>5</v>
@@ -55097,7 +55097,7 @@
         <v>96.7</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -55160,7 +55160,7 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>6</v>
@@ -55186,7 +55186,7 @@
         <v>83.3</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>90</v>
@@ -55249,7 +55249,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -55275,7 +55275,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -55338,7 +55338,7 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>6</v>
@@ -55364,7 +55364,7 @@
         <v>73.3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G12">
         <v>70</v>
@@ -55427,7 +55427,7 @@
         <v>8</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -55453,7 +55453,7 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>85</v>
@@ -55516,7 +55516,7 @@
         <v>9</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -55542,7 +55542,7 @@
         <v>63.3</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G14">
         <v>85</v>
@@ -55605,7 +55605,7 @@
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB14">
         <v>5</v>
@@ -55631,7 +55631,7 @@
         <v>86.7</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -55694,7 +55694,7 @@
         <v>10</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>5</v>
@@ -55720,7 +55720,7 @@
         <v>66.7</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G16">
         <v>85</v>
@@ -55783,7 +55783,7 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB16">
         <v>5</v>
@@ -55809,7 +55809,7 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -55872,7 +55872,7 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB17">
         <v>6</v>
@@ -55975,7 +55975,7 @@
         <v>93.3</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G19">
         <v>95</v>
@@ -56038,7 +56038,7 @@
         <v>10</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>6</v>
@@ -56064,7 +56064,7 @@
         <v>83.3</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G20">
         <v>75</v>
@@ -56127,7 +56127,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB20">
         <v>5</v>
@@ -56153,7 +56153,7 @@
         <v>86.7</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G21">
         <v>90</v>
@@ -56216,7 +56216,7 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB21">
         <v>5</v>
@@ -56242,7 +56242,7 @@
         <v>66.7</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G22">
         <v>75</v>
@@ -56305,7 +56305,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -56331,7 +56331,7 @@
         <v>76.7</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>85</v>
@@ -56394,7 +56394,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB23">
         <v>6</v>
@@ -56420,7 +56420,7 @@
         <v>66.7</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G24">
         <v>85</v>
@@ -56483,7 +56483,7 @@
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>6</v>
@@ -56509,7 +56509,7 @@
         <v>93.3</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>90</v>
@@ -56572,7 +56572,7 @@
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB25">
         <v>6</v>
@@ -56598,7 +56598,7 @@
         <v>90</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -56661,7 +56661,7 @@
         <v>10</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>6</v>
@@ -56687,7 +56687,7 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -56750,7 +56750,7 @@
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB27">
         <v>7</v>
@@ -56776,7 +56776,7 @@
         <v>66.7</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>85</v>
@@ -56839,7 +56839,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -73669,7 +73669,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>120</v>
@@ -73723,7 +73723,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -73746,7 +73746,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>115</v>
@@ -73800,7 +73800,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -73823,7 +73823,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>115</v>
@@ -73877,7 +73877,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -73900,7 +73900,7 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>120</v>
@@ -73954,7 +73954,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -73977,7 +73977,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>110</v>
@@ -74031,7 +74031,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -74054,7 +74054,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>120</v>
@@ -74108,7 +74108,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -74131,7 +74131,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -74185,7 +74185,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -74208,7 +74208,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>120</v>
@@ -74262,7 +74262,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -74285,7 +74285,7 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>120</v>
@@ -74339,7 +74339,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -74362,7 +74362,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>115</v>
@@ -74416,7 +74416,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -74439,7 +74439,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>115</v>
@@ -74493,7 +74493,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -74516,7 +74516,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>120</v>
@@ -74570,7 +74570,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -74593,7 +74593,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>120</v>
@@ -74647,7 +74647,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -74670,7 +74670,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -74724,7 +74724,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -74747,7 +74747,7 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>115</v>
@@ -74801,7 +74801,7 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -74878,7 +74878,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -74901,7 +74901,7 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>120</v>
@@ -74955,7 +74955,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -74978,7 +74978,7 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>110</v>
@@ -75032,7 +75032,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -75055,7 +75055,7 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>110</v>
@@ -75109,7 +75109,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -75132,7 +75132,7 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -75186,7 +75186,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>6</v>
@@ -75209,7 +75209,7 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>120</v>
@@ -75263,7 +75263,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -75286,7 +75286,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>115</v>
@@ -75340,7 +75340,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -75363,7 +75363,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>120</v>
@@ -75417,7 +75417,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -75440,7 +75440,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>120</v>
@@ -75494,7 +75494,7 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -75517,7 +75517,7 @@
         <v>90</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -75571,7 +75571,7 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -75594,7 +75594,7 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>120</v>
@@ -75648,7 +75648,7 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -75671,7 +75671,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>120</v>
@@ -75725,7 +75725,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -75748,7 +75748,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>110</v>
@@ -75802,7 +75802,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -75825,7 +75825,7 @@
         <v>4</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="D32">
         <v>30</v>
@@ -75879,7 +75879,7 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -75902,7 +75902,7 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>120</v>
@@ -75956,7 +75956,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -75979,7 +75979,7 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>120</v>
@@ -76033,7 +76033,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -76056,7 +76056,7 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>105</v>
@@ -76110,7 +76110,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -76133,7 +76133,7 @@
         <v>100</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>120</v>
@@ -76187,7 +76187,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -76210,7 +76210,7 @@
         <v>100</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>120</v>
@@ -76264,7 +76264,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -76287,7 +76287,7 @@
         <v>100</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -76341,7 +76341,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -76364,7 +76364,7 @@
         <v>100</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>120</v>
@@ -76418,7 +76418,7 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>8</v>
@@ -76441,7 +76441,7 @@
         <v>100</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>120</v>
@@ -76495,7 +76495,7 @@
         <v>8</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -76518,7 +76518,7 @@
         <v>100</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>115</v>
@@ -76572,7 +76572,7 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -76595,7 +76595,7 @@
         <v>100</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>115</v>
@@ -76649,7 +76649,7 @@
         <v>10</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>7</v>
@@ -76672,7 +76672,7 @@
         <v>100</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>120</v>
@@ -76726,7 +76726,7 @@
         <v>7</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V43">
         <v>6</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3913" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3917" uniqueCount="1108">
   <si>
     <t>Materia</t>
   </si>
@@ -2781,6 +2781,9 @@
     <t>ROJAS MORENO ALONDRA YURIDIA</t>
   </si>
   <si>
+    <t>ROMERO RAMIREZ CITLALI ESPERANZA</t>
+  </si>
+  <si>
     <t>RUGERIO SANCHEZ KIMBERLY</t>
   </si>
   <si>
@@ -2923,6 +2926,9 @@
   </si>
   <si>
     <t>JUAREZ JUAREZ NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>MARTINEZ JIMENEZ MICHEL</t>
   </si>
   <si>
     <t>MAYAHUA TETLACTLE OSCAR</t>
@@ -17780,7 +17786,7 @@
         <v>507</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>96</v>
@@ -51322,7 +51328,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -53509,7 +53515,7 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -53572,7 +53578,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -53862,25 +53868,25 @@
         <v>911</v>
       </c>
       <c r="B32">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>105.7</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>106.7</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -53925,25 +53931,25 @@
         <v>0</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="AC32">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -53951,19 +53957,19 @@
         <v>912</v>
       </c>
       <c r="B33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D33">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>120</v>
       </c>
       <c r="F33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>105.7</v>
@@ -54014,25 +54020,25 @@
         <v>0</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -54043,16 +54049,16 @@
         <v>115</v>
       </c>
       <c r="C34">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D34">
         <v>75</v>
       </c>
       <c r="E34">
-        <v>93.3</v>
+        <v>120</v>
       </c>
       <c r="F34">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G34">
         <v>105.7</v>
@@ -54103,25 +54109,25 @@
         <v>0</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>6</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC34">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -54132,16 +54138,16 @@
         <v>115</v>
       </c>
       <c r="C35">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D35">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E35">
         <v>93.3</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G35">
         <v>105.7</v>
@@ -54192,25 +54198,25 @@
         <v>0</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA35">
         <v>5</v>
       </c>
       <c r="AB35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -54227,10 +54233,10 @@
         <v>80</v>
       </c>
       <c r="E36">
-        <v>120</v>
+        <v>93.3</v>
       </c>
       <c r="F36">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>105.7</v>
@@ -54287,19 +54293,19 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA36">
         <v>5</v>
       </c>
       <c r="AB36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC36">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -54307,7 +54313,7 @@
         <v>916</v>
       </c>
       <c r="B37">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C37">
         <v>80</v>
@@ -54316,16 +54322,16 @@
         <v>80</v>
       </c>
       <c r="E37">
-        <v>66.7</v>
+        <v>120</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G37">
         <v>105.7</v>
       </c>
       <c r="H37">
-        <v>93.3</v>
+        <v>106.7</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -54370,25 +54376,25 @@
         <v>0</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA37">
         <v>5</v>
       </c>
       <c r="AB37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC37">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -54396,87 +54402,176 @@
         <v>917</v>
       </c>
       <c r="B38">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E38">
-        <v>120</v>
+        <v>66.7</v>
       </c>
       <c r="F38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <v>105.7</v>
       </c>
       <c r="H38">
+        <v>93.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>5</v>
+      </c>
+      <c r="X38">
+        <v>5</v>
+      </c>
+      <c r="Y38">
+        <v>5</v>
+      </c>
+      <c r="Z38">
+        <v>5</v>
+      </c>
+      <c r="AA38">
+        <v>5</v>
+      </c>
+      <c r="AB38">
+        <v>5</v>
+      </c>
+      <c r="AC38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
+      <c r="A39" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B39">
+        <v>120</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+      <c r="D39">
+        <v>100</v>
+      </c>
+      <c r="E39">
+        <v>120</v>
+      </c>
+      <c r="F39">
+        <v>100</v>
+      </c>
+      <c r="G39">
+        <v>105.7</v>
+      </c>
+      <c r="H39">
         <v>106.7</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>0</v>
-      </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
-      <c r="W38">
-        <v>7</v>
-      </c>
-      <c r="X38">
-        <v>8</v>
-      </c>
-      <c r="Y38">
-        <v>8</v>
-      </c>
-      <c r="Z38">
-        <v>8</v>
-      </c>
-      <c r="AA38">
-        <v>8</v>
-      </c>
-      <c r="AB38">
-        <v>9</v>
-      </c>
-      <c r="AC38">
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>7</v>
+      </c>
+      <c r="X39">
+        <v>8</v>
+      </c>
+      <c r="Y39">
+        <v>8</v>
+      </c>
+      <c r="Z39">
+        <v>8</v>
+      </c>
+      <c r="AA39">
+        <v>8</v>
+      </c>
+      <c r="AB39">
+        <v>9</v>
+      </c>
+      <c r="AC39">
         <v>8</v>
       </c>
     </row>
@@ -54637,7 +54732,7 @@
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -54726,7 +54821,7 @@
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B5">
         <v>85</v>
@@ -54815,7 +54910,7 @@
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B6">
         <v>70</v>
@@ -54904,7 +54999,7 @@
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B7">
         <v>85</v>
@@ -54993,7 +55088,7 @@
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B8">
         <v>70</v>
@@ -55082,7 +55177,7 @@
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B9">
         <v>75</v>
@@ -55171,7 +55266,7 @@
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B10">
         <v>70</v>
@@ -55260,7 +55355,7 @@
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -55349,7 +55444,7 @@
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B12">
         <v>70</v>
@@ -55438,7 +55533,7 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -55527,7 +55622,7 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B14">
         <v>70</v>
@@ -55616,7 +55711,7 @@
     </row>
     <row r="15" spans="1:29">
       <c r="A15" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -55705,7 +55800,7 @@
     </row>
     <row r="16" spans="1:29">
       <c r="A16" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B16">
         <v>80</v>
@@ -55794,7 +55889,7 @@
     </row>
     <row r="17" spans="1:29">
       <c r="A17" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -55883,7 +55978,7 @@
     </row>
     <row r="18" spans="1:29">
       <c r="A18" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -55952,7 +56047,7 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -55960,7 +56055,7 @@
     </row>
     <row r="19" spans="1:29">
       <c r="A19" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -56049,7 +56144,7 @@
     </row>
     <row r="20" spans="1:29">
       <c r="A20" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B20">
         <v>70</v>
@@ -56138,7 +56233,7 @@
     </row>
     <row r="21" spans="1:29">
       <c r="A21" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B21">
         <v>70</v>
@@ -56227,7 +56322,7 @@
     </row>
     <row r="22" spans="1:29">
       <c r="A22" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B22">
         <v>70</v>
@@ -56316,7 +56411,7 @@
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B23">
         <v>70</v>
@@ -56405,7 +56500,7 @@
     </row>
     <row r="24" spans="1:29">
       <c r="A24" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B24">
         <v>70</v>
@@ -56494,7 +56589,7 @@
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B25">
         <v>90</v>
@@ -56583,7 +56678,7 @@
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B26">
         <v>80</v>
@@ -56672,7 +56767,7 @@
     </row>
     <row r="27" spans="1:29">
       <c r="A27" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B27">
         <v>95</v>
@@ -56761,7 +56856,7 @@
     </row>
     <row r="28" spans="1:29">
       <c r="A28" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B28">
         <v>70</v>
@@ -56864,7 +56959,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -56989,7 +57084,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B4">
         <v>151.4</v>
@@ -57066,7 +57161,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B5">
         <v>151.4</v>
@@ -57143,7 +57238,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B6">
         <v>151.4</v>
@@ -57208,7 +57303,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B7">
         <v>151.4</v>
@@ -57285,7 +57380,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B8">
         <v>151.4</v>
@@ -57362,7 +57457,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B9">
         <v>151.4</v>
@@ -57439,7 +57534,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B10">
         <v>151.4</v>
@@ -57516,7 +57611,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B11">
         <v>151.4</v>
@@ -57593,7 +57688,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B12">
         <v>151.4</v>
@@ -57670,7 +57765,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B13">
         <v>151.4</v>
@@ -57747,7 +57842,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B14">
         <v>151.4</v>
@@ -57824,7 +57919,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B15">
         <v>151.4</v>
@@ -57901,7 +57996,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B16">
         <v>151.4</v>
@@ -57978,7 +58073,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B17">
         <v>151.4</v>
@@ -58055,7 +58150,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B18">
         <v>151.4</v>
@@ -58132,7 +58227,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B19">
         <v>151.4</v>
@@ -58209,25 +58304,25 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B20">
-        <v>151.4</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>113.3</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -58266,27 +58361,27 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B21">
         <v>151.4</v>
@@ -58298,13 +58393,13 @@
         <v>90</v>
       </c>
       <c r="E21">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
       </c>
       <c r="G21">
-        <v>93.3</v>
+        <v>113.3</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -58346,24 +58441,24 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B22">
         <v>151.4</v>
@@ -58372,16 +58467,16 @@
         <v>150</v>
       </c>
       <c r="D22">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E22">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F22">
         <v>100</v>
       </c>
       <c r="G22">
-        <v>40</v>
+        <v>93.3</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -58420,27 +58515,27 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B23">
         <v>151.4</v>
@@ -58449,16 +58544,16 @@
         <v>150</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F23">
         <v>100</v>
       </c>
       <c r="G23">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -58497,27 +58592,27 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B24">
         <v>151.4</v>
@@ -58583,10 +58678,10 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -58594,25 +58689,25 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B25">
         <v>151.4</v>
       </c>
       <c r="C25">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="D25">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25">
-        <v>46.7</v>
+        <v>120</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -58651,45 +58746,45 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B26">
         <v>151.4</v>
       </c>
       <c r="C26">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="D26">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E26">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>73.3</v>
+        <v>46.7</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -58728,27 +58823,27 @@
         <v>0</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>5</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B27">
         <v>151.4</v>
@@ -58760,13 +58855,13 @@
         <v>90</v>
       </c>
       <c r="E27">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F27">
         <v>100</v>
       </c>
       <c r="G27">
-        <v>106.7</v>
+        <v>73.3</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -58805,27 +58900,27 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>5</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B28">
         <v>151.4</v>
@@ -58837,13 +58932,13 @@
         <v>90</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F28">
         <v>100</v>
       </c>
       <c r="G28">
-        <v>113.3</v>
+        <v>106.7</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -58882,27 +58977,27 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>5</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B29">
         <v>151.4</v>
@@ -58911,7 +59006,7 @@
         <v>150</v>
       </c>
       <c r="D29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -58965,7 +59060,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -58979,7 +59074,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B30">
         <v>151.4</v>
@@ -58988,7 +59083,7 @@
         <v>150</v>
       </c>
       <c r="D30">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -58997,7 +59092,7 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>120</v>
+        <v>113.3</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -59042,7 +59137,7 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -59056,7 +59151,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B31">
         <v>151.4</v>
@@ -59068,13 +59163,13 @@
         <v>90</v>
       </c>
       <c r="E31">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>100</v>
       </c>
       <c r="G31">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -59113,13 +59208,13 @@
         <v>0</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>5</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -59128,12 +59223,12 @@
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B32">
         <v>151.4</v>
@@ -59145,66 +59240,143 @@
         <v>90</v>
       </c>
       <c r="E32">
+        <v>84</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32">
+        <v>80</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>8</v>
+      </c>
+      <c r="U32">
+        <v>5</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
+        <v>8</v>
+      </c>
+      <c r="X32">
+        <v>6</v>
+      </c>
+      <c r="Y32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
+      <c r="A33" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B33">
+        <v>151.4</v>
+      </c>
+      <c r="C33">
+        <v>150</v>
+      </c>
+      <c r="D33">
+        <v>90</v>
+      </c>
+      <c r="E33">
         <v>86</v>
       </c>
-      <c r="F32">
-        <v>100</v>
-      </c>
-      <c r="G32">
+      <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33">
         <v>60</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>8</v>
-      </c>
-      <c r="U32">
-        <v>6</v>
-      </c>
-      <c r="V32">
-        <v>8</v>
-      </c>
-      <c r="W32">
-        <v>8</v>
-      </c>
-      <c r="X32">
-        <v>6</v>
-      </c>
-      <c r="Y32">
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>8</v>
+      </c>
+      <c r="U33">
+        <v>6</v>
+      </c>
+      <c r="V33">
+        <v>8</v>
+      </c>
+      <c r="W33">
+        <v>8</v>
+      </c>
+      <c r="X33">
+        <v>6</v>
+      </c>
+      <c r="Y33">
         <v>7</v>
       </c>
     </row>
@@ -59270,10 +59442,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>256</v>
@@ -59288,10 +59460,10 @@
         <v>259</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>256</v>
@@ -59306,10 +59478,10 @@
         <v>259</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>256</v>
@@ -59324,10 +59496,10 @@
         <v>259</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>256</v>
@@ -59349,7 +59521,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B4">
         <v>76.40000000000001</v>
@@ -59426,7 +59598,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B5">
         <v>98.2</v>
@@ -59503,7 +59675,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B6">
         <v>96.40000000000001</v>
@@ -59580,7 +59752,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B7">
         <v>89.09999999999999</v>
@@ -59657,7 +59829,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B8">
         <v>96.40000000000001</v>
@@ -59734,7 +59906,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B9">
         <v>98.2</v>
@@ -59811,7 +59983,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B10">
         <v>89.09999999999999</v>
@@ -59888,7 +60060,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B11">
         <v>67.3</v>
@@ -59965,7 +60137,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B12">
         <v>96.40000000000001</v>
@@ -60042,7 +60214,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B13">
         <v>72.7</v>
@@ -60119,7 +60291,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -60196,7 +60368,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -60273,7 +60445,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B16">
         <v>67.3</v>
@@ -60350,7 +60522,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B17">
         <v>96.40000000000001</v>
@@ -60566,7 +60738,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B4">
         <v>120</v>
@@ -60643,7 +60815,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B5">
         <v>96</v>
@@ -60720,7 +60892,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B6">
         <v>120</v>
@@ -60797,7 +60969,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B7">
         <v>120</v>
@@ -60874,7 +61046,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -60951,7 +61123,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D9">
         <v>90</v>
@@ -60980,7 +61152,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B10">
         <v>120</v>
@@ -61057,7 +61229,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B11">
         <v>84</v>
@@ -61134,7 +61306,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B12">
         <v>116</v>
@@ -61211,7 +61383,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B13">
         <v>120</v>
@@ -61288,7 +61460,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B14">
         <v>120</v>
@@ -61365,7 +61537,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B15">
         <v>116</v>
@@ -61442,7 +61614,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D16">
         <v>75</v>
@@ -61471,7 +61643,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B17">
         <v>120</v>
@@ -61548,7 +61720,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B18">
         <v>120</v>
@@ -61625,7 +61797,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B19">
         <v>112</v>
@@ -61666,7 +61838,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B20">
         <v>116</v>
@@ -61743,7 +61915,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B21">
         <v>120</v>
@@ -61820,7 +61992,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B22">
         <v>120</v>
@@ -61897,7 +62069,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B23">
         <v>120</v>
@@ -61974,7 +62146,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B24">
         <v>92</v>
@@ -62051,7 +62223,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B25">
         <v>104</v>
@@ -62128,7 +62300,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B26">
         <v>120</v>
@@ -65970,7 +66142,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B4">
         <v>87.5</v>
@@ -66047,7 +66219,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -66124,7 +66296,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -66201,7 +66373,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -66278,7 +66450,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -66355,7 +66527,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -66432,7 +66604,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -66509,7 +66681,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -66586,7 +66758,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -66663,7 +66835,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -66740,7 +66912,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -66817,7 +66989,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -66894,7 +67066,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -66971,7 +67143,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -67048,7 +67220,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -67125,7 +67297,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -67202,7 +67374,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -67279,7 +67451,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -67356,7 +67528,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -67433,7 +67605,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -67510,7 +67682,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -67587,7 +67759,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -67664,7 +67836,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -67741,7 +67913,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -67818,7 +67990,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -67895,7 +68067,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -68111,7 +68283,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B4">
         <v>93.3</v>
@@ -68188,7 +68360,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B5">
         <v>83.3</v>
@@ -68265,7 +68437,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B6">
         <v>46.7</v>
@@ -68342,7 +68514,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -68419,7 +68591,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B8">
         <v>70</v>
@@ -68496,7 +68668,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B9">
         <v>80</v>
@@ -68573,7 +68745,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B10">
         <v>76.7</v>
@@ -68650,7 +68822,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B11">
         <v>83.3</v>
@@ -68727,7 +68899,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B12">
         <v>96.7</v>
@@ -68804,7 +68976,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B13">
         <v>80</v>
@@ -68881,7 +69053,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -68958,7 +69130,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B15">
         <v>96.7</v>
@@ -69035,7 +69207,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B16">
         <v>46.7</v>
@@ -69112,7 +69284,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B17">
         <v>96.7</v>
@@ -69189,7 +69361,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B18">
         <v>96.7</v>
@@ -69266,7 +69438,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B19">
         <v>96.7</v>
@@ -69343,7 +69515,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B20">
         <v>96.7</v>
@@ -69559,7 +69731,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B4">
         <v>97.5</v>
@@ -69636,7 +69808,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B5">
         <v>82.5</v>
@@ -69713,7 +69885,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B6">
         <v>92.5</v>
@@ -69790,7 +69962,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -69867,7 +70039,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B8">
         <v>95</v>
@@ -69944,7 +70116,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B9">
         <v>92.5</v>
@@ -70021,7 +70193,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B10">
         <v>97.5</v>
@@ -70098,7 +70270,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B11">
         <v>95</v>
@@ -70175,7 +70347,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B12">
         <v>90</v>
@@ -70252,7 +70424,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B13">
         <v>67.5</v>
@@ -70329,7 +70501,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B14">
         <v>77.5</v>
@@ -70406,7 +70578,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B15">
         <v>97.5</v>
@@ -70483,7 +70655,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B16">
         <v>77.5</v>
@@ -70560,7 +70732,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B17">
         <v>92.5</v>
@@ -70637,7 +70809,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B18">
         <v>75</v>
@@ -70714,7 +70886,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B19">
         <v>80</v>
@@ -70791,7 +70963,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B20">
         <v>85</v>
@@ -70868,7 +71040,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B21">
         <v>77.5</v>
@@ -70945,7 +71117,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -71022,7 +71194,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B23">
         <v>92.5</v>
@@ -71099,7 +71271,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B24">
         <v>95</v>
@@ -71176,7 +71348,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B25">
         <v>97.5</v>
@@ -71253,7 +71425,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -71330,7 +71502,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -71407,7 +71579,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B28">
         <v>97.5</v>
@@ -71484,7 +71656,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B29">
         <v>80</v>
@@ -71561,7 +71733,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B30">
         <v>92.5</v>
@@ -71638,7 +71810,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -71715,7 +71887,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B32">
         <v>65</v>
@@ -71792,7 +71964,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B33">
         <v>95</v>
@@ -71869,7 +72041,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B34">
         <v>95</v>
@@ -71982,13 +72154,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>480</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>481</v>
@@ -72000,13 +72172,13 @@
         <v>485</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>480</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>481</v>
@@ -72018,13 +72190,13 @@
         <v>485</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>480</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>481</v>
@@ -72036,13 +72208,13 @@
         <v>485</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="U2" s="1" t="s">
         <v>480</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>481</v>
@@ -72061,7 +72233,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B4">
         <v>80</v>
@@ -72138,7 +72310,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B5">
         <v>60</v>
@@ -72215,7 +72387,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B6">
         <v>90</v>
@@ -72292,7 +72464,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B7">
         <v>80</v>
@@ -72369,7 +72541,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B8">
         <v>90</v>
@@ -72446,7 +72618,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B9">
         <v>80</v>
@@ -72523,7 +72695,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -72600,7 +72772,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -72677,7 +72849,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="B12">
         <v>80</v>
@@ -72754,7 +72926,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B13">
         <v>90</v>
@@ -72831,7 +73003,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B14">
         <v>80</v>
@@ -72908,7 +73080,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B15">
         <v>90</v>
@@ -72985,7 +73157,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B16">
         <v>90</v>
@@ -73062,7 +73234,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B17">
         <v>70</v>
@@ -73139,7 +73311,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B18">
         <v>80</v>
@@ -73216,7 +73388,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -73293,7 +73465,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -73370,7 +73542,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B21">
         <v>70</v>
@@ -73447,7 +73619,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B22">
         <v>100</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -753,6 +753,9 @@
     <t>LUNA VAZQUEZ KAREN</t>
   </si>
   <si>
+    <t>MALDONADO RAMON JOSE ALBIN</t>
+  </si>
+  <si>
     <t>MARCIAL ACAHUA ALANIS YUMEI</t>
   </si>
   <si>
@@ -2245,9 +2248,6 @@
   </si>
   <si>
     <t>LOPEZ CIRUELO LUISA MARIA</t>
-  </si>
-  <si>
-    <t>MALDONADO RAMON JOSE ALBIN</t>
   </si>
   <si>
     <t>MARES HERNANDEZ JULIO ANTONIO</t>
@@ -6530,76 +6530,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -6609,7 +6609,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -6686,7 +6686,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -6763,7 +6763,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -6840,7 +6840,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -6917,7 +6917,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -6994,7 +6994,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -7148,7 +7148,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -7225,7 +7225,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -7302,7 +7302,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -7379,7 +7379,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -7456,7 +7456,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -7533,7 +7533,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -7610,7 +7610,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -7687,7 +7687,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -7764,7 +7764,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -7918,7 +7918,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -7995,7 +7995,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -8072,7 +8072,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -8149,7 +8149,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -8226,7 +8226,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -8303,7 +8303,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -8380,7 +8380,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B27">
         <v>42.9</v>
@@ -8457,7 +8457,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -8534,7 +8534,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -8611,7 +8611,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -8688,7 +8688,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -8765,7 +8765,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B32">
         <v>100</v>
@@ -8842,7 +8842,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -8919,7 +8919,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B34">
         <v>100</v>
@@ -8996,7 +8996,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B35">
         <v>100</v>
@@ -9073,7 +9073,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B36">
         <v>100</v>
@@ -9150,7 +9150,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B37">
         <v>100</v>
@@ -9227,7 +9227,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B38">
         <v>100</v>
@@ -9304,7 +9304,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B39">
         <v>100</v>
@@ -9381,7 +9381,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B40">
         <v>100</v>
@@ -9458,7 +9458,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B41">
         <v>100</v>
@@ -9599,88 +9599,88 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="AC2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -9690,7 +9690,7 @@
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -9779,7 +9779,7 @@
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -9868,7 +9868,7 @@
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -9957,7 +9957,7 @@
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B7">
         <v>40</v>
@@ -10046,7 +10046,7 @@
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B8">
         <v>95</v>
@@ -10135,7 +10135,7 @@
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B9">
         <v>75</v>
@@ -10224,7 +10224,7 @@
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B10">
         <v>95</v>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -10402,7 +10402,7 @@
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B12">
         <v>85</v>
@@ -10491,7 +10491,7 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B14">
         <v>95</v>
@@ -10669,7 +10669,7 @@
     </row>
     <row r="15" spans="1:29">
       <c r="A15" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B15">
         <v>95</v>
@@ -10758,7 +10758,7 @@
     </row>
     <row r="16" spans="1:29">
       <c r="A16" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B16">
         <v>80</v>
@@ -10847,7 +10847,7 @@
     </row>
     <row r="17" spans="1:29">
       <c r="A17" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B17">
         <v>75</v>
@@ -10936,7 +10936,7 @@
     </row>
     <row r="18" spans="1:29">
       <c r="A18" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B18">
         <v>80</v>
@@ -11025,7 +11025,7 @@
     </row>
     <row r="19" spans="1:29">
       <c r="A19" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B19">
         <v>75</v>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="20" spans="1:29">
       <c r="A20" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B20">
         <v>80</v>
@@ -11203,7 +11203,7 @@
     </row>
     <row r="21" spans="1:29">
       <c r="A21" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -11292,7 +11292,7 @@
     </row>
     <row r="22" spans="1:29">
       <c r="A22" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B22">
         <v>95</v>
@@ -11381,7 +11381,7 @@
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -11470,7 +11470,7 @@
     </row>
     <row r="24" spans="1:29">
       <c r="A24" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -11559,7 +11559,7 @@
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -11648,7 +11648,7 @@
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B26">
         <v>80</v>
@@ -11737,7 +11737,7 @@
     </row>
     <row r="27" spans="1:29">
       <c r="A27" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B27">
         <v>95</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="28" spans="1:29">
       <c r="A28" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -11915,7 +11915,7 @@
     </row>
     <row r="29" spans="1:29">
       <c r="A29" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B29">
         <v>95</v>
@@ -12004,7 +12004,7 @@
     </row>
     <row r="30" spans="1:29">
       <c r="A30" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B30">
         <v>80</v>
@@ -12093,7 +12093,7 @@
     </row>
     <row r="31" spans="1:29">
       <c r="A31" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B31">
         <v>95</v>
@@ -12182,7 +12182,7 @@
     </row>
     <row r="32" spans="1:29">
       <c r="A32" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F32">
         <v>80</v>
@@ -12287,88 +12287,88 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="AC2" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -12378,7 +12378,7 @@
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -12467,7 +12467,7 @@
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -12556,7 +12556,7 @@
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B6">
         <v>90</v>
@@ -12645,7 +12645,7 @@
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B7">
         <v>85</v>
@@ -12734,7 +12734,7 @@
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -12823,7 +12823,7 @@
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -12912,7 +12912,7 @@
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B10">
         <v>85</v>
@@ -13001,7 +13001,7 @@
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B11">
         <v>85</v>
@@ -13090,7 +13090,7 @@
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B12">
         <v>95</v>
@@ -13179,7 +13179,7 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B14">
         <v>80</v>
@@ -13357,7 +13357,7 @@
     </row>
     <row r="15" spans="1:29">
       <c r="A15" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="16" spans="1:29">
       <c r="A16" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B16">
         <v>95</v>
@@ -13535,7 +13535,7 @@
     </row>
     <row r="17" spans="1:29">
       <c r="A17" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B17">
         <v>65</v>
@@ -13624,7 +13624,7 @@
     </row>
     <row r="18" spans="1:29">
       <c r="A18" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -13713,7 +13713,7 @@
     </row>
     <row r="19" spans="1:29">
       <c r="A19" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B19">
         <v>95</v>
@@ -13802,7 +13802,7 @@
     </row>
     <row r="20" spans="1:29">
       <c r="A20" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B20">
         <v>85</v>
@@ -13891,7 +13891,7 @@
     </row>
     <row r="21" spans="1:29">
       <c r="A21" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -13980,7 +13980,7 @@
     </row>
     <row r="22" spans="1:29">
       <c r="A22" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B22">
         <v>95</v>
@@ -14069,7 +14069,7 @@
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -14158,7 +14158,7 @@
     </row>
     <row r="24" spans="1:29">
       <c r="A24" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B24">
         <v>90</v>
@@ -14247,7 +14247,7 @@
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -14336,7 +14336,7 @@
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B26">
         <v>80</v>
@@ -14425,7 +14425,7 @@
     </row>
     <row r="27" spans="1:29">
       <c r="A27" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B27">
         <v>95</v>
@@ -14514,7 +14514,7 @@
     </row>
     <row r="28" spans="1:29">
       <c r="A28" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B28">
         <v>85</v>
@@ -14603,7 +14603,7 @@
     </row>
     <row r="29" spans="1:29">
       <c r="A29" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B29">
         <v>75</v>
@@ -14692,7 +14692,7 @@
     </row>
     <row r="30" spans="1:29">
       <c r="A30" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B30">
         <v>85</v>
@@ -14781,7 +14781,7 @@
     </row>
     <row r="31" spans="1:29">
       <c r="A31" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -14870,7 +14870,7 @@
     </row>
     <row r="32" spans="1:29">
       <c r="A32" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B32">
         <v>100</v>
@@ -14959,7 +14959,7 @@
     </row>
     <row r="33" spans="1:29">
       <c r="A33" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -15048,7 +15048,7 @@
     </row>
     <row r="34" spans="1:29">
       <c r="A34" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B34">
         <v>90</v>
@@ -15137,7 +15137,7 @@
     </row>
     <row r="35" spans="1:29">
       <c r="A35" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B35">
         <v>100</v>
@@ -15226,7 +15226,7 @@
     </row>
     <row r="36" spans="1:29">
       <c r="A36" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B36">
         <v>100</v>
@@ -15315,7 +15315,7 @@
     </row>
     <row r="37" spans="1:29">
       <c r="A37" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B37">
         <v>95</v>
@@ -15404,7 +15404,7 @@
     </row>
     <row r="38" spans="1:29">
       <c r="A38" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B38">
         <v>75</v>
@@ -15493,7 +15493,7 @@
     </row>
     <row r="39" spans="1:29">
       <c r="A39" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B39">
         <v>75</v>
@@ -15582,7 +15582,7 @@
     </row>
     <row r="40" spans="1:29">
       <c r="A40" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B40">
         <v>95</v>
@@ -15671,7 +15671,7 @@
     </row>
     <row r="41" spans="1:29">
       <c r="A41" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B41">
         <v>100</v>
@@ -15760,7 +15760,7 @@
     </row>
     <row r="42" spans="1:29">
       <c r="A42" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B42">
         <v>80</v>
@@ -15849,7 +15849,7 @@
     </row>
     <row r="43" spans="1:29">
       <c r="A43" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B43">
         <v>100</v>
@@ -15938,7 +15938,7 @@
     </row>
     <row r="44" spans="1:29">
       <c r="A44" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B44">
         <v>95</v>
@@ -16087,76 +16087,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -16166,7 +16166,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -16243,7 +16243,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -16320,7 +16320,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -16397,7 +16397,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -16474,7 +16474,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -16551,7 +16551,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -16628,7 +16628,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -16705,7 +16705,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -16782,7 +16782,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -16859,7 +16859,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -16936,7 +16936,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -17013,7 +17013,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -17090,7 +17090,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -17167,7 +17167,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -17244,7 +17244,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -17321,7 +17321,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -17398,7 +17398,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -17475,7 +17475,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -17552,7 +17552,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -17629,7 +17629,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -17706,7 +17706,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -17783,7 +17783,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -17860,7 +17860,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -17937,7 +17937,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -18014,7 +18014,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -18091,7 +18091,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -18168,7 +18168,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -18245,7 +18245,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B31">
         <v>20</v>
@@ -18322,7 +18322,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B32">
         <v>100</v>
@@ -18399,7 +18399,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -18536,76 +18536,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -18615,7 +18615,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -18692,7 +18692,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -18769,7 +18769,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -18846,7 +18846,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -18923,7 +18923,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -19000,7 +19000,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -19077,7 +19077,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -19154,7 +19154,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B11">
         <v>92.5</v>
@@ -19231,7 +19231,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -19308,7 +19308,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -19385,7 +19385,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -19462,7 +19462,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -19539,7 +19539,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -19616,7 +19616,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B17">
         <v>95</v>
@@ -19693,7 +19693,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -19770,7 +19770,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -19847,7 +19847,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B20">
         <v>92.5</v>
@@ -19924,7 +19924,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -20001,7 +20001,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -20078,7 +20078,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -20155,7 +20155,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -20232,7 +20232,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -20309,7 +20309,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B26">
         <v>95</v>
@@ -20386,7 +20386,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B27">
         <v>95</v>
@@ -20463,7 +20463,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -20540,7 +20540,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B29">
         <v>95</v>
@@ -20617,7 +20617,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -20694,7 +20694,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -20771,7 +20771,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B32">
         <v>100</v>
@@ -20848,7 +20848,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -20925,7 +20925,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B34">
         <v>100</v>
@@ -21002,7 +21002,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B35">
         <v>100</v>
@@ -21079,7 +21079,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B36">
         <v>100</v>
@@ -21156,7 +21156,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B37">
         <v>100</v>
@@ -21293,76 +21293,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="U2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="S2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -21372,7 +21372,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -21449,7 +21449,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -21526,7 +21526,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -21603,7 +21603,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -21680,7 +21680,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B8">
         <v>80</v>
@@ -21757,7 +21757,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -21834,7 +21834,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -21911,7 +21911,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -21988,7 +21988,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -22065,7 +22065,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -22142,7 +22142,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -22219,7 +22219,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -22296,7 +22296,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -22373,7 +22373,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B17">
         <v>80</v>
@@ -22450,7 +22450,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -22527,7 +22527,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -22604,7 +22604,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -22681,7 +22681,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -22758,7 +22758,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -22835,7 +22835,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -22972,76 +22972,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -23051,7 +23051,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B4">
         <v>105</v>
@@ -23128,7 +23128,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B5">
         <v>105</v>
@@ -23205,7 +23205,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B6">
         <v>105</v>
@@ -23282,7 +23282,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B7">
         <v>105</v>
@@ -23359,7 +23359,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B8">
         <v>105</v>
@@ -23436,7 +23436,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B9">
         <v>105</v>
@@ -23513,7 +23513,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B10">
         <v>105</v>
@@ -23590,7 +23590,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B11">
         <v>105</v>
@@ -23667,7 +23667,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B12">
         <v>105</v>
@@ -23744,7 +23744,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B13">
         <v>105</v>
@@ -23821,7 +23821,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B14">
         <v>105</v>
@@ -23898,7 +23898,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B15">
         <v>105</v>
@@ -23975,7 +23975,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B16">
         <v>105</v>
@@ -24052,7 +24052,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B17">
         <v>105</v>
@@ -24129,7 +24129,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B18">
         <v>105</v>
@@ -24206,7 +24206,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B19">
         <v>105</v>
@@ -24283,7 +24283,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B20">
         <v>105</v>
@@ -24360,7 +24360,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B21">
         <v>105</v>
@@ -24437,7 +24437,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B22">
         <v>105</v>
@@ -24514,7 +24514,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B23">
         <v>105</v>
@@ -24591,7 +24591,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B24">
         <v>105</v>
@@ -24668,7 +24668,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B25">
         <v>105</v>
@@ -24745,7 +24745,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B26">
         <v>105</v>
@@ -24822,7 +24822,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B27">
         <v>105</v>
@@ -24899,7 +24899,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B28">
         <v>105</v>
@@ -24976,7 +24976,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B29">
         <v>105</v>
@@ -25053,7 +25053,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B30">
         <v>105</v>
@@ -25130,7 +25130,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B31">
         <v>105</v>
@@ -25207,7 +25207,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B32">
         <v>105</v>
@@ -25284,7 +25284,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B33">
         <v>105</v>
@@ -25361,7 +25361,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B34">
         <v>105</v>
@@ -25438,7 +25438,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B35">
         <v>105</v>
@@ -25515,7 +25515,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B36">
         <v>105</v>
@@ -25592,7 +25592,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B37">
         <v>105</v>
@@ -25669,7 +25669,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B38">
         <v>105</v>
@@ -25746,7 +25746,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B39">
         <v>105</v>
@@ -25883,76 +25883,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -25962,7 +25962,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -26039,7 +26039,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -26116,7 +26116,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -26193,7 +26193,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B7">
         <v>16</v>
@@ -26270,7 +26270,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -26347,7 +26347,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -26424,7 +26424,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -26501,7 +26501,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -26578,7 +26578,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -26655,7 +26655,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -26732,7 +26732,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -26809,7 +26809,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -26886,7 +26886,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -26963,7 +26963,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -27040,7 +27040,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -27117,7 +27117,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -27194,7 +27194,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -27271,7 +27271,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -27348,7 +27348,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -27425,7 +27425,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -27502,7 +27502,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -27579,7 +27579,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -27656,7 +27656,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -27733,7 +27733,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -27810,7 +27810,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -27887,7 +27887,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -27964,7 +27964,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -28041,7 +28041,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -28178,76 +28178,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -28257,7 +28257,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -28334,7 +28334,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -28411,7 +28411,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -28488,7 +28488,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -28565,7 +28565,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -28642,7 +28642,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -28719,7 +28719,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -28796,7 +28796,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -28873,7 +28873,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -28950,7 +28950,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -29027,7 +29027,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -29104,7 +29104,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -29181,7 +29181,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -29258,7 +29258,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -29335,7 +29335,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -29412,7 +29412,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -29489,7 +29489,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -29566,7 +29566,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -29643,7 +29643,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -29720,7 +29720,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -29797,7 +29797,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -29874,7 +29874,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -29951,7 +29951,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -30028,7 +30028,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -30105,7 +30105,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -30182,7 +30182,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -30259,7 +30259,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -30336,7 +30336,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -30413,7 +30413,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B32">
         <v>100</v>
@@ -30490,7 +30490,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -30567,7 +30567,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B34">
         <v>100</v>
@@ -30644,7 +30644,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B35">
         <v>100</v>
@@ -30860,7 +30860,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -30937,7 +30937,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B5">
         <v>93.3</v>
@@ -30966,7 +30966,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B6">
         <v>93.3</v>
@@ -31043,7 +31043,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -31120,7 +31120,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B8">
         <v>80</v>
@@ -31197,7 +31197,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B9">
         <v>80</v>
@@ -31274,7 +31274,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B10">
         <v>33.3</v>
@@ -31351,7 +31351,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -31428,7 +31428,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B12">
         <v>93.3</v>
@@ -31505,7 +31505,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -31582,7 +31582,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B14">
         <v>93.3</v>
@@ -31659,7 +31659,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B15">
         <v>93.3</v>
@@ -31736,7 +31736,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B16">
         <v>93.3</v>
@@ -31813,7 +31813,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B17">
         <v>80</v>
@@ -31890,7 +31890,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B18">
         <v>76.7</v>
@@ -31955,7 +31955,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B19">
         <v>76.7</v>
@@ -32032,7 +32032,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B20">
         <v>20</v>
@@ -32109,7 +32109,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B21">
         <v>93.3</v>
@@ -32186,7 +32186,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -32263,7 +32263,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B23">
         <v>96.7</v>
@@ -32340,7 +32340,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -32369,7 +32369,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B25">
         <v>73.3</v>
@@ -32446,7 +32446,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -32523,7 +32523,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -32600,7 +32600,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B28">
         <v>66.7</v>
@@ -32677,7 +32677,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B29">
         <v>80</v>
@@ -32754,7 +32754,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B30">
         <v>93.3</v>
@@ -32831,7 +32831,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B31">
         <v>73.3</v>
@@ -32908,7 +32908,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B32">
         <v>93.3</v>
@@ -32985,7 +32985,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B33">
         <v>80</v>
@@ -33062,7 +33062,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B34">
         <v>80</v>
@@ -33139,7 +33139,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B35">
         <v>93.3</v>
@@ -33216,7 +33216,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B36">
         <v>80</v>
@@ -36757,7 +36757,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -36882,7 +36882,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B4">
         <v>85</v>
@@ -36959,7 +36959,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -37036,7 +37036,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -37113,7 +37113,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -37190,7 +37190,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B8">
         <v>85</v>
@@ -37267,7 +37267,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B9">
         <v>70</v>
@@ -37344,7 +37344,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B10">
         <v>90</v>
@@ -37421,7 +37421,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -37498,7 +37498,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B12">
         <v>70</v>
@@ -37575,7 +37575,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B13">
         <v>80</v>
@@ -37652,7 +37652,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -37729,7 +37729,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B15">
         <v>70</v>
@@ -37806,7 +37806,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B16">
         <v>90</v>
@@ -37883,7 +37883,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B17">
         <v>85</v>
@@ -37960,7 +37960,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B18">
         <v>85</v>
@@ -38037,7 +38037,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -38114,7 +38114,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -38191,7 +38191,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -38268,7 +38268,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -38345,7 +38345,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B23">
         <v>85</v>
@@ -38422,7 +38422,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B24">
         <v>85</v>
@@ -38499,7 +38499,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -38576,7 +38576,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B26">
         <v>85</v>
@@ -38641,7 +38641,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B27">
         <v>85</v>
@@ -38718,16 +38718,16 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B28">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E28">
         <v>104</v>
@@ -38775,133 +38775,133 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="B29">
-        <v>100</v>
-      </c>
-      <c r="C29">
-        <v>100</v>
-      </c>
-      <c r="D29">
-        <v>90</v>
+        <v>735</v>
       </c>
       <c r="E29">
-        <v>104</v>
-      </c>
-      <c r="F29">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>100</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
       <c r="M29">
         <v>0</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
       <c r="Q29">
         <v>0</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
       <c r="S29">
         <v>0</v>
       </c>
-      <c r="T29">
-        <v>6</v>
-      </c>
-      <c r="U29">
-        <v>6</v>
-      </c>
-      <c r="V29">
-        <v>8</v>
-      </c>
       <c r="W29">
-        <v>7</v>
-      </c>
-      <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
+      </c>
+      <c r="B30">
+        <v>90</v>
+      </c>
+      <c r="C30">
+        <v>100</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
       </c>
       <c r="E30">
-        <v>88</v>
+        <v>104</v>
+      </c>
+      <c r="F30">
+        <v>90</v>
       </c>
       <c r="G30">
-        <v>83.3</v>
+        <v>100</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
       <c r="M30">
         <v>0</v>
       </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
       <c r="Q30">
         <v>0</v>
       </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
       <c r="S30">
         <v>0</v>
       </c>
+      <c r="T30">
+        <v>5</v>
+      </c>
+      <c r="U30">
+        <v>9</v>
+      </c>
+      <c r="V30">
+        <v>10</v>
+      </c>
       <c r="W30">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="X30">
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B31">
         <v>90</v>
@@ -38916,7 +38916,7 @@
         <v>104</v>
       </c>
       <c r="F31">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>100</v>
@@ -38958,36 +38958,36 @@
         <v>0</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B32">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E32">
         <v>104</v>
@@ -39035,27 +39035,27 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>6</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B33">
         <v>85</v>
@@ -39064,7 +39064,7 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>104</v>
@@ -39112,36 +39112,36 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B34">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>104</v>
@@ -39189,19 +39189,19 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -39209,16 +39209,16 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B35">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C35">
         <v>100</v>
       </c>
       <c r="D35">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E35">
         <v>104</v>
@@ -39266,16 +39266,16 @@
         <v>0</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -39286,16 +39286,16 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B36">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>100</v>
       </c>
       <c r="D36">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>104</v>
@@ -39343,19 +39343,19 @@
         <v>0</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>9</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -39363,10 +39363,10 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -39420,36 +39420,36 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>7</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B38">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>104</v>
@@ -39497,13 +39497,13 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -39512,27 +39512,27 @@
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B39">
         <v>90</v>
       </c>
       <c r="C39">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E39">
         <v>104</v>
       </c>
       <c r="F39">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -39577,10 +39577,10 @@
         <v>5</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>5</v>
@@ -39594,10 +39594,10 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B40">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -39609,7 +39609,7 @@
         <v>104</v>
       </c>
       <c r="F40">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G40">
         <v>100</v>
@@ -39651,30 +39651,30 @@
         <v>0</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y40">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B41">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -39686,7 +39686,7 @@
         <v>104</v>
       </c>
       <c r="F41">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G41">
         <v>100</v>
@@ -39728,27 +39728,27 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B42">
         <v>95</v>
@@ -39757,13 +39757,13 @@
         <v>100</v>
       </c>
       <c r="D42">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E42">
         <v>104</v>
       </c>
       <c r="F42">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -39808,39 +39808,39 @@
         <v>6</v>
       </c>
       <c r="U42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V42">
         <v>6</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X42">
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B43">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C43">
         <v>100</v>
       </c>
       <c r="D43">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>104</v>
       </c>
       <c r="F43">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G43">
         <v>100</v>
@@ -39882,36 +39882,36 @@
         <v>0</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U43">
         <v>7</v>
       </c>
       <c r="V43">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B44">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C44">
         <v>100</v>
       </c>
       <c r="D44">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E44">
         <v>104</v>
@@ -39959,36 +39959,36 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X44">
         <v>5</v>
       </c>
       <c r="Y44">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B45">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C45">
         <v>100</v>
       </c>
       <c r="D45">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E45">
         <v>104</v>
@@ -40036,13 +40036,13 @@
         <v>0</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U45">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W45">
         <v>5</v>
@@ -40051,83 +40051,6 @@
         <v>5</v>
       </c>
       <c r="Y45">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="B46">
-        <v>100</v>
-      </c>
-      <c r="C46">
-        <v>100</v>
-      </c>
-      <c r="D46">
-        <v>80</v>
-      </c>
-      <c r="E46">
-        <v>104</v>
-      </c>
-      <c r="F46">
-        <v>100</v>
-      </c>
-      <c r="G46">
-        <v>100</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>5</v>
-      </c>
-      <c r="U46">
-        <v>6</v>
-      </c>
-      <c r="V46">
-        <v>6</v>
-      </c>
-      <c r="W46">
-        <v>5</v>
-      </c>
-      <c r="X46">
-        <v>5</v>
-      </c>
-      <c r="Y46">
         <v>6</v>
       </c>
     </row>
@@ -48346,88 +48269,88 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="AC2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -51378,88 +51301,88 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="AC2" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -54641,88 +54564,88 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="R2" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="X2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="AC2" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -57005,76 +56928,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -59448,16 +59371,16 @@
         <v>975</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>974</v>
@@ -59466,16 +59389,16 @@
         <v>975</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>974</v>
@@ -59484,16 +59407,16 @@
         <v>975</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>974</v>
@@ -59502,16 +59425,16 @@
         <v>975</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -60659,76 +60582,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -66063,76 +65986,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -68204,76 +68127,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="U2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="S2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -69652,76 +69575,76 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -72157,73 +72080,73 @@
         <v>1087</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1088</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>1087</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>1088</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>1087</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>1088</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>1087</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>1088</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -79917,7 +79840,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -81585,16 +81508,16 @@
         <v>235</v>
       </c>
       <c r="B24">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C24">
         <v>100</v>
       </c>
       <c r="D24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -81639,22 +81562,22 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -81662,22 +81585,22 @@
         <v>236</v>
       </c>
       <c r="B25">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
       <c r="D25">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -81716,22 +81639,22 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -81739,22 +81662,22 @@
         <v>237</v>
       </c>
       <c r="B26">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="E26">
         <v>100</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -81793,22 +81716,22 @@
         <v>0</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -81870,22 +81793,22 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -81893,7 +81816,7 @@
         <v>239</v>
       </c>
       <c r="B28">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -81947,10 +81870,10 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -81959,10 +81882,10 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -81982,10 +81905,10 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G29">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -82024,22 +81947,22 @@
         <v>0</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -82047,7 +81970,7 @@
         <v>241</v>
       </c>
       <c r="B30">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -82059,10 +81982,10 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -82101,22 +82024,22 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>6</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -82124,22 +82047,22 @@
         <v>242</v>
       </c>
       <c r="B31">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C31">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G31">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -82178,22 +82101,22 @@
         <v>0</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>6</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -82201,22 +82124,22 @@
         <v>243</v>
       </c>
       <c r="B32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C32">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="D32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>100</v>
       </c>
       <c r="F32">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -82255,22 +82178,22 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -82332,22 +82255,22 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>10</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -82355,7 +82278,7 @@
         <v>245</v>
       </c>
       <c r="B34">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -82412,19 +82335,19 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -82432,7 +82355,7 @@
         <v>246</v>
       </c>
       <c r="B35">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -82486,22 +82409,22 @@
         <v>0</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -82563,7 +82486,7 @@
         <v>0</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U36">
         <v>8</v>
@@ -82572,10 +82495,10 @@
         <v>5</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -82598,7 +82521,7 @@
         <v>100</v>
       </c>
       <c r="F37">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>100</v>
@@ -82640,22 +82563,22 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -82669,13 +82592,13 @@
         <v>100</v>
       </c>
       <c r="D38">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E38">
         <v>100</v>
       </c>
       <c r="F38">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G38">
         <v>100</v>
@@ -82717,22 +82640,22 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>8</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -82740,19 +82663,19 @@
         <v>250</v>
       </c>
       <c r="B39">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C39">
         <v>100</v>
       </c>
       <c r="D39">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E39">
         <v>100</v>
       </c>
       <c r="F39">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -82794,19 +82717,19 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -82817,13 +82740,13 @@
         <v>251</v>
       </c>
       <c r="B40">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C40">
         <v>100</v>
       </c>
       <c r="D40">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E40">
         <v>100</v>
@@ -82832,7 +82755,7 @@
         <v>95</v>
       </c>
       <c r="G40">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -82871,7 +82794,7 @@
         <v>0</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -82880,10 +82803,10 @@
         <v>5</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -82894,22 +82817,22 @@
         <v>252</v>
       </c>
       <c r="B41">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C41">
         <v>100</v>
       </c>
       <c r="D41">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E41">
         <v>100</v>
       </c>
       <c r="F41">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -82948,22 +82871,22 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -83031,16 +82954,16 @@
         <v>9</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -83102,19 +83025,19 @@
         <v>0</v>
       </c>
       <c r="T43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y43">
         <v>8</v>
@@ -83125,7 +83048,7 @@
         <v>255</v>
       </c>
       <c r="B44">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -83140,60 +83063,137 @@
         <v>100</v>
       </c>
       <c r="G44">
+        <v>100</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>9</v>
+      </c>
+      <c r="U44">
+        <v>10</v>
+      </c>
+      <c r="V44">
+        <v>9</v>
+      </c>
+      <c r="W44">
+        <v>10</v>
+      </c>
+      <c r="X44">
+        <v>10</v>
+      </c>
+      <c r="Y44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
+      <c r="A45" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B45">
+        <v>115</v>
+      </c>
+      <c r="C45">
+        <v>100</v>
+      </c>
+      <c r="D45">
+        <v>120</v>
+      </c>
+      <c r="E45">
+        <v>100</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="G45">
         <v>85</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <v>6</v>
-      </c>
-      <c r="U44">
-        <v>9</v>
-      </c>
-      <c r="V44">
-        <v>7</v>
-      </c>
-      <c r="W44">
-        <v>8</v>
-      </c>
-      <c r="X44">
-        <v>9</v>
-      </c>
-      <c r="Y44">
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>6</v>
+      </c>
+      <c r="U45">
+        <v>9</v>
+      </c>
+      <c r="V45">
+        <v>7</v>
+      </c>
+      <c r="W45">
+        <v>8</v>
+      </c>
+      <c r="X45">
+        <v>9</v>
+      </c>
+      <c r="Y45">
         <v>7</v>
       </c>
     </row>
@@ -83263,88 +83263,88 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="AC2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -83354,7 +83354,7 @@
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -83443,7 +83443,7 @@
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -83532,7 +83532,7 @@
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B6">
         <v>90</v>
@@ -83621,7 +83621,7 @@
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B7">
         <v>85</v>
@@ -83710,7 +83710,7 @@
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B8">
         <v>95</v>
@@ -83799,7 +83799,7 @@
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B9">
         <v>80</v>
@@ -83888,7 +83888,7 @@
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -83977,7 +83977,7 @@
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -84066,7 +84066,7 @@
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B12">
         <v>90</v>
@@ -84155,7 +84155,7 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -84244,7 +84244,7 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -84333,7 +84333,7 @@
     </row>
     <row r="15" spans="1:29">
       <c r="A15" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B15">
         <v>75</v>
@@ -84422,7 +84422,7 @@
     </row>
     <row r="16" spans="1:29">
       <c r="A16" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B16">
         <v>80</v>
@@ -84511,7 +84511,7 @@
     </row>
     <row r="17" spans="1:29">
       <c r="A17" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B17">
         <v>75</v>
@@ -84600,7 +84600,7 @@
     </row>
     <row r="18" spans="1:29">
       <c r="A18" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B18">
         <v>90</v>
@@ -84689,7 +84689,7 @@
     </row>
     <row r="19" spans="1:29">
       <c r="A19" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B19">
         <v>80</v>
@@ -84778,7 +84778,7 @@
     </row>
     <row r="20" spans="1:29">
       <c r="A20" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B20">
         <v>95</v>
@@ -84867,7 +84867,7 @@
     </row>
     <row r="21" spans="1:29">
       <c r="A21" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -84956,7 +84956,7 @@
     </row>
     <row r="22" spans="1:29">
       <c r="A22" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -85045,7 +85045,7 @@
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -85134,7 +85134,7 @@
     </row>
     <row r="24" spans="1:29">
       <c r="A24" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B24">
         <v>85</v>
@@ -85223,7 +85223,7 @@
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -85312,7 +85312,7 @@
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B26">
         <v>95</v>
@@ -85401,7 +85401,7 @@
     </row>
     <row r="27" spans="1:29">
       <c r="A27" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B27">
         <v>90</v>
@@ -85490,7 +85490,7 @@
     </row>
     <row r="28" spans="1:29">
       <c r="A28" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -85579,7 +85579,7 @@
     </row>
     <row r="29" spans="1:29">
       <c r="A29" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -85668,7 +85668,7 @@
     </row>
     <row r="30" spans="1:29">
       <c r="A30" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -85757,7 +85757,7 @@
     </row>
     <row r="31" spans="1:29">
       <c r="A31" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B31">
         <v>90</v>
@@ -85846,7 +85846,7 @@
     </row>
     <row r="32" spans="1:29">
       <c r="A32" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B32">
         <v>100</v>
@@ -85935,7 +85935,7 @@
     </row>
     <row r="33" spans="1:29">
       <c r="A33" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -86024,7 +86024,7 @@
     </row>
     <row r="34" spans="1:29">
       <c r="A34" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B34">
         <v>100</v>
@@ -86177,88 +86177,88 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="AC2" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -86268,7 +86268,7 @@
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B4">
         <v>115</v>
@@ -86357,7 +86357,7 @@
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B5">
         <v>115</v>
@@ -86446,7 +86446,7 @@
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B6">
         <v>120</v>
@@ -86535,7 +86535,7 @@
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B7">
         <v>120</v>
@@ -86624,7 +86624,7 @@
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F8">
         <v>90</v>
@@ -86665,7 +86665,7 @@
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B9">
         <v>120</v>
@@ -86754,7 +86754,7 @@
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B10">
         <v>120</v>
@@ -86843,7 +86843,7 @@
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B11">
         <v>115</v>
@@ -86932,7 +86932,7 @@
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B12">
         <v>115</v>
@@ -87021,7 +87021,7 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B13">
         <v>120</v>
@@ -87110,7 +87110,7 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B14">
         <v>115</v>
@@ -87199,7 +87199,7 @@
     </row>
     <row r="15" spans="1:29">
       <c r="A15" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B15">
         <v>115</v>
@@ -87288,7 +87288,7 @@
     </row>
     <row r="16" spans="1:29">
       <c r="A16" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B16">
         <v>120</v>
@@ -87377,7 +87377,7 @@
     </row>
     <row r="17" spans="1:29">
       <c r="A17" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B17">
         <v>120</v>
@@ -87466,7 +87466,7 @@
     </row>
     <row r="18" spans="1:29">
       <c r="A18" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B18">
         <v>120</v>
@@ -87555,7 +87555,7 @@
     </row>
     <row r="19" spans="1:29">
       <c r="A19" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B19">
         <v>120</v>
@@ -87644,7 +87644,7 @@
     </row>
     <row r="20" spans="1:29">
       <c r="A20" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B20">
         <v>120</v>
@@ -87733,7 +87733,7 @@
     </row>
     <row r="21" spans="1:29">
       <c r="A21" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B21">
         <v>120</v>
@@ -87822,7 +87822,7 @@
     </row>
     <row r="22" spans="1:29">
       <c r="A22" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B22">
         <v>120</v>
@@ -87911,7 +87911,7 @@
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B23">
         <v>120</v>
@@ -88000,7 +88000,7 @@
     </row>
     <row r="24" spans="1:29">
       <c r="A24" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B24">
         <v>120</v>
@@ -88089,7 +88089,7 @@
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B25">
         <v>120</v>
@@ -88178,7 +88178,7 @@
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B26">
         <v>120</v>
@@ -88267,7 +88267,7 @@
     </row>
     <row r="27" spans="1:29">
       <c r="A27" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B27">
         <v>120</v>
@@ -88356,7 +88356,7 @@
     </row>
     <row r="28" spans="1:29">
       <c r="A28" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B28">
         <v>120</v>
@@ -88445,7 +88445,7 @@
     </row>
     <row r="29" spans="1:29">
       <c r="A29" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B29">
         <v>120</v>
@@ -88534,7 +88534,7 @@
     </row>
     <row r="30" spans="1:29">
       <c r="A30" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B30">
         <v>120</v>
@@ -88623,7 +88623,7 @@
     </row>
     <row r="31" spans="1:29">
       <c r="A31" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B31">
         <v>120</v>
@@ -88712,7 +88712,7 @@
     </row>
     <row r="32" spans="1:29">
       <c r="A32" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B32">
         <v>115</v>
@@ -88801,7 +88801,7 @@
     </row>
     <row r="33" spans="1:29">
       <c r="A33" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B33">
         <v>120</v>
@@ -88890,7 +88890,7 @@
     </row>
     <row r="34" spans="1:29">
       <c r="A34" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B34">
         <v>120</v>
@@ -88979,7 +88979,7 @@
     </row>
     <row r="35" spans="1:29">
       <c r="A35" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B35">
         <v>120</v>
@@ -89068,7 +89068,7 @@
     </row>
     <row r="36" spans="1:29">
       <c r="A36" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B36">
         <v>120</v>
@@ -89157,7 +89157,7 @@
     </row>
     <row r="37" spans="1:29">
       <c r="A37" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37">
         <v>120</v>
@@ -89246,7 +89246,7 @@
     </row>
     <row r="38" spans="1:29">
       <c r="A38" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38">
         <v>120</v>
@@ -89335,7 +89335,7 @@
     </row>
     <row r="39" spans="1:29">
       <c r="A39" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B39">
         <v>115</v>
@@ -89424,7 +89424,7 @@
     </row>
     <row r="40" spans="1:29">
       <c r="A40" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B40">
         <v>120</v>
@@ -89513,7 +89513,7 @@
     </row>
     <row r="41" spans="1:29">
       <c r="A41" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B41">
         <v>120</v>
@@ -89602,7 +89602,7 @@
     </row>
     <row r="42" spans="1:29">
       <c r="A42" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B42">
         <v>120</v>
@@ -89691,7 +89691,7 @@
     </row>
     <row r="43" spans="1:29">
       <c r="A43" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43">
         <v>120</v>
@@ -89780,7 +89780,7 @@
     </row>
     <row r="44" spans="1:29">
       <c r="A44" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B44">
         <v>120</v>
@@ -89869,7 +89869,7 @@
     </row>
     <row r="45" spans="1:29">
       <c r="A45" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B45">
         <v>120</v>
@@ -90022,88 +90022,88 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="R2" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="X2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="AC2" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -90113,7 +90113,7 @@
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -90202,7 +90202,7 @@
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -90291,7 +90291,7 @@
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -90380,7 +90380,7 @@
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B7">
         <v>70</v>
@@ -90469,7 +90469,7 @@
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -90558,7 +90558,7 @@
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B9">
         <v>95</v>
@@ -90647,7 +90647,7 @@
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -90736,7 +90736,7 @@
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -90825,7 +90825,7 @@
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -90914,7 +90914,7 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B13">
         <v>85</v>
@@ -91003,7 +91003,7 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B14">
         <v>95</v>
@@ -91092,7 +91092,7 @@
     </row>
     <row r="15" spans="1:29">
       <c r="A15" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -91181,7 +91181,7 @@
     </row>
     <row r="16" spans="1:29">
       <c r="A16" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B16">
         <v>95</v>
@@ -91270,7 +91270,7 @@
     </row>
     <row r="17" spans="1:29">
       <c r="A17" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -91359,7 +91359,7 @@
     </row>
     <row r="18" spans="1:29">
       <c r="A18" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -91448,7 +91448,7 @@
     </row>
     <row r="19" spans="1:29">
       <c r="A19" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -91537,7 +91537,7 @@
     </row>
     <row r="20" spans="1:29">
       <c r="A20" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B20">
         <v>80</v>
@@ -91590,7 +91590,7 @@
     </row>
     <row r="21" spans="1:29">
       <c r="A21" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -91679,7 +91679,7 @@
     </row>
     <row r="22" spans="1:29">
       <c r="A22" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B22">
         <v>85</v>
@@ -91768,7 +91768,7 @@
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B23">
         <v>85</v>
@@ -91857,7 +91857,7 @@
     </row>
     <row r="24" spans="1:29">
       <c r="A24" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -91946,7 +91946,7 @@
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -92035,7 +92035,7 @@
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -92124,7 +92124,7 @@
     </row>
     <row r="27" spans="1:29">
       <c r="A27" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -92213,7 +92213,7 @@
     </row>
     <row r="28" spans="1:29">
       <c r="A28" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -92302,7 +92302,7 @@
     </row>
     <row r="29" spans="1:29">
       <c r="A29" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B29">
         <v>85</v>
@@ -92391,7 +92391,7 @@
     </row>
     <row r="30" spans="1:29">
       <c r="A30" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -92480,7 +92480,7 @@
     </row>
     <row r="31" spans="1:29">
       <c r="A31" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B31">
         <v>100</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -3882,7 +3882,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -3959,7 +3959,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -4036,7 +4036,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -4072,7 +4072,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -4113,7 +4113,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -4190,7 +4190,7 @@
         <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -4267,7 +4267,7 @@
         <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -4303,7 +4303,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -4344,7 +4344,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -4380,7 +4380,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -4421,7 +4421,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -4457,7 +4457,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -4498,7 +4498,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -4575,7 +4575,7 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -4611,7 +4611,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -4652,7 +4652,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -4688,7 +4688,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -4729,7 +4729,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -4765,7 +4765,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -4806,7 +4806,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -4842,7 +4842,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -4883,7 +4883,7 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -4960,7 +4960,7 @@
         <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -4996,7 +4996,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -5037,7 +5037,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -5073,7 +5073,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -5114,7 +5114,7 @@
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -5191,7 +5191,7 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -5227,7 +5227,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -5268,7 +5268,7 @@
         <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -5304,7 +5304,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -5345,7 +5345,7 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -5422,7 +5422,7 @@
         <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -5499,7 +5499,7 @@
         <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -5535,7 +5535,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -5576,7 +5576,7 @@
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -5653,7 +5653,7 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -5689,7 +5689,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -5730,7 +5730,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -5807,7 +5807,7 @@
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -5843,7 +5843,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -5884,7 +5884,7 @@
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -5961,7 +5961,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -6038,7 +6038,7 @@
         <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -6115,7 +6115,7 @@
         <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -6192,7 +6192,7 @@
         <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -6269,7 +6269,7 @@
         <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -6346,7 +6346,7 @@
         <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -6423,7 +6423,7 @@
         <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -6459,7 +6459,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -6621,7 +6621,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -6698,7 +6698,7 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -6775,7 +6775,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -6852,7 +6852,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -6929,7 +6929,7 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -6965,7 +6965,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -7006,7 +7006,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -7083,7 +7083,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -7160,7 +7160,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -7237,7 +7237,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>8</v>
@@ -7314,7 +7314,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -7391,7 +7391,7 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -7468,7 +7468,7 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -7545,7 +7545,7 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>8</v>
@@ -7699,7 +7699,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -7735,7 +7735,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -7776,7 +7776,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>6</v>
@@ -7853,7 +7853,7 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -7966,7 +7966,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -8007,7 +8007,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -8084,7 +8084,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>5</v>
@@ -8161,7 +8161,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>5</v>
@@ -8197,7 +8197,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -8238,7 +8238,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -8315,7 +8315,7 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -8392,7 +8392,7 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>5</v>
@@ -8469,7 +8469,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>8</v>
@@ -8505,7 +8505,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -8546,7 +8546,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>8</v>
@@ -8623,7 +8623,7 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -8700,7 +8700,7 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>5</v>
@@ -8736,7 +8736,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -8777,7 +8777,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -8854,7 +8854,7 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -8931,7 +8931,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>6</v>
@@ -9008,7 +9008,7 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -9085,7 +9085,7 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
         <v>5</v>
@@ -9162,7 +9162,7 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>6</v>
@@ -9198,7 +9198,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>10</v>
@@ -9316,7 +9316,7 @@
         <v>7</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
         <v>8</v>
@@ -9393,7 +9393,7 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I40">
         <v>7</v>
@@ -9470,7 +9470,7 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I41">
         <v>5</v>
@@ -16172,7 +16172,7 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -16208,7 +16208,7 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -16249,7 +16249,7 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -16326,7 +16326,7 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>8</v>
@@ -16362,7 +16362,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -16403,7 +16403,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -16439,7 +16439,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -16480,7 +16480,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -16516,7 +16516,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -16557,7 +16557,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>9</v>
@@ -16634,7 +16634,7 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>8</v>
@@ -16711,7 +16711,7 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -16788,7 +16788,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -16865,7 +16865,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -16901,7 +16901,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -16942,7 +16942,7 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -17019,7 +17019,7 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>8</v>
@@ -17096,7 +17096,7 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -17173,7 +17173,7 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -17209,7 +17209,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -17250,7 +17250,7 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -17286,7 +17286,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -17327,7 +17327,7 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>10</v>
@@ -17404,7 +17404,7 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>8</v>
@@ -17440,7 +17440,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -17481,7 +17481,7 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>8</v>
@@ -17517,7 +17517,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -17558,7 +17558,7 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>6</v>
@@ -17635,7 +17635,7 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -17712,7 +17712,7 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>9</v>
@@ -17789,7 +17789,7 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -17866,7 +17866,7 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -17902,7 +17902,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -17943,7 +17943,7 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>10</v>
@@ -17979,7 +17979,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -18020,7 +18020,7 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -18056,7 +18056,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -18097,7 +18097,7 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -18133,7 +18133,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -18174,7 +18174,7 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>9</v>
@@ -18210,7 +18210,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -18251,7 +18251,7 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -18328,7 +18328,7 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
         <v>10</v>
@@ -18405,7 +18405,7 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>10</v>
@@ -18441,7 +18441,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -18624,7 +18624,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -18660,7 +18660,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -18701,7 +18701,7 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -18737,7 +18737,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -18778,7 +18778,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -18814,7 +18814,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -18932,7 +18932,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -18968,7 +18968,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -19009,7 +19009,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>9</v>
@@ -19086,7 +19086,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>8</v>
@@ -19122,7 +19122,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -19163,7 +19163,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -19199,7 +19199,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -19240,7 +19240,7 @@
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>8</v>
@@ -19317,7 +19317,7 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -19353,7 +19353,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -19394,7 +19394,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -19471,7 +19471,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -19548,7 +19548,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -19584,7 +19584,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -19625,7 +19625,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -19702,7 +19702,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -19779,7 +19779,7 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -19856,7 +19856,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -19933,7 +19933,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>8</v>
@@ -19969,7 +19969,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -20010,7 +20010,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -20087,7 +20087,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -20164,7 +20164,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -20241,7 +20241,7 @@
         <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>8</v>
@@ -20277,7 +20277,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -20318,7 +20318,7 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>7</v>
@@ -20395,7 +20395,7 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -20472,7 +20472,7 @@
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -20508,7 +20508,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -20549,7 +20549,7 @@
         <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -20585,7 +20585,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -20626,7 +20626,7 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -20703,7 +20703,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -20780,7 +20780,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -20816,7 +20816,7 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -20857,7 +20857,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -20893,7 +20893,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -20934,7 +20934,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>8</v>
@@ -20970,7 +20970,7 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -21011,7 +21011,7 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -21047,7 +21047,7 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -21088,7 +21088,7 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -21124,7 +21124,7 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -21165,7 +21165,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -25956,13 +25956,13 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -26033,13 +26033,13 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -26075,7 +26075,7 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -26110,13 +26110,13 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -26149,10 +26149,10 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -26187,13 +26187,13 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -26264,13 +26264,13 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -26341,13 +26341,13 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -26383,7 +26383,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -26418,13 +26418,13 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -26495,13 +26495,13 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>4</v>
@@ -26531,13 +26531,13 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -26572,13 +26572,13 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -26649,13 +26649,13 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -26685,13 +26685,13 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -26726,13 +26726,13 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -26768,7 +26768,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -26803,13 +26803,13 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -26880,13 +26880,13 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -26919,10 +26919,10 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -26957,13 +26957,13 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -27034,13 +27034,13 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -27111,13 +27111,13 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -27147,10 +27147,10 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -27188,13 +27188,13 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>9</v>
@@ -27224,13 +27224,13 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -27265,13 +27265,13 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -27301,10 +27301,10 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -27342,13 +27342,13 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>8</v>
@@ -27381,7 +27381,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -27419,13 +27419,13 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>8</v>
@@ -27458,10 +27458,10 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -27496,13 +27496,13 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -27532,13 +27532,13 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -27573,13 +27573,13 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>7</v>
@@ -27650,13 +27650,13 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -27686,10 +27686,10 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -27727,13 +27727,13 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -27766,7 +27766,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -27804,13 +27804,13 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -27843,7 +27843,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -27881,13 +27881,13 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>8</v>
@@ -27923,7 +27923,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -27958,13 +27958,13 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>6</v>
@@ -28000,7 +28000,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -28035,13 +28035,13 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>4</v>
@@ -28071,13 +28071,13 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>7</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>6</v>
@@ -30851,10 +30851,10 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -30957,10 +30957,10 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -30996,7 +30996,7 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -31034,10 +31034,10 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -31070,7 +31070,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -31111,10 +31111,10 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -31147,7 +31147,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -31188,10 +31188,10 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -31265,10 +31265,10 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -31342,10 +31342,10 @@
         <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -31419,10 +31419,10 @@
         <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -31455,7 +31455,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -31496,10 +31496,10 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -31532,7 +31532,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -31573,10 +31573,10 @@
         <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -31612,7 +31612,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -31650,10 +31650,10 @@
         <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -31686,10 +31686,10 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -31727,10 +31727,10 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -31804,10 +31804,10 @@
         <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -31878,7 +31878,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -31946,10 +31946,10 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -32023,10 +32023,10 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -32100,10 +32100,10 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -32136,7 +32136,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -32177,10 +32177,10 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -32254,10 +32254,10 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -32293,7 +32293,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -32360,10 +32360,10 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -32437,10 +32437,10 @@
         <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -32473,7 +32473,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -32514,10 +32514,10 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>7</v>
@@ -32550,7 +32550,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -32591,10 +32591,10 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -32668,10 +32668,10 @@
         <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -32745,10 +32745,10 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -32822,10 +32822,10 @@
         <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -32861,7 +32861,7 @@
         <v>5</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>5</v>
@@ -32899,10 +32899,10 @@
         <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -32976,10 +32976,10 @@
         <v>5</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -33015,7 +33015,7 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -33053,10 +33053,10 @@
         <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -33130,10 +33130,10 @@
         <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>6</v>
@@ -33169,7 +33169,7 @@
         <v>5</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -33207,10 +33207,10 @@
         <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>6</v>
@@ -33423,7 +33423,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -33500,7 +33500,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -33577,7 +33577,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -33613,7 +33613,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -33654,7 +33654,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -33731,7 +33731,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>7</v>
@@ -33808,7 +33808,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>8</v>
@@ -33885,7 +33885,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -33962,7 +33962,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -34039,7 +34039,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -34116,7 +34116,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>7</v>
@@ -34193,7 +34193,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -34270,7 +34270,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>8</v>
@@ -34347,7 +34347,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>8</v>
@@ -34383,7 +34383,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -34424,7 +34424,7 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -34501,7 +34501,7 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>8</v>
@@ -34537,7 +34537,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -34578,7 +34578,7 @@
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -34655,7 +34655,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -34691,7 +34691,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -34732,7 +34732,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -34768,7 +34768,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -34809,7 +34809,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>8</v>
@@ -34886,7 +34886,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -34922,7 +34922,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -34963,7 +34963,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>8</v>
@@ -34999,7 +34999,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -35040,7 +35040,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -35117,7 +35117,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -35153,7 +35153,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -35194,7 +35194,7 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -35271,7 +35271,7 @@
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -35348,7 +35348,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -35425,7 +35425,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -35502,7 +35502,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -35579,7 +35579,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>8</v>
@@ -35656,7 +35656,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -35733,7 +35733,7 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>7</v>
@@ -35769,7 +35769,7 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -35810,7 +35810,7 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
         <v>7</v>
@@ -35846,7 +35846,7 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -35887,7 +35887,7 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
         <v>7</v>
@@ -35964,7 +35964,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>8</v>
@@ -36000,7 +36000,7 @@
         <v>10</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -36041,7 +36041,7 @@
         <v>7</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>7</v>
@@ -36118,7 +36118,7 @@
         <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>10</v>
@@ -36195,7 +36195,7 @@
         <v>10</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>7</v>
@@ -36231,7 +36231,7 @@
         <v>10</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>7</v>
@@ -36272,7 +36272,7 @@
         <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>7</v>
@@ -36308,7 +36308,7 @@
         <v>10</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -36349,7 +36349,7 @@
         <v>10</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
         <v>10</v>
@@ -36426,7 +36426,7 @@
         <v>10</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -36462,7 +36462,7 @@
         <v>8</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>5</v>
@@ -36503,7 +36503,7 @@
         <v>10</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
         <v>7</v>
@@ -36580,7 +36580,7 @@
         <v>10</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L45">
         <v>7</v>
@@ -36657,7 +36657,7 @@
         <v>10</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L46">
         <v>10</v>
@@ -36867,10 +36867,10 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -36903,10 +36903,10 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -36944,10 +36944,10 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -37021,10 +37021,10 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -37098,10 +37098,10 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -37134,7 +37134,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -37175,10 +37175,10 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -37252,10 +37252,10 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -37288,7 +37288,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -37329,10 +37329,10 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -37365,7 +37365,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -37406,10 +37406,10 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -37442,7 +37442,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -37483,10 +37483,10 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -37560,10 +37560,10 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -37637,10 +37637,10 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -37673,7 +37673,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -37714,10 +37714,10 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -37791,10 +37791,10 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -37827,7 +37827,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -37868,10 +37868,10 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -37904,7 +37904,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -37945,10 +37945,10 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -37981,7 +37981,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -38022,10 +38022,10 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -38099,10 +38099,10 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -38176,10 +38176,10 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -38212,7 +38212,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -38253,10 +38253,10 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -38289,7 +38289,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -38330,10 +38330,10 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -38369,7 +38369,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -38407,10 +38407,10 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -38484,10 +38484,10 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -38520,7 +38520,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -38558,7 +38558,7 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -38626,10 +38626,10 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -38703,10 +38703,10 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>7</v>
@@ -38762,7 +38762,7 @@
         <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -38809,10 +38809,10 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>9</v>
@@ -38886,10 +38886,10 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -38963,10 +38963,10 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -39040,10 +39040,10 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>6</v>
@@ -39076,7 +39076,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -39117,10 +39117,10 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>8</v>
@@ -39194,10 +39194,10 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>7</v>
@@ -39230,7 +39230,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -39271,10 +39271,10 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -39348,10 +39348,10 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -39425,10 +39425,10 @@
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>8</v>
@@ -39461,7 +39461,7 @@
         <v>5</v>
       </c>
       <c r="V38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -39502,10 +39502,10 @@
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -39579,10 +39579,10 @@
         <v>-1</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
         <v>10</v>
@@ -39656,10 +39656,10 @@
         <v>-1</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>8</v>
@@ -39692,7 +39692,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>6</v>
@@ -39733,10 +39733,10 @@
         <v>-1</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L42">
         <v>7</v>
@@ -39810,10 +39810,10 @@
         <v>-1</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -39887,10 +39887,10 @@
         <v>-1</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L44">
         <v>7</v>
@@ -39964,10 +39964,10 @@
         <v>-1</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -40000,7 +40000,7 @@
         <v>6</v>
       </c>
       <c r="V45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W45">
         <v>5</v>
@@ -40199,7 +40199,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -40288,7 +40288,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -40377,7 +40377,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -40466,7 +40466,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -40555,7 +40555,7 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -40644,7 +40644,7 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -40733,7 +40733,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -40775,7 +40775,7 @@
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -40822,7 +40822,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -40864,7 +40864,7 @@
         <v>8</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -40911,7 +40911,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -41000,7 +41000,7 @@
         <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -41089,7 +41089,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -41178,7 +41178,7 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -41220,7 +41220,7 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15">
         <v>10</v>
@@ -41267,7 +41267,7 @@
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -41309,7 +41309,7 @@
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -41356,7 +41356,7 @@
         <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -41445,7 +41445,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -41534,7 +41534,7 @@
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -41576,7 +41576,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -41623,7 +41623,7 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -41665,7 +41665,7 @@
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>8</v>
@@ -41712,7 +41712,7 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -41801,7 +41801,7 @@
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -41890,7 +41890,7 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -41979,7 +41979,7 @@
         <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -42068,7 +42068,7 @@
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -42157,7 +42157,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -42246,7 +42246,7 @@
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -42335,7 +42335,7 @@
         <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -42424,7 +42424,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -42513,7 +42513,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -42602,7 +42602,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -42644,7 +42644,7 @@
         <v>6</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>9</v>
@@ -42691,7 +42691,7 @@
         <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -42780,7 +42780,7 @@
         <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -42822,7 +42822,7 @@
         <v>7</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>9</v>
@@ -42999,13 +42999,13 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -43041,7 +43041,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -43076,13 +43076,13 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -43153,13 +43153,13 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -43195,7 +43195,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -43230,13 +43230,13 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -43272,7 +43272,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -43307,13 +43307,13 @@
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -43343,13 +43343,13 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>7</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -43384,13 +43384,13 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -43461,13 +43461,13 @@
         <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -43497,13 +43497,13 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -43538,13 +43538,13 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -43574,13 +43574,13 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -43615,13 +43615,13 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -43692,13 +43692,13 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -43734,7 +43734,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -43769,13 +43769,13 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -43811,7 +43811,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -43846,13 +43846,13 @@
         <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>6</v>
@@ -43882,7 +43882,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -43923,13 +43923,13 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -44000,13 +44000,13 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -44042,7 +44042,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -44077,13 +44077,13 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -44154,13 +44154,13 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>6</v>
@@ -44196,7 +44196,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -44231,13 +44231,13 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>8</v>
@@ -44267,7 +44267,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -44299,7 +44299,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -44349,13 +44349,13 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>9</v>
@@ -44426,13 +44426,13 @@
         <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -44462,13 +44462,13 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -44503,13 +44503,13 @@
         <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -44539,7 +44539,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -44580,13 +44580,13 @@
         <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -44657,13 +44657,13 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>7</v>
@@ -44693,13 +44693,13 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -44734,13 +44734,13 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -44770,7 +44770,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -44811,13 +44811,13 @@
         <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>9</v>
@@ -44853,7 +44853,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -44870,13 +44870,13 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>9</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -44888,13 +44888,13 @@
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -44924,13 +44924,13 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -44965,13 +44965,13 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -45001,7 +45001,7 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -45042,13 +45042,13 @@
         <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>5</v>
@@ -45078,13 +45078,13 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -45119,13 +45119,13 @@
         <v>8</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -45155,7 +45155,7 @@
         <v>8</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -45196,13 +45196,13 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -45232,7 +45232,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -45273,13 +45273,13 @@
         <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>5</v>
@@ -45309,7 +45309,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -45350,13 +45350,13 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -45427,13 +45427,13 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
         <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -45504,13 +45504,13 @@
         <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>9</v>
@@ -45714,7 +45714,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -45750,7 +45750,7 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -45827,7 +45827,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -45868,7 +45868,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -45904,7 +45904,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -45945,7 +45945,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>9</v>
@@ -46022,7 +46022,7 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -46058,7 +46058,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -46099,7 +46099,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -46135,7 +46135,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -46176,7 +46176,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>8</v>
@@ -46212,7 +46212,7 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -46253,7 +46253,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -46289,7 +46289,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -46330,7 +46330,7 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>7</v>
@@ -46366,7 +46366,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -46407,7 +46407,7 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -46484,7 +46484,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -46561,7 +46561,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -46597,7 +46597,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -46638,7 +46638,7 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -46715,7 +46715,7 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -46751,7 +46751,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -46792,7 +46792,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>7</v>
@@ -46828,7 +46828,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -46869,7 +46869,7 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>7</v>
@@ -46905,7 +46905,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -46946,7 +46946,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -47023,7 +47023,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>7</v>
@@ -47100,7 +47100,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>8</v>
@@ -47177,7 +47177,7 @@
         <v>4</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>8</v>
@@ -47254,7 +47254,7 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>8</v>
@@ -47331,7 +47331,7 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>8</v>
@@ -47408,7 +47408,7 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -47444,7 +47444,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -47485,7 +47485,7 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -47521,7 +47521,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -47562,7 +47562,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>7</v>
@@ -47639,7 +47639,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -47675,7 +47675,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -47716,7 +47716,7 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>8</v>
@@ -47752,7 +47752,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -47870,7 +47870,7 @@
         <v>4</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>7</v>
@@ -47947,7 +47947,7 @@
         <v>4</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>7</v>
@@ -48024,7 +48024,7 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>9</v>
@@ -48101,7 +48101,7 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>8</v>
@@ -48137,7 +48137,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -48178,7 +48178,7 @@
         <v>7</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>9</v>
@@ -51451,10 +51451,10 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -51496,7 +51496,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -51540,10 +51540,10 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -51629,10 +51629,10 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -51671,10 +51671,10 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -51718,10 +51718,10 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -51807,10 +51807,10 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -51849,10 +51849,10 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -51896,10 +51896,10 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -51941,7 +51941,7 @@
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -51985,10 +51985,10 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -52030,7 +52030,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -52074,10 +52074,10 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -52119,7 +52119,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -52163,10 +52163,10 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -52252,10 +52252,10 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -52294,10 +52294,10 @@
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -52341,10 +52341,10 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -52386,7 +52386,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -52406,10 +52406,10 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -52427,7 +52427,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -52471,10 +52471,10 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -52516,7 +52516,7 @@
         <v>7</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -52560,10 +52560,10 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -52605,7 +52605,7 @@
         <v>7</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -52649,10 +52649,10 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -52691,7 +52691,7 @@
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -52738,10 +52738,10 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -52780,7 +52780,7 @@
         <v>9</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -52803,10 +52803,10 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -52821,7 +52821,7 @@
         <v>10</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>8</v>
@@ -52868,10 +52868,10 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -52910,7 +52910,7 @@
         <v>9</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -52957,10 +52957,10 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -52999,10 +52999,10 @@
         <v>7</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -53046,10 +53046,10 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -53088,10 +53088,10 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -53135,10 +53135,10 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -53177,7 +53177,7 @@
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC24">
         <v>9</v>
@@ -53224,10 +53224,10 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -53313,10 +53313,10 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -53358,7 +53358,7 @@
         <v>10</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -53402,10 +53402,10 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -53447,7 +53447,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -53491,10 +53491,10 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -53580,10 +53580,10 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -53625,7 +53625,7 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -53669,10 +53669,10 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -53711,10 +53711,10 @@
         <v>7</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -53758,10 +53758,10 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -53800,10 +53800,10 @@
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -53826,10 +53826,10 @@
         <v>10</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -53847,10 +53847,10 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -53889,10 +53889,10 @@
         <v>10</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -53936,10 +53936,10 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -53978,7 +53978,7 @@
         <v>8</v>
       </c>
       <c r="AB33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -54025,10 +54025,10 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -54067,10 +54067,10 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -54114,10 +54114,10 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -54156,10 +54156,10 @@
         <v>7</v>
       </c>
       <c r="AB35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -54203,10 +54203,10 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -54245,10 +54245,10 @@
         <v>5</v>
       </c>
       <c r="AB36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -54292,10 +54292,10 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -54337,7 +54337,7 @@
         <v>8</v>
       </c>
       <c r="AC37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -54381,10 +54381,10 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -54470,10 +54470,10 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -54512,10 +54512,10 @@
         <v>9</v>
       </c>
       <c r="AB39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -54708,7 +54708,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>7</v>
@@ -54797,7 +54797,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -54839,7 +54839,7 @@
         <v>7</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -54886,7 +54886,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>5</v>
@@ -54975,7 +54975,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>7</v>
@@ -55064,7 +55064,7 @@
         <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>6</v>
@@ -55153,7 +55153,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>9</v>
@@ -55242,7 +55242,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>7</v>
@@ -55331,7 +55331,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>5</v>
@@ -55420,7 +55420,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -55509,7 +55509,7 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>6</v>
@@ -55551,7 +55551,7 @@
         <v>9</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>8</v>
@@ -55598,7 +55598,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -55687,7 +55687,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>7</v>
@@ -55729,7 +55729,7 @@
         <v>10</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>6</v>
@@ -55776,7 +55776,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>5</v>
@@ -55865,7 +55865,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -55951,7 +55951,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -56031,7 +56031,7 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>7</v>
@@ -56120,7 +56120,7 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>5</v>
@@ -56209,7 +56209,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>6</v>
@@ -56298,7 +56298,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>6</v>
@@ -56387,7 +56387,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>7</v>
@@ -56476,7 +56476,7 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>7</v>
@@ -56518,7 +56518,7 @@
         <v>7</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>7</v>
@@ -56565,7 +56565,7 @@
         <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -56654,7 +56654,7 @@
         <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>7</v>
@@ -56743,7 +56743,7 @@
         <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>7</v>
@@ -56832,7 +56832,7 @@
         <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>5</v>
@@ -57054,7 +57054,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -57131,7 +57131,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -57205,7 +57205,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -57235,7 +57235,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -57273,7 +57273,7 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -57309,7 +57309,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -57350,7 +57350,7 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -57386,7 +57386,7 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -57427,7 +57427,7 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -57463,7 +57463,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -57504,7 +57504,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -57540,7 +57540,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -57581,7 +57581,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -57617,7 +57617,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -57658,7 +57658,7 @@
         <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -57694,7 +57694,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -57735,7 +57735,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -57771,7 +57771,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -57812,7 +57812,7 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -57889,7 +57889,7 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -57925,7 +57925,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -57966,7 +57966,7 @@
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -58043,7 +58043,7 @@
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -58079,7 +58079,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -58120,7 +58120,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -58156,7 +58156,7 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -58197,7 +58197,7 @@
         <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -58233,7 +58233,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -58256,7 +58256,7 @@
         <v>6</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -58274,7 +58274,7 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -58310,7 +58310,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>-1</v>
@@ -58351,7 +58351,7 @@
         <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -58387,7 +58387,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -58428,7 +58428,7 @@
         <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -58505,7 +58505,7 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -58541,7 +58541,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -58582,7 +58582,7 @@
         <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -58618,7 +58618,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -58659,7 +58659,7 @@
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -58695,7 +58695,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -58736,7 +58736,7 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -58772,7 +58772,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -58813,7 +58813,7 @@
         <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -58849,7 +58849,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -58890,7 +58890,7 @@
         <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -58967,7 +58967,7 @@
         <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -59003,7 +59003,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -59044,7 +59044,7 @@
         <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -59080,7 +59080,7 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -59121,7 +59121,7 @@
         <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -59198,7 +59198,7 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -59234,7 +59234,7 @@
         <v>7</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -59275,7 +59275,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -62499,7 +62499,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -62588,7 +62588,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>7</v>
@@ -62677,7 +62677,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -62766,7 +62766,7 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>9</v>
@@ -62855,7 +62855,7 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -62944,7 +62944,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -63033,7 +63033,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -63075,7 +63075,7 @@
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -63122,7 +63122,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>9</v>
@@ -63211,7 +63211,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -63253,7 +63253,7 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -63300,7 +63300,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -63342,7 +63342,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>5</v>
@@ -63389,7 +63389,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -63431,7 +63431,7 @@
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>7</v>
@@ -63478,7 +63478,7 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>8</v>
@@ -63520,7 +63520,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -63567,7 +63567,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>5</v>
@@ -63609,7 +63609,7 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -63656,7 +63656,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -63698,7 +63698,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -63745,7 +63745,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -63834,7 +63834,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -63876,7 +63876,7 @@
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -63923,7 +63923,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -63965,7 +63965,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -64012,7 +64012,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -64054,7 +64054,7 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -64101,7 +64101,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -64190,7 +64190,7 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -64232,7 +64232,7 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -64279,7 +64279,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -64321,7 +64321,7 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -64368,7 +64368,7 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -64410,7 +64410,7 @@
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -64457,7 +64457,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -64546,7 +64546,7 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -64635,7 +64635,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -64724,7 +64724,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>8</v>
@@ -64813,7 +64813,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>9</v>
@@ -64902,7 +64902,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -64944,7 +64944,7 @@
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -64991,7 +64991,7 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>9</v>
@@ -65080,7 +65080,7 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>5</v>
@@ -65169,7 +65169,7 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -65211,7 +65211,7 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC34">
         <v>7</v>
@@ -65258,7 +65258,7 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -65347,7 +65347,7 @@
         <v>8</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>8</v>
@@ -65436,7 +65436,7 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>5</v>
@@ -65478,7 +65478,7 @@
         <v>6</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC37">
         <v>6</v>
@@ -65525,7 +65525,7 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>9</v>
@@ -65614,7 +65614,7 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -65703,7 +65703,7 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -65745,7 +65745,7 @@
         <v>7</v>
       </c>
       <c r="AB40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC40">
         <v>7</v>
@@ -65792,7 +65792,7 @@
         <v>8</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>7</v>
@@ -65834,7 +65834,7 @@
         <v>9</v>
       </c>
       <c r="AB41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC41">
         <v>8</v>
@@ -65881,7 +65881,7 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -73772,7 +73772,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -73849,7 +73849,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -73885,7 +73885,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -73926,7 +73926,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -73962,7 +73962,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -74003,7 +74003,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -74080,7 +74080,7 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -74116,7 +74116,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -74157,7 +74157,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -74234,7 +74234,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -74311,7 +74311,7 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -74388,7 +74388,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -74465,7 +74465,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -74542,7 +74542,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -74578,7 +74578,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -74619,7 +74619,7 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -74696,7 +74696,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -74773,7 +74773,7 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -74809,7 +74809,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -74850,7 +74850,7 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -74927,7 +74927,7 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -75004,7 +75004,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -75040,7 +75040,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -75081,7 +75081,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -75117,7 +75117,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -75158,7 +75158,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -75235,7 +75235,7 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -75312,7 +75312,7 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -75348,7 +75348,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -75389,7 +75389,7 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -75466,7 +75466,7 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -75543,7 +75543,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -75579,7 +75579,7 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -75620,7 +75620,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -75656,7 +75656,7 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -75697,7 +75697,7 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -75774,7 +75774,7 @@
         <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -75851,7 +75851,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -75887,7 +75887,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -75928,7 +75928,7 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -76005,7 +76005,7 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -76082,7 +76082,7 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -76159,7 +76159,7 @@
         <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -76236,7 +76236,7 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -76272,7 +76272,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -76313,7 +76313,7 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -76349,7 +76349,7 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -76390,7 +76390,7 @@
         <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
         <v>-1</v>
@@ -76426,7 +76426,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -76467,7 +76467,7 @@
         <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -76544,7 +76544,7 @@
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
         <v>-1</v>
@@ -76580,7 +76580,7 @@
         <v>9</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -76621,7 +76621,7 @@
         <v>9</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>-1</v>
@@ -76657,7 +76657,7 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -76698,7 +76698,7 @@
         <v>8</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J42">
         <v>-1</v>
@@ -76734,7 +76734,7 @@
         <v>9</v>
       </c>
       <c r="U42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V42">
         <v>7</v>
@@ -76775,7 +76775,7 @@
         <v>6</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J43">
         <v>-1</v>
@@ -83377,7 +83377,7 @@
         <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -83419,7 +83419,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -83466,7 +83466,7 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -83555,7 +83555,7 @@
         <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -83597,7 +83597,7 @@
         <v>6</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -83644,7 +83644,7 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -83686,7 +83686,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -83733,7 +83733,7 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -83775,7 +83775,7 @@
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -83822,7 +83822,7 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -83911,7 +83911,7 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -83953,7 +83953,7 @@
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -84000,7 +84000,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -84178,7 +84178,7 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -84267,7 +84267,7 @@
         <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -84309,7 +84309,7 @@
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -84356,7 +84356,7 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -84398,7 +84398,7 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -84445,7 +84445,7 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -84487,7 +84487,7 @@
         <v>6</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -84801,7 +84801,7 @@
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -84843,7 +84843,7 @@
         <v>6</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -84890,7 +84890,7 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -84932,7 +84932,7 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -85068,7 +85068,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -85110,7 +85110,7 @@
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -85157,7 +85157,7 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -85199,7 +85199,7 @@
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -85246,7 +85246,7 @@
         <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -85288,7 +85288,7 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -85335,7 +85335,7 @@
         <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -85377,7 +85377,7 @@
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -85424,7 +85424,7 @@
         <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -85466,7 +85466,7 @@
         <v>9</v>
       </c>
       <c r="AC27">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -85513,7 +85513,7 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -85555,7 +85555,7 @@
         <v>9</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -85602,7 +85602,7 @@
         <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -85644,7 +85644,7 @@
         <v>9</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -85691,7 +85691,7 @@
         <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -85733,7 +85733,7 @@
         <v>7</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -85780,7 +85780,7 @@
         <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -85822,7 +85822,7 @@
         <v>7</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -85869,7 +85869,7 @@
         <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -85911,7 +85911,7 @@
         <v>7</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -85958,7 +85958,7 @@
         <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -86000,7 +86000,7 @@
         <v>7</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -86047,7 +86047,7 @@
         <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -86089,7 +86089,7 @@
         <v>8</v>
       </c>
       <c r="AC34">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -12393,7 +12393,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -12482,7 +12482,7 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -12571,7 +12571,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -12660,7 +12660,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -12749,7 +12749,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -12838,7 +12838,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -12927,7 +12927,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -13016,7 +13016,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -13105,7 +13105,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -13194,7 +13194,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -13283,7 +13283,7 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -13372,7 +13372,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -13461,7 +13461,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -13550,7 +13550,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -13639,7 +13639,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>6</v>
@@ -13728,7 +13728,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -13817,7 +13817,7 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>7</v>
@@ -13906,7 +13906,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -13995,7 +13995,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>7</v>
@@ -14084,7 +14084,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -14173,7 +14173,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>7</v>
@@ -14262,7 +14262,7 @@
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -14351,7 +14351,7 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -14440,7 +14440,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -14529,7 +14529,7 @@
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>7</v>
@@ -14618,7 +14618,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>6</v>
@@ -14707,7 +14707,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>6</v>
@@ -14796,7 +14796,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -14885,7 +14885,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -14974,7 +14974,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -15063,7 +15063,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>7</v>
@@ -15152,7 +15152,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -15241,7 +15241,7 @@
         <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -15330,7 +15330,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>6</v>
@@ -15419,7 +15419,7 @@
         <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -15508,7 +15508,7 @@
         <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
         <v>7</v>
@@ -15597,7 +15597,7 @@
         <v>10</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -15686,7 +15686,7 @@
         <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L41">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>5</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
         <v>5</v>
@@ -15864,7 +15864,7 @@
         <v>9</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L43">
         <v>10</v>
@@ -15953,7 +15953,7 @@
         <v>9</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
         <v>6</v>
@@ -16169,7 +16169,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -16246,7 +16246,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -16323,7 +16323,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -16400,7 +16400,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -16477,7 +16477,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>8</v>
@@ -16513,7 +16513,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -16554,7 +16554,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>8</v>
@@ -16631,7 +16631,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -16708,7 +16708,7 @@
         <v>4</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -16785,7 +16785,7 @@
         <v>4</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -16862,7 +16862,7 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -16898,7 +16898,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -16939,7 +16939,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -17016,7 +17016,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>8</v>
@@ -17093,7 +17093,7 @@
         <v>4</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -17170,7 +17170,7 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -17247,7 +17247,7 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -17283,7 +17283,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -17324,7 +17324,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -17401,7 +17401,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -17478,7 +17478,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -17632,7 +17632,7 @@
         <v>4</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -17709,7 +17709,7 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -17745,7 +17745,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>8</v>
@@ -17786,7 +17786,7 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>8</v>
@@ -17863,7 +17863,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -17940,7 +17940,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>7</v>
@@ -18017,7 +18017,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -18094,7 +18094,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>7</v>
@@ -18171,7 +18171,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>7</v>
@@ -18248,7 +18248,7 @@
         <v>4</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -18325,7 +18325,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>9</v>
@@ -18402,7 +18402,7 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>7</v>
@@ -21375,10 +21375,10 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -21411,10 +21411,10 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -21452,10 +21452,10 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -21491,7 +21491,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -21529,10 +21529,10 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -21568,7 +21568,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -21606,10 +21606,10 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -21683,10 +21683,10 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -21760,10 +21760,10 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -21837,10 +21837,10 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -21876,7 +21876,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -21914,10 +21914,10 @@
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -21991,10 +21991,10 @@
         <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -22068,10 +22068,10 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -22145,10 +22145,10 @@
         <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -22222,10 +22222,10 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -22299,10 +22299,10 @@
         <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>8</v>
@@ -22338,7 +22338,7 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -22376,10 +22376,10 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -22453,10 +22453,10 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -22530,10 +22530,10 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -22607,10 +22607,10 @@
         <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -22684,10 +22684,10 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -22761,10 +22761,10 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -22838,10 +22838,10 @@
         <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -22877,7 +22877,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -25953,7 +25953,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>7</v>
@@ -26030,7 +26030,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -26107,7 +26107,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -26184,7 +26184,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -26261,7 +26261,7 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -26338,7 +26338,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -26415,7 +26415,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>7</v>
@@ -26451,7 +26451,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -26492,7 +26492,7 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>8</v>
@@ -26569,7 +26569,7 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>8</v>
@@ -26605,7 +26605,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -26646,7 +26646,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -26723,7 +26723,7 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -26800,7 +26800,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -26877,7 +26877,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -26954,7 +26954,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>8</v>
@@ -26990,7 +26990,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -27031,7 +27031,7 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>9</v>
@@ -27067,7 +27067,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -27108,7 +27108,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -27144,7 +27144,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -27185,7 +27185,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
         <v>8</v>
@@ -27221,7 +27221,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -27262,7 +27262,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -27298,7 +27298,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -27339,7 +27339,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -27375,7 +27375,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -27416,7 +27416,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -27452,7 +27452,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -27493,7 +27493,7 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -27529,7 +27529,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -27570,7 +27570,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>6</v>
@@ -27647,7 +27647,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>7</v>
@@ -27724,7 +27724,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -27760,7 +27760,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -27801,7 +27801,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -27837,7 +27837,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -27878,7 +27878,7 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -27914,7 +27914,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>5</v>
@@ -27955,7 +27955,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>5</v>
@@ -28032,7 +28032,7 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>5</v>
@@ -36864,7 +36864,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -36900,7 +36900,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -36941,7 +36941,7 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -36977,7 +36977,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -37018,7 +37018,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -37054,7 +37054,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -37095,7 +37095,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -37131,7 +37131,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -37172,7 +37172,7 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>8</v>
@@ -37249,7 +37249,7 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -37285,7 +37285,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -37326,7 +37326,7 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>7</v>
@@ -37362,7 +37362,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -37403,7 +37403,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -37439,7 +37439,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -37480,7 +37480,7 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -37557,7 +37557,7 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -37593,7 +37593,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -37634,7 +37634,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>10</v>
@@ -37670,7 +37670,7 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -37711,7 +37711,7 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -37788,7 +37788,7 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -37824,7 +37824,7 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -37865,7 +37865,7 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -37901,7 +37901,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -37942,7 +37942,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -37978,7 +37978,7 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -38019,7 +38019,7 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -38055,7 +38055,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -38096,7 +38096,7 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -38132,7 +38132,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -38173,7 +38173,7 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -38209,7 +38209,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -38250,7 +38250,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>10</v>
@@ -38286,7 +38286,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -38327,7 +38327,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -38404,7 +38404,7 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -38440,7 +38440,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -38481,7 +38481,7 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>9</v>
@@ -38555,7 +38555,7 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>7</v>
@@ -38585,7 +38585,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -38623,7 +38623,7 @@
         <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -38700,7 +38700,7 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>7</v>
@@ -38736,7 +38736,7 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -38806,7 +38806,7 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>10</v>
@@ -38883,7 +38883,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>7</v>
@@ -38919,7 +38919,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -38960,7 +38960,7 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -38996,7 +38996,7 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -39037,7 +39037,7 @@
         <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
         <v>7</v>
@@ -39073,7 +39073,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -39114,7 +39114,7 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>8</v>
@@ -39150,7 +39150,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -39191,7 +39191,7 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
         <v>5</v>
@@ -39227,7 +39227,7 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>5</v>
@@ -39268,7 +39268,7 @@
         <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>9</v>
@@ -39345,7 +39345,7 @@
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
         <v>6</v>
@@ -39422,7 +39422,7 @@
         <v>5</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>7</v>
@@ -39499,7 +39499,7 @@
         <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
         <v>10</v>
@@ -39535,7 +39535,7 @@
         <v>5</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -39576,7 +39576,7 @@
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
         <v>8</v>
@@ -39653,7 +39653,7 @@
         <v>6</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>7</v>
@@ -39730,7 +39730,7 @@
         <v>5</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J42">
         <v>6</v>
@@ -39766,7 +39766,7 @@
         <v>5</v>
       </c>
       <c r="U42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>6</v>
@@ -39807,7 +39807,7 @@
         <v>5</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J43">
         <v>8</v>
@@ -39884,7 +39884,7 @@
         <v>5</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J44">
         <v>6</v>
@@ -39920,7 +39920,7 @@
         <v>5</v>
       </c>
       <c r="U44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V44">
         <v>5</v>
@@ -39961,7 +39961,7 @@
         <v>5</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J45">
         <v>5</v>
@@ -39997,7 +39997,7 @@
         <v>5</v>
       </c>
       <c r="U45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V45">
         <v>5</v>
@@ -40202,7 +40202,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>6</v>
@@ -40244,7 +40244,7 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -40291,7 +40291,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -40333,7 +40333,7 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -40380,7 +40380,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>7</v>
@@ -40422,7 +40422,7 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>6</v>
@@ -40469,7 +40469,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>6</v>
@@ -40511,7 +40511,7 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>5</v>
@@ -40558,7 +40558,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>10</v>
@@ -40647,7 +40647,7 @@
         <v>4</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <v>5</v>
@@ -40736,7 +40736,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -40778,7 +40778,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -40825,7 +40825,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>5</v>
@@ -40867,7 +40867,7 @@
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>5</v>
@@ -40914,7 +40914,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -40956,7 +40956,7 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -41003,7 +41003,7 @@
         <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>5</v>
@@ -41045,7 +41045,7 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>5</v>
@@ -41092,7 +41092,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>5</v>
@@ -41181,7 +41181,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>10</v>
@@ -41223,7 +41223,7 @@
         <v>9</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>10</v>
@@ -41270,7 +41270,7 @@
         <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>7</v>
@@ -41359,7 +41359,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>6</v>
@@ -41401,7 +41401,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -41448,7 +41448,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>7</v>
@@ -41490,7 +41490,7 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -41537,7 +41537,7 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>5</v>
@@ -41626,7 +41626,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>7</v>
@@ -41715,7 +41715,7 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>7</v>
@@ -41804,7 +41804,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>7</v>
@@ -41846,7 +41846,7 @@
         <v>6</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -41893,7 +41893,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>6</v>
@@ -41935,7 +41935,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -41982,7 +41982,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>7</v>
@@ -42071,7 +42071,7 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -42113,7 +42113,7 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB25">
         <v>5</v>
@@ -42160,7 +42160,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>5</v>
@@ -42202,7 +42202,7 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -42249,7 +42249,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N27">
         <v>5</v>
@@ -42338,7 +42338,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>7</v>
@@ -42427,7 +42427,7 @@
         <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>7</v>
@@ -42510,13 +42510,13 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>5</v>
@@ -42605,7 +42605,7 @@
         <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>9</v>
@@ -42694,7 +42694,7 @@
         <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>7</v>
@@ -42783,7 +42783,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>7</v>
@@ -43541,7 +43541,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -45723,7 +45723,7 @@
         <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -45800,7 +45800,7 @@
         <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -45877,7 +45877,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -45954,7 +45954,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -46031,7 +46031,7 @@
         <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>7</v>
@@ -46067,7 +46067,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -46108,7 +46108,7 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -46185,7 +46185,7 @@
         <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -46262,7 +46262,7 @@
         <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -46339,7 +46339,7 @@
         <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>7</v>
@@ -46375,7 +46375,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -46416,7 +46416,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -46493,7 +46493,7 @@
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -46570,7 +46570,7 @@
         <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -46647,7 +46647,7 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -46683,7 +46683,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -46724,7 +46724,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -46760,7 +46760,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -46801,7 +46801,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -46837,7 +46837,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -46878,7 +46878,7 @@
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>7</v>
@@ -46955,7 +46955,7 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>7</v>
@@ -46991,7 +46991,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -47032,7 +47032,7 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -47109,7 +47109,7 @@
         <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -47145,7 +47145,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -47186,7 +47186,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -47222,7 +47222,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -47263,7 +47263,7 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -47299,7 +47299,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -47340,7 +47340,7 @@
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -47376,7 +47376,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -47417,7 +47417,7 @@
         <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -47494,7 +47494,7 @@
         <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>8</v>
@@ -47530,7 +47530,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -47571,7 +47571,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -47648,7 +47648,7 @@
         <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -47725,7 +47725,7 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>9</v>
@@ -47802,7 +47802,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>6</v>
@@ -47879,7 +47879,7 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>5</v>
@@ -47915,7 +47915,7 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -47956,7 +47956,7 @@
         <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -48033,7 +48033,7 @@
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>8</v>
@@ -48069,7 +48069,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -48110,7 +48110,7 @@
         <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -48146,7 +48146,7 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -48187,7 +48187,7 @@
         <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>7</v>
@@ -48223,7 +48223,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -48413,10 +48413,10 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -48455,7 +48455,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <v>5</v>
@@ -48502,10 +48502,10 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -48544,7 +48544,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -48591,10 +48591,10 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -48680,10 +48680,10 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>4</v>
@@ -48722,7 +48722,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -48769,10 +48769,10 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -48811,7 +48811,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>8</v>
@@ -48858,10 +48858,10 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -48900,7 +48900,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -48947,10 +48947,10 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>6</v>
@@ -48989,7 +48989,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>9</v>
@@ -49078,10 +49078,10 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -49125,10 +49125,10 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -49167,7 +49167,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -49214,10 +49214,10 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -49256,7 +49256,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>8</v>
@@ -49303,10 +49303,10 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>9</v>
@@ -49345,7 +49345,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -49392,10 +49392,10 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -49481,10 +49481,10 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -49523,10 +49523,10 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>9</v>
@@ -49570,10 +49570,10 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -49612,10 +49612,10 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -49659,10 +49659,10 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>4</v>
@@ -49701,7 +49701,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -49748,10 +49748,10 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -49837,10 +49837,10 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -49926,10 +49926,10 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -49968,7 +49968,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -50015,10 +50015,10 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -50057,7 +50057,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -50104,10 +50104,10 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -50146,10 +50146,10 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -50178,7 +50178,7 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>4</v>
@@ -50202,7 +50202,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -50246,10 +50246,10 @@
         <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -50288,7 +50288,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -50332,7 +50332,7 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -50409,7 +50409,7 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -50489,10 +50489,10 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -50531,10 +50531,10 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
         <v>9</v>
@@ -50578,10 +50578,10 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -50620,7 +50620,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>9</v>
@@ -50667,10 +50667,10 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -50709,7 +50709,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>8</v>
@@ -50756,10 +50756,10 @@
         <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>8</v>
@@ -50845,10 +50845,10 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z32">
         <v>5</v>
@@ -50934,10 +50934,10 @@
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -50976,10 +50976,10 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -51023,10 +51023,10 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>7</v>
@@ -51065,10 +51065,10 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>7</v>
@@ -51112,10 +51112,10 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -51154,7 +51154,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z35">
         <v>9</v>
@@ -51201,10 +51201,10 @@
         <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>4</v>
@@ -51243,7 +51243,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -51445,7 +51445,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -51487,7 +51487,7 @@
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>7</v>
@@ -51534,7 +51534,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -51623,7 +51623,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -51665,7 +51665,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -51712,7 +51712,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -51754,7 +51754,7 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>7</v>
@@ -51801,7 +51801,7 @@
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -51843,7 +51843,7 @@
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -51890,7 +51890,7 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -52068,7 +52068,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -52110,7 +52110,7 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>8</v>
@@ -52157,7 +52157,7 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -52246,7 +52246,7 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -52288,7 +52288,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>5</v>
@@ -52335,7 +52335,7 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -52377,7 +52377,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>9</v>
@@ -52465,7 +52465,7 @@
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -52507,7 +52507,7 @@
         <v>5</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -52554,7 +52554,7 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>6</v>
@@ -52643,7 +52643,7 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -52732,7 +52732,7 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -52862,7 +52862,7 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -52951,7 +52951,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -53040,7 +53040,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -53129,7 +53129,7 @@
         <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -53218,7 +53218,7 @@
         <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -53307,7 +53307,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -53396,7 +53396,7 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -53438,7 +53438,7 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -53485,7 +53485,7 @@
         <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -53574,7 +53574,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -53663,7 +53663,7 @@
         <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>8</v>
@@ -53705,7 +53705,7 @@
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>7</v>
@@ -53752,7 +53752,7 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -53930,7 +53930,7 @@
         <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>8</v>
@@ -53972,7 +53972,7 @@
         <v>5</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -54019,7 +54019,7 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -54108,7 +54108,7 @@
         <v>5</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -54150,7 +54150,7 @@
         <v>5</v>
       </c>
       <c r="Z35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>7</v>
@@ -54197,7 +54197,7 @@
         <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>5</v>
@@ -54286,7 +54286,7 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>7</v>
@@ -54375,7 +54375,7 @@
         <v>5</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -54417,7 +54417,7 @@
         <v>5</v>
       </c>
       <c r="Z38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA38">
         <v>5</v>
@@ -54464,7 +54464,7 @@
         <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>10</v>
@@ -54714,7 +54714,7 @@
         <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -54756,7 +54756,7 @@
         <v>9</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -55070,7 +55070,7 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -55159,7 +55159,7 @@
         <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -55337,7 +55337,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -55515,7 +55515,7 @@
         <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -55604,7 +55604,7 @@
         <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -55693,7 +55693,7 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -55735,7 +55735,7 @@
         <v>6</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -56037,7 +56037,7 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -56079,7 +56079,7 @@
         <v>7</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -56482,7 +56482,7 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -56524,7 +56524,7 @@
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -56571,7 +56571,7 @@
         <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -56660,7 +56660,7 @@
         <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -56749,7 +56749,7 @@
         <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -56791,7 +56791,7 @@
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -57057,7 +57057,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -57093,7 +57093,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -57134,7 +57134,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -57276,7 +57276,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -57312,7 +57312,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -57353,7 +57353,7 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -57389,7 +57389,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -57430,7 +57430,7 @@
         <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -57466,7 +57466,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -57507,7 +57507,7 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -57543,7 +57543,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -57584,7 +57584,7 @@
         <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -57661,7 +57661,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -57738,7 +57738,7 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -57774,7 +57774,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -57815,7 +57815,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -57851,7 +57851,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -57892,7 +57892,7 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -57928,7 +57928,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -57969,7 +57969,7 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -58046,7 +58046,7 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -58082,7 +58082,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -58123,7 +58123,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -58159,7 +58159,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -58200,7 +58200,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -58236,7 +58236,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -58354,7 +58354,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -58390,7 +58390,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -58431,7 +58431,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -58467,7 +58467,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -58508,7 +58508,7 @@
         <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -58585,7 +58585,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -58621,7 +58621,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -58662,7 +58662,7 @@
         <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -58698,7 +58698,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -58739,7 +58739,7 @@
         <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -58816,7 +58816,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -58852,7 +58852,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -58893,7 +58893,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -58929,7 +58929,7 @@
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -58970,7 +58970,7 @@
         <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -59047,7 +59047,7 @@
         <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -59124,7 +59124,7 @@
         <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -59201,7 +59201,7 @@
         <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -59237,7 +59237,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -59278,7 +59278,7 @@
         <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -59314,7 +59314,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -59491,7 +59491,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -59568,7 +59568,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -59604,7 +59604,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -59645,7 +59645,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -59681,7 +59681,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -59722,7 +59722,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -59758,7 +59758,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -59799,7 +59799,7 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -59876,7 +59876,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -59953,7 +59953,7 @@
         <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -59989,7 +59989,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -60030,7 +60030,7 @@
         <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -60066,7 +60066,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -60107,7 +60107,7 @@
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -60184,7 +60184,7 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -60220,7 +60220,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -60261,7 +60261,7 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -60297,7 +60297,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -60338,7 +60338,7 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -60415,7 +60415,7 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -60451,7 +60451,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -60492,7 +60492,7 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -60528,7 +60528,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -66097,7 +66097,7 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -66174,7 +66174,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -66251,7 +66251,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -66328,7 +66328,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -66405,7 +66405,7 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -66482,7 +66482,7 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -66559,7 +66559,7 @@
         <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -66595,7 +66595,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -66636,7 +66636,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -66713,7 +66713,7 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>7</v>
@@ -66749,7 +66749,7 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -66790,7 +66790,7 @@
         <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -66826,7 +66826,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -66867,7 +66867,7 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -66944,7 +66944,7 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -67021,7 +67021,7 @@
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -67098,7 +67098,7 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -67134,7 +67134,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -67175,7 +67175,7 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -67252,7 +67252,7 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -67329,7 +67329,7 @@
         <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -67365,7 +67365,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -67406,7 +67406,7 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -67442,7 +67442,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -67483,7 +67483,7 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>8</v>
@@ -67519,7 +67519,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -67560,7 +67560,7 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>8</v>
@@ -67637,7 +67637,7 @@
         <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -67714,7 +67714,7 @@
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -67791,7 +67791,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -67868,7 +67868,7 @@
         <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -67904,7 +67904,7 @@
         <v>6</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -67945,7 +67945,7 @@
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>8</v>
@@ -68022,7 +68022,7 @@
         <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -68058,7 +68058,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -68235,7 +68235,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -68697,7 +68697,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -68774,7 +68774,7 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -69236,7 +69236,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -83365,7 +83365,7 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -83454,7 +83454,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -83543,7 +83543,7 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>8</v>
@@ -83632,7 +83632,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -83721,7 +83721,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -83810,7 +83810,7 @@
         <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -83899,7 +83899,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -83988,7 +83988,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -84077,7 +84077,7 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -84119,7 +84119,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -84166,7 +84166,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -84208,7 +84208,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -84255,7 +84255,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -84344,7 +84344,7 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -84433,7 +84433,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -84522,7 +84522,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -84564,7 +84564,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -84611,7 +84611,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -84700,7 +84700,7 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -84789,7 +84789,7 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -84878,7 +84878,7 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -84967,7 +84967,7 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -85056,7 +85056,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -85145,7 +85145,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -85234,7 +85234,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -85323,7 +85323,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>6</v>
@@ -85412,7 +85412,7 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -85501,7 +85501,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -85590,7 +85590,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -85679,7 +85679,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>8</v>
@@ -85768,7 +85768,7 @@
         <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>7</v>
@@ -85857,7 +85857,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>8</v>
@@ -85946,7 +85946,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -86035,7 +86035,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -90115,7 +90115,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -90127,7 +90127,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -90204,7 +90204,7 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>9</v>
@@ -90216,7 +90216,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -90293,7 +90293,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -90305,7 +90305,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>9</v>
@@ -90382,7 +90382,7 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -90394,7 +90394,7 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -90471,7 +90471,7 @@
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>8</v>
@@ -90483,7 +90483,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -90525,7 +90525,7 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -90560,7 +90560,7 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -90572,7 +90572,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -90614,7 +90614,7 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -90649,7 +90649,7 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>9</v>
@@ -90661,7 +90661,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -90738,7 +90738,7 @@
         <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -90750,7 +90750,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -90827,7 +90827,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -90839,7 +90839,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -90869,7 +90869,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -90916,7 +90916,7 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>9</v>
@@ -90928,7 +90928,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -90958,7 +90958,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -91005,7 +91005,7 @@
         <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>7</v>
@@ -91017,7 +91017,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -91047,7 +91047,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -91094,7 +91094,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -91106,7 +91106,7 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>7</v>
@@ -91183,7 +91183,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -91195,7 +91195,7 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>7</v>
@@ -91272,7 +91272,7 @@
         <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>9</v>
@@ -91284,7 +91284,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -91326,7 +91326,7 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -91361,7 +91361,7 @@
         <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -91373,7 +91373,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -91403,7 +91403,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -91450,7 +91450,7 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>9</v>
@@ -91462,7 +91462,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -91492,7 +91492,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -91592,7 +91592,7 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -91604,7 +91604,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -91681,7 +91681,7 @@
         <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>10</v>
@@ -91693,7 +91693,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -91770,7 +91770,7 @@
         <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -91782,7 +91782,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -91859,7 +91859,7 @@
         <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>8</v>
@@ -91871,7 +91871,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>10</v>
@@ -91948,7 +91948,7 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -91960,7 +91960,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -92037,7 +92037,7 @@
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -92049,7 +92049,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -92091,7 +92091,7 @@
         <v>10</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -92126,7 +92126,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -92138,7 +92138,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>8</v>
@@ -92168,7 +92168,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -92215,7 +92215,7 @@
         <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>9</v>
@@ -92227,7 +92227,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -92257,7 +92257,7 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -92304,7 +92304,7 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>10</v>
@@ -92316,7 +92316,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -92393,7 +92393,7 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>7</v>
@@ -92405,7 +92405,7 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -92435,7 +92435,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -92482,7 +92482,7 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>10</v>
@@ -92494,7 +92494,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>10</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -3870,7 +3870,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -3947,7 +3947,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -4024,7 +4024,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -4060,7 +4060,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -4101,7 +4101,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -4178,7 +4178,7 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -4214,7 +4214,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -4255,7 +4255,7 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -4332,7 +4332,7 @@
         <v>4</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -4368,7 +4368,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -4409,7 +4409,7 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -4445,7 +4445,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -4486,7 +4486,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -4563,7 +4563,7 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -4599,7 +4599,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -4640,7 +4640,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>10</v>
@@ -4676,7 +4676,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -4717,7 +4717,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -4753,7 +4753,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -4794,7 +4794,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>10</v>
@@ -4871,7 +4871,7 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -4948,7 +4948,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -4984,7 +4984,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -5025,7 +5025,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>9</v>
@@ -5061,7 +5061,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -5102,7 +5102,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -5179,7 +5179,7 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>10</v>
@@ -5215,7 +5215,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -5256,7 +5256,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>9</v>
@@ -5333,7 +5333,7 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -5410,7 +5410,7 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -5446,7 +5446,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -5487,7 +5487,7 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -5523,7 +5523,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -5564,7 +5564,7 @@
         <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>6</v>
@@ -5600,7 +5600,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -5641,7 +5641,7 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -5718,7 +5718,7 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>8</v>
@@ -5795,7 +5795,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -5831,7 +5831,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -5872,7 +5872,7 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>10</v>
@@ -5949,7 +5949,7 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -5985,7 +5985,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -6026,7 +6026,7 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>8</v>
@@ -6062,7 +6062,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -6103,7 +6103,7 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>8</v>
@@ -6139,7 +6139,7 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -6180,7 +6180,7 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>10</v>
@@ -6216,7 +6216,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -6257,7 +6257,7 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J35">
         <v>10</v>
@@ -6293,7 +6293,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -6334,7 +6334,7 @@
         <v>4</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>6</v>
@@ -6411,7 +6411,7 @@
         <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>8</v>
@@ -6447,7 +6447,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -7622,7 +7622,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -23048,7 +23048,7 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -23125,7 +23125,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>9</v>
@@ -23202,7 +23202,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -23238,7 +23238,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -23279,7 +23279,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>9</v>
@@ -23356,7 +23356,7 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -23433,7 +23433,7 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>9</v>
@@ -23510,7 +23510,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -23587,7 +23587,7 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -23623,7 +23623,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -23664,7 +23664,7 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -23741,7 +23741,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -23818,7 +23818,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>10</v>
@@ -23854,7 +23854,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -23895,7 +23895,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>10</v>
@@ -23931,7 +23931,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -23972,7 +23972,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>10</v>
@@ -24049,7 +24049,7 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>10</v>
@@ -24126,7 +24126,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>9</v>
@@ -24203,7 +24203,7 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>10</v>
@@ -24280,7 +24280,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -24357,7 +24357,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -24434,7 +24434,7 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
         <v>10</v>
@@ -24511,7 +24511,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -24547,7 +24547,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -24588,7 +24588,7 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>9</v>
@@ -24665,7 +24665,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -24742,7 +24742,7 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>10</v>
@@ -24778,7 +24778,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -24819,7 +24819,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>10</v>
@@ -24855,7 +24855,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -24896,7 +24896,7 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -24973,7 +24973,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -25050,7 +25050,7 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>10</v>
@@ -25127,7 +25127,7 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -25204,7 +25204,7 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>10</v>
@@ -25281,7 +25281,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>10</v>
@@ -25358,7 +25358,7 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>10</v>
@@ -25435,7 +25435,7 @@
         <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
         <v>9</v>
@@ -25512,7 +25512,7 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
         <v>10</v>
@@ -25589,7 +25589,7 @@
         <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <v>10</v>
@@ -25666,7 +25666,7 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
         <v>9</v>
@@ -25743,7 +25743,7 @@
         <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J39">
         <v>10</v>
@@ -33414,7 +33414,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -33450,7 +33450,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -33491,7 +33491,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -33527,7 +33527,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -33568,7 +33568,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -33604,7 +33604,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -33645,7 +33645,7 @@
         <v>3</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -33722,7 +33722,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -33758,7 +33758,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -33799,7 +33799,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -33835,7 +33835,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -33876,7 +33876,7 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>10</v>
@@ -33912,7 +33912,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -33953,7 +33953,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -33989,7 +33989,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -34030,7 +34030,7 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -34066,7 +34066,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -34107,7 +34107,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -34143,7 +34143,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -34184,7 +34184,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -34220,7 +34220,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -34261,7 +34261,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>8</v>
@@ -34297,7 +34297,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -34338,7 +34338,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>9</v>
@@ -34415,7 +34415,7 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -34451,7 +34451,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -34492,7 +34492,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -34569,7 +34569,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>9</v>
@@ -34646,7 +34646,7 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -34723,7 +34723,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -34800,7 +34800,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -34877,7 +34877,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -34954,7 +34954,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -34990,7 +34990,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -35031,7 +35031,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>10</v>
@@ -35108,7 +35108,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -35144,7 +35144,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -35185,7 +35185,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -35262,7 +35262,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -35339,7 +35339,7 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -35416,7 +35416,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>8</v>
@@ -35452,7 +35452,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>9</v>
@@ -35493,7 +35493,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>8</v>
@@ -35570,7 +35570,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>10</v>
@@ -35606,7 +35606,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -35647,7 +35647,7 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -35683,7 +35683,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -35724,7 +35724,7 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>8</v>
@@ -35760,7 +35760,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>9</v>
@@ -35801,7 +35801,7 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -35878,7 +35878,7 @@
         <v>4</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>6</v>
@@ -35914,7 +35914,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>7</v>
@@ -35955,7 +35955,7 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>10</v>
@@ -35991,7 +35991,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>10</v>
@@ -36032,7 +36032,7 @@
         <v>3</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I38">
         <v>5</v>
@@ -36109,7 +36109,7 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
         <v>10</v>
@@ -36186,7 +36186,7 @@
         <v>10</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I40">
         <v>9</v>
@@ -36222,7 +36222,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -36263,7 +36263,7 @@
         <v>9</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -36299,7 +36299,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>6</v>
@@ -36340,7 +36340,7 @@
         <v>10</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I42">
         <v>10</v>
@@ -36417,7 +36417,7 @@
         <v>9</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I43">
         <v>8</v>
@@ -36453,7 +36453,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U43">
         <v>8</v>
@@ -36494,7 +36494,7 @@
         <v>8</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I44">
         <v>6</v>
@@ -36530,7 +36530,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>8</v>
@@ -36571,7 +36571,7 @@
         <v>9</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I45">
         <v>8</v>
@@ -36607,7 +36607,7 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U45">
         <v>9</v>
@@ -36648,7 +36648,7 @@
         <v>10</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I46">
         <v>10</v>
@@ -48407,7 +48407,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -48422,7 +48422,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>5</v>
@@ -48496,7 +48496,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>8</v>
@@ -48511,7 +48511,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -48553,7 +48553,7 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -48585,7 +48585,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -48600,7 +48600,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -48674,7 +48674,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -48689,7 +48689,7 @@
         <v>4</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -48763,7 +48763,7 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -48778,7 +48778,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -48805,7 +48805,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -48852,7 +48852,7 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -48867,7 +48867,7 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -48894,7 +48894,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -48941,7 +48941,7 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>8</v>
@@ -48956,7 +48956,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -48998,7 +48998,7 @@
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -49030,7 +49030,7 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>7</v>
@@ -49045,7 +49045,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -49072,7 +49072,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -49087,7 +49087,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -49134,7 +49134,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -49208,7 +49208,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>10</v>
@@ -49223,7 +49223,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>8</v>
@@ -49265,7 +49265,7 @@
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -49297,7 +49297,7 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -49312,7 +49312,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -49339,7 +49339,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -49386,7 +49386,7 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -49401,7 +49401,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -49475,7 +49475,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>8</v>
@@ -49490,7 +49490,7 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -49517,7 +49517,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -49564,7 +49564,7 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -49579,7 +49579,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -49653,7 +49653,7 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>5</v>
@@ -49668,7 +49668,7 @@
         <v>4</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -49742,7 +49742,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>10</v>
@@ -49757,7 +49757,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -49831,7 +49831,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -49846,7 +49846,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -49920,7 +49920,7 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>5</v>
@@ -49935,7 +49935,7 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -50009,7 +50009,7 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>10</v>
@@ -50024,7 +50024,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>8</v>
@@ -50066,7 +50066,7 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -50098,7 +50098,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -50113,7 +50113,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>9</v>
@@ -50140,7 +50140,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -50155,7 +50155,7 @@
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -50184,7 +50184,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>5</v>
@@ -50240,7 +50240,7 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -50255,7 +50255,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>9</v>
@@ -50297,7 +50297,7 @@
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>8</v>
@@ -50326,7 +50326,7 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>8</v>
@@ -50338,7 +50338,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -50403,7 +50403,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -50415,7 +50415,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -50483,7 +50483,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>7</v>
@@ -50498,7 +50498,7 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>8</v>
@@ -50525,7 +50525,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -50540,7 +50540,7 @@
         <v>9</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -50572,7 +50572,7 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>10</v>
@@ -50587,7 +50587,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -50614,7 +50614,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -50661,7 +50661,7 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>8</v>
@@ -50676,7 +50676,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>7</v>
@@ -50750,7 +50750,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>7</v>
@@ -50765,7 +50765,7 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -50839,7 +50839,7 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>7</v>
@@ -50854,7 +50854,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>5</v>
@@ -50928,7 +50928,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>9</v>
@@ -50943,7 +50943,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>8</v>
@@ -50970,7 +50970,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>7</v>
@@ -51032,7 +51032,7 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -51059,7 +51059,7 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -51106,7 +51106,7 @@
         <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>10</v>
@@ -51121,7 +51121,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>9</v>
@@ -51148,7 +51148,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -51163,7 +51163,7 @@
         <v>10</v>
       </c>
       <c r="AB35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC35">
         <v>9</v>
@@ -51195,7 +51195,7 @@
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -51210,7 +51210,7 @@
         <v>4</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -53820,7 +53820,7 @@
         <v>6</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -53841,7 +53841,7 @@
         <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -53883,7 +53883,7 @@
         <v>5</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -54803,7 +54803,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -54892,7 +54892,7 @@
         <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -54981,7 +54981,7 @@
         <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -55023,7 +55023,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -55248,7 +55248,7 @@
         <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -55290,7 +55290,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -55426,7 +55426,7 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -55468,7 +55468,7 @@
         <v>7</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -55782,7 +55782,7 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -55871,7 +55871,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -55954,7 +55954,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -56126,7 +56126,7 @@
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -56215,7 +56215,7 @@
         <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -56304,7 +56304,7 @@
         <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -56393,7 +56393,7 @@
         <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -56838,7 +56838,7 @@
         <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -56880,7 +56880,7 @@
         <v>5</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -58259,7 +58259,7 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -58277,7 +58277,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -58313,7 +58313,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -69680,7 +69680,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -69757,7 +69757,7 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -69834,7 +69834,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -69911,7 +69911,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -69988,7 +69988,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -70024,7 +70024,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -70065,7 +70065,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -70101,7 +70101,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -70142,7 +70142,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -70178,7 +70178,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -70219,7 +70219,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -70296,7 +70296,7 @@
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -70332,7 +70332,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -70373,7 +70373,7 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -70409,7 +70409,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -70450,7 +70450,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -70486,7 +70486,7 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -70527,7 +70527,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -70563,7 +70563,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -70604,7 +70604,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>8</v>
@@ -70640,7 +70640,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -70681,7 +70681,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -70717,7 +70717,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -70758,7 +70758,7 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -70835,7 +70835,7 @@
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -70871,7 +70871,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -70912,7 +70912,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>9</v>
@@ -70948,7 +70948,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -70989,7 +70989,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -71066,7 +71066,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -71143,7 +71143,7 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -71220,7 +71220,7 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -71297,7 +71297,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -71374,7 +71374,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -71451,7 +71451,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -71528,7 +71528,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -71564,7 +71564,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -71605,7 +71605,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -71641,7 +71641,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -71682,7 +71682,7 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>9</v>
@@ -71718,7 +71718,7 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -71759,7 +71759,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -71836,7 +71836,7 @@
         <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -71872,7 +71872,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -71913,7 +71913,7 @@
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>9</v>
@@ -71981,7 +71981,7 @@
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -73775,7 +73775,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -73852,7 +73852,7 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -73929,7 +73929,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -73965,7 +73965,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -74006,7 +74006,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -74042,7 +74042,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -74083,7 +74083,7 @@
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -74160,7 +74160,7 @@
         <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>8</v>
@@ -74196,7 +74196,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -74237,7 +74237,7 @@
         <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -74314,7 +74314,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>8</v>
@@ -74350,7 +74350,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -74391,7 +74391,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -74468,7 +74468,7 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -74504,7 +74504,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -74545,7 +74545,7 @@
         <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -74581,7 +74581,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -74622,7 +74622,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -74658,7 +74658,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -74699,7 +74699,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -74776,7 +74776,7 @@
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>7</v>
@@ -74853,7 +74853,7 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>6</v>
@@ -74889,7 +74889,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -74930,7 +74930,7 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -75007,7 +75007,7 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>9</v>
@@ -75084,7 +75084,7 @@
         <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -75120,7 +75120,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -75161,7 +75161,7 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>6</v>
@@ -75197,7 +75197,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -75238,7 +75238,7 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>10</v>
@@ -75315,7 +75315,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>7</v>
@@ -75392,7 +75392,7 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>6</v>
@@ -75428,7 +75428,7 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -75469,7 +75469,7 @@
         <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>9</v>
@@ -75505,7 +75505,7 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -75546,7 +75546,7 @@
         <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -75582,7 +75582,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -75623,7 +75623,7 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -75700,7 +75700,7 @@
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>8</v>
@@ -75736,7 +75736,7 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -75777,7 +75777,7 @@
         <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -75813,7 +75813,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -75854,7 +75854,7 @@
         <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>6</v>
@@ -75890,7 +75890,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -75931,7 +75931,7 @@
         <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>5</v>
@@ -76008,7 +76008,7 @@
         <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>10</v>
@@ -76044,7 +76044,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -76085,7 +76085,7 @@
         <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>10</v>
@@ -76162,7 +76162,7 @@
         <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>8</v>
@@ -76198,7 +76198,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -76239,7 +76239,7 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>10</v>
@@ -76316,7 +76316,7 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>10</v>
@@ -76393,7 +76393,7 @@
         <v>8</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>7</v>
@@ -76429,7 +76429,7 @@
         <v>8</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -76470,7 +76470,7 @@
         <v>9</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
         <v>10</v>
@@ -76547,7 +76547,7 @@
         <v>9</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>9</v>
@@ -76583,7 +76583,7 @@
         <v>9</v>
       </c>
       <c r="V40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -76624,7 +76624,7 @@
         <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
         <v>9</v>
@@ -76660,7 +76660,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>9</v>
@@ -76701,7 +76701,7 @@
         <v>9</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K42">
         <v>8</v>
@@ -76778,7 +76778,7 @@
         <v>7</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K43">
         <v>5</v>
@@ -76814,7 +76814,7 @@
         <v>8</v>
       </c>
       <c r="V43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W43">
         <v>5</v>
@@ -79970,7 +79970,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -80006,7 +80006,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -80047,7 +80047,7 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -80124,7 +80124,7 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -80201,7 +80201,7 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -80278,7 +80278,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>8</v>
@@ -80355,7 +80355,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -80432,7 +80432,7 @@
         <v>3</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -80509,7 +80509,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -80586,7 +80586,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -80663,7 +80663,7 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -80699,7 +80699,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -80740,7 +80740,7 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>9</v>
@@ -80817,7 +80817,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -80894,7 +80894,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>8</v>
@@ -80930,7 +80930,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -80971,7 +80971,7 @@
         <v>3</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>5</v>
@@ -81007,7 +81007,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -81048,7 +81048,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>8</v>
@@ -81084,7 +81084,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -81125,7 +81125,7 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>10</v>
@@ -81202,7 +81202,7 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>10</v>
@@ -81279,7 +81279,7 @@
         <v>3</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -81356,7 +81356,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -81392,7 +81392,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -81433,7 +81433,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -81510,7 +81510,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -81546,7 +81546,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -81587,7 +81587,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>10</v>
@@ -81741,7 +81741,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -81818,7 +81818,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>10</v>
@@ -81854,7 +81854,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -81895,7 +81895,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -81931,7 +81931,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -81972,7 +81972,7 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>7</v>
@@ -82008,7 +82008,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -82049,7 +82049,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>8</v>
@@ -82085,7 +82085,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -82126,7 +82126,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -82203,7 +82203,7 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -82280,7 +82280,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>9</v>
@@ -82316,7 +82316,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -82357,7 +82357,7 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -82434,7 +82434,7 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>6</v>
@@ -82511,7 +82511,7 @@
         <v>5</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>10</v>
@@ -82547,7 +82547,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>9</v>
@@ -82588,7 +82588,7 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I38">
         <v>6</v>
@@ -82624,7 +82624,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>6</v>
@@ -82665,7 +82665,7 @@
         <v>5</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>9</v>
@@ -82701,7 +82701,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>10</v>
@@ -82742,7 +82742,7 @@
         <v>3</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>6</v>
@@ -82778,7 +82778,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -82819,7 +82819,7 @@
         <v>2</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -82896,7 +82896,7 @@
         <v>7</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>9</v>
@@ -82973,7 +82973,7 @@
         <v>8</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>8</v>
@@ -83050,7 +83050,7 @@
         <v>8</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I44">
         <v>10</v>
@@ -83086,7 +83086,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U44">
         <v>10</v>
@@ -83127,7 +83127,7 @@
         <v>7</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I45">
         <v>9</v>
@@ -84089,7 +84089,7 @@
         <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -84131,7 +84131,7 @@
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -84534,7 +84534,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -84576,7 +84576,7 @@
         <v>6</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -84623,7 +84623,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -84665,7 +84665,7 @@
         <v>6</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -84712,7 +84712,7 @@
         <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -84754,7 +84754,7 @@
         <v>6</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -84979,7 +84979,7 @@
         <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -81664,7 +81664,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>5</v>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -6639,13 +6639,13 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -6654,7 +6654,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -6716,13 +6716,13 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -6793,13 +6793,13 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -6808,7 +6808,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -6826,7 +6826,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -6870,13 +6870,13 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>9</v>
@@ -6885,7 +6885,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -6947,13 +6947,13 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -6962,16 +6962,16 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>7</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -6980,7 +6980,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -7024,13 +7024,13 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>8</v>
@@ -7039,7 +7039,7 @@
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -7101,13 +7101,13 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -7116,7 +7116,7 @@
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -7134,7 +7134,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -7178,13 +7178,13 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -7193,7 +7193,7 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -7255,13 +7255,13 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -7270,7 +7270,7 @@
         <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -7332,13 +7332,13 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -7347,7 +7347,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -7409,13 +7409,13 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -7424,7 +7424,7 @@
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -7442,7 +7442,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -7486,13 +7486,13 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -7501,7 +7501,7 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -7510,7 +7510,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -7563,13 +7563,13 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -7578,7 +7578,7 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -7640,13 +7640,13 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -7655,16 +7655,16 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>7</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -7717,13 +7717,13 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -7732,7 +7732,7 @@
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -7794,13 +7794,13 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>7</v>
@@ -7809,7 +7809,7 @@
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -7871,13 +7871,13 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -7886,7 +7886,7 @@
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -7904,7 +7904,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -7948,13 +7948,13 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>5</v>
@@ -7963,10 +7963,10 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -8025,13 +8025,13 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -8049,7 +8049,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -8058,7 +8058,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -8102,13 +8102,13 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -8117,7 +8117,7 @@
         <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>5</v>
@@ -8179,13 +8179,13 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -8194,7 +8194,7 @@
         <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -8212,7 +8212,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -8256,13 +8256,13 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -8271,7 +8271,7 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -8333,13 +8333,13 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -8348,7 +8348,7 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -8366,7 +8366,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -8410,13 +8410,13 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>5</v>
@@ -8425,7 +8425,7 @@
         <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -8487,13 +8487,13 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -8502,7 +8502,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -8511,7 +8511,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -8564,13 +8564,13 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>8</v>
@@ -8579,7 +8579,7 @@
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -8641,13 +8641,13 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>8</v>
@@ -8656,7 +8656,7 @@
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -8665,7 +8665,7 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -8718,13 +8718,13 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>8</v>
@@ -8733,10 +8733,10 @@
         <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -8751,7 +8751,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -8795,13 +8795,13 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -8810,7 +8810,7 @@
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -8872,13 +8872,13 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -8887,7 +8887,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -8949,13 +8949,13 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -8964,7 +8964,7 @@
         <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -8982,7 +8982,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -9026,13 +9026,13 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -9041,7 +9041,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -9103,13 +9103,13 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -9118,7 +9118,7 @@
         <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -9127,7 +9127,7 @@
         <v>6</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -9180,13 +9180,13 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>9</v>
@@ -9195,7 +9195,7 @@
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -9213,7 +9213,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -9257,13 +9257,13 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9272,7 +9272,7 @@
         <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -9334,13 +9334,13 @@
         <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>10</v>
@@ -9349,7 +9349,7 @@
         <v>8</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -9411,13 +9411,13 @@
         <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
         <v>9</v>
@@ -9426,7 +9426,7 @@
         <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -9488,13 +9488,13 @@
         <v>6</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9503,7 +9503,7 @@
         <v>5</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
         <v>9</v>
@@ -9521,7 +9521,7 @@
         <v>5</v>
       </c>
       <c r="Y41">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -36882,7 +36882,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -36900,7 +36900,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -36959,7 +36959,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -37036,7 +37036,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>8</v>
@@ -37113,7 +37113,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>5</v>
@@ -37131,7 +37131,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -37190,7 +37190,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -37267,7 +37267,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>5</v>
@@ -37285,7 +37285,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -37344,7 +37344,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -37421,7 +37421,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -37652,7 +37652,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>10</v>
@@ -37806,7 +37806,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -37883,7 +37883,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>7</v>
@@ -37960,7 +37960,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>10</v>
@@ -38037,7 +38037,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>5</v>
@@ -38114,7 +38114,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -38191,7 +38191,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>8</v>
@@ -38268,7 +38268,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>9</v>
@@ -38345,7 +38345,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>5</v>
@@ -38422,7 +38422,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>5</v>
@@ -38499,7 +38499,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>9</v>
@@ -38570,7 +38570,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -38585,7 +38585,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -38718,7 +38718,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>6</v>
@@ -38824,7 +38824,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>10</v>
@@ -38901,7 +38901,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>7</v>
@@ -38978,7 +38978,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>8</v>
@@ -39055,7 +39055,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>6</v>
@@ -39132,7 +39132,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>8</v>
@@ -39209,7 +39209,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>8</v>
@@ -39227,7 +39227,7 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>6</v>
@@ -39286,7 +39286,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <v>5</v>
@@ -39304,7 +39304,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -39363,7 +39363,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>5</v>
@@ -39440,7 +39440,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P38">
         <v>5</v>
@@ -39458,7 +39458,7 @@
         <v>5</v>
       </c>
       <c r="U38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -39517,7 +39517,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
         <v>10</v>
@@ -39535,7 +39535,7 @@
         <v>5</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -39594,7 +39594,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
         <v>8</v>
@@ -39671,7 +39671,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P41">
         <v>6</v>
@@ -39748,7 +39748,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P42">
         <v>6</v>
@@ -39825,7 +39825,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P43">
         <v>10</v>
@@ -39902,7 +39902,7 @@
         <v>-1</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P44">
         <v>5</v>
@@ -39920,7 +39920,7 @@
         <v>5</v>
       </c>
       <c r="U44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V44">
         <v>5</v>
@@ -39979,7 +39979,7 @@
         <v>-1</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P45">
         <v>7</v>
@@ -40211,19 +40211,19 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -40238,13 +40238,13 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>6</v>
@@ -40300,19 +40300,19 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -40321,7 +40321,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -40389,19 +40389,19 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -40410,19 +40410,19 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>7</v>
@@ -40478,19 +40478,19 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -40499,13 +40499,13 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -40567,19 +40567,19 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -40656,19 +40656,19 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U9">
         <v>5</v>
@@ -40745,19 +40745,19 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -40778,7 +40778,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -40834,19 +40834,19 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -40855,7 +40855,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -40923,19 +40923,19 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -40944,19 +40944,19 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -41012,19 +41012,19 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -41033,13 +41033,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -41101,19 +41101,19 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -41122,19 +41122,19 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>6</v>
@@ -41190,19 +41190,19 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -41279,19 +41279,19 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -41300,7 +41300,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -41312,7 +41312,7 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -41368,19 +41368,19 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -41389,7 +41389,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -41401,7 +41401,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>6</v>
@@ -41457,19 +41457,19 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -41478,13 +41478,13 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>7</v>
@@ -41546,19 +41546,19 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>9</v>
@@ -41579,7 +41579,7 @@
         <v>6</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -41635,19 +41635,19 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -41668,7 +41668,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>7</v>
@@ -41724,19 +41724,19 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>6</v>
@@ -41813,19 +41813,19 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -41840,13 +41840,13 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>6</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -41902,19 +41902,19 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>10</v>
@@ -41991,19 +41991,19 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -42018,13 +42018,13 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>6</v>
@@ -42080,19 +42080,19 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -42101,19 +42101,19 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>5</v>
@@ -42169,19 +42169,19 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>6</v>
@@ -42190,19 +42190,19 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -42258,19 +42258,19 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -42279,7 +42279,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -42347,19 +42347,19 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -42374,13 +42374,13 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>7</v>
@@ -42436,19 +42436,19 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -42457,7 +42457,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -42525,19 +42525,19 @@
         <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -42614,19 +42614,19 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -42635,7 +42635,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -42703,19 +42703,19 @@
         <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -42736,7 +42736,7 @@
         <v>7</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>7</v>
@@ -42792,19 +42792,19 @@
         <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -42825,7 +42825,7 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB33">
         <v>7</v>
@@ -43020,7 +43020,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>5</v>
@@ -43097,7 +43097,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>6</v>
@@ -43174,7 +43174,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -43251,7 +43251,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>6</v>
@@ -43328,7 +43328,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>7</v>
@@ -43405,7 +43405,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>8</v>
@@ -43482,7 +43482,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -43559,7 +43559,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -43577,7 +43577,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -43636,7 +43636,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>5</v>
@@ -43713,7 +43713,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -43790,7 +43790,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -43944,7 +43944,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>5</v>
@@ -44021,7 +44021,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -44039,7 +44039,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -44098,7 +44098,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>5</v>
@@ -44175,7 +44175,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>7</v>
@@ -44252,7 +44252,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -44270,7 +44270,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -44370,7 +44370,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -44447,7 +44447,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>8</v>
@@ -44524,7 +44524,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -44601,7 +44601,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>6</v>
@@ -44678,7 +44678,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -44755,7 +44755,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>6</v>
@@ -44832,7 +44832,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -44909,7 +44909,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>6</v>
@@ -44927,7 +44927,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -44986,7 +44986,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -45063,7 +45063,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -45140,7 +45140,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -45217,7 +45217,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -45294,7 +45294,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>5</v>
@@ -45371,7 +45371,7 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -45448,7 +45448,7 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -45525,7 +45525,7 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>10</v>
@@ -45729,16 +45729,16 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -45756,7 +45756,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -45806,16 +45806,16 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>8</v>
@@ -45830,10 +45830,10 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -45883,16 +45883,16 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>9</v>
@@ -45907,10 +45907,10 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -45960,16 +45960,16 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -46037,16 +46037,16 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -46114,16 +46114,16 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>9</v>
@@ -46132,7 +46132,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -46191,16 +46191,16 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -46268,16 +46268,16 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -46345,16 +46345,16 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>7</v>
@@ -46369,7 +46369,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -46422,16 +46422,16 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -46440,7 +46440,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -46449,7 +46449,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -46499,16 +46499,16 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -46523,7 +46523,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -46576,16 +46576,16 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>9</v>
@@ -46594,7 +46594,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -46653,16 +46653,16 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>8</v>
@@ -46671,13 +46671,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -46730,16 +46730,16 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -46754,7 +46754,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -46807,16 +46807,16 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>9</v>
@@ -46825,7 +46825,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -46884,16 +46884,16 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -46961,16 +46961,16 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>8</v>
@@ -46979,16 +46979,16 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>7</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -47038,16 +47038,16 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>9</v>
@@ -47115,16 +47115,16 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>10</v>
@@ -47139,7 +47139,7 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -47192,16 +47192,16 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <v>5</v>
@@ -47210,13 +47210,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>5</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -47269,16 +47269,16 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -47287,7 +47287,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -47346,16 +47346,16 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>8</v>
@@ -47373,7 +47373,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -47423,16 +47423,16 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -47450,7 +47450,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -47500,16 +47500,16 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -47577,16 +47577,16 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>6</v>
@@ -47604,7 +47604,7 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -47654,16 +47654,16 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -47731,16 +47731,16 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -47755,10 +47755,10 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -47808,16 +47808,16 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -47835,7 +47835,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -47885,16 +47885,16 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>7</v>
@@ -47903,16 +47903,16 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>5</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -47962,16 +47962,16 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>5</v>
@@ -47980,16 +47980,16 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>5</v>
@@ -48039,16 +48039,16 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -48063,10 +48063,10 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -48116,16 +48116,16 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
         <v>7</v>
@@ -48134,16 +48134,16 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>5</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -48193,16 +48193,16 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -48211,7 +48211,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>6</v>
@@ -48431,13 +48431,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>6</v>
@@ -48446,13 +48446,13 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>5</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -48520,13 +48520,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -48535,19 +48535,19 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>6</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>6</v>
@@ -48556,7 +48556,7 @@
         <v>6</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -48609,13 +48609,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -48624,19 +48624,19 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>6</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>6</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -48645,7 +48645,7 @@
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -48698,13 +48698,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -48713,7 +48713,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -48787,13 +48787,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -48802,7 +48802,7 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -48814,7 +48814,7 @@
         <v>7</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -48876,13 +48876,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -48891,19 +48891,19 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -48912,7 +48912,7 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -48965,13 +48965,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -48980,13 +48980,13 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -49054,13 +49054,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -49069,7 +49069,7 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -49143,13 +49143,13 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T12">
         <v>3</v>
@@ -49158,13 +49158,13 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>5</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -49232,13 +49232,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -49247,7 +49247,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -49259,7 +49259,7 @@
         <v>8</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13">
         <v>10</v>
@@ -49321,13 +49321,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -49336,7 +49336,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -49348,7 +49348,7 @@
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -49410,13 +49410,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -49425,19 +49425,19 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>5</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>6</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -49446,7 +49446,7 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -49499,13 +49499,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -49514,7 +49514,7 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -49526,7 +49526,7 @@
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -49588,13 +49588,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -49603,7 +49603,7 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -49615,7 +49615,7 @@
         <v>7</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -49624,7 +49624,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -49677,13 +49677,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T18">
         <v>3</v>
@@ -49692,7 +49692,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -49766,13 +49766,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -49781,7 +49781,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -49802,7 +49802,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -49855,13 +49855,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -49870,7 +49870,7 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -49882,7 +49882,7 @@
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -49891,7 +49891,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -49944,13 +49944,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -49959,7 +49959,7 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -50033,13 +50033,13 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -50048,19 +50048,19 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -50122,13 +50122,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -50137,7 +50137,7 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -50149,7 +50149,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -50158,7 +50158,7 @@
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -50190,7 +50190,7 @@
         <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>4</v>
@@ -50199,7 +50199,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z24">
         <v>5</v>
@@ -50211,7 +50211,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -50264,13 +50264,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -50279,7 +50279,7 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -50291,7 +50291,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -50347,7 +50347,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -50359,13 +50359,13 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>6</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -50377,7 +50377,7 @@
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -50424,7 +50424,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -50436,13 +50436,13 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -50507,13 +50507,13 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
  